--- a/LULU.xlsx
+++ b/LULU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96996C54-02B7-4529-B991-7FF41FF6604C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4958FF7-1954-4A7B-85E6-42D8FAD05E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{307BA413-EEF9-4958-8DCC-E913E47A6543}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{307BA413-EEF9-4958-8DCC-E913E47A6543}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="120">
   <si>
     <t>SEC</t>
   </si>
@@ -414,6 +414,9 @@
   </si>
   <si>
     <t>Cash EoP</t>
+  </si>
+  <si>
+    <t>FY25</t>
   </si>
 </sst>
 </file>
@@ -964,7 +967,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="16">
-        <v>204.5</v>
+        <v>156.36000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -972,10 +975,10 @@
         <v>27</v>
       </c>
       <c r="I3" s="3">
-        <v>112.19004099999999</v>
+        <v>110.482671</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -995,7 +998,7 @@
       </c>
       <c r="I4" s="7">
         <f>I3*I2</f>
-        <v>22942.8633845</v>
+        <v>17275.07043756</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1014,10 +1017,10 @@
         <v>4</v>
       </c>
       <c r="I5" s="7">
-        <v>1035.8620000000001</v>
+        <v>1807.202</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -1028,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1037,7 +1040,7 @@
       </c>
       <c r="I7" s="7">
         <f>I4+I6-I5</f>
-        <v>21907.001384499999</v>
+        <v>15467.868437560001</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1046,7 +1049,7 @@
       </c>
       <c r="I9" s="8">
         <f>+I4/Model!V28</f>
-        <v>12.643371040760135</v>
+        <v>9.51995928480736</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1055,7 +1058,7 @@
       </c>
       <c r="I10" s="8">
         <f>+I7/Model!V24</f>
-        <v>8.7428772850428427</v>
+        <v>6.1730801599554921</v>
       </c>
     </row>
   </sheetData>
@@ -1140,6 +1143,9 @@
       <c r="V2" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="W2" s="17" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="3" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -1204,6 +1210,9 @@
       <c r="V3" s="4">
         <v>462</v>
       </c>
+      <c r="W3" s="2">
+        <v>476</v>
+      </c>
     </row>
     <row r="4" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
@@ -1263,6 +1272,9 @@
       </c>
       <c r="V4" s="4">
         <v>151</v>
+      </c>
+      <c r="W4" s="2">
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:49" x14ac:dyDescent="0.2">
@@ -1328,6 +1340,9 @@
       <c r="V5" s="4">
         <v>107</v>
       </c>
+      <c r="W5" s="2">
+        <v>114</v>
+      </c>
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
@@ -1391,6 +1406,9 @@
       </c>
       <c r="V6" s="4">
         <v>47</v>
+      </c>
+      <c r="W6" s="2">
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:49" x14ac:dyDescent="0.2">
@@ -1468,8 +1486,12 @@
         <v>711</v>
       </c>
       <c r="V7" s="9">
-        <f t="shared" ref="V7" si="7">+SUM(V3:V6)</f>
+        <f t="shared" ref="V7:W7" si="7">+SUM(V3:V6)</f>
         <v>767</v>
+      </c>
+      <c r="W7" s="9">
+        <f t="shared" si="7"/>
+        <v>811</v>
       </c>
     </row>
     <row r="8" spans="1:49" x14ac:dyDescent="0.2">
@@ -1526,7 +1548,7 @@
         <v>4.8326431818181819</v>
       </c>
       <c r="Q8" s="10">
-        <f t="shared" ref="Q8:V8" si="10">+Q16/Q7</f>
+        <f t="shared" ref="Q8:W8" si="10">+Q16/Q7</f>
         <v>2.3173564154786148</v>
       </c>
       <c r="R8" s="10">
@@ -1548,6 +1570,10 @@
       <c r="V8" s="10">
         <f t="shared" si="10"/>
         <v>6.5291681877444594</v>
+      </c>
+      <c r="W8" s="10">
+        <f>+W16/W7</f>
+        <v>6.2265647348951907</v>
       </c>
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.2">
@@ -1637,7 +1663,9 @@
       <c r="V10" s="3">
         <v>7928.1559999999999</v>
       </c>
-      <c r="W10" s="3"/>
+      <c r="W10" s="3">
+        <v>7847.0439999999999</v>
+      </c>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
@@ -1727,7 +1755,9 @@
       <c r="V11" s="3">
         <v>1361.337</v>
       </c>
-      <c r="W11" s="3"/>
+      <c r="W11" s="3">
+        <v>1754.799</v>
+      </c>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
@@ -1817,7 +1847,9 @@
       <c r="V12" s="3">
         <v>1298.633</v>
       </c>
-      <c r="W12" s="3"/>
+      <c r="W12" s="3">
+        <v>1500.7570000000001</v>
+      </c>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
@@ -1907,7 +1939,9 @@
       <c r="V13" s="3">
         <v>6692.63</v>
       </c>
-      <c r="W13" s="3"/>
+      <c r="W13" s="3">
+        <v>6995.3649999999998</v>
+      </c>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
@@ -1997,7 +2031,9 @@
       <c r="V14" s="3">
         <v>2558.38</v>
       </c>
-      <c r="W14" s="3"/>
+      <c r="W14" s="3">
+        <v>2666.9859999999999</v>
+      </c>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
@@ -2087,7 +2123,9 @@
       <c r="V15" s="3">
         <v>1337.116</v>
       </c>
-      <c r="W15" s="3"/>
+      <c r="W15" s="3">
+        <v>1443.249</v>
+      </c>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
@@ -2177,7 +2215,9 @@
       <c r="V16" s="3">
         <v>5007.8720000000003</v>
       </c>
-      <c r="W16" s="3"/>
+      <c r="W16" s="3">
+        <v>5049.7439999999997</v>
+      </c>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
@@ -2267,7 +2307,9 @@
       <c r="V17" s="3">
         <v>4570.4459999999999</v>
       </c>
-      <c r="W17" s="3"/>
+      <c r="W17" s="3">
+        <v>4918.6970000000001</v>
+      </c>
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
@@ -2357,7 +2399,9 @@
       <c r="V18" s="3">
         <v>1009.808</v>
       </c>
-      <c r="W18" s="3"/>
+      <c r="W18" s="3">
+        <v>1134.1590000000001</v>
+      </c>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
@@ -2445,6 +2489,9 @@
       <c r="V19" s="11">
         <v>10588.126</v>
       </c>
+      <c r="W19" s="11">
+        <v>11102.6</v>
+      </c>
     </row>
     <row r="20" spans="2:49" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
@@ -2505,6 +2552,9 @@
       </c>
       <c r="V20" s="3">
         <v>4317.3149999999996</v>
+      </c>
+      <c r="W20" s="2">
+        <v>4818.4679999999998</v>
       </c>
     </row>
     <row r="21" spans="2:49" x14ac:dyDescent="0.2">
@@ -2582,8 +2632,12 @@
         <v>5609.4050000000007</v>
       </c>
       <c r="V21" s="3">
-        <f t="shared" ref="V21" si="21">V19-V20</f>
+        <f t="shared" ref="V21:W21" si="21">V19-V20</f>
         <v>6270.8110000000006</v>
+      </c>
+      <c r="W21" s="3">
+        <f t="shared" si="21"/>
+        <v>6284.1320000000005</v>
       </c>
     </row>
     <row r="22" spans="2:49" x14ac:dyDescent="0.2">
@@ -2646,6 +2700,9 @@
       <c r="V22" s="3">
         <v>3762.3789999999999</v>
       </c>
+      <c r="W22" s="2">
+        <v>4066.556</v>
+      </c>
     </row>
     <row r="23" spans="2:49" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
@@ -2711,6 +2768,9 @@
       </c>
       <c r="V23" s="3">
         <v>2.7349999999999999</v>
+      </c>
+      <c r="W23" s="2">
+        <v>6.9610000000000003</v>
       </c>
     </row>
     <row r="24" spans="2:49" x14ac:dyDescent="0.2">
@@ -2788,8 +2848,12 @@
         <v>2132.6760000000008</v>
       </c>
       <c r="V24" s="3">
-        <f t="shared" ref="V24" si="29">V21-SUM(V22:V23)</f>
+        <f t="shared" ref="V24:W24" si="29">V21-SUM(V22:V23)</f>
         <v>2505.6970000000006</v>
+      </c>
+      <c r="W24" s="3">
+        <f t="shared" si="29"/>
+        <v>2210.6150000000007</v>
       </c>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
@@ -2864,6 +2928,9 @@
       <c r="V25" s="3">
         <v>70.38</v>
       </c>
+      <c r="W25" s="2">
+        <v>28.352</v>
+      </c>
     </row>
     <row r="26" spans="2:49" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
@@ -2940,8 +3007,12 @@
         <v>2175.735000000001</v>
       </c>
       <c r="V26" s="3">
-        <f t="shared" ref="V26" si="38">V24+V25</f>
+        <f t="shared" ref="V26:W26" si="38">V24+V25</f>
         <v>2576.0770000000007</v>
+      </c>
+      <c r="W26" s="3">
+        <f t="shared" si="38"/>
+        <v>2238.9670000000006</v>
       </c>
     </row>
     <row r="27" spans="2:49" x14ac:dyDescent="0.2">
@@ -3004,6 +3075,9 @@
       <c r="V27" s="3">
         <v>761.46100000000001</v>
       </c>
+      <c r="W27" s="2">
+        <v>659.78399999999999</v>
+      </c>
     </row>
     <row r="28" spans="2:49" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
@@ -3056,7 +3130,7 @@
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3">
-        <f t="shared" ref="P28:V28" si="41">P26-P27</f>
+        <f t="shared" ref="P28:W28" si="41">P26-P27</f>
         <v>493.80200000000019</v>
       </c>
       <c r="Q28" s="3">
@@ -3082,6 +3156,10 @@
       <c r="V28" s="3">
         <f t="shared" si="41"/>
         <v>1814.6160000000007</v>
+      </c>
+      <c r="W28" s="3">
+        <f t="shared" si="41"/>
+        <v>1579.1830000000004</v>
       </c>
     </row>
     <row r="29" spans="2:49" x14ac:dyDescent="0.2">
@@ -3161,7 +3239,7 @@
         <v>3.7013034711759736</v>
       </c>
       <c r="Q30" s="14">
-        <f t="shared" ref="Q30:V30" si="43">+Q28/Q31</f>
+        <f t="shared" ref="Q30:W30" si="43">+Q28/Q31</f>
         <v>4.9511553534315444</v>
       </c>
       <c r="R30" s="14">
@@ -3184,7 +3262,10 @@
         <f t="shared" si="43"/>
         <v>14.665341253485277</v>
       </c>
-      <c r="W30" s="14"/>
+      <c r="W30" s="14">
+        <f t="shared" si="43"/>
+        <v>13.272564527109374</v>
+      </c>
       <c r="X30" s="14"/>
       <c r="Y30" s="14"/>
       <c r="Z30" s="14"/>
@@ -3253,6 +3334,9 @@
       </c>
       <c r="V31" s="3">
         <v>123.735</v>
+      </c>
+      <c r="W31" s="2">
+        <v>118.98099999999999</v>
       </c>
     </row>
     <row r="32" spans="2:49" x14ac:dyDescent="0.2">
@@ -3270,7 +3354,7 @@
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B33" s="1" t="s">
         <v>32</v>
       </c>
@@ -3333,8 +3417,12 @@
         <f>V19/U19-1</f>
         <v>0.1007194095024595</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="12">
+        <f>W19/V19-1</f>
+        <v>4.8589712664923068E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>33</v>
       </c>
@@ -3409,8 +3497,12 @@
         <f>V21/V19</f>
         <v>0.59224937444076509</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="13">
+        <f>W21/W19</f>
+        <v>0.56600544016716803</v>
+      </c>
+    </row>
+    <row r="35" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>34</v>
       </c>
@@ -3485,8 +3577,12 @@
         <f>V24/V19</f>
         <v>0.23665160388155568</v>
       </c>
-    </row>
-    <row r="36" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="13">
+        <f>W24/W19</f>
+        <v>0.19910786662583543</v>
+      </c>
+    </row>
+    <row r="36" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
         <v>35</v>
       </c>
@@ -3561,8 +3657,12 @@
         <f>V28/V19</f>
         <v>0.17138216904483386</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W36" s="13">
+        <f>W28/W19</f>
+        <v>0.1422354223335075</v>
+      </c>
+    </row>
+    <row r="37" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
         <v>36</v>
       </c>
@@ -3637,8 +3737,12 @@
         <f>V27/V26</f>
         <v>0.2955893787336325</v>
       </c>
-    </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W37" s="13">
+        <f>W27/W26</f>
+        <v>0.29468232448267428</v>
+      </c>
+    </row>
+    <row r="38" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -3660,7 +3764,7 @@
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B39" s="15" t="s">
         <v>65</v>
       </c>
@@ -3688,8 +3792,11 @@
       <c r="V39" s="3">
         <v>1984.336</v>
       </c>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3">
+        <v>1807.202</v>
+      </c>
+    </row>
+    <row r="40" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B40" s="15" t="s">
         <v>66</v>
       </c>
@@ -3717,8 +3824,11 @@
       <c r="V40" s="3">
         <v>120.173</v>
       </c>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3">
+        <v>190.65700000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B41" s="15" t="s">
         <v>67</v>
       </c>
@@ -3746,8 +3856,11 @@
       <c r="V41" s="3">
         <v>1442.0809999999999</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3">
+        <v>1700.7529999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B42" s="15" t="s">
         <v>68</v>
       </c>
@@ -3775,8 +3888,11 @@
       <c r="V42" s="3">
         <v>182.25299999999999</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>352.46899999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B43" s="15" t="s">
         <v>69</v>
       </c>
@@ -3804,8 +3920,11 @@
       <c r="V43" s="3">
         <v>251.459</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>211.62</v>
+      </c>
+    </row>
+    <row r="44" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B44" s="15" t="s">
         <v>70</v>
       </c>
@@ -3841,8 +3960,33 @@
         <f>+SUM(V39:V43)</f>
         <v>3980.3020000000001</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <f>+SUM(W39:W43)</f>
+        <v>4262.701</v>
+      </c>
+      <c r="X44" s="3"/>
+      <c r="Y44" s="3"/>
+      <c r="Z44" s="3"/>
+      <c r="AA44" s="3"/>
+      <c r="AB44" s="3"/>
+      <c r="AC44" s="3"/>
+      <c r="AD44" s="3"/>
+      <c r="AE44" s="3"/>
+      <c r="AF44" s="3"/>
+      <c r="AG44" s="3"/>
+      <c r="AH44" s="3"/>
+      <c r="AI44" s="3"/>
+      <c r="AJ44" s="3"/>
+      <c r="AK44" s="3"/>
+      <c r="AL44" s="3"/>
+      <c r="AM44" s="3"/>
+      <c r="AN44" s="3"/>
+      <c r="AO44" s="3"/>
+      <c r="AP44" s="3"/>
+      <c r="AQ44" s="3"/>
+      <c r="AR44" s="3"/>
+    </row>
+    <row r="45" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B45" s="15" t="s">
         <v>71</v>
       </c>
@@ -3870,8 +4014,32 @@
       <c r="V45" s="3">
         <v>1780.617</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>2033.72</v>
+      </c>
+      <c r="X45" s="3"/>
+      <c r="Y45" s="3"/>
+      <c r="Z45" s="3"/>
+      <c r="AA45" s="3"/>
+      <c r="AB45" s="3"/>
+      <c r="AC45" s="3"/>
+      <c r="AD45" s="3"/>
+      <c r="AE45" s="3"/>
+      <c r="AF45" s="3"/>
+      <c r="AG45" s="3"/>
+      <c r="AH45" s="3"/>
+      <c r="AI45" s="3"/>
+      <c r="AJ45" s="3"/>
+      <c r="AK45" s="3"/>
+      <c r="AL45" s="3"/>
+      <c r="AM45" s="3"/>
+      <c r="AN45" s="3"/>
+      <c r="AO45" s="3"/>
+      <c r="AP45" s="3"/>
+      <c r="AQ45" s="3"/>
+      <c r="AR45" s="3"/>
+    </row>
+    <row r="46" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B46" s="15" t="s">
         <v>72</v>
       </c>
@@ -3899,8 +4067,32 @@
       <c r="V46" s="3">
         <v>1416.2560000000001</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>1630.181</v>
+      </c>
+      <c r="X46" s="3"/>
+      <c r="Y46" s="3"/>
+      <c r="Z46" s="3"/>
+      <c r="AA46" s="3"/>
+      <c r="AB46" s="3"/>
+      <c r="AC46" s="3"/>
+      <c r="AD46" s="3"/>
+      <c r="AE46" s="3"/>
+      <c r="AF46" s="3"/>
+      <c r="AG46" s="3"/>
+      <c r="AH46" s="3"/>
+      <c r="AI46" s="3"/>
+      <c r="AJ46" s="3"/>
+      <c r="AK46" s="3"/>
+      <c r="AL46" s="3"/>
+      <c r="AM46" s="3"/>
+      <c r="AN46" s="3"/>
+      <c r="AO46" s="3"/>
+      <c r="AP46" s="3"/>
+      <c r="AQ46" s="3"/>
+      <c r="AR46" s="3"/>
+    </row>
+    <row r="47" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B47" s="15" t="s">
         <v>73</v>
       </c>
@@ -3928,8 +4120,32 @@
       <c r="V47" s="3">
         <v>159.518</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>184.911</v>
+      </c>
+      <c r="X47" s="3"/>
+      <c r="Y47" s="3"/>
+      <c r="Z47" s="3"/>
+      <c r="AA47" s="3"/>
+      <c r="AB47" s="3"/>
+      <c r="AC47" s="3"/>
+      <c r="AD47" s="3"/>
+      <c r="AE47" s="3"/>
+      <c r="AF47" s="3"/>
+      <c r="AG47" s="3"/>
+      <c r="AH47" s="3"/>
+      <c r="AI47" s="3"/>
+      <c r="AJ47" s="3"/>
+      <c r="AK47" s="3"/>
+      <c r="AL47" s="3"/>
+      <c r="AM47" s="3"/>
+      <c r="AN47" s="3"/>
+      <c r="AO47" s="3"/>
+      <c r="AP47" s="3"/>
+      <c r="AQ47" s="3"/>
+      <c r="AR47" s="3"/>
+    </row>
+    <row r="48" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B48" s="15" t="s">
         <v>74</v>
       </c>
@@ -3957,8 +4173,32 @@
       <c r="V48" s="3">
         <v>11.673</v>
       </c>
-    </row>
-    <row r="49" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>6.2830000000000004</v>
+      </c>
+      <c r="X48" s="3"/>
+      <c r="Y48" s="3"/>
+      <c r="Z48" s="3"/>
+      <c r="AA48" s="3"/>
+      <c r="AB48" s="3"/>
+      <c r="AC48" s="3"/>
+      <c r="AD48" s="3"/>
+      <c r="AE48" s="3"/>
+      <c r="AF48" s="3"/>
+      <c r="AG48" s="3"/>
+      <c r="AH48" s="3"/>
+      <c r="AI48" s="3"/>
+      <c r="AJ48" s="3"/>
+      <c r="AK48" s="3"/>
+      <c r="AL48" s="3"/>
+      <c r="AM48" s="3"/>
+      <c r="AN48" s="3"/>
+      <c r="AO48" s="3"/>
+      <c r="AP48" s="3"/>
+      <c r="AQ48" s="3"/>
+      <c r="AR48" s="3"/>
+    </row>
+    <row r="49" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B49" s="15" t="s">
         <v>75</v>
       </c>
@@ -3986,8 +4226,32 @@
       <c r="V49" s="3">
         <v>17.085000000000001</v>
       </c>
-    </row>
-    <row r="50" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>24.036999999999999</v>
+      </c>
+      <c r="X49" s="3"/>
+      <c r="Y49" s="3"/>
+      <c r="Z49" s="3"/>
+      <c r="AA49" s="3"/>
+      <c r="AB49" s="3"/>
+      <c r="AC49" s="3"/>
+      <c r="AD49" s="3"/>
+      <c r="AE49" s="3"/>
+      <c r="AF49" s="3"/>
+      <c r="AG49" s="3"/>
+      <c r="AH49" s="3"/>
+      <c r="AI49" s="3"/>
+      <c r="AJ49" s="3"/>
+      <c r="AK49" s="3"/>
+      <c r="AL49" s="3"/>
+      <c r="AM49" s="3"/>
+      <c r="AN49" s="3"/>
+      <c r="AO49" s="3"/>
+      <c r="AP49" s="3"/>
+      <c r="AQ49" s="3"/>
+      <c r="AR49" s="3"/>
+    </row>
+    <row r="50" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B50" s="15" t="s">
         <v>47</v>
       </c>
@@ -4015,8 +4279,32 @@
       <c r="V50" s="3">
         <v>237.84100000000001</v>
       </c>
-    </row>
-    <row r="51" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>314.91000000000003</v>
+      </c>
+      <c r="X50" s="3"/>
+      <c r="Y50" s="3"/>
+      <c r="Z50" s="3"/>
+      <c r="AA50" s="3"/>
+      <c r="AB50" s="3"/>
+      <c r="AC50" s="3"/>
+      <c r="AD50" s="3"/>
+      <c r="AE50" s="3"/>
+      <c r="AF50" s="3"/>
+      <c r="AG50" s="3"/>
+      <c r="AH50" s="3"/>
+      <c r="AI50" s="3"/>
+      <c r="AJ50" s="3"/>
+      <c r="AK50" s="3"/>
+      <c r="AL50" s="3"/>
+      <c r="AM50" s="3"/>
+      <c r="AN50" s="3"/>
+      <c r="AO50" s="3"/>
+      <c r="AP50" s="3"/>
+      <c r="AQ50" s="3"/>
+      <c r="AR50" s="3"/>
+    </row>
+    <row r="51" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B51" s="15" t="s">
         <v>76</v>
       </c>
@@ -4049,8 +4337,33 @@
         <f>+SUM(V45:V50)</f>
         <v>3622.99</v>
       </c>
-    </row>
-    <row r="52" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <f>+SUM(W45:W50)</f>
+        <v>4194.0419999999995</v>
+      </c>
+      <c r="X51" s="3"/>
+      <c r="Y51" s="3"/>
+      <c r="Z51" s="3"/>
+      <c r="AA51" s="3"/>
+      <c r="AB51" s="3"/>
+      <c r="AC51" s="3"/>
+      <c r="AD51" s="3"/>
+      <c r="AE51" s="3"/>
+      <c r="AF51" s="3"/>
+      <c r="AG51" s="3"/>
+      <c r="AH51" s="3"/>
+      <c r="AI51" s="3"/>
+      <c r="AJ51" s="3"/>
+      <c r="AK51" s="3"/>
+      <c r="AL51" s="3"/>
+      <c r="AM51" s="3"/>
+      <c r="AN51" s="3"/>
+      <c r="AO51" s="3"/>
+      <c r="AP51" s="3"/>
+      <c r="AQ51" s="3"/>
+      <c r="AR51" s="3"/>
+    </row>
+    <row r="52" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
         <v>77</v>
       </c>
@@ -4083,8 +4396,33 @@
         <f>+V51+V44</f>
         <v>7603.2919999999995</v>
       </c>
-    </row>
-    <row r="53" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="11">
+        <f>+W51+W44</f>
+        <v>8456.7429999999986</v>
+      </c>
+      <c r="X52" s="3"/>
+      <c r="Y52" s="3"/>
+      <c r="Z52" s="3"/>
+      <c r="AA52" s="3"/>
+      <c r="AB52" s="3"/>
+      <c r="AC52" s="3"/>
+      <c r="AD52" s="3"/>
+      <c r="AE52" s="3"/>
+      <c r="AF52" s="3"/>
+      <c r="AG52" s="3"/>
+      <c r="AH52" s="3"/>
+      <c r="AI52" s="3"/>
+      <c r="AJ52" s="3"/>
+      <c r="AK52" s="3"/>
+      <c r="AL52" s="3"/>
+      <c r="AM52" s="3"/>
+      <c r="AN52" s="3"/>
+      <c r="AO52" s="3"/>
+      <c r="AP52" s="3"/>
+      <c r="AQ52" s="3"/>
+      <c r="AR52" s="3"/>
+    </row>
+    <row r="53" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B53" s="15" t="s">
         <v>80</v>
       </c>
@@ -4112,8 +4450,32 @@
       <c r="V53" s="3">
         <v>271.40600000000001</v>
       </c>
-    </row>
-    <row r="54" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>331.42099999999999</v>
+      </c>
+      <c r="X53" s="3"/>
+      <c r="Y53" s="3"/>
+      <c r="Z53" s="3"/>
+      <c r="AA53" s="3"/>
+      <c r="AB53" s="3"/>
+      <c r="AC53" s="3"/>
+      <c r="AD53" s="3"/>
+      <c r="AE53" s="3"/>
+      <c r="AF53" s="3"/>
+      <c r="AG53" s="3"/>
+      <c r="AH53" s="3"/>
+      <c r="AI53" s="3"/>
+      <c r="AJ53" s="3"/>
+      <c r="AK53" s="3"/>
+      <c r="AL53" s="3"/>
+      <c r="AM53" s="3"/>
+      <c r="AN53" s="3"/>
+      <c r="AO53" s="3"/>
+      <c r="AP53" s="3"/>
+      <c r="AQ53" s="3"/>
+      <c r="AR53" s="3"/>
+    </row>
+    <row r="54" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B54" s="15" t="s">
         <v>81</v>
       </c>
@@ -4141,8 +4503,32 @@
       <c r="V54" s="3">
         <v>559.46299999999997</v>
       </c>
-    </row>
-    <row r="55" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3">
+        <v>662.98199999999997</v>
+      </c>
+      <c r="X54" s="3"/>
+      <c r="Y54" s="3"/>
+      <c r="Z54" s="3"/>
+      <c r="AA54" s="3"/>
+      <c r="AB54" s="3"/>
+      <c r="AC54" s="3"/>
+      <c r="AD54" s="3"/>
+      <c r="AE54" s="3"/>
+      <c r="AF54" s="3"/>
+      <c r="AG54" s="3"/>
+      <c r="AH54" s="3"/>
+      <c r="AI54" s="3"/>
+      <c r="AJ54" s="3"/>
+      <c r="AK54" s="3"/>
+      <c r="AL54" s="3"/>
+      <c r="AM54" s="3"/>
+      <c r="AN54" s="3"/>
+      <c r="AO54" s="3"/>
+      <c r="AP54" s="3"/>
+      <c r="AQ54" s="3"/>
+      <c r="AR54" s="3"/>
+    </row>
+    <row r="55" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B55" s="15" t="s">
         <v>82</v>
       </c>
@@ -4170,8 +4556,32 @@
       <c r="V55" s="3">
         <v>204.54300000000001</v>
       </c>
-    </row>
-    <row r="56" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3">
+        <v>187.887</v>
+      </c>
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
+      <c r="AR55" s="3"/>
+    </row>
+    <row r="56" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B56" s="15" t="s">
         <v>83</v>
       </c>
@@ -4199,8 +4609,32 @@
       <c r="V56" s="3">
         <v>275.154</v>
       </c>
-    </row>
-    <row r="57" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3">
+        <v>298.72399999999999</v>
+      </c>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
+      <c r="AR56" s="3"/>
+    </row>
+    <row r="57" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B57" s="15" t="s">
         <v>84</v>
       </c>
@@ -4228,8 +4662,32 @@
       <c r="V57" s="3">
         <v>183.126</v>
       </c>
-    </row>
-    <row r="58" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>43.948</v>
+      </c>
+      <c r="X57" s="3"/>
+      <c r="Y57" s="3"/>
+      <c r="Z57" s="3"/>
+      <c r="AA57" s="3"/>
+      <c r="AB57" s="3"/>
+      <c r="AC57" s="3"/>
+      <c r="AD57" s="3"/>
+      <c r="AE57" s="3"/>
+      <c r="AF57" s="3"/>
+      <c r="AG57" s="3"/>
+      <c r="AH57" s="3"/>
+      <c r="AI57" s="3"/>
+      <c r="AJ57" s="3"/>
+      <c r="AK57" s="3"/>
+      <c r="AL57" s="3"/>
+      <c r="AM57" s="3"/>
+      <c r="AN57" s="3"/>
+      <c r="AO57" s="3"/>
+      <c r="AP57" s="3"/>
+      <c r="AQ57" s="3"/>
+      <c r="AR57" s="3"/>
+    </row>
+    <row r="58" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B58" s="15" t="s">
         <v>85</v>
       </c>
@@ -4257,8 +4715,32 @@
       <c r="V58" s="3">
         <v>308.35199999999998</v>
       </c>
-    </row>
-    <row r="59" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>316.63200000000001</v>
+      </c>
+      <c r="X58" s="3"/>
+      <c r="Y58" s="3"/>
+      <c r="Z58" s="3"/>
+      <c r="AA58" s="3"/>
+      <c r="AB58" s="3"/>
+      <c r="AC58" s="3"/>
+      <c r="AD58" s="3"/>
+      <c r="AE58" s="3"/>
+      <c r="AF58" s="3"/>
+      <c r="AG58" s="3"/>
+      <c r="AH58" s="3"/>
+      <c r="AI58" s="3"/>
+      <c r="AJ58" s="3"/>
+      <c r="AK58" s="3"/>
+      <c r="AL58" s="3"/>
+      <c r="AM58" s="3"/>
+      <c r="AN58" s="3"/>
+      <c r="AO58" s="3"/>
+      <c r="AP58" s="3"/>
+      <c r="AQ58" s="3"/>
+      <c r="AR58" s="3"/>
+    </row>
+    <row r="59" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B59" s="15" t="s">
         <v>47</v>
       </c>
@@ -4286,8 +4768,32 @@
       <c r="V59" s="3">
         <v>37.585999999999999</v>
       </c>
-    </row>
-    <row r="60" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3">
+        <v>45.954000000000001</v>
+      </c>
+      <c r="X59" s="3"/>
+      <c r="Y59" s="3"/>
+      <c r="Z59" s="3"/>
+      <c r="AA59" s="3"/>
+      <c r="AB59" s="3"/>
+      <c r="AC59" s="3"/>
+      <c r="AD59" s="3"/>
+      <c r="AE59" s="3"/>
+      <c r="AF59" s="3"/>
+      <c r="AG59" s="3"/>
+      <c r="AH59" s="3"/>
+      <c r="AI59" s="3"/>
+      <c r="AJ59" s="3"/>
+      <c r="AK59" s="3"/>
+      <c r="AL59" s="3"/>
+      <c r="AM59" s="3"/>
+      <c r="AN59" s="3"/>
+      <c r="AO59" s="3"/>
+      <c r="AP59" s="3"/>
+      <c r="AQ59" s="3"/>
+      <c r="AR59" s="3"/>
+    </row>
+    <row r="60" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B60" s="15" t="s">
         <v>86</v>
       </c>
@@ -4320,8 +4826,33 @@
         <f>+SUM(V53:V59)</f>
         <v>1839.6299999999999</v>
       </c>
-    </row>
-    <row r="61" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <f>+SUM(W53:W59)</f>
+        <v>1887.548</v>
+      </c>
+      <c r="X60" s="3"/>
+      <c r="Y60" s="3"/>
+      <c r="Z60" s="3"/>
+      <c r="AA60" s="3"/>
+      <c r="AB60" s="3"/>
+      <c r="AC60" s="3"/>
+      <c r="AD60" s="3"/>
+      <c r="AE60" s="3"/>
+      <c r="AF60" s="3"/>
+      <c r="AG60" s="3"/>
+      <c r="AH60" s="3"/>
+      <c r="AI60" s="3"/>
+      <c r="AJ60" s="3"/>
+      <c r="AK60" s="3"/>
+      <c r="AL60" s="3"/>
+      <c r="AM60" s="3"/>
+      <c r="AN60" s="3"/>
+      <c r="AO60" s="3"/>
+      <c r="AP60" s="3"/>
+      <c r="AQ60" s="3"/>
+      <c r="AR60" s="3"/>
+    </row>
+    <row r="61" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B61" s="15" t="s">
         <v>83</v>
       </c>
@@ -4349,8 +4880,32 @@
       <c r="V61" s="3">
         <v>1300.6369999999999</v>
       </c>
-    </row>
-    <row r="62" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>1499.7170000000001</v>
+      </c>
+      <c r="X61" s="3"/>
+      <c r="Y61" s="3"/>
+      <c r="Z61" s="3"/>
+      <c r="AA61" s="3"/>
+      <c r="AB61" s="3"/>
+      <c r="AC61" s="3"/>
+      <c r="AD61" s="3"/>
+      <c r="AE61" s="3"/>
+      <c r="AF61" s="3"/>
+      <c r="AG61" s="3"/>
+      <c r="AH61" s="3"/>
+      <c r="AI61" s="3"/>
+      <c r="AJ61" s="3"/>
+      <c r="AK61" s="3"/>
+      <c r="AL61" s="3"/>
+      <c r="AM61" s="3"/>
+      <c r="AN61" s="3"/>
+      <c r="AO61" s="3"/>
+      <c r="AP61" s="3"/>
+      <c r="AQ61" s="3"/>
+      <c r="AR61" s="3"/>
+    </row>
+    <row r="62" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B62" s="15" t="s">
         <v>84</v>
       </c>
@@ -4378,8 +4933,32 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3"/>
+      <c r="Y62" s="3"/>
+      <c r="Z62" s="3"/>
+      <c r="AA62" s="3"/>
+      <c r="AB62" s="3"/>
+      <c r="AC62" s="3"/>
+      <c r="AD62" s="3"/>
+      <c r="AE62" s="3"/>
+      <c r="AF62" s="3"/>
+      <c r="AG62" s="3"/>
+      <c r="AH62" s="3"/>
+      <c r="AI62" s="3"/>
+      <c r="AJ62" s="3"/>
+      <c r="AK62" s="3"/>
+      <c r="AL62" s="3"/>
+      <c r="AM62" s="3"/>
+      <c r="AN62" s="3"/>
+      <c r="AO62" s="3"/>
+      <c r="AP62" s="3"/>
+      <c r="AQ62" s="3"/>
+      <c r="AR62" s="3"/>
+    </row>
+    <row r="63" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B63" s="15" t="s">
         <v>75</v>
       </c>
@@ -4407,8 +4986,32 @@
       <c r="V63" s="3">
         <v>98.188000000000002</v>
       </c>
-    </row>
-    <row r="64" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>52.277999999999999</v>
+      </c>
+      <c r="X63" s="3"/>
+      <c r="Y63" s="3"/>
+      <c r="Z63" s="3"/>
+      <c r="AA63" s="3"/>
+      <c r="AB63" s="3"/>
+      <c r="AC63" s="3"/>
+      <c r="AD63" s="3"/>
+      <c r="AE63" s="3"/>
+      <c r="AF63" s="3"/>
+      <c r="AG63" s="3"/>
+      <c r="AH63" s="3"/>
+      <c r="AI63" s="3"/>
+      <c r="AJ63" s="3"/>
+      <c r="AK63" s="3"/>
+      <c r="AL63" s="3"/>
+      <c r="AM63" s="3"/>
+      <c r="AN63" s="3"/>
+      <c r="AO63" s="3"/>
+      <c r="AP63" s="3"/>
+      <c r="AQ63" s="3"/>
+      <c r="AR63" s="3"/>
+    </row>
+    <row r="64" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B64" s="15" t="s">
         <v>47</v>
       </c>
@@ -4436,8 +5039,32 @@
       <c r="V64" s="3">
         <v>40.79</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>55.36</v>
+      </c>
+      <c r="X64" s="3"/>
+      <c r="Y64" s="3"/>
+      <c r="Z64" s="3"/>
+      <c r="AA64" s="3"/>
+      <c r="AB64" s="3"/>
+      <c r="AC64" s="3"/>
+      <c r="AD64" s="3"/>
+      <c r="AE64" s="3"/>
+      <c r="AF64" s="3"/>
+      <c r="AG64" s="3"/>
+      <c r="AH64" s="3"/>
+      <c r="AI64" s="3"/>
+      <c r="AJ64" s="3"/>
+      <c r="AK64" s="3"/>
+      <c r="AL64" s="3"/>
+      <c r="AM64" s="3"/>
+      <c r="AN64" s="3"/>
+      <c r="AO64" s="3"/>
+      <c r="AP64" s="3"/>
+      <c r="AQ64" s="3"/>
+      <c r="AR64" s="3"/>
+    </row>
+    <row r="65" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B65" s="15" t="s">
         <v>79</v>
       </c>
@@ -4467,8 +5094,33 @@
         <f>+SUM(V61:V64)</f>
         <v>1439.615</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <f>+SUM(W61:W64)</f>
+        <v>1607.355</v>
+      </c>
+      <c r="X65" s="3"/>
+      <c r="Y65" s="3"/>
+      <c r="Z65" s="3"/>
+      <c r="AA65" s="3"/>
+      <c r="AB65" s="3"/>
+      <c r="AC65" s="3"/>
+      <c r="AD65" s="3"/>
+      <c r="AE65" s="3"/>
+      <c r="AF65" s="3"/>
+      <c r="AG65" s="3"/>
+      <c r="AH65" s="3"/>
+      <c r="AI65" s="3"/>
+      <c r="AJ65" s="3"/>
+      <c r="AK65" s="3"/>
+      <c r="AL65" s="3"/>
+      <c r="AM65" s="3"/>
+      <c r="AN65" s="3"/>
+      <c r="AO65" s="3"/>
+      <c r="AP65" s="3"/>
+      <c r="AQ65" s="3"/>
+      <c r="AR65" s="3"/>
+    </row>
+    <row r="66" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B66" s="15" t="s">
         <v>87</v>
       </c>
@@ -4496,8 +5148,32 @@
       <c r="V66" s="3">
         <v>4324.0469999999996</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3">
+        <v>4961.84</v>
+      </c>
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3"/>
+      <c r="Z66" s="3"/>
+      <c r="AA66" s="3"/>
+      <c r="AB66" s="3"/>
+      <c r="AC66" s="3"/>
+      <c r="AD66" s="3"/>
+      <c r="AE66" s="3"/>
+      <c r="AF66" s="3"/>
+      <c r="AG66" s="3"/>
+      <c r="AH66" s="3"/>
+      <c r="AI66" s="3"/>
+      <c r="AJ66" s="3"/>
+      <c r="AK66" s="3"/>
+      <c r="AL66" s="3"/>
+      <c r="AM66" s="3"/>
+      <c r="AN66" s="3"/>
+      <c r="AO66" s="3"/>
+      <c r="AP66" s="3"/>
+      <c r="AQ66" s="3"/>
+      <c r="AR66" s="3"/>
+    </row>
+    <row r="67" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B67" s="1" t="s">
         <v>78</v>
       </c>
@@ -4530,8 +5206,33 @@
         <f>+V66+V65+V60</f>
         <v>7603.2919999999995</v>
       </c>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="11">
+        <f>+W66+W65+W60</f>
+        <v>8456.7430000000004</v>
+      </c>
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
+      <c r="AR67" s="3"/>
+    </row>
+    <row r="68" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -4552,8 +5253,30 @@
       <c r="T68" s="3"/>
       <c r="U68" s="3"/>
       <c r="V68" s="3"/>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3"/>
+      <c r="X68" s="3"/>
+      <c r="Y68" s="3"/>
+      <c r="Z68" s="3"/>
+      <c r="AA68" s="3"/>
+      <c r="AB68" s="3"/>
+      <c r="AC68" s="3"/>
+      <c r="AD68" s="3"/>
+      <c r="AE68" s="3"/>
+      <c r="AF68" s="3"/>
+      <c r="AG68" s="3"/>
+      <c r="AH68" s="3"/>
+      <c r="AI68" s="3"/>
+      <c r="AJ68" s="3"/>
+      <c r="AK68" s="3"/>
+      <c r="AL68" s="3"/>
+      <c r="AM68" s="3"/>
+      <c r="AN68" s="3"/>
+      <c r="AO68" s="3"/>
+      <c r="AP68" s="3"/>
+      <c r="AQ68" s="3"/>
+      <c r="AR68" s="3"/>
+    </row>
+    <row r="69" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B69" s="15" t="s">
         <v>26</v>
       </c>
@@ -4586,8 +5309,33 @@
         <f>+V28</f>
         <v>1814.6160000000007</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <f>+W28</f>
+        <v>1579.1830000000004</v>
+      </c>
+      <c r="X69" s="3"/>
+      <c r="Y69" s="3"/>
+      <c r="Z69" s="3"/>
+      <c r="AA69" s="3"/>
+      <c r="AB69" s="3"/>
+      <c r="AC69" s="3"/>
+      <c r="AD69" s="3"/>
+      <c r="AE69" s="3"/>
+      <c r="AF69" s="3"/>
+      <c r="AG69" s="3"/>
+      <c r="AH69" s="3"/>
+      <c r="AI69" s="3"/>
+      <c r="AJ69" s="3"/>
+      <c r="AK69" s="3"/>
+      <c r="AL69" s="3"/>
+      <c r="AM69" s="3"/>
+      <c r="AN69" s="3"/>
+      <c r="AO69" s="3"/>
+      <c r="AP69" s="3"/>
+      <c r="AQ69" s="3"/>
+      <c r="AR69" s="3"/>
+    </row>
+    <row r="70" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B70" s="15" t="s">
         <v>89</v>
       </c>
@@ -4617,8 +5365,32 @@
       <c r="V70" s="3">
         <v>446.524</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>496.22800000000001</v>
+      </c>
+      <c r="X70" s="3"/>
+      <c r="Y70" s="3"/>
+      <c r="Z70" s="3"/>
+      <c r="AA70" s="3"/>
+      <c r="AB70" s="3"/>
+      <c r="AC70" s="3"/>
+      <c r="AD70" s="3"/>
+      <c r="AE70" s="3"/>
+      <c r="AF70" s="3"/>
+      <c r="AG70" s="3"/>
+      <c r="AH70" s="3"/>
+      <c r="AI70" s="3"/>
+      <c r="AJ70" s="3"/>
+      <c r="AK70" s="3"/>
+      <c r="AL70" s="3"/>
+      <c r="AM70" s="3"/>
+      <c r="AN70" s="3"/>
+      <c r="AO70" s="3"/>
+      <c r="AP70" s="3"/>
+      <c r="AQ70" s="3"/>
+      <c r="AR70" s="3"/>
+    </row>
+    <row r="71" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B71" s="15" t="s">
         <v>90</v>
       </c>
@@ -4650,8 +5422,32 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3"/>
+      <c r="Y71" s="3"/>
+      <c r="Z71" s="3"/>
+      <c r="AA71" s="3"/>
+      <c r="AB71" s="3"/>
+      <c r="AC71" s="3"/>
+      <c r="AD71" s="3"/>
+      <c r="AE71" s="3"/>
+      <c r="AF71" s="3"/>
+      <c r="AG71" s="3"/>
+      <c r="AH71" s="3"/>
+      <c r="AI71" s="3"/>
+      <c r="AJ71" s="3"/>
+      <c r="AK71" s="3"/>
+      <c r="AL71" s="3"/>
+      <c r="AM71" s="3"/>
+      <c r="AN71" s="3"/>
+      <c r="AO71" s="3"/>
+      <c r="AP71" s="3"/>
+      <c r="AQ71" s="3"/>
+      <c r="AR71" s="3"/>
+    </row>
+    <row r="72" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B72" s="15" t="s">
         <v>91</v>
       </c>
@@ -4681,8 +5477,32 @@
       <c r="V72" s="3">
         <v>90.010999999999996</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3">
+        <v>62.203000000000003</v>
+      </c>
+      <c r="X72" s="3"/>
+      <c r="Y72" s="3"/>
+      <c r="Z72" s="3"/>
+      <c r="AA72" s="3"/>
+      <c r="AB72" s="3"/>
+      <c r="AC72" s="3"/>
+      <c r="AD72" s="3"/>
+      <c r="AE72" s="3"/>
+      <c r="AF72" s="3"/>
+      <c r="AG72" s="3"/>
+      <c r="AH72" s="3"/>
+      <c r="AI72" s="3"/>
+      <c r="AJ72" s="3"/>
+      <c r="AK72" s="3"/>
+      <c r="AL72" s="3"/>
+      <c r="AM72" s="3"/>
+      <c r="AN72" s="3"/>
+      <c r="AO72" s="3"/>
+      <c r="AP72" s="3"/>
+      <c r="AQ72" s="3"/>
+      <c r="AR72" s="3"/>
+    </row>
+    <row r="73" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B73" s="15" t="s">
         <v>92</v>
       </c>
@@ -4712,8 +5532,32 @@
       <c r="V73" s="3">
         <v>-36.231000000000002</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>-37.765999999999998</v>
+      </c>
+      <c r="X73" s="3"/>
+      <c r="Y73" s="3"/>
+      <c r="Z73" s="3"/>
+      <c r="AA73" s="3"/>
+      <c r="AB73" s="3"/>
+      <c r="AC73" s="3"/>
+      <c r="AD73" s="3"/>
+      <c r="AE73" s="3"/>
+      <c r="AF73" s="3"/>
+      <c r="AG73" s="3"/>
+      <c r="AH73" s="3"/>
+      <c r="AI73" s="3"/>
+      <c r="AJ73" s="3"/>
+      <c r="AK73" s="3"/>
+      <c r="AL73" s="3"/>
+      <c r="AM73" s="3"/>
+      <c r="AN73" s="3"/>
+      <c r="AO73" s="3"/>
+      <c r="AP73" s="3"/>
+      <c r="AQ73" s="3"/>
+      <c r="AR73" s="3"/>
+    </row>
+    <row r="74" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B74" s="15" t="s">
         <v>93</v>
       </c>
@@ -4743,8 +5587,32 @@
       <c r="V74" s="3">
         <v>-47.762999999999998</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>-34.552</v>
+      </c>
+      <c r="X74" s="3"/>
+      <c r="Y74" s="3"/>
+      <c r="Z74" s="3"/>
+      <c r="AA74" s="3"/>
+      <c r="AB74" s="3"/>
+      <c r="AC74" s="3"/>
+      <c r="AD74" s="3"/>
+      <c r="AE74" s="3"/>
+      <c r="AF74" s="3"/>
+      <c r="AG74" s="3"/>
+      <c r="AH74" s="3"/>
+      <c r="AI74" s="3"/>
+      <c r="AJ74" s="3"/>
+      <c r="AK74" s="3"/>
+      <c r="AL74" s="3"/>
+      <c r="AM74" s="3"/>
+      <c r="AN74" s="3"/>
+      <c r="AO74" s="3"/>
+      <c r="AP74" s="3"/>
+      <c r="AQ74" s="3"/>
+      <c r="AR74" s="3"/>
+    </row>
+    <row r="75" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B75" s="15" t="s">
         <v>75</v>
       </c>
@@ -4774,8 +5642,32 @@
       <c r="V75" s="3">
         <v>57.451000000000001</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>-53.378999999999998</v>
+      </c>
+      <c r="X75" s="3"/>
+      <c r="Y75" s="3"/>
+      <c r="Z75" s="3"/>
+      <c r="AA75" s="3"/>
+      <c r="AB75" s="3"/>
+      <c r="AC75" s="3"/>
+      <c r="AD75" s="3"/>
+      <c r="AE75" s="3"/>
+      <c r="AF75" s="3"/>
+      <c r="AG75" s="3"/>
+      <c r="AH75" s="3"/>
+      <c r="AI75" s="3"/>
+      <c r="AJ75" s="3"/>
+      <c r="AK75" s="3"/>
+      <c r="AL75" s="3"/>
+      <c r="AM75" s="3"/>
+      <c r="AN75" s="3"/>
+      <c r="AO75" s="3"/>
+      <c r="AP75" s="3"/>
+      <c r="AQ75" s="3"/>
+      <c r="AR75" s="3"/>
+    </row>
+    <row r="76" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B76" s="15" t="s">
         <v>94</v>
       </c>
@@ -4805,8 +5697,32 @@
       <c r="V76" s="3">
         <v>1.6259999999999999</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3">
+        <v>-65.754999999999995</v>
+      </c>
+      <c r="X76" s="3"/>
+      <c r="Y76" s="3"/>
+      <c r="Z76" s="3"/>
+      <c r="AA76" s="3"/>
+      <c r="AB76" s="3"/>
+      <c r="AC76" s="3"/>
+      <c r="AD76" s="3"/>
+      <c r="AE76" s="3"/>
+      <c r="AF76" s="3"/>
+      <c r="AG76" s="3"/>
+      <c r="AH76" s="3"/>
+      <c r="AI76" s="3"/>
+      <c r="AJ76" s="3"/>
+      <c r="AK76" s="3"/>
+      <c r="AL76" s="3"/>
+      <c r="AM76" s="3"/>
+      <c r="AN76" s="3"/>
+      <c r="AO76" s="3"/>
+      <c r="AP76" s="3"/>
+      <c r="AQ76" s="3"/>
+      <c r="AR76" s="3"/>
+    </row>
+    <row r="77" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B77" s="15" t="s">
         <v>106</v>
       </c>
@@ -4836,8 +5752,32 @@
       <c r="V77" s="3">
         <v>-156.08500000000001</v>
       </c>
-    </row>
-    <row r="78" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>-188.71</v>
+      </c>
+      <c r="X77" s="3"/>
+      <c r="Y77" s="3"/>
+      <c r="Z77" s="3"/>
+      <c r="AA77" s="3"/>
+      <c r="AB77" s="3"/>
+      <c r="AC77" s="3"/>
+      <c r="AD77" s="3"/>
+      <c r="AE77" s="3"/>
+      <c r="AF77" s="3"/>
+      <c r="AG77" s="3"/>
+      <c r="AH77" s="3"/>
+      <c r="AI77" s="3"/>
+      <c r="AJ77" s="3"/>
+      <c r="AK77" s="3"/>
+      <c r="AL77" s="3"/>
+      <c r="AM77" s="3"/>
+      <c r="AN77" s="3"/>
+      <c r="AO77" s="3"/>
+      <c r="AP77" s="3"/>
+      <c r="AQ77" s="3"/>
+      <c r="AR77" s="3"/>
+    </row>
+    <row r="78" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B78" s="15" t="s">
         <v>95</v>
       </c>
@@ -4867,8 +5807,32 @@
       <c r="V78" s="3">
         <v>-2.0310000000000001</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W78" s="3">
+        <v>-170.21600000000001</v>
+      </c>
+      <c r="X78" s="3"/>
+      <c r="Y78" s="3"/>
+      <c r="Z78" s="3"/>
+      <c r="AA78" s="3"/>
+      <c r="AB78" s="3"/>
+      <c r="AC78" s="3"/>
+      <c r="AD78" s="3"/>
+      <c r="AE78" s="3"/>
+      <c r="AF78" s="3"/>
+      <c r="AG78" s="3"/>
+      <c r="AH78" s="3"/>
+      <c r="AI78" s="3"/>
+      <c r="AJ78" s="3"/>
+      <c r="AK78" s="3"/>
+      <c r="AL78" s="3"/>
+      <c r="AM78" s="3"/>
+      <c r="AN78" s="3"/>
+      <c r="AO78" s="3"/>
+      <c r="AP78" s="3"/>
+      <c r="AQ78" s="3"/>
+      <c r="AR78" s="3"/>
+    </row>
+    <row r="79" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B79" s="15" t="s">
         <v>96</v>
       </c>
@@ -4898,8 +5862,32 @@
       <c r="V79" s="3">
         <v>-71.789000000000001</v>
       </c>
-    </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W79" s="3">
+        <v>47.779000000000003</v>
+      </c>
+      <c r="X79" s="3"/>
+      <c r="Y79" s="3"/>
+      <c r="Z79" s="3"/>
+      <c r="AA79" s="3"/>
+      <c r="AB79" s="3"/>
+      <c r="AC79" s="3"/>
+      <c r="AD79" s="3"/>
+      <c r="AE79" s="3"/>
+      <c r="AF79" s="3"/>
+      <c r="AG79" s="3"/>
+      <c r="AH79" s="3"/>
+      <c r="AI79" s="3"/>
+      <c r="AJ79" s="3"/>
+      <c r="AK79" s="3"/>
+      <c r="AL79" s="3"/>
+      <c r="AM79" s="3"/>
+      <c r="AN79" s="3"/>
+      <c r="AO79" s="3"/>
+      <c r="AP79" s="3"/>
+      <c r="AQ79" s="3"/>
+      <c r="AR79" s="3"/>
+    </row>
+    <row r="80" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B80" s="15" t="s">
         <v>97</v>
       </c>
@@ -4929,8 +5917,32 @@
       <c r="V80" s="3">
         <v>-73.204999999999998</v>
       </c>
-    </row>
-    <row r="81" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="3">
+        <v>-70.350999999999999</v>
+      </c>
+      <c r="X80" s="3"/>
+      <c r="Y80" s="3"/>
+      <c r="Z80" s="3"/>
+      <c r="AA80" s="3"/>
+      <c r="AB80" s="3"/>
+      <c r="AC80" s="3"/>
+      <c r="AD80" s="3"/>
+      <c r="AE80" s="3"/>
+      <c r="AF80" s="3"/>
+      <c r="AG80" s="3"/>
+      <c r="AH80" s="3"/>
+      <c r="AI80" s="3"/>
+      <c r="AJ80" s="3"/>
+      <c r="AK80" s="3"/>
+      <c r="AL80" s="3"/>
+      <c r="AM80" s="3"/>
+      <c r="AN80" s="3"/>
+      <c r="AO80" s="3"/>
+      <c r="AP80" s="3"/>
+      <c r="AQ80" s="3"/>
+      <c r="AR80" s="3"/>
+    </row>
+    <row r="81" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B81" s="15" t="s">
         <v>98</v>
       </c>
@@ -4960,8 +5972,32 @@
       <c r="V81" s="3">
         <v>-57.043999999999997</v>
       </c>
-    </row>
-    <row r="82" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3">
+        <v>45.856000000000002</v>
+      </c>
+      <c r="X81" s="3"/>
+      <c r="Y81" s="3"/>
+      <c r="Z81" s="3"/>
+      <c r="AA81" s="3"/>
+      <c r="AB81" s="3"/>
+      <c r="AC81" s="3"/>
+      <c r="AD81" s="3"/>
+      <c r="AE81" s="3"/>
+      <c r="AF81" s="3"/>
+      <c r="AG81" s="3"/>
+      <c r="AH81" s="3"/>
+      <c r="AI81" s="3"/>
+      <c r="AJ81" s="3"/>
+      <c r="AK81" s="3"/>
+      <c r="AL81" s="3"/>
+      <c r="AM81" s="3"/>
+      <c r="AN81" s="3"/>
+      <c r="AO81" s="3"/>
+      <c r="AP81" s="3"/>
+      <c r="AQ81" s="3"/>
+      <c r="AR81" s="3"/>
+    </row>
+    <row r="82" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B82" s="15" t="s">
         <v>99</v>
       </c>
@@ -4991,8 +6027,32 @@
       <c r="V82" s="3">
         <v>193.13900000000001</v>
       </c>
-    </row>
-    <row r="83" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3">
+        <v>98.421000000000006</v>
+      </c>
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
+      <c r="AR82" s="3"/>
+    </row>
+    <row r="83" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B83" s="15" t="s">
         <v>100</v>
       </c>
@@ -5022,8 +6082,32 @@
       <c r="V83" s="3">
         <v>-112.11</v>
       </c>
-    </row>
-    <row r="84" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>-24.736999999999998</v>
+      </c>
+      <c r="X83" s="3"/>
+      <c r="Y83" s="3"/>
+      <c r="Z83" s="3"/>
+      <c r="AA83" s="3"/>
+      <c r="AB83" s="3"/>
+      <c r="AC83" s="3"/>
+      <c r="AD83" s="3"/>
+      <c r="AE83" s="3"/>
+      <c r="AF83" s="3"/>
+      <c r="AG83" s="3"/>
+      <c r="AH83" s="3"/>
+      <c r="AI83" s="3"/>
+      <c r="AJ83" s="3"/>
+      <c r="AK83" s="3"/>
+      <c r="AL83" s="3"/>
+      <c r="AM83" s="3"/>
+      <c r="AN83" s="3"/>
+      <c r="AO83" s="3"/>
+      <c r="AP83" s="3"/>
+      <c r="AQ83" s="3"/>
+      <c r="AR83" s="3"/>
+    </row>
+    <row r="84" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B84" s="15" t="s">
         <v>101</v>
       </c>
@@ -5053,8 +6137,32 @@
       <c r="V84" s="3">
         <v>157.20500000000001</v>
       </c>
-    </row>
-    <row r="85" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>-150.48599999999999</v>
+      </c>
+      <c r="X84" s="3"/>
+      <c r="Y84" s="3"/>
+      <c r="Z84" s="3"/>
+      <c r="AA84" s="3"/>
+      <c r="AB84" s="3"/>
+      <c r="AC84" s="3"/>
+      <c r="AD84" s="3"/>
+      <c r="AE84" s="3"/>
+      <c r="AF84" s="3"/>
+      <c r="AG84" s="3"/>
+      <c r="AH84" s="3"/>
+      <c r="AI84" s="3"/>
+      <c r="AJ84" s="3"/>
+      <c r="AK84" s="3"/>
+      <c r="AL84" s="3"/>
+      <c r="AM84" s="3"/>
+      <c r="AN84" s="3"/>
+      <c r="AO84" s="3"/>
+      <c r="AP84" s="3"/>
+      <c r="AQ84" s="3"/>
+      <c r="AR84" s="3"/>
+    </row>
+    <row r="85" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B85" s="15" t="s">
         <v>102</v>
       </c>
@@ -5084,8 +6192,32 @@
       <c r="V85" s="3">
         <v>42.41</v>
       </c>
-    </row>
-    <row r="86" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>41.253</v>
+      </c>
+      <c r="X85" s="3"/>
+      <c r="Y85" s="3"/>
+      <c r="Z85" s="3"/>
+      <c r="AA85" s="3"/>
+      <c r="AB85" s="3"/>
+      <c r="AC85" s="3"/>
+      <c r="AD85" s="3"/>
+      <c r="AE85" s="3"/>
+      <c r="AF85" s="3"/>
+      <c r="AG85" s="3"/>
+      <c r="AH85" s="3"/>
+      <c r="AI85" s="3"/>
+      <c r="AJ85" s="3"/>
+      <c r="AK85" s="3"/>
+      <c r="AL85" s="3"/>
+      <c r="AM85" s="3"/>
+      <c r="AN85" s="3"/>
+      <c r="AO85" s="3"/>
+      <c r="AP85" s="3"/>
+      <c r="AQ85" s="3"/>
+      <c r="AR85" s="3"/>
+    </row>
+    <row r="86" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B86" s="15" t="s">
         <v>103</v>
       </c>
@@ -5115,8 +6247,32 @@
       <c r="V86" s="3">
         <v>23.501000000000001</v>
       </c>
-    </row>
-    <row r="87" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>6.8840000000000003</v>
+      </c>
+      <c r="X86" s="3"/>
+      <c r="Y86" s="3"/>
+      <c r="Z86" s="3"/>
+      <c r="AA86" s="3"/>
+      <c r="AB86" s="3"/>
+      <c r="AC86" s="3"/>
+      <c r="AD86" s="3"/>
+      <c r="AE86" s="3"/>
+      <c r="AF86" s="3"/>
+      <c r="AG86" s="3"/>
+      <c r="AH86" s="3"/>
+      <c r="AI86" s="3"/>
+      <c r="AJ86" s="3"/>
+      <c r="AK86" s="3"/>
+      <c r="AL86" s="3"/>
+      <c r="AM86" s="3"/>
+      <c r="AN86" s="3"/>
+      <c r="AO86" s="3"/>
+      <c r="AP86" s="3"/>
+      <c r="AQ86" s="3"/>
+      <c r="AR86" s="3"/>
+    </row>
+    <row r="87" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B87" s="15" t="s">
         <v>104</v>
       </c>
@@ -5146,8 +6302,32 @@
       <c r="V87" s="3">
         <v>2.488</v>
       </c>
-    </row>
-    <row r="88" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>20.632000000000001</v>
+      </c>
+      <c r="X87" s="3"/>
+      <c r="Y87" s="3"/>
+      <c r="Z87" s="3"/>
+      <c r="AA87" s="3"/>
+      <c r="AB87" s="3"/>
+      <c r="AC87" s="3"/>
+      <c r="AD87" s="3"/>
+      <c r="AE87" s="3"/>
+      <c r="AF87" s="3"/>
+      <c r="AG87" s="3"/>
+      <c r="AH87" s="3"/>
+      <c r="AI87" s="3"/>
+      <c r="AJ87" s="3"/>
+      <c r="AK87" s="3"/>
+      <c r="AL87" s="3"/>
+      <c r="AM87" s="3"/>
+      <c r="AN87" s="3"/>
+      <c r="AO87" s="3"/>
+      <c r="AP87" s="3"/>
+      <c r="AQ87" s="3"/>
+      <c r="AR87" s="3"/>
+    </row>
+    <row r="88" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B88" s="15" t="s">
         <v>105</v>
       </c>
@@ -5183,8 +6363,33 @@
         <f>+SUM(V76:V87)</f>
         <v>-51.894999999999953</v>
       </c>
-    </row>
-    <row r="89" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <f>+SUM(W76:W87)</f>
+        <v>-409.43000000000006</v>
+      </c>
+      <c r="X88" s="3"/>
+      <c r="Y88" s="3"/>
+      <c r="Z88" s="3"/>
+      <c r="AA88" s="3"/>
+      <c r="AB88" s="3"/>
+      <c r="AC88" s="3"/>
+      <c r="AD88" s="3"/>
+      <c r="AE88" s="3"/>
+      <c r="AF88" s="3"/>
+      <c r="AG88" s="3"/>
+      <c r="AH88" s="3"/>
+      <c r="AI88" s="3"/>
+      <c r="AJ88" s="3"/>
+      <c r="AK88" s="3"/>
+      <c r="AL88" s="3"/>
+      <c r="AM88" s="3"/>
+      <c r="AN88" s="3"/>
+      <c r="AO88" s="3"/>
+      <c r="AP88" s="3"/>
+      <c r="AQ88" s="3"/>
+      <c r="AR88" s="3"/>
+    </row>
+    <row r="89" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B89" s="1" t="s">
         <v>88</v>
       </c>
@@ -5229,8 +6434,33 @@
         <f>+SUM(V88,V69:V75)</f>
         <v>2272.7130000000006</v>
       </c>
-    </row>
-    <row r="90" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="11">
+        <f>+SUM(W88,W69:W75)</f>
+        <v>1602.4870000000005</v>
+      </c>
+      <c r="X89" s="3"/>
+      <c r="Y89" s="3"/>
+      <c r="Z89" s="3"/>
+      <c r="AA89" s="3"/>
+      <c r="AB89" s="3"/>
+      <c r="AC89" s="3"/>
+      <c r="AD89" s="3"/>
+      <c r="AE89" s="3"/>
+      <c r="AF89" s="3"/>
+      <c r="AG89" s="3"/>
+      <c r="AH89" s="3"/>
+      <c r="AI89" s="3"/>
+      <c r="AJ89" s="3"/>
+      <c r="AK89" s="3"/>
+      <c r="AL89" s="3"/>
+      <c r="AM89" s="3"/>
+      <c r="AN89" s="3"/>
+      <c r="AO89" s="3"/>
+      <c r="AP89" s="3"/>
+      <c r="AQ89" s="3"/>
+      <c r="AR89" s="3"/>
+    </row>
+    <row r="90" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B90" s="15" t="s">
         <v>108</v>
       </c>
@@ -5260,8 +6490,32 @@
       <c r="V90" s="3">
         <v>-689.23199999999997</v>
       </c>
-    </row>
-    <row r="91" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3">
+        <v>-680.80200000000002</v>
+      </c>
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
+      <c r="AR90" s="3"/>
+    </row>
+    <row r="91" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B91" s="15" t="s">
         <v>109</v>
       </c>
@@ -5291,8 +6545,32 @@
       <c r="V91" s="3">
         <v>50.213000000000001</v>
       </c>
-    </row>
-    <row r="92" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>27.204999999999998</v>
+      </c>
+      <c r="X91" s="3"/>
+      <c r="Y91" s="3"/>
+      <c r="Z91" s="3"/>
+      <c r="AA91" s="3"/>
+      <c r="AB91" s="3"/>
+      <c r="AC91" s="3"/>
+      <c r="AD91" s="3"/>
+      <c r="AE91" s="3"/>
+      <c r="AF91" s="3"/>
+      <c r="AG91" s="3"/>
+      <c r="AH91" s="3"/>
+      <c r="AI91" s="3"/>
+      <c r="AJ91" s="3"/>
+      <c r="AK91" s="3"/>
+      <c r="AL91" s="3"/>
+      <c r="AM91" s="3"/>
+      <c r="AN91" s="3"/>
+      <c r="AO91" s="3"/>
+      <c r="AP91" s="3"/>
+      <c r="AQ91" s="3"/>
+      <c r="AR91" s="3"/>
+    </row>
+    <row r="92" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B92" s="15" t="s">
         <v>110</v>
       </c>
@@ -5322,8 +6600,32 @@
       <c r="V92" s="3">
         <v>-154.14599999999999</v>
       </c>
-    </row>
-    <row r="93" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3"/>
+      <c r="Y92" s="3"/>
+      <c r="Z92" s="3"/>
+      <c r="AA92" s="3"/>
+      <c r="AB92" s="3"/>
+      <c r="AC92" s="3"/>
+      <c r="AD92" s="3"/>
+      <c r="AE92" s="3"/>
+      <c r="AF92" s="3"/>
+      <c r="AG92" s="3"/>
+      <c r="AH92" s="3"/>
+      <c r="AI92" s="3"/>
+      <c r="AJ92" s="3"/>
+      <c r="AK92" s="3"/>
+      <c r="AL92" s="3"/>
+      <c r="AM92" s="3"/>
+      <c r="AN92" s="3"/>
+      <c r="AO92" s="3"/>
+      <c r="AP92" s="3"/>
+      <c r="AQ92" s="3"/>
+      <c r="AR92" s="3"/>
+    </row>
+    <row r="93" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B93" s="15" t="s">
         <v>47</v>
       </c>
@@ -5353,8 +6655,32 @@
       <c r="V93" s="3">
         <v>-5.0090000000000003</v>
       </c>
-    </row>
-    <row r="94" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>-8.5210000000000008</v>
+      </c>
+      <c r="X93" s="3"/>
+      <c r="Y93" s="3"/>
+      <c r="Z93" s="3"/>
+      <c r="AA93" s="3"/>
+      <c r="AB93" s="3"/>
+      <c r="AC93" s="3"/>
+      <c r="AD93" s="3"/>
+      <c r="AE93" s="3"/>
+      <c r="AF93" s="3"/>
+      <c r="AG93" s="3"/>
+      <c r="AH93" s="3"/>
+      <c r="AI93" s="3"/>
+      <c r="AJ93" s="3"/>
+      <c r="AK93" s="3"/>
+      <c r="AL93" s="3"/>
+      <c r="AM93" s="3"/>
+      <c r="AN93" s="3"/>
+      <c r="AO93" s="3"/>
+      <c r="AP93" s="3"/>
+      <c r="AQ93" s="3"/>
+      <c r="AR93" s="3"/>
+    </row>
+    <row r="94" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B94" s="1" t="s">
         <v>107</v>
       </c>
@@ -5390,8 +6716,33 @@
         <f>+SUM(V90:V93)</f>
         <v>-798.17399999999998</v>
       </c>
-    </row>
-    <row r="95" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="11">
+        <f>+SUM(W90:W93)</f>
+        <v>-662.11799999999994</v>
+      </c>
+      <c r="X94" s="3"/>
+      <c r="Y94" s="3"/>
+      <c r="Z94" s="3"/>
+      <c r="AA94" s="3"/>
+      <c r="AB94" s="3"/>
+      <c r="AC94" s="3"/>
+      <c r="AD94" s="3"/>
+      <c r="AE94" s="3"/>
+      <c r="AF94" s="3"/>
+      <c r="AG94" s="3"/>
+      <c r="AH94" s="3"/>
+      <c r="AI94" s="3"/>
+      <c r="AJ94" s="3"/>
+      <c r="AK94" s="3"/>
+      <c r="AL94" s="3"/>
+      <c r="AM94" s="3"/>
+      <c r="AN94" s="3"/>
+      <c r="AO94" s="3"/>
+      <c r="AP94" s="3"/>
+      <c r="AQ94" s="3"/>
+      <c r="AR94" s="3"/>
+    </row>
+    <row r="95" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B95" s="15" t="s">
         <v>111</v>
       </c>
@@ -5421,8 +6772,32 @@
       <c r="V95" s="3">
         <v>19.812999999999999</v>
       </c>
-    </row>
-    <row r="96" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3">
+        <v>8.3770000000000007</v>
+      </c>
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
+      <c r="AR95" s="3"/>
+    </row>
+    <row r="96" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B96" s="15" t="s">
         <v>112</v>
       </c>
@@ -5452,8 +6827,32 @@
       <c r="V96" s="3">
         <v>-35.409999999999997</v>
       </c>
-    </row>
-    <row r="97" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>-27.372</v>
+      </c>
+      <c r="X96" s="3"/>
+      <c r="Y96" s="3"/>
+      <c r="Z96" s="3"/>
+      <c r="AA96" s="3"/>
+      <c r="AB96" s="3"/>
+      <c r="AC96" s="3"/>
+      <c r="AD96" s="3"/>
+      <c r="AE96" s="3"/>
+      <c r="AF96" s="3"/>
+      <c r="AG96" s="3"/>
+      <c r="AH96" s="3"/>
+      <c r="AI96" s="3"/>
+      <c r="AJ96" s="3"/>
+      <c r="AK96" s="3"/>
+      <c r="AL96" s="3"/>
+      <c r="AM96" s="3"/>
+      <c r="AN96" s="3"/>
+      <c r="AO96" s="3"/>
+      <c r="AP96" s="3"/>
+      <c r="AQ96" s="3"/>
+      <c r="AR96" s="3"/>
+    </row>
+    <row r="97" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B97" s="15" t="s">
         <v>113</v>
       </c>
@@ -5483,8 +6882,32 @@
       <c r="V97" s="3">
         <v>-1636.8789999999999</v>
       </c>
-    </row>
-    <row r="98" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>-1178.3489999999999</v>
+      </c>
+      <c r="X97" s="3"/>
+      <c r="Y97" s="3"/>
+      <c r="Z97" s="3"/>
+      <c r="AA97" s="3"/>
+      <c r="AB97" s="3"/>
+      <c r="AC97" s="3"/>
+      <c r="AD97" s="3"/>
+      <c r="AE97" s="3"/>
+      <c r="AF97" s="3"/>
+      <c r="AG97" s="3"/>
+      <c r="AH97" s="3"/>
+      <c r="AI97" s="3"/>
+      <c r="AJ97" s="3"/>
+      <c r="AK97" s="3"/>
+      <c r="AL97" s="3"/>
+      <c r="AM97" s="3"/>
+      <c r="AN97" s="3"/>
+      <c r="AO97" s="3"/>
+      <c r="AP97" s="3"/>
+      <c r="AQ97" s="3"/>
+      <c r="AR97" s="3"/>
+    </row>
+    <row r="98" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B98" s="15" t="s">
         <v>47</v>
       </c>
@@ -5514,8 +6937,32 @@
       <c r="V98" s="3">
         <v>-3.2000000000000001E-2</v>
       </c>
-    </row>
-    <row r="99" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>-11.311999999999999</v>
+      </c>
+      <c r="X98" s="3"/>
+      <c r="Y98" s="3"/>
+      <c r="Z98" s="3"/>
+      <c r="AA98" s="3"/>
+      <c r="AB98" s="3"/>
+      <c r="AC98" s="3"/>
+      <c r="AD98" s="3"/>
+      <c r="AE98" s="3"/>
+      <c r="AF98" s="3"/>
+      <c r="AG98" s="3"/>
+      <c r="AH98" s="3"/>
+      <c r="AI98" s="3"/>
+      <c r="AJ98" s="3"/>
+      <c r="AK98" s="3"/>
+      <c r="AL98" s="3"/>
+      <c r="AM98" s="3"/>
+      <c r="AN98" s="3"/>
+      <c r="AO98" s="3"/>
+      <c r="AP98" s="3"/>
+      <c r="AQ98" s="3"/>
+      <c r="AR98" s="3"/>
+    </row>
+    <row r="99" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B99" s="1" t="s">
         <v>114</v>
       </c>
@@ -5551,8 +6998,33 @@
         <f>+SUM(V95:V98)</f>
         <v>-1652.5079999999998</v>
       </c>
-    </row>
-    <row r="100" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="11">
+        <f>+SUM(W95:W98)</f>
+        <v>-1208.6559999999997</v>
+      </c>
+      <c r="X99" s="3"/>
+      <c r="Y99" s="3"/>
+      <c r="Z99" s="3"/>
+      <c r="AA99" s="3"/>
+      <c r="AB99" s="3"/>
+      <c r="AC99" s="3"/>
+      <c r="AD99" s="3"/>
+      <c r="AE99" s="3"/>
+      <c r="AF99" s="3"/>
+      <c r="AG99" s="3"/>
+      <c r="AH99" s="3"/>
+      <c r="AI99" s="3"/>
+      <c r="AJ99" s="3"/>
+      <c r="AK99" s="3"/>
+      <c r="AL99" s="3"/>
+      <c r="AM99" s="3"/>
+      <c r="AN99" s="3"/>
+      <c r="AO99" s="3"/>
+      <c r="AP99" s="3"/>
+      <c r="AQ99" s="3"/>
+      <c r="AR99" s="3"/>
+    </row>
+    <row r="100" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B100" s="15" t="s">
         <v>115</v>
       </c>
@@ -5582,8 +7054,32 @@
       <c r="V100" s="3">
         <v>-81.665999999999997</v>
       </c>
-    </row>
-    <row r="101" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>91.162999999999997</v>
+      </c>
+      <c r="X100" s="3"/>
+      <c r="Y100" s="3"/>
+      <c r="Z100" s="3"/>
+      <c r="AA100" s="3"/>
+      <c r="AB100" s="3"/>
+      <c r="AC100" s="3"/>
+      <c r="AD100" s="3"/>
+      <c r="AE100" s="3"/>
+      <c r="AF100" s="3"/>
+      <c r="AG100" s="3"/>
+      <c r="AH100" s="3"/>
+      <c r="AI100" s="3"/>
+      <c r="AJ100" s="3"/>
+      <c r="AK100" s="3"/>
+      <c r="AL100" s="3"/>
+      <c r="AM100" s="3"/>
+      <c r="AN100" s="3"/>
+      <c r="AO100" s="3"/>
+      <c r="AP100" s="3"/>
+      <c r="AQ100" s="3"/>
+      <c r="AR100" s="3"/>
+    </row>
+    <row r="101" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B101" s="15" t="s">
         <v>116</v>
       </c>
@@ -5619,8 +7115,33 @@
         <f>+SUM(V99,V100,V94,V89)</f>
         <v>-259.63499999999931</v>
       </c>
-    </row>
-    <row r="102" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <f>+SUM(W99,W100,W94,W89)</f>
+        <v>-177.12399999999911</v>
+      </c>
+      <c r="X101" s="3"/>
+      <c r="Y101" s="3"/>
+      <c r="Z101" s="3"/>
+      <c r="AA101" s="3"/>
+      <c r="AB101" s="3"/>
+      <c r="AC101" s="3"/>
+      <c r="AD101" s="3"/>
+      <c r="AE101" s="3"/>
+      <c r="AF101" s="3"/>
+      <c r="AG101" s="3"/>
+      <c r="AH101" s="3"/>
+      <c r="AI101" s="3"/>
+      <c r="AJ101" s="3"/>
+      <c r="AK101" s="3"/>
+      <c r="AL101" s="3"/>
+      <c r="AM101" s="3"/>
+      <c r="AN101" s="3"/>
+      <c r="AO101" s="3"/>
+      <c r="AP101" s="3"/>
+      <c r="AQ101" s="3"/>
+      <c r="AR101" s="3"/>
+    </row>
+    <row r="102" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B102" s="15" t="s">
         <v>117</v>
       </c>
@@ -5650,8 +7171,33 @@
       <c r="V102" s="3">
         <v>2243.971</v>
       </c>
-    </row>
-    <row r="103" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W102" s="3">
+        <f>+V103</f>
+        <v>1984.3360000000007</v>
+      </c>
+      <c r="X102" s="3"/>
+      <c r="Y102" s="3"/>
+      <c r="Z102" s="3"/>
+      <c r="AA102" s="3"/>
+      <c r="AB102" s="3"/>
+      <c r="AC102" s="3"/>
+      <c r="AD102" s="3"/>
+      <c r="AE102" s="3"/>
+      <c r="AF102" s="3"/>
+      <c r="AG102" s="3"/>
+      <c r="AH102" s="3"/>
+      <c r="AI102" s="3"/>
+      <c r="AJ102" s="3"/>
+      <c r="AK102" s="3"/>
+      <c r="AL102" s="3"/>
+      <c r="AM102" s="3"/>
+      <c r="AN102" s="3"/>
+      <c r="AO102" s="3"/>
+      <c r="AP102" s="3"/>
+      <c r="AQ102" s="3"/>
+      <c r="AR102" s="3"/>
+    </row>
+    <row r="103" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B103" s="15" t="s">
         <v>118</v>
       </c>
@@ -5684,8 +7230,33 @@
         <f>+V102+V101</f>
         <v>1984.3360000000007</v>
       </c>
-    </row>
-    <row r="104" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W103" s="3">
+        <f>+W101+W102</f>
+        <v>1807.2120000000016</v>
+      </c>
+      <c r="X103" s="3"/>
+      <c r="Y103" s="3"/>
+      <c r="Z103" s="3"/>
+      <c r="AA103" s="3"/>
+      <c r="AB103" s="3"/>
+      <c r="AC103" s="3"/>
+      <c r="AD103" s="3"/>
+      <c r="AE103" s="3"/>
+      <c r="AF103" s="3"/>
+      <c r="AG103" s="3"/>
+      <c r="AH103" s="3"/>
+      <c r="AI103" s="3"/>
+      <c r="AJ103" s="3"/>
+      <c r="AK103" s="3"/>
+      <c r="AL103" s="3"/>
+      <c r="AM103" s="3"/>
+      <c r="AN103" s="3"/>
+      <c r="AO103" s="3"/>
+      <c r="AP103" s="3"/>
+      <c r="AQ103" s="3"/>
+      <c r="AR103" s="3"/>
+    </row>
+    <row r="104" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
@@ -5706,8 +7277,30 @@
       <c r="T104" s="3"/>
       <c r="U104" s="3"/>
       <c r="V104" s="3"/>
-    </row>
-    <row r="105" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W104" s="3"/>
+      <c r="X104" s="3"/>
+      <c r="Y104" s="3"/>
+      <c r="Z104" s="3"/>
+      <c r="AA104" s="3"/>
+      <c r="AB104" s="3"/>
+      <c r="AC104" s="3"/>
+      <c r="AD104" s="3"/>
+      <c r="AE104" s="3"/>
+      <c r="AF104" s="3"/>
+      <c r="AG104" s="3"/>
+      <c r="AH104" s="3"/>
+      <c r="AI104" s="3"/>
+      <c r="AJ104" s="3"/>
+      <c r="AK104" s="3"/>
+      <c r="AL104" s="3"/>
+      <c r="AM104" s="3"/>
+      <c r="AN104" s="3"/>
+      <c r="AO104" s="3"/>
+      <c r="AP104" s="3"/>
+      <c r="AQ104" s="3"/>
+      <c r="AR104" s="3"/>
+    </row>
+    <row r="105" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -5728,8 +7321,30 @@
       <c r="T105" s="3"/>
       <c r="U105" s="3"/>
       <c r="V105" s="3"/>
-    </row>
-    <row r="106" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W105" s="3"/>
+      <c r="X105" s="3"/>
+      <c r="Y105" s="3"/>
+      <c r="Z105" s="3"/>
+      <c r="AA105" s="3"/>
+      <c r="AB105" s="3"/>
+      <c r="AC105" s="3"/>
+      <c r="AD105" s="3"/>
+      <c r="AE105" s="3"/>
+      <c r="AF105" s="3"/>
+      <c r="AG105" s="3"/>
+      <c r="AH105" s="3"/>
+      <c r="AI105" s="3"/>
+      <c r="AJ105" s="3"/>
+      <c r="AK105" s="3"/>
+      <c r="AL105" s="3"/>
+      <c r="AM105" s="3"/>
+      <c r="AN105" s="3"/>
+      <c r="AO105" s="3"/>
+      <c r="AP105" s="3"/>
+      <c r="AQ105" s="3"/>
+      <c r="AR105" s="3"/>
+    </row>
+    <row r="106" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -5750,8 +7365,30 @@
       <c r="T106" s="3"/>
       <c r="U106" s="3"/>
       <c r="V106" s="3"/>
-    </row>
-    <row r="107" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W106" s="3"/>
+      <c r="X106" s="3"/>
+      <c r="Y106" s="3"/>
+      <c r="Z106" s="3"/>
+      <c r="AA106" s="3"/>
+      <c r="AB106" s="3"/>
+      <c r="AC106" s="3"/>
+      <c r="AD106" s="3"/>
+      <c r="AE106" s="3"/>
+      <c r="AF106" s="3"/>
+      <c r="AG106" s="3"/>
+      <c r="AH106" s="3"/>
+      <c r="AI106" s="3"/>
+      <c r="AJ106" s="3"/>
+      <c r="AK106" s="3"/>
+      <c r="AL106" s="3"/>
+      <c r="AM106" s="3"/>
+      <c r="AN106" s="3"/>
+      <c r="AO106" s="3"/>
+      <c r="AP106" s="3"/>
+      <c r="AQ106" s="3"/>
+      <c r="AR106" s="3"/>
+    </row>
+    <row r="107" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -5772,8 +7409,30 @@
       <c r="T107" s="3"/>
       <c r="U107" s="3"/>
       <c r="V107" s="3"/>
-    </row>
-    <row r="108" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W107" s="3"/>
+      <c r="X107" s="3"/>
+      <c r="Y107" s="3"/>
+      <c r="Z107" s="3"/>
+      <c r="AA107" s="3"/>
+      <c r="AB107" s="3"/>
+      <c r="AC107" s="3"/>
+      <c r="AD107" s="3"/>
+      <c r="AE107" s="3"/>
+      <c r="AF107" s="3"/>
+      <c r="AG107" s="3"/>
+      <c r="AH107" s="3"/>
+      <c r="AI107" s="3"/>
+      <c r="AJ107" s="3"/>
+      <c r="AK107" s="3"/>
+      <c r="AL107" s="3"/>
+      <c r="AM107" s="3"/>
+      <c r="AN107" s="3"/>
+      <c r="AO107" s="3"/>
+      <c r="AP107" s="3"/>
+      <c r="AQ107" s="3"/>
+      <c r="AR107" s="3"/>
+    </row>
+    <row r="108" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -5794,8 +7453,30 @@
       <c r="T108" s="3"/>
       <c r="U108" s="3"/>
       <c r="V108" s="3"/>
-    </row>
-    <row r="109" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W108" s="3"/>
+      <c r="X108" s="3"/>
+      <c r="Y108" s="3"/>
+      <c r="Z108" s="3"/>
+      <c r="AA108" s="3"/>
+      <c r="AB108" s="3"/>
+      <c r="AC108" s="3"/>
+      <c r="AD108" s="3"/>
+      <c r="AE108" s="3"/>
+      <c r="AF108" s="3"/>
+      <c r="AG108" s="3"/>
+      <c r="AH108" s="3"/>
+      <c r="AI108" s="3"/>
+      <c r="AJ108" s="3"/>
+      <c r="AK108" s="3"/>
+      <c r="AL108" s="3"/>
+      <c r="AM108" s="3"/>
+      <c r="AN108" s="3"/>
+      <c r="AO108" s="3"/>
+      <c r="AP108" s="3"/>
+      <c r="AQ108" s="3"/>
+      <c r="AR108" s="3"/>
+    </row>
+    <row r="109" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -5816,8 +7497,30 @@
       <c r="T109" s="3"/>
       <c r="U109" s="3"/>
       <c r="V109" s="3"/>
-    </row>
-    <row r="110" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W109" s="3"/>
+      <c r="X109" s="3"/>
+      <c r="Y109" s="3"/>
+      <c r="Z109" s="3"/>
+      <c r="AA109" s="3"/>
+      <c r="AB109" s="3"/>
+      <c r="AC109" s="3"/>
+      <c r="AD109" s="3"/>
+      <c r="AE109" s="3"/>
+      <c r="AF109" s="3"/>
+      <c r="AG109" s="3"/>
+      <c r="AH109" s="3"/>
+      <c r="AI109" s="3"/>
+      <c r="AJ109" s="3"/>
+      <c r="AK109" s="3"/>
+      <c r="AL109" s="3"/>
+      <c r="AM109" s="3"/>
+      <c r="AN109" s="3"/>
+      <c r="AO109" s="3"/>
+      <c r="AP109" s="3"/>
+      <c r="AQ109" s="3"/>
+      <c r="AR109" s="3"/>
+    </row>
+    <row r="110" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -5838,8 +7541,30 @@
       <c r="T110" s="3"/>
       <c r="U110" s="3"/>
       <c r="V110" s="3"/>
-    </row>
-    <row r="111" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W110" s="3"/>
+      <c r="X110" s="3"/>
+      <c r="Y110" s="3"/>
+      <c r="Z110" s="3"/>
+      <c r="AA110" s="3"/>
+      <c r="AB110" s="3"/>
+      <c r="AC110" s="3"/>
+      <c r="AD110" s="3"/>
+      <c r="AE110" s="3"/>
+      <c r="AF110" s="3"/>
+      <c r="AG110" s="3"/>
+      <c r="AH110" s="3"/>
+      <c r="AI110" s="3"/>
+      <c r="AJ110" s="3"/>
+      <c r="AK110" s="3"/>
+      <c r="AL110" s="3"/>
+      <c r="AM110" s="3"/>
+      <c r="AN110" s="3"/>
+      <c r="AO110" s="3"/>
+      <c r="AP110" s="3"/>
+      <c r="AQ110" s="3"/>
+      <c r="AR110" s="3"/>
+    </row>
+    <row r="111" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -5860,8 +7585,30 @@
       <c r="T111" s="3"/>
       <c r="U111" s="3"/>
       <c r="V111" s="3"/>
-    </row>
-    <row r="112" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W111" s="3"/>
+      <c r="X111" s="3"/>
+      <c r="Y111" s="3"/>
+      <c r="Z111" s="3"/>
+      <c r="AA111" s="3"/>
+      <c r="AB111" s="3"/>
+      <c r="AC111" s="3"/>
+      <c r="AD111" s="3"/>
+      <c r="AE111" s="3"/>
+      <c r="AF111" s="3"/>
+      <c r="AG111" s="3"/>
+      <c r="AH111" s="3"/>
+      <c r="AI111" s="3"/>
+      <c r="AJ111" s="3"/>
+      <c r="AK111" s="3"/>
+      <c r="AL111" s="3"/>
+      <c r="AM111" s="3"/>
+      <c r="AN111" s="3"/>
+      <c r="AO111" s="3"/>
+      <c r="AP111" s="3"/>
+      <c r="AQ111" s="3"/>
+      <c r="AR111" s="3"/>
+    </row>
+    <row r="112" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -5882,8 +7629,30 @@
       <c r="T112" s="3"/>
       <c r="U112" s="3"/>
       <c r="V112" s="3"/>
-    </row>
-    <row r="113" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W112" s="3"/>
+      <c r="X112" s="3"/>
+      <c r="Y112" s="3"/>
+      <c r="Z112" s="3"/>
+      <c r="AA112" s="3"/>
+      <c r="AB112" s="3"/>
+      <c r="AC112" s="3"/>
+      <c r="AD112" s="3"/>
+      <c r="AE112" s="3"/>
+      <c r="AF112" s="3"/>
+      <c r="AG112" s="3"/>
+      <c r="AH112" s="3"/>
+      <c r="AI112" s="3"/>
+      <c r="AJ112" s="3"/>
+      <c r="AK112" s="3"/>
+      <c r="AL112" s="3"/>
+      <c r="AM112" s="3"/>
+      <c r="AN112" s="3"/>
+      <c r="AO112" s="3"/>
+      <c r="AP112" s="3"/>
+      <c r="AQ112" s="3"/>
+      <c r="AR112" s="3"/>
+    </row>
+    <row r="113" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -5904,8 +7673,30 @@
       <c r="T113" s="3"/>
       <c r="U113" s="3"/>
       <c r="V113" s="3"/>
-    </row>
-    <row r="114" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W113" s="3"/>
+      <c r="X113" s="3"/>
+      <c r="Y113" s="3"/>
+      <c r="Z113" s="3"/>
+      <c r="AA113" s="3"/>
+      <c r="AB113" s="3"/>
+      <c r="AC113" s="3"/>
+      <c r="AD113" s="3"/>
+      <c r="AE113" s="3"/>
+      <c r="AF113" s="3"/>
+      <c r="AG113" s="3"/>
+      <c r="AH113" s="3"/>
+      <c r="AI113" s="3"/>
+      <c r="AJ113" s="3"/>
+      <c r="AK113" s="3"/>
+      <c r="AL113" s="3"/>
+      <c r="AM113" s="3"/>
+      <c r="AN113" s="3"/>
+      <c r="AO113" s="3"/>
+      <c r="AP113" s="3"/>
+      <c r="AQ113" s="3"/>
+      <c r="AR113" s="3"/>
+    </row>
+    <row r="114" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -5926,8 +7717,30 @@
       <c r="T114" s="3"/>
       <c r="U114" s="3"/>
       <c r="V114" s="3"/>
-    </row>
-    <row r="115" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W114" s="3"/>
+      <c r="X114" s="3"/>
+      <c r="Y114" s="3"/>
+      <c r="Z114" s="3"/>
+      <c r="AA114" s="3"/>
+      <c r="AB114" s="3"/>
+      <c r="AC114" s="3"/>
+      <c r="AD114" s="3"/>
+      <c r="AE114" s="3"/>
+      <c r="AF114" s="3"/>
+      <c r="AG114" s="3"/>
+      <c r="AH114" s="3"/>
+      <c r="AI114" s="3"/>
+      <c r="AJ114" s="3"/>
+      <c r="AK114" s="3"/>
+      <c r="AL114" s="3"/>
+      <c r="AM114" s="3"/>
+      <c r="AN114" s="3"/>
+      <c r="AO114" s="3"/>
+      <c r="AP114" s="3"/>
+      <c r="AQ114" s="3"/>
+      <c r="AR114" s="3"/>
+    </row>
+    <row r="115" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -5948,8 +7761,30 @@
       <c r="T115" s="3"/>
       <c r="U115" s="3"/>
       <c r="V115" s="3"/>
-    </row>
-    <row r="116" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W115" s="3"/>
+      <c r="X115" s="3"/>
+      <c r="Y115" s="3"/>
+      <c r="Z115" s="3"/>
+      <c r="AA115" s="3"/>
+      <c r="AB115" s="3"/>
+      <c r="AC115" s="3"/>
+      <c r="AD115" s="3"/>
+      <c r="AE115" s="3"/>
+      <c r="AF115" s="3"/>
+      <c r="AG115" s="3"/>
+      <c r="AH115" s="3"/>
+      <c r="AI115" s="3"/>
+      <c r="AJ115" s="3"/>
+      <c r="AK115" s="3"/>
+      <c r="AL115" s="3"/>
+      <c r="AM115" s="3"/>
+      <c r="AN115" s="3"/>
+      <c r="AO115" s="3"/>
+      <c r="AP115" s="3"/>
+      <c r="AQ115" s="3"/>
+      <c r="AR115" s="3"/>
+    </row>
+    <row r="116" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -5970,8 +7805,30 @@
       <c r="T116" s="3"/>
       <c r="U116" s="3"/>
       <c r="V116" s="3"/>
-    </row>
-    <row r="117" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W116" s="3"/>
+      <c r="X116" s="3"/>
+      <c r="Y116" s="3"/>
+      <c r="Z116" s="3"/>
+      <c r="AA116" s="3"/>
+      <c r="AB116" s="3"/>
+      <c r="AC116" s="3"/>
+      <c r="AD116" s="3"/>
+      <c r="AE116" s="3"/>
+      <c r="AF116" s="3"/>
+      <c r="AG116" s="3"/>
+      <c r="AH116" s="3"/>
+      <c r="AI116" s="3"/>
+      <c r="AJ116" s="3"/>
+      <c r="AK116" s="3"/>
+      <c r="AL116" s="3"/>
+      <c r="AM116" s="3"/>
+      <c r="AN116" s="3"/>
+      <c r="AO116" s="3"/>
+      <c r="AP116" s="3"/>
+      <c r="AQ116" s="3"/>
+      <c r="AR116" s="3"/>
+    </row>
+    <row r="117" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -5992,8 +7849,30 @@
       <c r="T117" s="3"/>
       <c r="U117" s="3"/>
       <c r="V117" s="3"/>
-    </row>
-    <row r="118" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W117" s="3"/>
+      <c r="X117" s="3"/>
+      <c r="Y117" s="3"/>
+      <c r="Z117" s="3"/>
+      <c r="AA117" s="3"/>
+      <c r="AB117" s="3"/>
+      <c r="AC117" s="3"/>
+      <c r="AD117" s="3"/>
+      <c r="AE117" s="3"/>
+      <c r="AF117" s="3"/>
+      <c r="AG117" s="3"/>
+      <c r="AH117" s="3"/>
+      <c r="AI117" s="3"/>
+      <c r="AJ117" s="3"/>
+      <c r="AK117" s="3"/>
+      <c r="AL117" s="3"/>
+      <c r="AM117" s="3"/>
+      <c r="AN117" s="3"/>
+      <c r="AO117" s="3"/>
+      <c r="AP117" s="3"/>
+      <c r="AQ117" s="3"/>
+      <c r="AR117" s="3"/>
+    </row>
+    <row r="118" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -6014,8 +7893,30 @@
       <c r="T118" s="3"/>
       <c r="U118" s="3"/>
       <c r="V118" s="3"/>
-    </row>
-    <row r="119" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W118" s="3"/>
+      <c r="X118" s="3"/>
+      <c r="Y118" s="3"/>
+      <c r="Z118" s="3"/>
+      <c r="AA118" s="3"/>
+      <c r="AB118" s="3"/>
+      <c r="AC118" s="3"/>
+      <c r="AD118" s="3"/>
+      <c r="AE118" s="3"/>
+      <c r="AF118" s="3"/>
+      <c r="AG118" s="3"/>
+      <c r="AH118" s="3"/>
+      <c r="AI118" s="3"/>
+      <c r="AJ118" s="3"/>
+      <c r="AK118" s="3"/>
+      <c r="AL118" s="3"/>
+      <c r="AM118" s="3"/>
+      <c r="AN118" s="3"/>
+      <c r="AO118" s="3"/>
+      <c r="AP118" s="3"/>
+      <c r="AQ118" s="3"/>
+      <c r="AR118" s="3"/>
+    </row>
+    <row r="119" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -6036,8 +7937,30 @@
       <c r="T119" s="3"/>
       <c r="U119" s="3"/>
       <c r="V119" s="3"/>
-    </row>
-    <row r="120" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W119" s="3"/>
+      <c r="X119" s="3"/>
+      <c r="Y119" s="3"/>
+      <c r="Z119" s="3"/>
+      <c r="AA119" s="3"/>
+      <c r="AB119" s="3"/>
+      <c r="AC119" s="3"/>
+      <c r="AD119" s="3"/>
+      <c r="AE119" s="3"/>
+      <c r="AF119" s="3"/>
+      <c r="AG119" s="3"/>
+      <c r="AH119" s="3"/>
+      <c r="AI119" s="3"/>
+      <c r="AJ119" s="3"/>
+      <c r="AK119" s="3"/>
+      <c r="AL119" s="3"/>
+      <c r="AM119" s="3"/>
+      <c r="AN119" s="3"/>
+      <c r="AO119" s="3"/>
+      <c r="AP119" s="3"/>
+      <c r="AQ119" s="3"/>
+      <c r="AR119" s="3"/>
+    </row>
+    <row r="120" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -6058,8 +7981,30 @@
       <c r="T120" s="3"/>
       <c r="U120" s="3"/>
       <c r="V120" s="3"/>
-    </row>
-    <row r="121" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W120" s="3"/>
+      <c r="X120" s="3"/>
+      <c r="Y120" s="3"/>
+      <c r="Z120" s="3"/>
+      <c r="AA120" s="3"/>
+      <c r="AB120" s="3"/>
+      <c r="AC120" s="3"/>
+      <c r="AD120" s="3"/>
+      <c r="AE120" s="3"/>
+      <c r="AF120" s="3"/>
+      <c r="AG120" s="3"/>
+      <c r="AH120" s="3"/>
+      <c r="AI120" s="3"/>
+      <c r="AJ120" s="3"/>
+      <c r="AK120" s="3"/>
+      <c r="AL120" s="3"/>
+      <c r="AM120" s="3"/>
+      <c r="AN120" s="3"/>
+      <c r="AO120" s="3"/>
+      <c r="AP120" s="3"/>
+      <c r="AQ120" s="3"/>
+      <c r="AR120" s="3"/>
+    </row>
+    <row r="121" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -6080,8 +8025,30 @@
       <c r="T121" s="3"/>
       <c r="U121" s="3"/>
       <c r="V121" s="3"/>
-    </row>
-    <row r="122" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W121" s="3"/>
+      <c r="X121" s="3"/>
+      <c r="Y121" s="3"/>
+      <c r="Z121" s="3"/>
+      <c r="AA121" s="3"/>
+      <c r="AB121" s="3"/>
+      <c r="AC121" s="3"/>
+      <c r="AD121" s="3"/>
+      <c r="AE121" s="3"/>
+      <c r="AF121" s="3"/>
+      <c r="AG121" s="3"/>
+      <c r="AH121" s="3"/>
+      <c r="AI121" s="3"/>
+      <c r="AJ121" s="3"/>
+      <c r="AK121" s="3"/>
+      <c r="AL121" s="3"/>
+      <c r="AM121" s="3"/>
+      <c r="AN121" s="3"/>
+      <c r="AO121" s="3"/>
+      <c r="AP121" s="3"/>
+      <c r="AQ121" s="3"/>
+      <c r="AR121" s="3"/>
+    </row>
+    <row r="122" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -6102,8 +8069,30 @@
       <c r="T122" s="3"/>
       <c r="U122" s="3"/>
       <c r="V122" s="3"/>
-    </row>
-    <row r="123" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W122" s="3"/>
+      <c r="X122" s="3"/>
+      <c r="Y122" s="3"/>
+      <c r="Z122" s="3"/>
+      <c r="AA122" s="3"/>
+      <c r="AB122" s="3"/>
+      <c r="AC122" s="3"/>
+      <c r="AD122" s="3"/>
+      <c r="AE122" s="3"/>
+      <c r="AF122" s="3"/>
+      <c r="AG122" s="3"/>
+      <c r="AH122" s="3"/>
+      <c r="AI122" s="3"/>
+      <c r="AJ122" s="3"/>
+      <c r="AK122" s="3"/>
+      <c r="AL122" s="3"/>
+      <c r="AM122" s="3"/>
+      <c r="AN122" s="3"/>
+      <c r="AO122" s="3"/>
+      <c r="AP122" s="3"/>
+      <c r="AQ122" s="3"/>
+      <c r="AR122" s="3"/>
+    </row>
+    <row r="123" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -6124,8 +8113,30 @@
       <c r="T123" s="3"/>
       <c r="U123" s="3"/>
       <c r="V123" s="3"/>
-    </row>
-    <row r="124" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W123" s="3"/>
+      <c r="X123" s="3"/>
+      <c r="Y123" s="3"/>
+      <c r="Z123" s="3"/>
+      <c r="AA123" s="3"/>
+      <c r="AB123" s="3"/>
+      <c r="AC123" s="3"/>
+      <c r="AD123" s="3"/>
+      <c r="AE123" s="3"/>
+      <c r="AF123" s="3"/>
+      <c r="AG123" s="3"/>
+      <c r="AH123" s="3"/>
+      <c r="AI123" s="3"/>
+      <c r="AJ123" s="3"/>
+      <c r="AK123" s="3"/>
+      <c r="AL123" s="3"/>
+      <c r="AM123" s="3"/>
+      <c r="AN123" s="3"/>
+      <c r="AO123" s="3"/>
+      <c r="AP123" s="3"/>
+      <c r="AQ123" s="3"/>
+      <c r="AR123" s="3"/>
+    </row>
+    <row r="124" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -6146,8 +8157,30 @@
       <c r="T124" s="3"/>
       <c r="U124" s="3"/>
       <c r="V124" s="3"/>
-    </row>
-    <row r="125" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W124" s="3"/>
+      <c r="X124" s="3"/>
+      <c r="Y124" s="3"/>
+      <c r="Z124" s="3"/>
+      <c r="AA124" s="3"/>
+      <c r="AB124" s="3"/>
+      <c r="AC124" s="3"/>
+      <c r="AD124" s="3"/>
+      <c r="AE124" s="3"/>
+      <c r="AF124" s="3"/>
+      <c r="AG124" s="3"/>
+      <c r="AH124" s="3"/>
+      <c r="AI124" s="3"/>
+      <c r="AJ124" s="3"/>
+      <c r="AK124" s="3"/>
+      <c r="AL124" s="3"/>
+      <c r="AM124" s="3"/>
+      <c r="AN124" s="3"/>
+      <c r="AO124" s="3"/>
+      <c r="AP124" s="3"/>
+      <c r="AQ124" s="3"/>
+      <c r="AR124" s="3"/>
+    </row>
+    <row r="125" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -6168,8 +8201,30 @@
       <c r="T125" s="3"/>
       <c r="U125" s="3"/>
       <c r="V125" s="3"/>
-    </row>
-    <row r="126" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W125" s="3"/>
+      <c r="X125" s="3"/>
+      <c r="Y125" s="3"/>
+      <c r="Z125" s="3"/>
+      <c r="AA125" s="3"/>
+      <c r="AB125" s="3"/>
+      <c r="AC125" s="3"/>
+      <c r="AD125" s="3"/>
+      <c r="AE125" s="3"/>
+      <c r="AF125" s="3"/>
+      <c r="AG125" s="3"/>
+      <c r="AH125" s="3"/>
+      <c r="AI125" s="3"/>
+      <c r="AJ125" s="3"/>
+      <c r="AK125" s="3"/>
+      <c r="AL125" s="3"/>
+      <c r="AM125" s="3"/>
+      <c r="AN125" s="3"/>
+      <c r="AO125" s="3"/>
+      <c r="AP125" s="3"/>
+      <c r="AQ125" s="3"/>
+      <c r="AR125" s="3"/>
+    </row>
+    <row r="126" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -6190,8 +8245,30 @@
       <c r="T126" s="3"/>
       <c r="U126" s="3"/>
       <c r="V126" s="3"/>
-    </row>
-    <row r="127" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W126" s="3"/>
+      <c r="X126" s="3"/>
+      <c r="Y126" s="3"/>
+      <c r="Z126" s="3"/>
+      <c r="AA126" s="3"/>
+      <c r="AB126" s="3"/>
+      <c r="AC126" s="3"/>
+      <c r="AD126" s="3"/>
+      <c r="AE126" s="3"/>
+      <c r="AF126" s="3"/>
+      <c r="AG126" s="3"/>
+      <c r="AH126" s="3"/>
+      <c r="AI126" s="3"/>
+      <c r="AJ126" s="3"/>
+      <c r="AK126" s="3"/>
+      <c r="AL126" s="3"/>
+      <c r="AM126" s="3"/>
+      <c r="AN126" s="3"/>
+      <c r="AO126" s="3"/>
+      <c r="AP126" s="3"/>
+      <c r="AQ126" s="3"/>
+      <c r="AR126" s="3"/>
+    </row>
+    <row r="127" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -6212,8 +8289,30 @@
       <c r="T127" s="3"/>
       <c r="U127" s="3"/>
       <c r="V127" s="3"/>
-    </row>
-    <row r="128" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W127" s="3"/>
+      <c r="X127" s="3"/>
+      <c r="Y127" s="3"/>
+      <c r="Z127" s="3"/>
+      <c r="AA127" s="3"/>
+      <c r="AB127" s="3"/>
+      <c r="AC127" s="3"/>
+      <c r="AD127" s="3"/>
+      <c r="AE127" s="3"/>
+      <c r="AF127" s="3"/>
+      <c r="AG127" s="3"/>
+      <c r="AH127" s="3"/>
+      <c r="AI127" s="3"/>
+      <c r="AJ127" s="3"/>
+      <c r="AK127" s="3"/>
+      <c r="AL127" s="3"/>
+      <c r="AM127" s="3"/>
+      <c r="AN127" s="3"/>
+      <c r="AO127" s="3"/>
+      <c r="AP127" s="3"/>
+      <c r="AQ127" s="3"/>
+      <c r="AR127" s="3"/>
+    </row>
+    <row r="128" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -6234,8 +8333,30 @@
       <c r="T128" s="3"/>
       <c r="U128" s="3"/>
       <c r="V128" s="3"/>
-    </row>
-    <row r="129" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W128" s="3"/>
+      <c r="X128" s="3"/>
+      <c r="Y128" s="3"/>
+      <c r="Z128" s="3"/>
+      <c r="AA128" s="3"/>
+      <c r="AB128" s="3"/>
+      <c r="AC128" s="3"/>
+      <c r="AD128" s="3"/>
+      <c r="AE128" s="3"/>
+      <c r="AF128" s="3"/>
+      <c r="AG128" s="3"/>
+      <c r="AH128" s="3"/>
+      <c r="AI128" s="3"/>
+      <c r="AJ128" s="3"/>
+      <c r="AK128" s="3"/>
+      <c r="AL128" s="3"/>
+      <c r="AM128" s="3"/>
+      <c r="AN128" s="3"/>
+      <c r="AO128" s="3"/>
+      <c r="AP128" s="3"/>
+      <c r="AQ128" s="3"/>
+      <c r="AR128" s="3"/>
+    </row>
+    <row r="129" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -6256,8 +8377,30 @@
       <c r="T129" s="3"/>
       <c r="U129" s="3"/>
       <c r="V129" s="3"/>
-    </row>
-    <row r="130" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W129" s="3"/>
+      <c r="X129" s="3"/>
+      <c r="Y129" s="3"/>
+      <c r="Z129" s="3"/>
+      <c r="AA129" s="3"/>
+      <c r="AB129" s="3"/>
+      <c r="AC129" s="3"/>
+      <c r="AD129" s="3"/>
+      <c r="AE129" s="3"/>
+      <c r="AF129" s="3"/>
+      <c r="AG129" s="3"/>
+      <c r="AH129" s="3"/>
+      <c r="AI129" s="3"/>
+      <c r="AJ129" s="3"/>
+      <c r="AK129" s="3"/>
+      <c r="AL129" s="3"/>
+      <c r="AM129" s="3"/>
+      <c r="AN129" s="3"/>
+      <c r="AO129" s="3"/>
+      <c r="AP129" s="3"/>
+      <c r="AQ129" s="3"/>
+      <c r="AR129" s="3"/>
+    </row>
+    <row r="130" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -6278,8 +8421,30 @@
       <c r="T130" s="3"/>
       <c r="U130" s="3"/>
       <c r="V130" s="3"/>
-    </row>
-    <row r="131" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W130" s="3"/>
+      <c r="X130" s="3"/>
+      <c r="Y130" s="3"/>
+      <c r="Z130" s="3"/>
+      <c r="AA130" s="3"/>
+      <c r="AB130" s="3"/>
+      <c r="AC130" s="3"/>
+      <c r="AD130" s="3"/>
+      <c r="AE130" s="3"/>
+      <c r="AF130" s="3"/>
+      <c r="AG130" s="3"/>
+      <c r="AH130" s="3"/>
+      <c r="AI130" s="3"/>
+      <c r="AJ130" s="3"/>
+      <c r="AK130" s="3"/>
+      <c r="AL130" s="3"/>
+      <c r="AM130" s="3"/>
+      <c r="AN130" s="3"/>
+      <c r="AO130" s="3"/>
+      <c r="AP130" s="3"/>
+      <c r="AQ130" s="3"/>
+      <c r="AR130" s="3"/>
+    </row>
+    <row r="131" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -6300,8 +8465,30 @@
       <c r="T131" s="3"/>
       <c r="U131" s="3"/>
       <c r="V131" s="3"/>
-    </row>
-    <row r="132" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W131" s="3"/>
+      <c r="X131" s="3"/>
+      <c r="Y131" s="3"/>
+      <c r="Z131" s="3"/>
+      <c r="AA131" s="3"/>
+      <c r="AB131" s="3"/>
+      <c r="AC131" s="3"/>
+      <c r="AD131" s="3"/>
+      <c r="AE131" s="3"/>
+      <c r="AF131" s="3"/>
+      <c r="AG131" s="3"/>
+      <c r="AH131" s="3"/>
+      <c r="AI131" s="3"/>
+      <c r="AJ131" s="3"/>
+      <c r="AK131" s="3"/>
+      <c r="AL131" s="3"/>
+      <c r="AM131" s="3"/>
+      <c r="AN131" s="3"/>
+      <c r="AO131" s="3"/>
+      <c r="AP131" s="3"/>
+      <c r="AQ131" s="3"/>
+      <c r="AR131" s="3"/>
+    </row>
+    <row r="132" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -6322,8 +8509,30 @@
       <c r="T132" s="3"/>
       <c r="U132" s="3"/>
       <c r="V132" s="3"/>
-    </row>
-    <row r="133" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W132" s="3"/>
+      <c r="X132" s="3"/>
+      <c r="Y132" s="3"/>
+      <c r="Z132" s="3"/>
+      <c r="AA132" s="3"/>
+      <c r="AB132" s="3"/>
+      <c r="AC132" s="3"/>
+      <c r="AD132" s="3"/>
+      <c r="AE132" s="3"/>
+      <c r="AF132" s="3"/>
+      <c r="AG132" s="3"/>
+      <c r="AH132" s="3"/>
+      <c r="AI132" s="3"/>
+      <c r="AJ132" s="3"/>
+      <c r="AK132" s="3"/>
+      <c r="AL132" s="3"/>
+      <c r="AM132" s="3"/>
+      <c r="AN132" s="3"/>
+      <c r="AO132" s="3"/>
+      <c r="AP132" s="3"/>
+      <c r="AQ132" s="3"/>
+      <c r="AR132" s="3"/>
+    </row>
+    <row r="133" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -6344,8 +8553,30 @@
       <c r="T133" s="3"/>
       <c r="U133" s="3"/>
       <c r="V133" s="3"/>
-    </row>
-    <row r="134" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W133" s="3"/>
+      <c r="X133" s="3"/>
+      <c r="Y133" s="3"/>
+      <c r="Z133" s="3"/>
+      <c r="AA133" s="3"/>
+      <c r="AB133" s="3"/>
+      <c r="AC133" s="3"/>
+      <c r="AD133" s="3"/>
+      <c r="AE133" s="3"/>
+      <c r="AF133" s="3"/>
+      <c r="AG133" s="3"/>
+      <c r="AH133" s="3"/>
+      <c r="AI133" s="3"/>
+      <c r="AJ133" s="3"/>
+      <c r="AK133" s="3"/>
+      <c r="AL133" s="3"/>
+      <c r="AM133" s="3"/>
+      <c r="AN133" s="3"/>
+      <c r="AO133" s="3"/>
+      <c r="AP133" s="3"/>
+      <c r="AQ133" s="3"/>
+      <c r="AR133" s="3"/>
+    </row>
+    <row r="134" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -6366,8 +8597,30 @@
       <c r="T134" s="3"/>
       <c r="U134" s="3"/>
       <c r="V134" s="3"/>
-    </row>
-    <row r="135" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W134" s="3"/>
+      <c r="X134" s="3"/>
+      <c r="Y134" s="3"/>
+      <c r="Z134" s="3"/>
+      <c r="AA134" s="3"/>
+      <c r="AB134" s="3"/>
+      <c r="AC134" s="3"/>
+      <c r="AD134" s="3"/>
+      <c r="AE134" s="3"/>
+      <c r="AF134" s="3"/>
+      <c r="AG134" s="3"/>
+      <c r="AH134" s="3"/>
+      <c r="AI134" s="3"/>
+      <c r="AJ134" s="3"/>
+      <c r="AK134" s="3"/>
+      <c r="AL134" s="3"/>
+      <c r="AM134" s="3"/>
+      <c r="AN134" s="3"/>
+      <c r="AO134" s="3"/>
+      <c r="AP134" s="3"/>
+      <c r="AQ134" s="3"/>
+      <c r="AR134" s="3"/>
+    </row>
+    <row r="135" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -6388,8 +8641,30 @@
       <c r="T135" s="3"/>
       <c r="U135" s="3"/>
       <c r="V135" s="3"/>
-    </row>
-    <row r="136" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W135" s="3"/>
+      <c r="X135" s="3"/>
+      <c r="Y135" s="3"/>
+      <c r="Z135" s="3"/>
+      <c r="AA135" s="3"/>
+      <c r="AB135" s="3"/>
+      <c r="AC135" s="3"/>
+      <c r="AD135" s="3"/>
+      <c r="AE135" s="3"/>
+      <c r="AF135" s="3"/>
+      <c r="AG135" s="3"/>
+      <c r="AH135" s="3"/>
+      <c r="AI135" s="3"/>
+      <c r="AJ135" s="3"/>
+      <c r="AK135" s="3"/>
+      <c r="AL135" s="3"/>
+      <c r="AM135" s="3"/>
+      <c r="AN135" s="3"/>
+      <c r="AO135" s="3"/>
+      <c r="AP135" s="3"/>
+      <c r="AQ135" s="3"/>
+      <c r="AR135" s="3"/>
+    </row>
+    <row r="136" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -6410,8 +8685,30 @@
       <c r="T136" s="3"/>
       <c r="U136" s="3"/>
       <c r="V136" s="3"/>
-    </row>
-    <row r="137" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W136" s="3"/>
+      <c r="X136" s="3"/>
+      <c r="Y136" s="3"/>
+      <c r="Z136" s="3"/>
+      <c r="AA136" s="3"/>
+      <c r="AB136" s="3"/>
+      <c r="AC136" s="3"/>
+      <c r="AD136" s="3"/>
+      <c r="AE136" s="3"/>
+      <c r="AF136" s="3"/>
+      <c r="AG136" s="3"/>
+      <c r="AH136" s="3"/>
+      <c r="AI136" s="3"/>
+      <c r="AJ136" s="3"/>
+      <c r="AK136" s="3"/>
+      <c r="AL136" s="3"/>
+      <c r="AM136" s="3"/>
+      <c r="AN136" s="3"/>
+      <c r="AO136" s="3"/>
+      <c r="AP136" s="3"/>
+      <c r="AQ136" s="3"/>
+      <c r="AR136" s="3"/>
+    </row>
+    <row r="137" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -6432,8 +8729,30 @@
       <c r="T137" s="3"/>
       <c r="U137" s="3"/>
       <c r="V137" s="3"/>
-    </row>
-    <row r="138" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W137" s="3"/>
+      <c r="X137" s="3"/>
+      <c r="Y137" s="3"/>
+      <c r="Z137" s="3"/>
+      <c r="AA137" s="3"/>
+      <c r="AB137" s="3"/>
+      <c r="AC137" s="3"/>
+      <c r="AD137" s="3"/>
+      <c r="AE137" s="3"/>
+      <c r="AF137" s="3"/>
+      <c r="AG137" s="3"/>
+      <c r="AH137" s="3"/>
+      <c r="AI137" s="3"/>
+      <c r="AJ137" s="3"/>
+      <c r="AK137" s="3"/>
+      <c r="AL137" s="3"/>
+      <c r="AM137" s="3"/>
+      <c r="AN137" s="3"/>
+      <c r="AO137" s="3"/>
+      <c r="AP137" s="3"/>
+      <c r="AQ137" s="3"/>
+      <c r="AR137" s="3"/>
+    </row>
+    <row r="138" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -6454,8 +8773,30 @@
       <c r="T138" s="3"/>
       <c r="U138" s="3"/>
       <c r="V138" s="3"/>
-    </row>
-    <row r="139" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W138" s="3"/>
+      <c r="X138" s="3"/>
+      <c r="Y138" s="3"/>
+      <c r="Z138" s="3"/>
+      <c r="AA138" s="3"/>
+      <c r="AB138" s="3"/>
+      <c r="AC138" s="3"/>
+      <c r="AD138" s="3"/>
+      <c r="AE138" s="3"/>
+      <c r="AF138" s="3"/>
+      <c r="AG138" s="3"/>
+      <c r="AH138" s="3"/>
+      <c r="AI138" s="3"/>
+      <c r="AJ138" s="3"/>
+      <c r="AK138" s="3"/>
+      <c r="AL138" s="3"/>
+      <c r="AM138" s="3"/>
+      <c r="AN138" s="3"/>
+      <c r="AO138" s="3"/>
+      <c r="AP138" s="3"/>
+      <c r="AQ138" s="3"/>
+      <c r="AR138" s="3"/>
+    </row>
+    <row r="139" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -6476,8 +8817,30 @@
       <c r="T139" s="3"/>
       <c r="U139" s="3"/>
       <c r="V139" s="3"/>
-    </row>
-    <row r="140" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W139" s="3"/>
+      <c r="X139" s="3"/>
+      <c r="Y139" s="3"/>
+      <c r="Z139" s="3"/>
+      <c r="AA139" s="3"/>
+      <c r="AB139" s="3"/>
+      <c r="AC139" s="3"/>
+      <c r="AD139" s="3"/>
+      <c r="AE139" s="3"/>
+      <c r="AF139" s="3"/>
+      <c r="AG139" s="3"/>
+      <c r="AH139" s="3"/>
+      <c r="AI139" s="3"/>
+      <c r="AJ139" s="3"/>
+      <c r="AK139" s="3"/>
+      <c r="AL139" s="3"/>
+      <c r="AM139" s="3"/>
+      <c r="AN139" s="3"/>
+      <c r="AO139" s="3"/>
+      <c r="AP139" s="3"/>
+      <c r="AQ139" s="3"/>
+      <c r="AR139" s="3"/>
+    </row>
+    <row r="140" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -6498,8 +8861,30 @@
       <c r="T140" s="3"/>
       <c r="U140" s="3"/>
       <c r="V140" s="3"/>
-    </row>
-    <row r="141" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W140" s="3"/>
+      <c r="X140" s="3"/>
+      <c r="Y140" s="3"/>
+      <c r="Z140" s="3"/>
+      <c r="AA140" s="3"/>
+      <c r="AB140" s="3"/>
+      <c r="AC140" s="3"/>
+      <c r="AD140" s="3"/>
+      <c r="AE140" s="3"/>
+      <c r="AF140" s="3"/>
+      <c r="AG140" s="3"/>
+      <c r="AH140" s="3"/>
+      <c r="AI140" s="3"/>
+      <c r="AJ140" s="3"/>
+      <c r="AK140" s="3"/>
+      <c r="AL140" s="3"/>
+      <c r="AM140" s="3"/>
+      <c r="AN140" s="3"/>
+      <c r="AO140" s="3"/>
+      <c r="AP140" s="3"/>
+      <c r="AQ140" s="3"/>
+      <c r="AR140" s="3"/>
+    </row>
+    <row r="141" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -6520,8 +8905,30 @@
       <c r="T141" s="3"/>
       <c r="U141" s="3"/>
       <c r="V141" s="3"/>
-    </row>
-    <row r="142" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W141" s="3"/>
+      <c r="X141" s="3"/>
+      <c r="Y141" s="3"/>
+      <c r="Z141" s="3"/>
+      <c r="AA141" s="3"/>
+      <c r="AB141" s="3"/>
+      <c r="AC141" s="3"/>
+      <c r="AD141" s="3"/>
+      <c r="AE141" s="3"/>
+      <c r="AF141" s="3"/>
+      <c r="AG141" s="3"/>
+      <c r="AH141" s="3"/>
+      <c r="AI141" s="3"/>
+      <c r="AJ141" s="3"/>
+      <c r="AK141" s="3"/>
+      <c r="AL141" s="3"/>
+      <c r="AM141" s="3"/>
+      <c r="AN141" s="3"/>
+      <c r="AO141" s="3"/>
+      <c r="AP141" s="3"/>
+      <c r="AQ141" s="3"/>
+      <c r="AR141" s="3"/>
+    </row>
+    <row r="142" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -6542,8 +8949,30 @@
       <c r="T142" s="3"/>
       <c r="U142" s="3"/>
       <c r="V142" s="3"/>
-    </row>
-    <row r="143" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W142" s="3"/>
+      <c r="X142" s="3"/>
+      <c r="Y142" s="3"/>
+      <c r="Z142" s="3"/>
+      <c r="AA142" s="3"/>
+      <c r="AB142" s="3"/>
+      <c r="AC142" s="3"/>
+      <c r="AD142" s="3"/>
+      <c r="AE142" s="3"/>
+      <c r="AF142" s="3"/>
+      <c r="AG142" s="3"/>
+      <c r="AH142" s="3"/>
+      <c r="AI142" s="3"/>
+      <c r="AJ142" s="3"/>
+      <c r="AK142" s="3"/>
+      <c r="AL142" s="3"/>
+      <c r="AM142" s="3"/>
+      <c r="AN142" s="3"/>
+      <c r="AO142" s="3"/>
+      <c r="AP142" s="3"/>
+      <c r="AQ142" s="3"/>
+      <c r="AR142" s="3"/>
+    </row>
+    <row r="143" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -6564,8 +8993,30 @@
       <c r="T143" s="3"/>
       <c r="U143" s="3"/>
       <c r="V143" s="3"/>
-    </row>
-    <row r="144" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W143" s="3"/>
+      <c r="X143" s="3"/>
+      <c r="Y143" s="3"/>
+      <c r="Z143" s="3"/>
+      <c r="AA143" s="3"/>
+      <c r="AB143" s="3"/>
+      <c r="AC143" s="3"/>
+      <c r="AD143" s="3"/>
+      <c r="AE143" s="3"/>
+      <c r="AF143" s="3"/>
+      <c r="AG143" s="3"/>
+      <c r="AH143" s="3"/>
+      <c r="AI143" s="3"/>
+      <c r="AJ143" s="3"/>
+      <c r="AK143" s="3"/>
+      <c r="AL143" s="3"/>
+      <c r="AM143" s="3"/>
+      <c r="AN143" s="3"/>
+      <c r="AO143" s="3"/>
+      <c r="AP143" s="3"/>
+      <c r="AQ143" s="3"/>
+      <c r="AR143" s="3"/>
+    </row>
+    <row r="144" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -6586,8 +9037,30 @@
       <c r="T144" s="3"/>
       <c r="U144" s="3"/>
       <c r="V144" s="3"/>
-    </row>
-    <row r="145" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W144" s="3"/>
+      <c r="X144" s="3"/>
+      <c r="Y144" s="3"/>
+      <c r="Z144" s="3"/>
+      <c r="AA144" s="3"/>
+      <c r="AB144" s="3"/>
+      <c r="AC144" s="3"/>
+      <c r="AD144" s="3"/>
+      <c r="AE144" s="3"/>
+      <c r="AF144" s="3"/>
+      <c r="AG144" s="3"/>
+      <c r="AH144" s="3"/>
+      <c r="AI144" s="3"/>
+      <c r="AJ144" s="3"/>
+      <c r="AK144" s="3"/>
+      <c r="AL144" s="3"/>
+      <c r="AM144" s="3"/>
+      <c r="AN144" s="3"/>
+      <c r="AO144" s="3"/>
+      <c r="AP144" s="3"/>
+      <c r="AQ144" s="3"/>
+      <c r="AR144" s="3"/>
+    </row>
+    <row r="145" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -6608,8 +9081,30 @@
       <c r="T145" s="3"/>
       <c r="U145" s="3"/>
       <c r="V145" s="3"/>
-    </row>
-    <row r="146" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W145" s="3"/>
+      <c r="X145" s="3"/>
+      <c r="Y145" s="3"/>
+      <c r="Z145" s="3"/>
+      <c r="AA145" s="3"/>
+      <c r="AB145" s="3"/>
+      <c r="AC145" s="3"/>
+      <c r="AD145" s="3"/>
+      <c r="AE145" s="3"/>
+      <c r="AF145" s="3"/>
+      <c r="AG145" s="3"/>
+      <c r="AH145" s="3"/>
+      <c r="AI145" s="3"/>
+      <c r="AJ145" s="3"/>
+      <c r="AK145" s="3"/>
+      <c r="AL145" s="3"/>
+      <c r="AM145" s="3"/>
+      <c r="AN145" s="3"/>
+      <c r="AO145" s="3"/>
+      <c r="AP145" s="3"/>
+      <c r="AQ145" s="3"/>
+      <c r="AR145" s="3"/>
+    </row>
+    <row r="146" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -6630,8 +9125,30 @@
       <c r="T146" s="3"/>
       <c r="U146" s="3"/>
       <c r="V146" s="3"/>
-    </row>
-    <row r="147" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W146" s="3"/>
+      <c r="X146" s="3"/>
+      <c r="Y146" s="3"/>
+      <c r="Z146" s="3"/>
+      <c r="AA146" s="3"/>
+      <c r="AB146" s="3"/>
+      <c r="AC146" s="3"/>
+      <c r="AD146" s="3"/>
+      <c r="AE146" s="3"/>
+      <c r="AF146" s="3"/>
+      <c r="AG146" s="3"/>
+      <c r="AH146" s="3"/>
+      <c r="AI146" s="3"/>
+      <c r="AJ146" s="3"/>
+      <c r="AK146" s="3"/>
+      <c r="AL146" s="3"/>
+      <c r="AM146" s="3"/>
+      <c r="AN146" s="3"/>
+      <c r="AO146" s="3"/>
+      <c r="AP146" s="3"/>
+      <c r="AQ146" s="3"/>
+      <c r="AR146" s="3"/>
+    </row>
+    <row r="147" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -6652,8 +9169,30 @@
       <c r="T147" s="3"/>
       <c r="U147" s="3"/>
       <c r="V147" s="3"/>
-    </row>
-    <row r="148" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W147" s="3"/>
+      <c r="X147" s="3"/>
+      <c r="Y147" s="3"/>
+      <c r="Z147" s="3"/>
+      <c r="AA147" s="3"/>
+      <c r="AB147" s="3"/>
+      <c r="AC147" s="3"/>
+      <c r="AD147" s="3"/>
+      <c r="AE147" s="3"/>
+      <c r="AF147" s="3"/>
+      <c r="AG147" s="3"/>
+      <c r="AH147" s="3"/>
+      <c r="AI147" s="3"/>
+      <c r="AJ147" s="3"/>
+      <c r="AK147" s="3"/>
+      <c r="AL147" s="3"/>
+      <c r="AM147" s="3"/>
+      <c r="AN147" s="3"/>
+      <c r="AO147" s="3"/>
+      <c r="AP147" s="3"/>
+      <c r="AQ147" s="3"/>
+      <c r="AR147" s="3"/>
+    </row>
+    <row r="148" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -6674,8 +9213,30 @@
       <c r="T148" s="3"/>
       <c r="U148" s="3"/>
       <c r="V148" s="3"/>
-    </row>
-    <row r="149" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W148" s="3"/>
+      <c r="X148" s="3"/>
+      <c r="Y148" s="3"/>
+      <c r="Z148" s="3"/>
+      <c r="AA148" s="3"/>
+      <c r="AB148" s="3"/>
+      <c r="AC148" s="3"/>
+      <c r="AD148" s="3"/>
+      <c r="AE148" s="3"/>
+      <c r="AF148" s="3"/>
+      <c r="AG148" s="3"/>
+      <c r="AH148" s="3"/>
+      <c r="AI148" s="3"/>
+      <c r="AJ148" s="3"/>
+      <c r="AK148" s="3"/>
+      <c r="AL148" s="3"/>
+      <c r="AM148" s="3"/>
+      <c r="AN148" s="3"/>
+      <c r="AO148" s="3"/>
+      <c r="AP148" s="3"/>
+      <c r="AQ148" s="3"/>
+      <c r="AR148" s="3"/>
+    </row>
+    <row r="149" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -6696,8 +9257,30 @@
       <c r="T149" s="3"/>
       <c r="U149" s="3"/>
       <c r="V149" s="3"/>
-    </row>
-    <row r="150" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W149" s="3"/>
+      <c r="X149" s="3"/>
+      <c r="Y149" s="3"/>
+      <c r="Z149" s="3"/>
+      <c r="AA149" s="3"/>
+      <c r="AB149" s="3"/>
+      <c r="AC149" s="3"/>
+      <c r="AD149" s="3"/>
+      <c r="AE149" s="3"/>
+      <c r="AF149" s="3"/>
+      <c r="AG149" s="3"/>
+      <c r="AH149" s="3"/>
+      <c r="AI149" s="3"/>
+      <c r="AJ149" s="3"/>
+      <c r="AK149" s="3"/>
+      <c r="AL149" s="3"/>
+      <c r="AM149" s="3"/>
+      <c r="AN149" s="3"/>
+      <c r="AO149" s="3"/>
+      <c r="AP149" s="3"/>
+      <c r="AQ149" s="3"/>
+      <c r="AR149" s="3"/>
+    </row>
+    <row r="150" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -6718,8 +9301,30 @@
       <c r="T150" s="3"/>
       <c r="U150" s="3"/>
       <c r="V150" s="3"/>
-    </row>
-    <row r="151" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W150" s="3"/>
+      <c r="X150" s="3"/>
+      <c r="Y150" s="3"/>
+      <c r="Z150" s="3"/>
+      <c r="AA150" s="3"/>
+      <c r="AB150" s="3"/>
+      <c r="AC150" s="3"/>
+      <c r="AD150" s="3"/>
+      <c r="AE150" s="3"/>
+      <c r="AF150" s="3"/>
+      <c r="AG150" s="3"/>
+      <c r="AH150" s="3"/>
+      <c r="AI150" s="3"/>
+      <c r="AJ150" s="3"/>
+      <c r="AK150" s="3"/>
+      <c r="AL150" s="3"/>
+      <c r="AM150" s="3"/>
+      <c r="AN150" s="3"/>
+      <c r="AO150" s="3"/>
+      <c r="AP150" s="3"/>
+      <c r="AQ150" s="3"/>
+      <c r="AR150" s="3"/>
+    </row>
+    <row r="151" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -6740,8 +9345,30 @@
       <c r="T151" s="3"/>
       <c r="U151" s="3"/>
       <c r="V151" s="3"/>
-    </row>
-    <row r="152" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W151" s="3"/>
+      <c r="X151" s="3"/>
+      <c r="Y151" s="3"/>
+      <c r="Z151" s="3"/>
+      <c r="AA151" s="3"/>
+      <c r="AB151" s="3"/>
+      <c r="AC151" s="3"/>
+      <c r="AD151" s="3"/>
+      <c r="AE151" s="3"/>
+      <c r="AF151" s="3"/>
+      <c r="AG151" s="3"/>
+      <c r="AH151" s="3"/>
+      <c r="AI151" s="3"/>
+      <c r="AJ151" s="3"/>
+      <c r="AK151" s="3"/>
+      <c r="AL151" s="3"/>
+      <c r="AM151" s="3"/>
+      <c r="AN151" s="3"/>
+      <c r="AO151" s="3"/>
+      <c r="AP151" s="3"/>
+      <c r="AQ151" s="3"/>
+      <c r="AR151" s="3"/>
+    </row>
+    <row r="152" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -6762,8 +9389,30 @@
       <c r="T152" s="3"/>
       <c r="U152" s="3"/>
       <c r="V152" s="3"/>
-    </row>
-    <row r="153" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W152" s="3"/>
+      <c r="X152" s="3"/>
+      <c r="Y152" s="3"/>
+      <c r="Z152" s="3"/>
+      <c r="AA152" s="3"/>
+      <c r="AB152" s="3"/>
+      <c r="AC152" s="3"/>
+      <c r="AD152" s="3"/>
+      <c r="AE152" s="3"/>
+      <c r="AF152" s="3"/>
+      <c r="AG152" s="3"/>
+      <c r="AH152" s="3"/>
+      <c r="AI152" s="3"/>
+      <c r="AJ152" s="3"/>
+      <c r="AK152" s="3"/>
+      <c r="AL152" s="3"/>
+      <c r="AM152" s="3"/>
+      <c r="AN152" s="3"/>
+      <c r="AO152" s="3"/>
+      <c r="AP152" s="3"/>
+      <c r="AQ152" s="3"/>
+      <c r="AR152" s="3"/>
+    </row>
+    <row r="153" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -6784,8 +9433,30 @@
       <c r="T153" s="3"/>
       <c r="U153" s="3"/>
       <c r="V153" s="3"/>
-    </row>
-    <row r="154" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W153" s="3"/>
+      <c r="X153" s="3"/>
+      <c r="Y153" s="3"/>
+      <c r="Z153" s="3"/>
+      <c r="AA153" s="3"/>
+      <c r="AB153" s="3"/>
+      <c r="AC153" s="3"/>
+      <c r="AD153" s="3"/>
+      <c r="AE153" s="3"/>
+      <c r="AF153" s="3"/>
+      <c r="AG153" s="3"/>
+      <c r="AH153" s="3"/>
+      <c r="AI153" s="3"/>
+      <c r="AJ153" s="3"/>
+      <c r="AK153" s="3"/>
+      <c r="AL153" s="3"/>
+      <c r="AM153" s="3"/>
+      <c r="AN153" s="3"/>
+      <c r="AO153" s="3"/>
+      <c r="AP153" s="3"/>
+      <c r="AQ153" s="3"/>
+      <c r="AR153" s="3"/>
+    </row>
+    <row r="154" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -6806,8 +9477,30 @@
       <c r="T154" s="3"/>
       <c r="U154" s="3"/>
       <c r="V154" s="3"/>
-    </row>
-    <row r="155" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W154" s="3"/>
+      <c r="X154" s="3"/>
+      <c r="Y154" s="3"/>
+      <c r="Z154" s="3"/>
+      <c r="AA154" s="3"/>
+      <c r="AB154" s="3"/>
+      <c r="AC154" s="3"/>
+      <c r="AD154" s="3"/>
+      <c r="AE154" s="3"/>
+      <c r="AF154" s="3"/>
+      <c r="AG154" s="3"/>
+      <c r="AH154" s="3"/>
+      <c r="AI154" s="3"/>
+      <c r="AJ154" s="3"/>
+      <c r="AK154" s="3"/>
+      <c r="AL154" s="3"/>
+      <c r="AM154" s="3"/>
+      <c r="AN154" s="3"/>
+      <c r="AO154" s="3"/>
+      <c r="AP154" s="3"/>
+      <c r="AQ154" s="3"/>
+      <c r="AR154" s="3"/>
+    </row>
+    <row r="155" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -6828,8 +9521,30 @@
       <c r="T155" s="3"/>
       <c r="U155" s="3"/>
       <c r="V155" s="3"/>
-    </row>
-    <row r="156" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W155" s="3"/>
+      <c r="X155" s="3"/>
+      <c r="Y155" s="3"/>
+      <c r="Z155" s="3"/>
+      <c r="AA155" s="3"/>
+      <c r="AB155" s="3"/>
+      <c r="AC155" s="3"/>
+      <c r="AD155" s="3"/>
+      <c r="AE155" s="3"/>
+      <c r="AF155" s="3"/>
+      <c r="AG155" s="3"/>
+      <c r="AH155" s="3"/>
+      <c r="AI155" s="3"/>
+      <c r="AJ155" s="3"/>
+      <c r="AK155" s="3"/>
+      <c r="AL155" s="3"/>
+      <c r="AM155" s="3"/>
+      <c r="AN155" s="3"/>
+      <c r="AO155" s="3"/>
+      <c r="AP155" s="3"/>
+      <c r="AQ155" s="3"/>
+      <c r="AR155" s="3"/>
+    </row>
+    <row r="156" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -6850,8 +9565,30 @@
       <c r="T156" s="3"/>
       <c r="U156" s="3"/>
       <c r="V156" s="3"/>
-    </row>
-    <row r="157" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W156" s="3"/>
+      <c r="X156" s="3"/>
+      <c r="Y156" s="3"/>
+      <c r="Z156" s="3"/>
+      <c r="AA156" s="3"/>
+      <c r="AB156" s="3"/>
+      <c r="AC156" s="3"/>
+      <c r="AD156" s="3"/>
+      <c r="AE156" s="3"/>
+      <c r="AF156" s="3"/>
+      <c r="AG156" s="3"/>
+      <c r="AH156" s="3"/>
+      <c r="AI156" s="3"/>
+      <c r="AJ156" s="3"/>
+      <c r="AK156" s="3"/>
+      <c r="AL156" s="3"/>
+      <c r="AM156" s="3"/>
+      <c r="AN156" s="3"/>
+      <c r="AO156" s="3"/>
+      <c r="AP156" s="3"/>
+      <c r="AQ156" s="3"/>
+      <c r="AR156" s="3"/>
+    </row>
+    <row r="157" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -6872,8 +9609,30 @@
       <c r="T157" s="3"/>
       <c r="U157" s="3"/>
       <c r="V157" s="3"/>
-    </row>
-    <row r="158" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W157" s="3"/>
+      <c r="X157" s="3"/>
+      <c r="Y157" s="3"/>
+      <c r="Z157" s="3"/>
+      <c r="AA157" s="3"/>
+      <c r="AB157" s="3"/>
+      <c r="AC157" s="3"/>
+      <c r="AD157" s="3"/>
+      <c r="AE157" s="3"/>
+      <c r="AF157" s="3"/>
+      <c r="AG157" s="3"/>
+      <c r="AH157" s="3"/>
+      <c r="AI157" s="3"/>
+      <c r="AJ157" s="3"/>
+      <c r="AK157" s="3"/>
+      <c r="AL157" s="3"/>
+      <c r="AM157" s="3"/>
+      <c r="AN157" s="3"/>
+      <c r="AO157" s="3"/>
+      <c r="AP157" s="3"/>
+      <c r="AQ157" s="3"/>
+      <c r="AR157" s="3"/>
+    </row>
+    <row r="158" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -6894,8 +9653,30 @@
       <c r="T158" s="3"/>
       <c r="U158" s="3"/>
       <c r="V158" s="3"/>
-    </row>
-    <row r="159" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W158" s="3"/>
+      <c r="X158" s="3"/>
+      <c r="Y158" s="3"/>
+      <c r="Z158" s="3"/>
+      <c r="AA158" s="3"/>
+      <c r="AB158" s="3"/>
+      <c r="AC158" s="3"/>
+      <c r="AD158" s="3"/>
+      <c r="AE158" s="3"/>
+      <c r="AF158" s="3"/>
+      <c r="AG158" s="3"/>
+      <c r="AH158" s="3"/>
+      <c r="AI158" s="3"/>
+      <c r="AJ158" s="3"/>
+      <c r="AK158" s="3"/>
+      <c r="AL158" s="3"/>
+      <c r="AM158" s="3"/>
+      <c r="AN158" s="3"/>
+      <c r="AO158" s="3"/>
+      <c r="AP158" s="3"/>
+      <c r="AQ158" s="3"/>
+      <c r="AR158" s="3"/>
+    </row>
+    <row r="159" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -6916,8 +9697,30 @@
       <c r="T159" s="3"/>
       <c r="U159" s="3"/>
       <c r="V159" s="3"/>
-    </row>
-    <row r="160" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W159" s="3"/>
+      <c r="X159" s="3"/>
+      <c r="Y159" s="3"/>
+      <c r="Z159" s="3"/>
+      <c r="AA159" s="3"/>
+      <c r="AB159" s="3"/>
+      <c r="AC159" s="3"/>
+      <c r="AD159" s="3"/>
+      <c r="AE159" s="3"/>
+      <c r="AF159" s="3"/>
+      <c r="AG159" s="3"/>
+      <c r="AH159" s="3"/>
+      <c r="AI159" s="3"/>
+      <c r="AJ159" s="3"/>
+      <c r="AK159" s="3"/>
+      <c r="AL159" s="3"/>
+      <c r="AM159" s="3"/>
+      <c r="AN159" s="3"/>
+      <c r="AO159" s="3"/>
+      <c r="AP159" s="3"/>
+      <c r="AQ159" s="3"/>
+      <c r="AR159" s="3"/>
+    </row>
+    <row r="160" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -6938,8 +9741,30 @@
       <c r="T160" s="3"/>
       <c r="U160" s="3"/>
       <c r="V160" s="3"/>
-    </row>
-    <row r="161" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W160" s="3"/>
+      <c r="X160" s="3"/>
+      <c r="Y160" s="3"/>
+      <c r="Z160" s="3"/>
+      <c r="AA160" s="3"/>
+      <c r="AB160" s="3"/>
+      <c r="AC160" s="3"/>
+      <c r="AD160" s="3"/>
+      <c r="AE160" s="3"/>
+      <c r="AF160" s="3"/>
+      <c r="AG160" s="3"/>
+      <c r="AH160" s="3"/>
+      <c r="AI160" s="3"/>
+      <c r="AJ160" s="3"/>
+      <c r="AK160" s="3"/>
+      <c r="AL160" s="3"/>
+      <c r="AM160" s="3"/>
+      <c r="AN160" s="3"/>
+      <c r="AO160" s="3"/>
+      <c r="AP160" s="3"/>
+      <c r="AQ160" s="3"/>
+      <c r="AR160" s="3"/>
+    </row>
+    <row r="161" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -6960,8 +9785,30 @@
       <c r="T161" s="3"/>
       <c r="U161" s="3"/>
       <c r="V161" s="3"/>
-    </row>
-    <row r="162" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W161" s="3"/>
+      <c r="X161" s="3"/>
+      <c r="Y161" s="3"/>
+      <c r="Z161" s="3"/>
+      <c r="AA161" s="3"/>
+      <c r="AB161" s="3"/>
+      <c r="AC161" s="3"/>
+      <c r="AD161" s="3"/>
+      <c r="AE161" s="3"/>
+      <c r="AF161" s="3"/>
+      <c r="AG161" s="3"/>
+      <c r="AH161" s="3"/>
+      <c r="AI161" s="3"/>
+      <c r="AJ161" s="3"/>
+      <c r="AK161" s="3"/>
+      <c r="AL161" s="3"/>
+      <c r="AM161" s="3"/>
+      <c r="AN161" s="3"/>
+      <c r="AO161" s="3"/>
+      <c r="AP161" s="3"/>
+      <c r="AQ161" s="3"/>
+      <c r="AR161" s="3"/>
+    </row>
+    <row r="162" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -6982,8 +9829,30 @@
       <c r="T162" s="3"/>
       <c r="U162" s="3"/>
       <c r="V162" s="3"/>
-    </row>
-    <row r="163" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W162" s="3"/>
+      <c r="X162" s="3"/>
+      <c r="Y162" s="3"/>
+      <c r="Z162" s="3"/>
+      <c r="AA162" s="3"/>
+      <c r="AB162" s="3"/>
+      <c r="AC162" s="3"/>
+      <c r="AD162" s="3"/>
+      <c r="AE162" s="3"/>
+      <c r="AF162" s="3"/>
+      <c r="AG162" s="3"/>
+      <c r="AH162" s="3"/>
+      <c r="AI162" s="3"/>
+      <c r="AJ162" s="3"/>
+      <c r="AK162" s="3"/>
+      <c r="AL162" s="3"/>
+      <c r="AM162" s="3"/>
+      <c r="AN162" s="3"/>
+      <c r="AO162" s="3"/>
+      <c r="AP162" s="3"/>
+      <c r="AQ162" s="3"/>
+      <c r="AR162" s="3"/>
+    </row>
+    <row r="163" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -7004,8 +9873,30 @@
       <c r="T163" s="3"/>
       <c r="U163" s="3"/>
       <c r="V163" s="3"/>
-    </row>
-    <row r="164" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W163" s="3"/>
+      <c r="X163" s="3"/>
+      <c r="Y163" s="3"/>
+      <c r="Z163" s="3"/>
+      <c r="AA163" s="3"/>
+      <c r="AB163" s="3"/>
+      <c r="AC163" s="3"/>
+      <c r="AD163" s="3"/>
+      <c r="AE163" s="3"/>
+      <c r="AF163" s="3"/>
+      <c r="AG163" s="3"/>
+      <c r="AH163" s="3"/>
+      <c r="AI163" s="3"/>
+      <c r="AJ163" s="3"/>
+      <c r="AK163" s="3"/>
+      <c r="AL163" s="3"/>
+      <c r="AM163" s="3"/>
+      <c r="AN163" s="3"/>
+      <c r="AO163" s="3"/>
+      <c r="AP163" s="3"/>
+      <c r="AQ163" s="3"/>
+      <c r="AR163" s="3"/>
+    </row>
+    <row r="164" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -7026,8 +9917,30 @@
       <c r="T164" s="3"/>
       <c r="U164" s="3"/>
       <c r="V164" s="3"/>
-    </row>
-    <row r="165" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W164" s="3"/>
+      <c r="X164" s="3"/>
+      <c r="Y164" s="3"/>
+      <c r="Z164" s="3"/>
+      <c r="AA164" s="3"/>
+      <c r="AB164" s="3"/>
+      <c r="AC164" s="3"/>
+      <c r="AD164" s="3"/>
+      <c r="AE164" s="3"/>
+      <c r="AF164" s="3"/>
+      <c r="AG164" s="3"/>
+      <c r="AH164" s="3"/>
+      <c r="AI164" s="3"/>
+      <c r="AJ164" s="3"/>
+      <c r="AK164" s="3"/>
+      <c r="AL164" s="3"/>
+      <c r="AM164" s="3"/>
+      <c r="AN164" s="3"/>
+      <c r="AO164" s="3"/>
+      <c r="AP164" s="3"/>
+      <c r="AQ164" s="3"/>
+      <c r="AR164" s="3"/>
+    </row>
+    <row r="165" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -7048,8 +9961,30 @@
       <c r="T165" s="3"/>
       <c r="U165" s="3"/>
       <c r="V165" s="3"/>
-    </row>
-    <row r="166" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W165" s="3"/>
+      <c r="X165" s="3"/>
+      <c r="Y165" s="3"/>
+      <c r="Z165" s="3"/>
+      <c r="AA165" s="3"/>
+      <c r="AB165" s="3"/>
+      <c r="AC165" s="3"/>
+      <c r="AD165" s="3"/>
+      <c r="AE165" s="3"/>
+      <c r="AF165" s="3"/>
+      <c r="AG165" s="3"/>
+      <c r="AH165" s="3"/>
+      <c r="AI165" s="3"/>
+      <c r="AJ165" s="3"/>
+      <c r="AK165" s="3"/>
+      <c r="AL165" s="3"/>
+      <c r="AM165" s="3"/>
+      <c r="AN165" s="3"/>
+      <c r="AO165" s="3"/>
+      <c r="AP165" s="3"/>
+      <c r="AQ165" s="3"/>
+      <c r="AR165" s="3"/>
+    </row>
+    <row r="166" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -7070,8 +10005,30 @@
       <c r="T166" s="3"/>
       <c r="U166" s="3"/>
       <c r="V166" s="3"/>
-    </row>
-    <row r="167" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W166" s="3"/>
+      <c r="X166" s="3"/>
+      <c r="Y166" s="3"/>
+      <c r="Z166" s="3"/>
+      <c r="AA166" s="3"/>
+      <c r="AB166" s="3"/>
+      <c r="AC166" s="3"/>
+      <c r="AD166" s="3"/>
+      <c r="AE166" s="3"/>
+      <c r="AF166" s="3"/>
+      <c r="AG166" s="3"/>
+      <c r="AH166" s="3"/>
+      <c r="AI166" s="3"/>
+      <c r="AJ166" s="3"/>
+      <c r="AK166" s="3"/>
+      <c r="AL166" s="3"/>
+      <c r="AM166" s="3"/>
+      <c r="AN166" s="3"/>
+      <c r="AO166" s="3"/>
+      <c r="AP166" s="3"/>
+      <c r="AQ166" s="3"/>
+      <c r="AR166" s="3"/>
+    </row>
+    <row r="167" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -7092,8 +10049,30 @@
       <c r="T167" s="3"/>
       <c r="U167" s="3"/>
       <c r="V167" s="3"/>
-    </row>
-    <row r="168" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W167" s="3"/>
+      <c r="X167" s="3"/>
+      <c r="Y167" s="3"/>
+      <c r="Z167" s="3"/>
+      <c r="AA167" s="3"/>
+      <c r="AB167" s="3"/>
+      <c r="AC167" s="3"/>
+      <c r="AD167" s="3"/>
+      <c r="AE167" s="3"/>
+      <c r="AF167" s="3"/>
+      <c r="AG167" s="3"/>
+      <c r="AH167" s="3"/>
+      <c r="AI167" s="3"/>
+      <c r="AJ167" s="3"/>
+      <c r="AK167" s="3"/>
+      <c r="AL167" s="3"/>
+      <c r="AM167" s="3"/>
+      <c r="AN167" s="3"/>
+      <c r="AO167" s="3"/>
+      <c r="AP167" s="3"/>
+      <c r="AQ167" s="3"/>
+      <c r="AR167" s="3"/>
+    </row>
+    <row r="168" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -7114,8 +10093,30 @@
       <c r="T168" s="3"/>
       <c r="U168" s="3"/>
       <c r="V168" s="3"/>
-    </row>
-    <row r="169" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W168" s="3"/>
+      <c r="X168" s="3"/>
+      <c r="Y168" s="3"/>
+      <c r="Z168" s="3"/>
+      <c r="AA168" s="3"/>
+      <c r="AB168" s="3"/>
+      <c r="AC168" s="3"/>
+      <c r="AD168" s="3"/>
+      <c r="AE168" s="3"/>
+      <c r="AF168" s="3"/>
+      <c r="AG168" s="3"/>
+      <c r="AH168" s="3"/>
+      <c r="AI168" s="3"/>
+      <c r="AJ168" s="3"/>
+      <c r="AK168" s="3"/>
+      <c r="AL168" s="3"/>
+      <c r="AM168" s="3"/>
+      <c r="AN168" s="3"/>
+      <c r="AO168" s="3"/>
+      <c r="AP168" s="3"/>
+      <c r="AQ168" s="3"/>
+      <c r="AR168" s="3"/>
+    </row>
+    <row r="169" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -7136,8 +10137,30 @@
       <c r="T169" s="3"/>
       <c r="U169" s="3"/>
       <c r="V169" s="3"/>
-    </row>
-    <row r="170" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W169" s="3"/>
+      <c r="X169" s="3"/>
+      <c r="Y169" s="3"/>
+      <c r="Z169" s="3"/>
+      <c r="AA169" s="3"/>
+      <c r="AB169" s="3"/>
+      <c r="AC169" s="3"/>
+      <c r="AD169" s="3"/>
+      <c r="AE169" s="3"/>
+      <c r="AF169" s="3"/>
+      <c r="AG169" s="3"/>
+      <c r="AH169" s="3"/>
+      <c r="AI169" s="3"/>
+      <c r="AJ169" s="3"/>
+      <c r="AK169" s="3"/>
+      <c r="AL169" s="3"/>
+      <c r="AM169" s="3"/>
+      <c r="AN169" s="3"/>
+      <c r="AO169" s="3"/>
+      <c r="AP169" s="3"/>
+      <c r="AQ169" s="3"/>
+      <c r="AR169" s="3"/>
+    </row>
+    <row r="170" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -7158,8 +10181,30 @@
       <c r="T170" s="3"/>
       <c r="U170" s="3"/>
       <c r="V170" s="3"/>
-    </row>
-    <row r="171" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W170" s="3"/>
+      <c r="X170" s="3"/>
+      <c r="Y170" s="3"/>
+      <c r="Z170" s="3"/>
+      <c r="AA170" s="3"/>
+      <c r="AB170" s="3"/>
+      <c r="AC170" s="3"/>
+      <c r="AD170" s="3"/>
+      <c r="AE170" s="3"/>
+      <c r="AF170" s="3"/>
+      <c r="AG170" s="3"/>
+      <c r="AH170" s="3"/>
+      <c r="AI170" s="3"/>
+      <c r="AJ170" s="3"/>
+      <c r="AK170" s="3"/>
+      <c r="AL170" s="3"/>
+      <c r="AM170" s="3"/>
+      <c r="AN170" s="3"/>
+      <c r="AO170" s="3"/>
+      <c r="AP170" s="3"/>
+      <c r="AQ170" s="3"/>
+      <c r="AR170" s="3"/>
+    </row>
+    <row r="171" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -7180,8 +10225,30 @@
       <c r="T171" s="3"/>
       <c r="U171" s="3"/>
       <c r="V171" s="3"/>
-    </row>
-    <row r="172" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W171" s="3"/>
+      <c r="X171" s="3"/>
+      <c r="Y171" s="3"/>
+      <c r="Z171" s="3"/>
+      <c r="AA171" s="3"/>
+      <c r="AB171" s="3"/>
+      <c r="AC171" s="3"/>
+      <c r="AD171" s="3"/>
+      <c r="AE171" s="3"/>
+      <c r="AF171" s="3"/>
+      <c r="AG171" s="3"/>
+      <c r="AH171" s="3"/>
+      <c r="AI171" s="3"/>
+      <c r="AJ171" s="3"/>
+      <c r="AK171" s="3"/>
+      <c r="AL171" s="3"/>
+      <c r="AM171" s="3"/>
+      <c r="AN171" s="3"/>
+      <c r="AO171" s="3"/>
+      <c r="AP171" s="3"/>
+      <c r="AQ171" s="3"/>
+      <c r="AR171" s="3"/>
+    </row>
+    <row r="172" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -7202,8 +10269,30 @@
       <c r="T172" s="3"/>
       <c r="U172" s="3"/>
       <c r="V172" s="3"/>
-    </row>
-    <row r="173" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W172" s="3"/>
+      <c r="X172" s="3"/>
+      <c r="Y172" s="3"/>
+      <c r="Z172" s="3"/>
+      <c r="AA172" s="3"/>
+      <c r="AB172" s="3"/>
+      <c r="AC172" s="3"/>
+      <c r="AD172" s="3"/>
+      <c r="AE172" s="3"/>
+      <c r="AF172" s="3"/>
+      <c r="AG172" s="3"/>
+      <c r="AH172" s="3"/>
+      <c r="AI172" s="3"/>
+      <c r="AJ172" s="3"/>
+      <c r="AK172" s="3"/>
+      <c r="AL172" s="3"/>
+      <c r="AM172" s="3"/>
+      <c r="AN172" s="3"/>
+      <c r="AO172" s="3"/>
+      <c r="AP172" s="3"/>
+      <c r="AQ172" s="3"/>
+      <c r="AR172" s="3"/>
+    </row>
+    <row r="173" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -7224,8 +10313,30 @@
       <c r="T173" s="3"/>
       <c r="U173" s="3"/>
       <c r="V173" s="3"/>
-    </row>
-    <row r="174" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W173" s="3"/>
+      <c r="X173" s="3"/>
+      <c r="Y173" s="3"/>
+      <c r="Z173" s="3"/>
+      <c r="AA173" s="3"/>
+      <c r="AB173" s="3"/>
+      <c r="AC173" s="3"/>
+      <c r="AD173" s="3"/>
+      <c r="AE173" s="3"/>
+      <c r="AF173" s="3"/>
+      <c r="AG173" s="3"/>
+      <c r="AH173" s="3"/>
+      <c r="AI173" s="3"/>
+      <c r="AJ173" s="3"/>
+      <c r="AK173" s="3"/>
+      <c r="AL173" s="3"/>
+      <c r="AM173" s="3"/>
+      <c r="AN173" s="3"/>
+      <c r="AO173" s="3"/>
+      <c r="AP173" s="3"/>
+      <c r="AQ173" s="3"/>
+      <c r="AR173" s="3"/>
+    </row>
+    <row r="174" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -7246,8 +10357,30 @@
       <c r="T174" s="3"/>
       <c r="U174" s="3"/>
       <c r="V174" s="3"/>
-    </row>
-    <row r="175" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W174" s="3"/>
+      <c r="X174" s="3"/>
+      <c r="Y174" s="3"/>
+      <c r="Z174" s="3"/>
+      <c r="AA174" s="3"/>
+      <c r="AB174" s="3"/>
+      <c r="AC174" s="3"/>
+      <c r="AD174" s="3"/>
+      <c r="AE174" s="3"/>
+      <c r="AF174" s="3"/>
+      <c r="AG174" s="3"/>
+      <c r="AH174" s="3"/>
+      <c r="AI174" s="3"/>
+      <c r="AJ174" s="3"/>
+      <c r="AK174" s="3"/>
+      <c r="AL174" s="3"/>
+      <c r="AM174" s="3"/>
+      <c r="AN174" s="3"/>
+      <c r="AO174" s="3"/>
+      <c r="AP174" s="3"/>
+      <c r="AQ174" s="3"/>
+      <c r="AR174" s="3"/>
+    </row>
+    <row r="175" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -7268,8 +10401,30 @@
       <c r="T175" s="3"/>
       <c r="U175" s="3"/>
       <c r="V175" s="3"/>
-    </row>
-    <row r="176" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W175" s="3"/>
+      <c r="X175" s="3"/>
+      <c r="Y175" s="3"/>
+      <c r="Z175" s="3"/>
+      <c r="AA175" s="3"/>
+      <c r="AB175" s="3"/>
+      <c r="AC175" s="3"/>
+      <c r="AD175" s="3"/>
+      <c r="AE175" s="3"/>
+      <c r="AF175" s="3"/>
+      <c r="AG175" s="3"/>
+      <c r="AH175" s="3"/>
+      <c r="AI175" s="3"/>
+      <c r="AJ175" s="3"/>
+      <c r="AK175" s="3"/>
+      <c r="AL175" s="3"/>
+      <c r="AM175" s="3"/>
+      <c r="AN175" s="3"/>
+      <c r="AO175" s="3"/>
+      <c r="AP175" s="3"/>
+      <c r="AQ175" s="3"/>
+      <c r="AR175" s="3"/>
+    </row>
+    <row r="176" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -7290,8 +10445,30 @@
       <c r="T176" s="3"/>
       <c r="U176" s="3"/>
       <c r="V176" s="3"/>
-    </row>
-    <row r="177" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W176" s="3"/>
+      <c r="X176" s="3"/>
+      <c r="Y176" s="3"/>
+      <c r="Z176" s="3"/>
+      <c r="AA176" s="3"/>
+      <c r="AB176" s="3"/>
+      <c r="AC176" s="3"/>
+      <c r="AD176" s="3"/>
+      <c r="AE176" s="3"/>
+      <c r="AF176" s="3"/>
+      <c r="AG176" s="3"/>
+      <c r="AH176" s="3"/>
+      <c r="AI176" s="3"/>
+      <c r="AJ176" s="3"/>
+      <c r="AK176" s="3"/>
+      <c r="AL176" s="3"/>
+      <c r="AM176" s="3"/>
+      <c r="AN176" s="3"/>
+      <c r="AO176" s="3"/>
+      <c r="AP176" s="3"/>
+      <c r="AQ176" s="3"/>
+      <c r="AR176" s="3"/>
+    </row>
+    <row r="177" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -7312,8 +10489,30 @@
       <c r="T177" s="3"/>
       <c r="U177" s="3"/>
       <c r="V177" s="3"/>
-    </row>
-    <row r="178" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W177" s="3"/>
+      <c r="X177" s="3"/>
+      <c r="Y177" s="3"/>
+      <c r="Z177" s="3"/>
+      <c r="AA177" s="3"/>
+      <c r="AB177" s="3"/>
+      <c r="AC177" s="3"/>
+      <c r="AD177" s="3"/>
+      <c r="AE177" s="3"/>
+      <c r="AF177" s="3"/>
+      <c r="AG177" s="3"/>
+      <c r="AH177" s="3"/>
+      <c r="AI177" s="3"/>
+      <c r="AJ177" s="3"/>
+      <c r="AK177" s="3"/>
+      <c r="AL177" s="3"/>
+      <c r="AM177" s="3"/>
+      <c r="AN177" s="3"/>
+      <c r="AO177" s="3"/>
+      <c r="AP177" s="3"/>
+      <c r="AQ177" s="3"/>
+      <c r="AR177" s="3"/>
+    </row>
+    <row r="178" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -7334,8 +10533,30 @@
       <c r="T178" s="3"/>
       <c r="U178" s="3"/>
       <c r="V178" s="3"/>
-    </row>
-    <row r="179" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W178" s="3"/>
+      <c r="X178" s="3"/>
+      <c r="Y178" s="3"/>
+      <c r="Z178" s="3"/>
+      <c r="AA178" s="3"/>
+      <c r="AB178" s="3"/>
+      <c r="AC178" s="3"/>
+      <c r="AD178" s="3"/>
+      <c r="AE178" s="3"/>
+      <c r="AF178" s="3"/>
+      <c r="AG178" s="3"/>
+      <c r="AH178" s="3"/>
+      <c r="AI178" s="3"/>
+      <c r="AJ178" s="3"/>
+      <c r="AK178" s="3"/>
+      <c r="AL178" s="3"/>
+      <c r="AM178" s="3"/>
+      <c r="AN178" s="3"/>
+      <c r="AO178" s="3"/>
+      <c r="AP178" s="3"/>
+      <c r="AQ178" s="3"/>
+      <c r="AR178" s="3"/>
+    </row>
+    <row r="179" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -7356,8 +10577,30 @@
       <c r="T179" s="3"/>
       <c r="U179" s="3"/>
       <c r="V179" s="3"/>
-    </row>
-    <row r="180" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W179" s="3"/>
+      <c r="X179" s="3"/>
+      <c r="Y179" s="3"/>
+      <c r="Z179" s="3"/>
+      <c r="AA179" s="3"/>
+      <c r="AB179" s="3"/>
+      <c r="AC179" s="3"/>
+      <c r="AD179" s="3"/>
+      <c r="AE179" s="3"/>
+      <c r="AF179" s="3"/>
+      <c r="AG179" s="3"/>
+      <c r="AH179" s="3"/>
+      <c r="AI179" s="3"/>
+      <c r="AJ179" s="3"/>
+      <c r="AK179" s="3"/>
+      <c r="AL179" s="3"/>
+      <c r="AM179" s="3"/>
+      <c r="AN179" s="3"/>
+      <c r="AO179" s="3"/>
+      <c r="AP179" s="3"/>
+      <c r="AQ179" s="3"/>
+      <c r="AR179" s="3"/>
+    </row>
+    <row r="180" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -7378,8 +10621,30 @@
       <c r="T180" s="3"/>
       <c r="U180" s="3"/>
       <c r="V180" s="3"/>
-    </row>
-    <row r="181" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W180" s="3"/>
+      <c r="X180" s="3"/>
+      <c r="Y180" s="3"/>
+      <c r="Z180" s="3"/>
+      <c r="AA180" s="3"/>
+      <c r="AB180" s="3"/>
+      <c r="AC180" s="3"/>
+      <c r="AD180" s="3"/>
+      <c r="AE180" s="3"/>
+      <c r="AF180" s="3"/>
+      <c r="AG180" s="3"/>
+      <c r="AH180" s="3"/>
+      <c r="AI180" s="3"/>
+      <c r="AJ180" s="3"/>
+      <c r="AK180" s="3"/>
+      <c r="AL180" s="3"/>
+      <c r="AM180" s="3"/>
+      <c r="AN180" s="3"/>
+      <c r="AO180" s="3"/>
+      <c r="AP180" s="3"/>
+      <c r="AQ180" s="3"/>
+      <c r="AR180" s="3"/>
+    </row>
+    <row r="181" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -7400,8 +10665,30 @@
       <c r="T181" s="3"/>
       <c r="U181" s="3"/>
       <c r="V181" s="3"/>
-    </row>
-    <row r="182" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W181" s="3"/>
+      <c r="X181" s="3"/>
+      <c r="Y181" s="3"/>
+      <c r="Z181" s="3"/>
+      <c r="AA181" s="3"/>
+      <c r="AB181" s="3"/>
+      <c r="AC181" s="3"/>
+      <c r="AD181" s="3"/>
+      <c r="AE181" s="3"/>
+      <c r="AF181" s="3"/>
+      <c r="AG181" s="3"/>
+      <c r="AH181" s="3"/>
+      <c r="AI181" s="3"/>
+      <c r="AJ181" s="3"/>
+      <c r="AK181" s="3"/>
+      <c r="AL181" s="3"/>
+      <c r="AM181" s="3"/>
+      <c r="AN181" s="3"/>
+      <c r="AO181" s="3"/>
+      <c r="AP181" s="3"/>
+      <c r="AQ181" s="3"/>
+      <c r="AR181" s="3"/>
+    </row>
+    <row r="182" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -7422,8 +10709,30 @@
       <c r="T182" s="3"/>
       <c r="U182" s="3"/>
       <c r="V182" s="3"/>
-    </row>
-    <row r="183" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W182" s="3"/>
+      <c r="X182" s="3"/>
+      <c r="Y182" s="3"/>
+      <c r="Z182" s="3"/>
+      <c r="AA182" s="3"/>
+      <c r="AB182" s="3"/>
+      <c r="AC182" s="3"/>
+      <c r="AD182" s="3"/>
+      <c r="AE182" s="3"/>
+      <c r="AF182" s="3"/>
+      <c r="AG182" s="3"/>
+      <c r="AH182" s="3"/>
+      <c r="AI182" s="3"/>
+      <c r="AJ182" s="3"/>
+      <c r="AK182" s="3"/>
+      <c r="AL182" s="3"/>
+      <c r="AM182" s="3"/>
+      <c r="AN182" s="3"/>
+      <c r="AO182" s="3"/>
+      <c r="AP182" s="3"/>
+      <c r="AQ182" s="3"/>
+      <c r="AR182" s="3"/>
+    </row>
+    <row r="183" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -7444,8 +10753,30 @@
       <c r="T183" s="3"/>
       <c r="U183" s="3"/>
       <c r="V183" s="3"/>
-    </row>
-    <row r="184" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W183" s="3"/>
+      <c r="X183" s="3"/>
+      <c r="Y183" s="3"/>
+      <c r="Z183" s="3"/>
+      <c r="AA183" s="3"/>
+      <c r="AB183" s="3"/>
+      <c r="AC183" s="3"/>
+      <c r="AD183" s="3"/>
+      <c r="AE183" s="3"/>
+      <c r="AF183" s="3"/>
+      <c r="AG183" s="3"/>
+      <c r="AH183" s="3"/>
+      <c r="AI183" s="3"/>
+      <c r="AJ183" s="3"/>
+      <c r="AK183" s="3"/>
+      <c r="AL183" s="3"/>
+      <c r="AM183" s="3"/>
+      <c r="AN183" s="3"/>
+      <c r="AO183" s="3"/>
+      <c r="AP183" s="3"/>
+      <c r="AQ183" s="3"/>
+      <c r="AR183" s="3"/>
+    </row>
+    <row r="184" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -7466,8 +10797,30 @@
       <c r="T184" s="3"/>
       <c r="U184" s="3"/>
       <c r="V184" s="3"/>
-    </row>
-    <row r="185" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W184" s="3"/>
+      <c r="X184" s="3"/>
+      <c r="Y184" s="3"/>
+      <c r="Z184" s="3"/>
+      <c r="AA184" s="3"/>
+      <c r="AB184" s="3"/>
+      <c r="AC184" s="3"/>
+      <c r="AD184" s="3"/>
+      <c r="AE184" s="3"/>
+      <c r="AF184" s="3"/>
+      <c r="AG184" s="3"/>
+      <c r="AH184" s="3"/>
+      <c r="AI184" s="3"/>
+      <c r="AJ184" s="3"/>
+      <c r="AK184" s="3"/>
+      <c r="AL184" s="3"/>
+      <c r="AM184" s="3"/>
+      <c r="AN184" s="3"/>
+      <c r="AO184" s="3"/>
+      <c r="AP184" s="3"/>
+      <c r="AQ184" s="3"/>
+      <c r="AR184" s="3"/>
+    </row>
+    <row r="185" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -7488,8 +10841,30 @@
       <c r="T185" s="3"/>
       <c r="U185" s="3"/>
       <c r="V185" s="3"/>
-    </row>
-    <row r="186" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W185" s="3"/>
+      <c r="X185" s="3"/>
+      <c r="Y185" s="3"/>
+      <c r="Z185" s="3"/>
+      <c r="AA185" s="3"/>
+      <c r="AB185" s="3"/>
+      <c r="AC185" s="3"/>
+      <c r="AD185" s="3"/>
+      <c r="AE185" s="3"/>
+      <c r="AF185" s="3"/>
+      <c r="AG185" s="3"/>
+      <c r="AH185" s="3"/>
+      <c r="AI185" s="3"/>
+      <c r="AJ185" s="3"/>
+      <c r="AK185" s="3"/>
+      <c r="AL185" s="3"/>
+      <c r="AM185" s="3"/>
+      <c r="AN185" s="3"/>
+      <c r="AO185" s="3"/>
+      <c r="AP185" s="3"/>
+      <c r="AQ185" s="3"/>
+      <c r="AR185" s="3"/>
+    </row>
+    <row r="186" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -7510,8 +10885,30 @@
       <c r="T186" s="3"/>
       <c r="U186" s="3"/>
       <c r="V186" s="3"/>
-    </row>
-    <row r="187" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W186" s="3"/>
+      <c r="X186" s="3"/>
+      <c r="Y186" s="3"/>
+      <c r="Z186" s="3"/>
+      <c r="AA186" s="3"/>
+      <c r="AB186" s="3"/>
+      <c r="AC186" s="3"/>
+      <c r="AD186" s="3"/>
+      <c r="AE186" s="3"/>
+      <c r="AF186" s="3"/>
+      <c r="AG186" s="3"/>
+      <c r="AH186" s="3"/>
+      <c r="AI186" s="3"/>
+      <c r="AJ186" s="3"/>
+      <c r="AK186" s="3"/>
+      <c r="AL186" s="3"/>
+      <c r="AM186" s="3"/>
+      <c r="AN186" s="3"/>
+      <c r="AO186" s="3"/>
+      <c r="AP186" s="3"/>
+      <c r="AQ186" s="3"/>
+      <c r="AR186" s="3"/>
+    </row>
+    <row r="187" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -7532,8 +10929,30 @@
       <c r="T187" s="3"/>
       <c r="U187" s="3"/>
       <c r="V187" s="3"/>
-    </row>
-    <row r="188" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W187" s="3"/>
+      <c r="X187" s="3"/>
+      <c r="Y187" s="3"/>
+      <c r="Z187" s="3"/>
+      <c r="AA187" s="3"/>
+      <c r="AB187" s="3"/>
+      <c r="AC187" s="3"/>
+      <c r="AD187" s="3"/>
+      <c r="AE187" s="3"/>
+      <c r="AF187" s="3"/>
+      <c r="AG187" s="3"/>
+      <c r="AH187" s="3"/>
+      <c r="AI187" s="3"/>
+      <c r="AJ187" s="3"/>
+      <c r="AK187" s="3"/>
+      <c r="AL187" s="3"/>
+      <c r="AM187" s="3"/>
+      <c r="AN187" s="3"/>
+      <c r="AO187" s="3"/>
+      <c r="AP187" s="3"/>
+      <c r="AQ187" s="3"/>
+      <c r="AR187" s="3"/>
+    </row>
+    <row r="188" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -7554,8 +10973,30 @@
       <c r="T188" s="3"/>
       <c r="U188" s="3"/>
       <c r="V188" s="3"/>
-    </row>
-    <row r="189" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W188" s="3"/>
+      <c r="X188" s="3"/>
+      <c r="Y188" s="3"/>
+      <c r="Z188" s="3"/>
+      <c r="AA188" s="3"/>
+      <c r="AB188" s="3"/>
+      <c r="AC188" s="3"/>
+      <c r="AD188" s="3"/>
+      <c r="AE188" s="3"/>
+      <c r="AF188" s="3"/>
+      <c r="AG188" s="3"/>
+      <c r="AH188" s="3"/>
+      <c r="AI188" s="3"/>
+      <c r="AJ188" s="3"/>
+      <c r="AK188" s="3"/>
+      <c r="AL188" s="3"/>
+      <c r="AM188" s="3"/>
+      <c r="AN188" s="3"/>
+      <c r="AO188" s="3"/>
+      <c r="AP188" s="3"/>
+      <c r="AQ188" s="3"/>
+      <c r="AR188" s="3"/>
+    </row>
+    <row r="189" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -7576,8 +11017,30 @@
       <c r="T189" s="3"/>
       <c r="U189" s="3"/>
       <c r="V189" s="3"/>
-    </row>
-    <row r="190" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W189" s="3"/>
+      <c r="X189" s="3"/>
+      <c r="Y189" s="3"/>
+      <c r="Z189" s="3"/>
+      <c r="AA189" s="3"/>
+      <c r="AB189" s="3"/>
+      <c r="AC189" s="3"/>
+      <c r="AD189" s="3"/>
+      <c r="AE189" s="3"/>
+      <c r="AF189" s="3"/>
+      <c r="AG189" s="3"/>
+      <c r="AH189" s="3"/>
+      <c r="AI189" s="3"/>
+      <c r="AJ189" s="3"/>
+      <c r="AK189" s="3"/>
+      <c r="AL189" s="3"/>
+      <c r="AM189" s="3"/>
+      <c r="AN189" s="3"/>
+      <c r="AO189" s="3"/>
+      <c r="AP189" s="3"/>
+      <c r="AQ189" s="3"/>
+      <c r="AR189" s="3"/>
+    </row>
+    <row r="190" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -7598,8 +11061,30 @@
       <c r="T190" s="3"/>
       <c r="U190" s="3"/>
       <c r="V190" s="3"/>
-    </row>
-    <row r="191" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W190" s="3"/>
+      <c r="X190" s="3"/>
+      <c r="Y190" s="3"/>
+      <c r="Z190" s="3"/>
+      <c r="AA190" s="3"/>
+      <c r="AB190" s="3"/>
+      <c r="AC190" s="3"/>
+      <c r="AD190" s="3"/>
+      <c r="AE190" s="3"/>
+      <c r="AF190" s="3"/>
+      <c r="AG190" s="3"/>
+      <c r="AH190" s="3"/>
+      <c r="AI190" s="3"/>
+      <c r="AJ190" s="3"/>
+      <c r="AK190" s="3"/>
+      <c r="AL190" s="3"/>
+      <c r="AM190" s="3"/>
+      <c r="AN190" s="3"/>
+      <c r="AO190" s="3"/>
+      <c r="AP190" s="3"/>
+      <c r="AQ190" s="3"/>
+      <c r="AR190" s="3"/>
+    </row>
+    <row r="191" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -7620,8 +11105,30 @@
       <c r="T191" s="3"/>
       <c r="U191" s="3"/>
       <c r="V191" s="3"/>
-    </row>
-    <row r="192" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W191" s="3"/>
+      <c r="X191" s="3"/>
+      <c r="Y191" s="3"/>
+      <c r="Z191" s="3"/>
+      <c r="AA191" s="3"/>
+      <c r="AB191" s="3"/>
+      <c r="AC191" s="3"/>
+      <c r="AD191" s="3"/>
+      <c r="AE191" s="3"/>
+      <c r="AF191" s="3"/>
+      <c r="AG191" s="3"/>
+      <c r="AH191" s="3"/>
+      <c r="AI191" s="3"/>
+      <c r="AJ191" s="3"/>
+      <c r="AK191" s="3"/>
+      <c r="AL191" s="3"/>
+      <c r="AM191" s="3"/>
+      <c r="AN191" s="3"/>
+      <c r="AO191" s="3"/>
+      <c r="AP191" s="3"/>
+      <c r="AQ191" s="3"/>
+      <c r="AR191" s="3"/>
+    </row>
+    <row r="192" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -7642,8 +11149,30 @@
       <c r="T192" s="3"/>
       <c r="U192" s="3"/>
       <c r="V192" s="3"/>
-    </row>
-    <row r="193" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W192" s="3"/>
+      <c r="X192" s="3"/>
+      <c r="Y192" s="3"/>
+      <c r="Z192" s="3"/>
+      <c r="AA192" s="3"/>
+      <c r="AB192" s="3"/>
+      <c r="AC192" s="3"/>
+      <c r="AD192" s="3"/>
+      <c r="AE192" s="3"/>
+      <c r="AF192" s="3"/>
+      <c r="AG192" s="3"/>
+      <c r="AH192" s="3"/>
+      <c r="AI192" s="3"/>
+      <c r="AJ192" s="3"/>
+      <c r="AK192" s="3"/>
+      <c r="AL192" s="3"/>
+      <c r="AM192" s="3"/>
+      <c r="AN192" s="3"/>
+      <c r="AO192" s="3"/>
+      <c r="AP192" s="3"/>
+      <c r="AQ192" s="3"/>
+      <c r="AR192" s="3"/>
+    </row>
+    <row r="193" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -7664,8 +11193,30 @@
       <c r="T193" s="3"/>
       <c r="U193" s="3"/>
       <c r="V193" s="3"/>
-    </row>
-    <row r="194" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W193" s="3"/>
+      <c r="X193" s="3"/>
+      <c r="Y193" s="3"/>
+      <c r="Z193" s="3"/>
+      <c r="AA193" s="3"/>
+      <c r="AB193" s="3"/>
+      <c r="AC193" s="3"/>
+      <c r="AD193" s="3"/>
+      <c r="AE193" s="3"/>
+      <c r="AF193" s="3"/>
+      <c r="AG193" s="3"/>
+      <c r="AH193" s="3"/>
+      <c r="AI193" s="3"/>
+      <c r="AJ193" s="3"/>
+      <c r="AK193" s="3"/>
+      <c r="AL193" s="3"/>
+      <c r="AM193" s="3"/>
+      <c r="AN193" s="3"/>
+      <c r="AO193" s="3"/>
+      <c r="AP193" s="3"/>
+      <c r="AQ193" s="3"/>
+      <c r="AR193" s="3"/>
+    </row>
+    <row r="194" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -7686,8 +11237,30 @@
       <c r="T194" s="3"/>
       <c r="U194" s="3"/>
       <c r="V194" s="3"/>
-    </row>
-    <row r="195" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W194" s="3"/>
+      <c r="X194" s="3"/>
+      <c r="Y194" s="3"/>
+      <c r="Z194" s="3"/>
+      <c r="AA194" s="3"/>
+      <c r="AB194" s="3"/>
+      <c r="AC194" s="3"/>
+      <c r="AD194" s="3"/>
+      <c r="AE194" s="3"/>
+      <c r="AF194" s="3"/>
+      <c r="AG194" s="3"/>
+      <c r="AH194" s="3"/>
+      <c r="AI194" s="3"/>
+      <c r="AJ194" s="3"/>
+      <c r="AK194" s="3"/>
+      <c r="AL194" s="3"/>
+      <c r="AM194" s="3"/>
+      <c r="AN194" s="3"/>
+      <c r="AO194" s="3"/>
+      <c r="AP194" s="3"/>
+      <c r="AQ194" s="3"/>
+      <c r="AR194" s="3"/>
+    </row>
+    <row r="195" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -7708,8 +11281,30 @@
       <c r="T195" s="3"/>
       <c r="U195" s="3"/>
       <c r="V195" s="3"/>
-    </row>
-    <row r="196" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W195" s="3"/>
+      <c r="X195" s="3"/>
+      <c r="Y195" s="3"/>
+      <c r="Z195" s="3"/>
+      <c r="AA195" s="3"/>
+      <c r="AB195" s="3"/>
+      <c r="AC195" s="3"/>
+      <c r="AD195" s="3"/>
+      <c r="AE195" s="3"/>
+      <c r="AF195" s="3"/>
+      <c r="AG195" s="3"/>
+      <c r="AH195" s="3"/>
+      <c r="AI195" s="3"/>
+      <c r="AJ195" s="3"/>
+      <c r="AK195" s="3"/>
+      <c r="AL195" s="3"/>
+      <c r="AM195" s="3"/>
+      <c r="AN195" s="3"/>
+      <c r="AO195" s="3"/>
+      <c r="AP195" s="3"/>
+      <c r="AQ195" s="3"/>
+      <c r="AR195" s="3"/>
+    </row>
+    <row r="196" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -7730,8 +11325,30 @@
       <c r="T196" s="3"/>
       <c r="U196" s="3"/>
       <c r="V196" s="3"/>
-    </row>
-    <row r="197" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W196" s="3"/>
+      <c r="X196" s="3"/>
+      <c r="Y196" s="3"/>
+      <c r="Z196" s="3"/>
+      <c r="AA196" s="3"/>
+      <c r="AB196" s="3"/>
+      <c r="AC196" s="3"/>
+      <c r="AD196" s="3"/>
+      <c r="AE196" s="3"/>
+      <c r="AF196" s="3"/>
+      <c r="AG196" s="3"/>
+      <c r="AH196" s="3"/>
+      <c r="AI196" s="3"/>
+      <c r="AJ196" s="3"/>
+      <c r="AK196" s="3"/>
+      <c r="AL196" s="3"/>
+      <c r="AM196" s="3"/>
+      <c r="AN196" s="3"/>
+      <c r="AO196" s="3"/>
+      <c r="AP196" s="3"/>
+      <c r="AQ196" s="3"/>
+      <c r="AR196" s="3"/>
+    </row>
+    <row r="197" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -7752,8 +11369,30 @@
       <c r="T197" s="3"/>
       <c r="U197" s="3"/>
       <c r="V197" s="3"/>
-    </row>
-    <row r="198" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W197" s="3"/>
+      <c r="X197" s="3"/>
+      <c r="Y197" s="3"/>
+      <c r="Z197" s="3"/>
+      <c r="AA197" s="3"/>
+      <c r="AB197" s="3"/>
+      <c r="AC197" s="3"/>
+      <c r="AD197" s="3"/>
+      <c r="AE197" s="3"/>
+      <c r="AF197" s="3"/>
+      <c r="AG197" s="3"/>
+      <c r="AH197" s="3"/>
+      <c r="AI197" s="3"/>
+      <c r="AJ197" s="3"/>
+      <c r="AK197" s="3"/>
+      <c r="AL197" s="3"/>
+      <c r="AM197" s="3"/>
+      <c r="AN197" s="3"/>
+      <c r="AO197" s="3"/>
+      <c r="AP197" s="3"/>
+      <c r="AQ197" s="3"/>
+      <c r="AR197" s="3"/>
+    </row>
+    <row r="198" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -7774,8 +11413,30 @@
       <c r="T198" s="3"/>
       <c r="U198" s="3"/>
       <c r="V198" s="3"/>
-    </row>
-    <row r="199" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W198" s="3"/>
+      <c r="X198" s="3"/>
+      <c r="Y198" s="3"/>
+      <c r="Z198" s="3"/>
+      <c r="AA198" s="3"/>
+      <c r="AB198" s="3"/>
+      <c r="AC198" s="3"/>
+      <c r="AD198" s="3"/>
+      <c r="AE198" s="3"/>
+      <c r="AF198" s="3"/>
+      <c r="AG198" s="3"/>
+      <c r="AH198" s="3"/>
+      <c r="AI198" s="3"/>
+      <c r="AJ198" s="3"/>
+      <c r="AK198" s="3"/>
+      <c r="AL198" s="3"/>
+      <c r="AM198" s="3"/>
+      <c r="AN198" s="3"/>
+      <c r="AO198" s="3"/>
+      <c r="AP198" s="3"/>
+      <c r="AQ198" s="3"/>
+      <c r="AR198" s="3"/>
+    </row>
+    <row r="199" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -7796,8 +11457,30 @@
       <c r="T199" s="3"/>
       <c r="U199" s="3"/>
       <c r="V199" s="3"/>
-    </row>
-    <row r="200" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W199" s="3"/>
+      <c r="X199" s="3"/>
+      <c r="Y199" s="3"/>
+      <c r="Z199" s="3"/>
+      <c r="AA199" s="3"/>
+      <c r="AB199" s="3"/>
+      <c r="AC199" s="3"/>
+      <c r="AD199" s="3"/>
+      <c r="AE199" s="3"/>
+      <c r="AF199" s="3"/>
+      <c r="AG199" s="3"/>
+      <c r="AH199" s="3"/>
+      <c r="AI199" s="3"/>
+      <c r="AJ199" s="3"/>
+      <c r="AK199" s="3"/>
+      <c r="AL199" s="3"/>
+      <c r="AM199" s="3"/>
+      <c r="AN199" s="3"/>
+      <c r="AO199" s="3"/>
+      <c r="AP199" s="3"/>
+      <c r="AQ199" s="3"/>
+      <c r="AR199" s="3"/>
+    </row>
+    <row r="200" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -7818,8 +11501,30 @@
       <c r="T200" s="3"/>
       <c r="U200" s="3"/>
       <c r="V200" s="3"/>
-    </row>
-    <row r="201" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W200" s="3"/>
+      <c r="X200" s="3"/>
+      <c r="Y200" s="3"/>
+      <c r="Z200" s="3"/>
+      <c r="AA200" s="3"/>
+      <c r="AB200" s="3"/>
+      <c r="AC200" s="3"/>
+      <c r="AD200" s="3"/>
+      <c r="AE200" s="3"/>
+      <c r="AF200" s="3"/>
+      <c r="AG200" s="3"/>
+      <c r="AH200" s="3"/>
+      <c r="AI200" s="3"/>
+      <c r="AJ200" s="3"/>
+      <c r="AK200" s="3"/>
+      <c r="AL200" s="3"/>
+      <c r="AM200" s="3"/>
+      <c r="AN200" s="3"/>
+      <c r="AO200" s="3"/>
+      <c r="AP200" s="3"/>
+      <c r="AQ200" s="3"/>
+      <c r="AR200" s="3"/>
+    </row>
+    <row r="201" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -7840,8 +11545,30 @@
       <c r="T201" s="3"/>
       <c r="U201" s="3"/>
       <c r="V201" s="3"/>
-    </row>
-    <row r="202" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W201" s="3"/>
+      <c r="X201" s="3"/>
+      <c r="Y201" s="3"/>
+      <c r="Z201" s="3"/>
+      <c r="AA201" s="3"/>
+      <c r="AB201" s="3"/>
+      <c r="AC201" s="3"/>
+      <c r="AD201" s="3"/>
+      <c r="AE201" s="3"/>
+      <c r="AF201" s="3"/>
+      <c r="AG201" s="3"/>
+      <c r="AH201" s="3"/>
+      <c r="AI201" s="3"/>
+      <c r="AJ201" s="3"/>
+      <c r="AK201" s="3"/>
+      <c r="AL201" s="3"/>
+      <c r="AM201" s="3"/>
+      <c r="AN201" s="3"/>
+      <c r="AO201" s="3"/>
+      <c r="AP201" s="3"/>
+      <c r="AQ201" s="3"/>
+      <c r="AR201" s="3"/>
+    </row>
+    <row r="202" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -7862,8 +11589,30 @@
       <c r="T202" s="3"/>
       <c r="U202" s="3"/>
       <c r="V202" s="3"/>
-    </row>
-    <row r="203" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W202" s="3"/>
+      <c r="X202" s="3"/>
+      <c r="Y202" s="3"/>
+      <c r="Z202" s="3"/>
+      <c r="AA202" s="3"/>
+      <c r="AB202" s="3"/>
+      <c r="AC202" s="3"/>
+      <c r="AD202" s="3"/>
+      <c r="AE202" s="3"/>
+      <c r="AF202" s="3"/>
+      <c r="AG202" s="3"/>
+      <c r="AH202" s="3"/>
+      <c r="AI202" s="3"/>
+      <c r="AJ202" s="3"/>
+      <c r="AK202" s="3"/>
+      <c r="AL202" s="3"/>
+      <c r="AM202" s="3"/>
+      <c r="AN202" s="3"/>
+      <c r="AO202" s="3"/>
+      <c r="AP202" s="3"/>
+      <c r="AQ202" s="3"/>
+      <c r="AR202" s="3"/>
+    </row>
+    <row r="203" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -7884,8 +11633,30 @@
       <c r="T203" s="3"/>
       <c r="U203" s="3"/>
       <c r="V203" s="3"/>
-    </row>
-    <row r="204" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W203" s="3"/>
+      <c r="X203" s="3"/>
+      <c r="Y203" s="3"/>
+      <c r="Z203" s="3"/>
+      <c r="AA203" s="3"/>
+      <c r="AB203" s="3"/>
+      <c r="AC203" s="3"/>
+      <c r="AD203" s="3"/>
+      <c r="AE203" s="3"/>
+      <c r="AF203" s="3"/>
+      <c r="AG203" s="3"/>
+      <c r="AH203" s="3"/>
+      <c r="AI203" s="3"/>
+      <c r="AJ203" s="3"/>
+      <c r="AK203" s="3"/>
+      <c r="AL203" s="3"/>
+      <c r="AM203" s="3"/>
+      <c r="AN203" s="3"/>
+      <c r="AO203" s="3"/>
+      <c r="AP203" s="3"/>
+      <c r="AQ203" s="3"/>
+      <c r="AR203" s="3"/>
+    </row>
+    <row r="204" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -7906,8 +11677,30 @@
       <c r="T204" s="3"/>
       <c r="U204" s="3"/>
       <c r="V204" s="3"/>
-    </row>
-    <row r="205" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W204" s="3"/>
+      <c r="X204" s="3"/>
+      <c r="Y204" s="3"/>
+      <c r="Z204" s="3"/>
+      <c r="AA204" s="3"/>
+      <c r="AB204" s="3"/>
+      <c r="AC204" s="3"/>
+      <c r="AD204" s="3"/>
+      <c r="AE204" s="3"/>
+      <c r="AF204" s="3"/>
+      <c r="AG204" s="3"/>
+      <c r="AH204" s="3"/>
+      <c r="AI204" s="3"/>
+      <c r="AJ204" s="3"/>
+      <c r="AK204" s="3"/>
+      <c r="AL204" s="3"/>
+      <c r="AM204" s="3"/>
+      <c r="AN204" s="3"/>
+      <c r="AO204" s="3"/>
+      <c r="AP204" s="3"/>
+      <c r="AQ204" s="3"/>
+      <c r="AR204" s="3"/>
+    </row>
+    <row r="205" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -7928,8 +11721,30 @@
       <c r="T205" s="3"/>
       <c r="U205" s="3"/>
       <c r="V205" s="3"/>
-    </row>
-    <row r="206" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W205" s="3"/>
+      <c r="X205" s="3"/>
+      <c r="Y205" s="3"/>
+      <c r="Z205" s="3"/>
+      <c r="AA205" s="3"/>
+      <c r="AB205" s="3"/>
+      <c r="AC205" s="3"/>
+      <c r="AD205" s="3"/>
+      <c r="AE205" s="3"/>
+      <c r="AF205" s="3"/>
+      <c r="AG205" s="3"/>
+      <c r="AH205" s="3"/>
+      <c r="AI205" s="3"/>
+      <c r="AJ205" s="3"/>
+      <c r="AK205" s="3"/>
+      <c r="AL205" s="3"/>
+      <c r="AM205" s="3"/>
+      <c r="AN205" s="3"/>
+      <c r="AO205" s="3"/>
+      <c r="AP205" s="3"/>
+      <c r="AQ205" s="3"/>
+      <c r="AR205" s="3"/>
+    </row>
+    <row r="206" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -7950,8 +11765,30 @@
       <c r="T206" s="3"/>
       <c r="U206" s="3"/>
       <c r="V206" s="3"/>
-    </row>
-    <row r="207" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W206" s="3"/>
+      <c r="X206" s="3"/>
+      <c r="Y206" s="3"/>
+      <c r="Z206" s="3"/>
+      <c r="AA206" s="3"/>
+      <c r="AB206" s="3"/>
+      <c r="AC206" s="3"/>
+      <c r="AD206" s="3"/>
+      <c r="AE206" s="3"/>
+      <c r="AF206" s="3"/>
+      <c r="AG206" s="3"/>
+      <c r="AH206" s="3"/>
+      <c r="AI206" s="3"/>
+      <c r="AJ206" s="3"/>
+      <c r="AK206" s="3"/>
+      <c r="AL206" s="3"/>
+      <c r="AM206" s="3"/>
+      <c r="AN206" s="3"/>
+      <c r="AO206" s="3"/>
+      <c r="AP206" s="3"/>
+      <c r="AQ206" s="3"/>
+      <c r="AR206" s="3"/>
+    </row>
+    <row r="207" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -7972,8 +11809,30 @@
       <c r="T207" s="3"/>
       <c r="U207" s="3"/>
       <c r="V207" s="3"/>
-    </row>
-    <row r="208" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W207" s="3"/>
+      <c r="X207" s="3"/>
+      <c r="Y207" s="3"/>
+      <c r="Z207" s="3"/>
+      <c r="AA207" s="3"/>
+      <c r="AB207" s="3"/>
+      <c r="AC207" s="3"/>
+      <c r="AD207" s="3"/>
+      <c r="AE207" s="3"/>
+      <c r="AF207" s="3"/>
+      <c r="AG207" s="3"/>
+      <c r="AH207" s="3"/>
+      <c r="AI207" s="3"/>
+      <c r="AJ207" s="3"/>
+      <c r="AK207" s="3"/>
+      <c r="AL207" s="3"/>
+      <c r="AM207" s="3"/>
+      <c r="AN207" s="3"/>
+      <c r="AO207" s="3"/>
+      <c r="AP207" s="3"/>
+      <c r="AQ207" s="3"/>
+      <c r="AR207" s="3"/>
+    </row>
+    <row r="208" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -7994,8 +11853,30 @@
       <c r="T208" s="3"/>
       <c r="U208" s="3"/>
       <c r="V208" s="3"/>
-    </row>
-    <row r="209" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W208" s="3"/>
+      <c r="X208" s="3"/>
+      <c r="Y208" s="3"/>
+      <c r="Z208" s="3"/>
+      <c r="AA208" s="3"/>
+      <c r="AB208" s="3"/>
+      <c r="AC208" s="3"/>
+      <c r="AD208" s="3"/>
+      <c r="AE208" s="3"/>
+      <c r="AF208" s="3"/>
+      <c r="AG208" s="3"/>
+      <c r="AH208" s="3"/>
+      <c r="AI208" s="3"/>
+      <c r="AJ208" s="3"/>
+      <c r="AK208" s="3"/>
+      <c r="AL208" s="3"/>
+      <c r="AM208" s="3"/>
+      <c r="AN208" s="3"/>
+      <c r="AO208" s="3"/>
+      <c r="AP208" s="3"/>
+      <c r="AQ208" s="3"/>
+      <c r="AR208" s="3"/>
+    </row>
+    <row r="209" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -8016,8 +11897,30 @@
       <c r="T209" s="3"/>
       <c r="U209" s="3"/>
       <c r="V209" s="3"/>
-    </row>
-    <row r="210" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W209" s="3"/>
+      <c r="X209" s="3"/>
+      <c r="Y209" s="3"/>
+      <c r="Z209" s="3"/>
+      <c r="AA209" s="3"/>
+      <c r="AB209" s="3"/>
+      <c r="AC209" s="3"/>
+      <c r="AD209" s="3"/>
+      <c r="AE209" s="3"/>
+      <c r="AF209" s="3"/>
+      <c r="AG209" s="3"/>
+      <c r="AH209" s="3"/>
+      <c r="AI209" s="3"/>
+      <c r="AJ209" s="3"/>
+      <c r="AK209" s="3"/>
+      <c r="AL209" s="3"/>
+      <c r="AM209" s="3"/>
+      <c r="AN209" s="3"/>
+      <c r="AO209" s="3"/>
+      <c r="AP209" s="3"/>
+      <c r="AQ209" s="3"/>
+      <c r="AR209" s="3"/>
+    </row>
+    <row r="210" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -8038,8 +11941,30 @@
       <c r="T210" s="3"/>
       <c r="U210" s="3"/>
       <c r="V210" s="3"/>
-    </row>
-    <row r="211" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W210" s="3"/>
+      <c r="X210" s="3"/>
+      <c r="Y210" s="3"/>
+      <c r="Z210" s="3"/>
+      <c r="AA210" s="3"/>
+      <c r="AB210" s="3"/>
+      <c r="AC210" s="3"/>
+      <c r="AD210" s="3"/>
+      <c r="AE210" s="3"/>
+      <c r="AF210" s="3"/>
+      <c r="AG210" s="3"/>
+      <c r="AH210" s="3"/>
+      <c r="AI210" s="3"/>
+      <c r="AJ210" s="3"/>
+      <c r="AK210" s="3"/>
+      <c r="AL210" s="3"/>
+      <c r="AM210" s="3"/>
+      <c r="AN210" s="3"/>
+      <c r="AO210" s="3"/>
+      <c r="AP210" s="3"/>
+      <c r="AQ210" s="3"/>
+      <c r="AR210" s="3"/>
+    </row>
+    <row r="211" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -8060,8 +11985,30 @@
       <c r="T211" s="3"/>
       <c r="U211" s="3"/>
       <c r="V211" s="3"/>
-    </row>
-    <row r="212" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W211" s="3"/>
+      <c r="X211" s="3"/>
+      <c r="Y211" s="3"/>
+      <c r="Z211" s="3"/>
+      <c r="AA211" s="3"/>
+      <c r="AB211" s="3"/>
+      <c r="AC211" s="3"/>
+      <c r="AD211" s="3"/>
+      <c r="AE211" s="3"/>
+      <c r="AF211" s="3"/>
+      <c r="AG211" s="3"/>
+      <c r="AH211" s="3"/>
+      <c r="AI211" s="3"/>
+      <c r="AJ211" s="3"/>
+      <c r="AK211" s="3"/>
+      <c r="AL211" s="3"/>
+      <c r="AM211" s="3"/>
+      <c r="AN211" s="3"/>
+      <c r="AO211" s="3"/>
+      <c r="AP211" s="3"/>
+      <c r="AQ211" s="3"/>
+      <c r="AR211" s="3"/>
+    </row>
+    <row r="212" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -8082,8 +12029,30 @@
       <c r="T212" s="3"/>
       <c r="U212" s="3"/>
       <c r="V212" s="3"/>
-    </row>
-    <row r="213" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W212" s="3"/>
+      <c r="X212" s="3"/>
+      <c r="Y212" s="3"/>
+      <c r="Z212" s="3"/>
+      <c r="AA212" s="3"/>
+      <c r="AB212" s="3"/>
+      <c r="AC212" s="3"/>
+      <c r="AD212" s="3"/>
+      <c r="AE212" s="3"/>
+      <c r="AF212" s="3"/>
+      <c r="AG212" s="3"/>
+      <c r="AH212" s="3"/>
+      <c r="AI212" s="3"/>
+      <c r="AJ212" s="3"/>
+      <c r="AK212" s="3"/>
+      <c r="AL212" s="3"/>
+      <c r="AM212" s="3"/>
+      <c r="AN212" s="3"/>
+      <c r="AO212" s="3"/>
+      <c r="AP212" s="3"/>
+      <c r="AQ212" s="3"/>
+      <c r="AR212" s="3"/>
+    </row>
+    <row r="213" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -8104,8 +12073,30 @@
       <c r="T213" s="3"/>
       <c r="U213" s="3"/>
       <c r="V213" s="3"/>
-    </row>
-    <row r="214" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W213" s="3"/>
+      <c r="X213" s="3"/>
+      <c r="Y213" s="3"/>
+      <c r="Z213" s="3"/>
+      <c r="AA213" s="3"/>
+      <c r="AB213" s="3"/>
+      <c r="AC213" s="3"/>
+      <c r="AD213" s="3"/>
+      <c r="AE213" s="3"/>
+      <c r="AF213" s="3"/>
+      <c r="AG213" s="3"/>
+      <c r="AH213" s="3"/>
+      <c r="AI213" s="3"/>
+      <c r="AJ213" s="3"/>
+      <c r="AK213" s="3"/>
+      <c r="AL213" s="3"/>
+      <c r="AM213" s="3"/>
+      <c r="AN213" s="3"/>
+      <c r="AO213" s="3"/>
+      <c r="AP213" s="3"/>
+      <c r="AQ213" s="3"/>
+      <c r="AR213" s="3"/>
+    </row>
+    <row r="214" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -8126,8 +12117,30 @@
       <c r="T214" s="3"/>
       <c r="U214" s="3"/>
       <c r="V214" s="3"/>
-    </row>
-    <row r="215" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W214" s="3"/>
+      <c r="X214" s="3"/>
+      <c r="Y214" s="3"/>
+      <c r="Z214" s="3"/>
+      <c r="AA214" s="3"/>
+      <c r="AB214" s="3"/>
+      <c r="AC214" s="3"/>
+      <c r="AD214" s="3"/>
+      <c r="AE214" s="3"/>
+      <c r="AF214" s="3"/>
+      <c r="AG214" s="3"/>
+      <c r="AH214" s="3"/>
+      <c r="AI214" s="3"/>
+      <c r="AJ214" s="3"/>
+      <c r="AK214" s="3"/>
+      <c r="AL214" s="3"/>
+      <c r="AM214" s="3"/>
+      <c r="AN214" s="3"/>
+      <c r="AO214" s="3"/>
+      <c r="AP214" s="3"/>
+      <c r="AQ214" s="3"/>
+      <c r="AR214" s="3"/>
+    </row>
+    <row r="215" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -8148,8 +12161,30 @@
       <c r="T215" s="3"/>
       <c r="U215" s="3"/>
       <c r="V215" s="3"/>
-    </row>
-    <row r="216" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W215" s="3"/>
+      <c r="X215" s="3"/>
+      <c r="Y215" s="3"/>
+      <c r="Z215" s="3"/>
+      <c r="AA215" s="3"/>
+      <c r="AB215" s="3"/>
+      <c r="AC215" s="3"/>
+      <c r="AD215" s="3"/>
+      <c r="AE215" s="3"/>
+      <c r="AF215" s="3"/>
+      <c r="AG215" s="3"/>
+      <c r="AH215" s="3"/>
+      <c r="AI215" s="3"/>
+      <c r="AJ215" s="3"/>
+      <c r="AK215" s="3"/>
+      <c r="AL215" s="3"/>
+      <c r="AM215" s="3"/>
+      <c r="AN215" s="3"/>
+      <c r="AO215" s="3"/>
+      <c r="AP215" s="3"/>
+      <c r="AQ215" s="3"/>
+      <c r="AR215" s="3"/>
+    </row>
+    <row r="216" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -8170,8 +12205,30 @@
       <c r="T216" s="3"/>
       <c r="U216" s="3"/>
       <c r="V216" s="3"/>
-    </row>
-    <row r="217" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W216" s="3"/>
+      <c r="X216" s="3"/>
+      <c r="Y216" s="3"/>
+      <c r="Z216" s="3"/>
+      <c r="AA216" s="3"/>
+      <c r="AB216" s="3"/>
+      <c r="AC216" s="3"/>
+      <c r="AD216" s="3"/>
+      <c r="AE216" s="3"/>
+      <c r="AF216" s="3"/>
+      <c r="AG216" s="3"/>
+      <c r="AH216" s="3"/>
+      <c r="AI216" s="3"/>
+      <c r="AJ216" s="3"/>
+      <c r="AK216" s="3"/>
+      <c r="AL216" s="3"/>
+      <c r="AM216" s="3"/>
+      <c r="AN216" s="3"/>
+      <c r="AO216" s="3"/>
+      <c r="AP216" s="3"/>
+      <c r="AQ216" s="3"/>
+      <c r="AR216" s="3"/>
+    </row>
+    <row r="217" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -8192,8 +12249,30 @@
       <c r="T217" s="3"/>
       <c r="U217" s="3"/>
       <c r="V217" s="3"/>
-    </row>
-    <row r="218" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W217" s="3"/>
+      <c r="X217" s="3"/>
+      <c r="Y217" s="3"/>
+      <c r="Z217" s="3"/>
+      <c r="AA217" s="3"/>
+      <c r="AB217" s="3"/>
+      <c r="AC217" s="3"/>
+      <c r="AD217" s="3"/>
+      <c r="AE217" s="3"/>
+      <c r="AF217" s="3"/>
+      <c r="AG217" s="3"/>
+      <c r="AH217" s="3"/>
+      <c r="AI217" s="3"/>
+      <c r="AJ217" s="3"/>
+      <c r="AK217" s="3"/>
+      <c r="AL217" s="3"/>
+      <c r="AM217" s="3"/>
+      <c r="AN217" s="3"/>
+      <c r="AO217" s="3"/>
+      <c r="AP217" s="3"/>
+      <c r="AQ217" s="3"/>
+      <c r="AR217" s="3"/>
+    </row>
+    <row r="218" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -8214,8 +12293,30 @@
       <c r="T218" s="3"/>
       <c r="U218" s="3"/>
       <c r="V218" s="3"/>
-    </row>
-    <row r="219" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W218" s="3"/>
+      <c r="X218" s="3"/>
+      <c r="Y218" s="3"/>
+      <c r="Z218" s="3"/>
+      <c r="AA218" s="3"/>
+      <c r="AB218" s="3"/>
+      <c r="AC218" s="3"/>
+      <c r="AD218" s="3"/>
+      <c r="AE218" s="3"/>
+      <c r="AF218" s="3"/>
+      <c r="AG218" s="3"/>
+      <c r="AH218" s="3"/>
+      <c r="AI218" s="3"/>
+      <c r="AJ218" s="3"/>
+      <c r="AK218" s="3"/>
+      <c r="AL218" s="3"/>
+      <c r="AM218" s="3"/>
+      <c r="AN218" s="3"/>
+      <c r="AO218" s="3"/>
+      <c r="AP218" s="3"/>
+      <c r="AQ218" s="3"/>
+      <c r="AR218" s="3"/>
+    </row>
+    <row r="219" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -8236,8 +12337,30 @@
       <c r="T219" s="3"/>
       <c r="U219" s="3"/>
       <c r="V219" s="3"/>
-    </row>
-    <row r="220" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W219" s="3"/>
+      <c r="X219" s="3"/>
+      <c r="Y219" s="3"/>
+      <c r="Z219" s="3"/>
+      <c r="AA219" s="3"/>
+      <c r="AB219" s="3"/>
+      <c r="AC219" s="3"/>
+      <c r="AD219" s="3"/>
+      <c r="AE219" s="3"/>
+      <c r="AF219" s="3"/>
+      <c r="AG219" s="3"/>
+      <c r="AH219" s="3"/>
+      <c r="AI219" s="3"/>
+      <c r="AJ219" s="3"/>
+      <c r="AK219" s="3"/>
+      <c r="AL219" s="3"/>
+      <c r="AM219" s="3"/>
+      <c r="AN219" s="3"/>
+      <c r="AO219" s="3"/>
+      <c r="AP219" s="3"/>
+      <c r="AQ219" s="3"/>
+      <c r="AR219" s="3"/>
+    </row>
+    <row r="220" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -8258,8 +12381,30 @@
       <c r="T220" s="3"/>
       <c r="U220" s="3"/>
       <c r="V220" s="3"/>
-    </row>
-    <row r="221" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W220" s="3"/>
+      <c r="X220" s="3"/>
+      <c r="Y220" s="3"/>
+      <c r="Z220" s="3"/>
+      <c r="AA220" s="3"/>
+      <c r="AB220" s="3"/>
+      <c r="AC220" s="3"/>
+      <c r="AD220" s="3"/>
+      <c r="AE220" s="3"/>
+      <c r="AF220" s="3"/>
+      <c r="AG220" s="3"/>
+      <c r="AH220" s="3"/>
+      <c r="AI220" s="3"/>
+      <c r="AJ220" s="3"/>
+      <c r="AK220" s="3"/>
+      <c r="AL220" s="3"/>
+      <c r="AM220" s="3"/>
+      <c r="AN220" s="3"/>
+      <c r="AO220" s="3"/>
+      <c r="AP220" s="3"/>
+      <c r="AQ220" s="3"/>
+      <c r="AR220" s="3"/>
+    </row>
+    <row r="221" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -8280,8 +12425,30 @@
       <c r="T221" s="3"/>
       <c r="U221" s="3"/>
       <c r="V221" s="3"/>
-    </row>
-    <row r="222" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W221" s="3"/>
+      <c r="X221" s="3"/>
+      <c r="Y221" s="3"/>
+      <c r="Z221" s="3"/>
+      <c r="AA221" s="3"/>
+      <c r="AB221" s="3"/>
+      <c r="AC221" s="3"/>
+      <c r="AD221" s="3"/>
+      <c r="AE221" s="3"/>
+      <c r="AF221" s="3"/>
+      <c r="AG221" s="3"/>
+      <c r="AH221" s="3"/>
+      <c r="AI221" s="3"/>
+      <c r="AJ221" s="3"/>
+      <c r="AK221" s="3"/>
+      <c r="AL221" s="3"/>
+      <c r="AM221" s="3"/>
+      <c r="AN221" s="3"/>
+      <c r="AO221" s="3"/>
+      <c r="AP221" s="3"/>
+      <c r="AQ221" s="3"/>
+      <c r="AR221" s="3"/>
+    </row>
+    <row r="222" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -8302,8 +12469,30 @@
       <c r="T222" s="3"/>
       <c r="U222" s="3"/>
       <c r="V222" s="3"/>
-    </row>
-    <row r="223" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W222" s="3"/>
+      <c r="X222" s="3"/>
+      <c r="Y222" s="3"/>
+      <c r="Z222" s="3"/>
+      <c r="AA222" s="3"/>
+      <c r="AB222" s="3"/>
+      <c r="AC222" s="3"/>
+      <c r="AD222" s="3"/>
+      <c r="AE222" s="3"/>
+      <c r="AF222" s="3"/>
+      <c r="AG222" s="3"/>
+      <c r="AH222" s="3"/>
+      <c r="AI222" s="3"/>
+      <c r="AJ222" s="3"/>
+      <c r="AK222" s="3"/>
+      <c r="AL222" s="3"/>
+      <c r="AM222" s="3"/>
+      <c r="AN222" s="3"/>
+      <c r="AO222" s="3"/>
+      <c r="AP222" s="3"/>
+      <c r="AQ222" s="3"/>
+      <c r="AR222" s="3"/>
+    </row>
+    <row r="223" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -8324,8 +12513,30 @@
       <c r="T223" s="3"/>
       <c r="U223" s="3"/>
       <c r="V223" s="3"/>
-    </row>
-    <row r="224" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W223" s="3"/>
+      <c r="X223" s="3"/>
+      <c r="Y223" s="3"/>
+      <c r="Z223" s="3"/>
+      <c r="AA223" s="3"/>
+      <c r="AB223" s="3"/>
+      <c r="AC223" s="3"/>
+      <c r="AD223" s="3"/>
+      <c r="AE223" s="3"/>
+      <c r="AF223" s="3"/>
+      <c r="AG223" s="3"/>
+      <c r="AH223" s="3"/>
+      <c r="AI223" s="3"/>
+      <c r="AJ223" s="3"/>
+      <c r="AK223" s="3"/>
+      <c r="AL223" s="3"/>
+      <c r="AM223" s="3"/>
+      <c r="AN223" s="3"/>
+      <c r="AO223" s="3"/>
+      <c r="AP223" s="3"/>
+      <c r="AQ223" s="3"/>
+      <c r="AR223" s="3"/>
+    </row>
+    <row r="224" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -8346,8 +12557,30 @@
       <c r="T224" s="3"/>
       <c r="U224" s="3"/>
       <c r="V224" s="3"/>
-    </row>
-    <row r="225" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W224" s="3"/>
+      <c r="X224" s="3"/>
+      <c r="Y224" s="3"/>
+      <c r="Z224" s="3"/>
+      <c r="AA224" s="3"/>
+      <c r="AB224" s="3"/>
+      <c r="AC224" s="3"/>
+      <c r="AD224" s="3"/>
+      <c r="AE224" s="3"/>
+      <c r="AF224" s="3"/>
+      <c r="AG224" s="3"/>
+      <c r="AH224" s="3"/>
+      <c r="AI224" s="3"/>
+      <c r="AJ224" s="3"/>
+      <c r="AK224" s="3"/>
+      <c r="AL224" s="3"/>
+      <c r="AM224" s="3"/>
+      <c r="AN224" s="3"/>
+      <c r="AO224" s="3"/>
+      <c r="AP224" s="3"/>
+      <c r="AQ224" s="3"/>
+      <c r="AR224" s="3"/>
+    </row>
+    <row r="225" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
@@ -8368,8 +12601,30 @@
       <c r="T225" s="3"/>
       <c r="U225" s="3"/>
       <c r="V225" s="3"/>
-    </row>
-    <row r="226" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W225" s="3"/>
+      <c r="X225" s="3"/>
+      <c r="Y225" s="3"/>
+      <c r="Z225" s="3"/>
+      <c r="AA225" s="3"/>
+      <c r="AB225" s="3"/>
+      <c r="AC225" s="3"/>
+      <c r="AD225" s="3"/>
+      <c r="AE225" s="3"/>
+      <c r="AF225" s="3"/>
+      <c r="AG225" s="3"/>
+      <c r="AH225" s="3"/>
+      <c r="AI225" s="3"/>
+      <c r="AJ225" s="3"/>
+      <c r="AK225" s="3"/>
+      <c r="AL225" s="3"/>
+      <c r="AM225" s="3"/>
+      <c r="AN225" s="3"/>
+      <c r="AO225" s="3"/>
+      <c r="AP225" s="3"/>
+      <c r="AQ225" s="3"/>
+      <c r="AR225" s="3"/>
+    </row>
+    <row r="226" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
@@ -8390,8 +12645,30 @@
       <c r="T226" s="3"/>
       <c r="U226" s="3"/>
       <c r="V226" s="3"/>
-    </row>
-    <row r="227" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W226" s="3"/>
+      <c r="X226" s="3"/>
+      <c r="Y226" s="3"/>
+      <c r="Z226" s="3"/>
+      <c r="AA226" s="3"/>
+      <c r="AB226" s="3"/>
+      <c r="AC226" s="3"/>
+      <c r="AD226" s="3"/>
+      <c r="AE226" s="3"/>
+      <c r="AF226" s="3"/>
+      <c r="AG226" s="3"/>
+      <c r="AH226" s="3"/>
+      <c r="AI226" s="3"/>
+      <c r="AJ226" s="3"/>
+      <c r="AK226" s="3"/>
+      <c r="AL226" s="3"/>
+      <c r="AM226" s="3"/>
+      <c r="AN226" s="3"/>
+      <c r="AO226" s="3"/>
+      <c r="AP226" s="3"/>
+      <c r="AQ226" s="3"/>
+      <c r="AR226" s="3"/>
+    </row>
+    <row r="227" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
       <c r="E227" s="3"/>
@@ -8412,8 +12689,30 @@
       <c r="T227" s="3"/>
       <c r="U227" s="3"/>
       <c r="V227" s="3"/>
-    </row>
-    <row r="228" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W227" s="3"/>
+      <c r="X227" s="3"/>
+      <c r="Y227" s="3"/>
+      <c r="Z227" s="3"/>
+      <c r="AA227" s="3"/>
+      <c r="AB227" s="3"/>
+      <c r="AC227" s="3"/>
+      <c r="AD227" s="3"/>
+      <c r="AE227" s="3"/>
+      <c r="AF227" s="3"/>
+      <c r="AG227" s="3"/>
+      <c r="AH227" s="3"/>
+      <c r="AI227" s="3"/>
+      <c r="AJ227" s="3"/>
+      <c r="AK227" s="3"/>
+      <c r="AL227" s="3"/>
+      <c r="AM227" s="3"/>
+      <c r="AN227" s="3"/>
+      <c r="AO227" s="3"/>
+      <c r="AP227" s="3"/>
+      <c r="AQ227" s="3"/>
+      <c r="AR227" s="3"/>
+    </row>
+    <row r="228" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -8434,8 +12733,30 @@
       <c r="T228" s="3"/>
       <c r="U228" s="3"/>
       <c r="V228" s="3"/>
-    </row>
-    <row r="229" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W228" s="3"/>
+      <c r="X228" s="3"/>
+      <c r="Y228" s="3"/>
+      <c r="Z228" s="3"/>
+      <c r="AA228" s="3"/>
+      <c r="AB228" s="3"/>
+      <c r="AC228" s="3"/>
+      <c r="AD228" s="3"/>
+      <c r="AE228" s="3"/>
+      <c r="AF228" s="3"/>
+      <c r="AG228" s="3"/>
+      <c r="AH228" s="3"/>
+      <c r="AI228" s="3"/>
+      <c r="AJ228" s="3"/>
+      <c r="AK228" s="3"/>
+      <c r="AL228" s="3"/>
+      <c r="AM228" s="3"/>
+      <c r="AN228" s="3"/>
+      <c r="AO228" s="3"/>
+      <c r="AP228" s="3"/>
+      <c r="AQ228" s="3"/>
+      <c r="AR228" s="3"/>
+    </row>
+    <row r="229" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -8456,8 +12777,30 @@
       <c r="T229" s="3"/>
       <c r="U229" s="3"/>
       <c r="V229" s="3"/>
-    </row>
-    <row r="230" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W229" s="3"/>
+      <c r="X229" s="3"/>
+      <c r="Y229" s="3"/>
+      <c r="Z229" s="3"/>
+      <c r="AA229" s="3"/>
+      <c r="AB229" s="3"/>
+      <c r="AC229" s="3"/>
+      <c r="AD229" s="3"/>
+      <c r="AE229" s="3"/>
+      <c r="AF229" s="3"/>
+      <c r="AG229" s="3"/>
+      <c r="AH229" s="3"/>
+      <c r="AI229" s="3"/>
+      <c r="AJ229" s="3"/>
+      <c r="AK229" s="3"/>
+      <c r="AL229" s="3"/>
+      <c r="AM229" s="3"/>
+      <c r="AN229" s="3"/>
+      <c r="AO229" s="3"/>
+      <c r="AP229" s="3"/>
+      <c r="AQ229" s="3"/>
+      <c r="AR229" s="3"/>
+    </row>
+    <row r="230" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -8478,8 +12821,30 @@
       <c r="T230" s="3"/>
       <c r="U230" s="3"/>
       <c r="V230" s="3"/>
-    </row>
-    <row r="231" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W230" s="3"/>
+      <c r="X230" s="3"/>
+      <c r="Y230" s="3"/>
+      <c r="Z230" s="3"/>
+      <c r="AA230" s="3"/>
+      <c r="AB230" s="3"/>
+      <c r="AC230" s="3"/>
+      <c r="AD230" s="3"/>
+      <c r="AE230" s="3"/>
+      <c r="AF230" s="3"/>
+      <c r="AG230" s="3"/>
+      <c r="AH230" s="3"/>
+      <c r="AI230" s="3"/>
+      <c r="AJ230" s="3"/>
+      <c r="AK230" s="3"/>
+      <c r="AL230" s="3"/>
+      <c r="AM230" s="3"/>
+      <c r="AN230" s="3"/>
+      <c r="AO230" s="3"/>
+      <c r="AP230" s="3"/>
+      <c r="AQ230" s="3"/>
+      <c r="AR230" s="3"/>
+    </row>
+    <row r="231" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
@@ -8500,8 +12865,30 @@
       <c r="T231" s="3"/>
       <c r="U231" s="3"/>
       <c r="V231" s="3"/>
-    </row>
-    <row r="232" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W231" s="3"/>
+      <c r="X231" s="3"/>
+      <c r="Y231" s="3"/>
+      <c r="Z231" s="3"/>
+      <c r="AA231" s="3"/>
+      <c r="AB231" s="3"/>
+      <c r="AC231" s="3"/>
+      <c r="AD231" s="3"/>
+      <c r="AE231" s="3"/>
+      <c r="AF231" s="3"/>
+      <c r="AG231" s="3"/>
+      <c r="AH231" s="3"/>
+      <c r="AI231" s="3"/>
+      <c r="AJ231" s="3"/>
+      <c r="AK231" s="3"/>
+      <c r="AL231" s="3"/>
+      <c r="AM231" s="3"/>
+      <c r="AN231" s="3"/>
+      <c r="AO231" s="3"/>
+      <c r="AP231" s="3"/>
+      <c r="AQ231" s="3"/>
+      <c r="AR231" s="3"/>
+    </row>
+    <row r="232" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -8522,8 +12909,30 @@
       <c r="T232" s="3"/>
       <c r="U232" s="3"/>
       <c r="V232" s="3"/>
-    </row>
-    <row r="233" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W232" s="3"/>
+      <c r="X232" s="3"/>
+      <c r="Y232" s="3"/>
+      <c r="Z232" s="3"/>
+      <c r="AA232" s="3"/>
+      <c r="AB232" s="3"/>
+      <c r="AC232" s="3"/>
+      <c r="AD232" s="3"/>
+      <c r="AE232" s="3"/>
+      <c r="AF232" s="3"/>
+      <c r="AG232" s="3"/>
+      <c r="AH232" s="3"/>
+      <c r="AI232" s="3"/>
+      <c r="AJ232" s="3"/>
+      <c r="AK232" s="3"/>
+      <c r="AL232" s="3"/>
+      <c r="AM232" s="3"/>
+      <c r="AN232" s="3"/>
+      <c r="AO232" s="3"/>
+      <c r="AP232" s="3"/>
+      <c r="AQ232" s="3"/>
+      <c r="AR232" s="3"/>
+    </row>
+    <row r="233" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
@@ -8544,8 +12953,30 @@
       <c r="T233" s="3"/>
       <c r="U233" s="3"/>
       <c r="V233" s="3"/>
-    </row>
-    <row r="234" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W233" s="3"/>
+      <c r="X233" s="3"/>
+      <c r="Y233" s="3"/>
+      <c r="Z233" s="3"/>
+      <c r="AA233" s="3"/>
+      <c r="AB233" s="3"/>
+      <c r="AC233" s="3"/>
+      <c r="AD233" s="3"/>
+      <c r="AE233" s="3"/>
+      <c r="AF233" s="3"/>
+      <c r="AG233" s="3"/>
+      <c r="AH233" s="3"/>
+      <c r="AI233" s="3"/>
+      <c r="AJ233" s="3"/>
+      <c r="AK233" s="3"/>
+      <c r="AL233" s="3"/>
+      <c r="AM233" s="3"/>
+      <c r="AN233" s="3"/>
+      <c r="AO233" s="3"/>
+      <c r="AP233" s="3"/>
+      <c r="AQ233" s="3"/>
+      <c r="AR233" s="3"/>
+    </row>
+    <row r="234" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -8566,8 +12997,30 @@
       <c r="T234" s="3"/>
       <c r="U234" s="3"/>
       <c r="V234" s="3"/>
-    </row>
-    <row r="235" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W234" s="3"/>
+      <c r="X234" s="3"/>
+      <c r="Y234" s="3"/>
+      <c r="Z234" s="3"/>
+      <c r="AA234" s="3"/>
+      <c r="AB234" s="3"/>
+      <c r="AC234" s="3"/>
+      <c r="AD234" s="3"/>
+      <c r="AE234" s="3"/>
+      <c r="AF234" s="3"/>
+      <c r="AG234" s="3"/>
+      <c r="AH234" s="3"/>
+      <c r="AI234" s="3"/>
+      <c r="AJ234" s="3"/>
+      <c r="AK234" s="3"/>
+      <c r="AL234" s="3"/>
+      <c r="AM234" s="3"/>
+      <c r="AN234" s="3"/>
+      <c r="AO234" s="3"/>
+      <c r="AP234" s="3"/>
+      <c r="AQ234" s="3"/>
+      <c r="AR234" s="3"/>
+    </row>
+    <row r="235" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
@@ -8588,8 +13041,30 @@
       <c r="T235" s="3"/>
       <c r="U235" s="3"/>
       <c r="V235" s="3"/>
-    </row>
-    <row r="236" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W235" s="3"/>
+      <c r="X235" s="3"/>
+      <c r="Y235" s="3"/>
+      <c r="Z235" s="3"/>
+      <c r="AA235" s="3"/>
+      <c r="AB235" s="3"/>
+      <c r="AC235" s="3"/>
+      <c r="AD235" s="3"/>
+      <c r="AE235" s="3"/>
+      <c r="AF235" s="3"/>
+      <c r="AG235" s="3"/>
+      <c r="AH235" s="3"/>
+      <c r="AI235" s="3"/>
+      <c r="AJ235" s="3"/>
+      <c r="AK235" s="3"/>
+      <c r="AL235" s="3"/>
+      <c r="AM235" s="3"/>
+      <c r="AN235" s="3"/>
+      <c r="AO235" s="3"/>
+      <c r="AP235" s="3"/>
+      <c r="AQ235" s="3"/>
+      <c r="AR235" s="3"/>
+    </row>
+    <row r="236" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -8610,8 +13085,30 @@
       <c r="T236" s="3"/>
       <c r="U236" s="3"/>
       <c r="V236" s="3"/>
-    </row>
-    <row r="237" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W236" s="3"/>
+      <c r="X236" s="3"/>
+      <c r="Y236" s="3"/>
+      <c r="Z236" s="3"/>
+      <c r="AA236" s="3"/>
+      <c r="AB236" s="3"/>
+      <c r="AC236" s="3"/>
+      <c r="AD236" s="3"/>
+      <c r="AE236" s="3"/>
+      <c r="AF236" s="3"/>
+      <c r="AG236" s="3"/>
+      <c r="AH236" s="3"/>
+      <c r="AI236" s="3"/>
+      <c r="AJ236" s="3"/>
+      <c r="AK236" s="3"/>
+      <c r="AL236" s="3"/>
+      <c r="AM236" s="3"/>
+      <c r="AN236" s="3"/>
+      <c r="AO236" s="3"/>
+      <c r="AP236" s="3"/>
+      <c r="AQ236" s="3"/>
+      <c r="AR236" s="3"/>
+    </row>
+    <row r="237" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="3"/>
@@ -8632,8 +13129,30 @@
       <c r="T237" s="3"/>
       <c r="U237" s="3"/>
       <c r="V237" s="3"/>
-    </row>
-    <row r="238" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W237" s="3"/>
+      <c r="X237" s="3"/>
+      <c r="Y237" s="3"/>
+      <c r="Z237" s="3"/>
+      <c r="AA237" s="3"/>
+      <c r="AB237" s="3"/>
+      <c r="AC237" s="3"/>
+      <c r="AD237" s="3"/>
+      <c r="AE237" s="3"/>
+      <c r="AF237" s="3"/>
+      <c r="AG237" s="3"/>
+      <c r="AH237" s="3"/>
+      <c r="AI237" s="3"/>
+      <c r="AJ237" s="3"/>
+      <c r="AK237" s="3"/>
+      <c r="AL237" s="3"/>
+      <c r="AM237" s="3"/>
+      <c r="AN237" s="3"/>
+      <c r="AO237" s="3"/>
+      <c r="AP237" s="3"/>
+      <c r="AQ237" s="3"/>
+      <c r="AR237" s="3"/>
+    </row>
+    <row r="238" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -8654,8 +13173,30 @@
       <c r="T238" s="3"/>
       <c r="U238" s="3"/>
       <c r="V238" s="3"/>
-    </row>
-    <row r="239" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W238" s="3"/>
+      <c r="X238" s="3"/>
+      <c r="Y238" s="3"/>
+      <c r="Z238" s="3"/>
+      <c r="AA238" s="3"/>
+      <c r="AB238" s="3"/>
+      <c r="AC238" s="3"/>
+      <c r="AD238" s="3"/>
+      <c r="AE238" s="3"/>
+      <c r="AF238" s="3"/>
+      <c r="AG238" s="3"/>
+      <c r="AH238" s="3"/>
+      <c r="AI238" s="3"/>
+      <c r="AJ238" s="3"/>
+      <c r="AK238" s="3"/>
+      <c r="AL238" s="3"/>
+      <c r="AM238" s="3"/>
+      <c r="AN238" s="3"/>
+      <c r="AO238" s="3"/>
+      <c r="AP238" s="3"/>
+      <c r="AQ238" s="3"/>
+      <c r="AR238" s="3"/>
+    </row>
+    <row r="239" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
       <c r="E239" s="3"/>
@@ -8676,8 +13217,30 @@
       <c r="T239" s="3"/>
       <c r="U239" s="3"/>
       <c r="V239" s="3"/>
-    </row>
-    <row r="240" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W239" s="3"/>
+      <c r="X239" s="3"/>
+      <c r="Y239" s="3"/>
+      <c r="Z239" s="3"/>
+      <c r="AA239" s="3"/>
+      <c r="AB239" s="3"/>
+      <c r="AC239" s="3"/>
+      <c r="AD239" s="3"/>
+      <c r="AE239" s="3"/>
+      <c r="AF239" s="3"/>
+      <c r="AG239" s="3"/>
+      <c r="AH239" s="3"/>
+      <c r="AI239" s="3"/>
+      <c r="AJ239" s="3"/>
+      <c r="AK239" s="3"/>
+      <c r="AL239" s="3"/>
+      <c r="AM239" s="3"/>
+      <c r="AN239" s="3"/>
+      <c r="AO239" s="3"/>
+      <c r="AP239" s="3"/>
+      <c r="AQ239" s="3"/>
+      <c r="AR239" s="3"/>
+    </row>
+    <row r="240" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
@@ -8698,8 +13261,30 @@
       <c r="T240" s="3"/>
       <c r="U240" s="3"/>
       <c r="V240" s="3"/>
-    </row>
-    <row r="241" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W240" s="3"/>
+      <c r="X240" s="3"/>
+      <c r="Y240" s="3"/>
+      <c r="Z240" s="3"/>
+      <c r="AA240" s="3"/>
+      <c r="AB240" s="3"/>
+      <c r="AC240" s="3"/>
+      <c r="AD240" s="3"/>
+      <c r="AE240" s="3"/>
+      <c r="AF240" s="3"/>
+      <c r="AG240" s="3"/>
+      <c r="AH240" s="3"/>
+      <c r="AI240" s="3"/>
+      <c r="AJ240" s="3"/>
+      <c r="AK240" s="3"/>
+      <c r="AL240" s="3"/>
+      <c r="AM240" s="3"/>
+      <c r="AN240" s="3"/>
+      <c r="AO240" s="3"/>
+      <c r="AP240" s="3"/>
+      <c r="AQ240" s="3"/>
+      <c r="AR240" s="3"/>
+    </row>
+    <row r="241" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
       <c r="E241" s="3"/>
@@ -8720,8 +13305,30 @@
       <c r="T241" s="3"/>
       <c r="U241" s="3"/>
       <c r="V241" s="3"/>
-    </row>
-    <row r="242" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W241" s="3"/>
+      <c r="X241" s="3"/>
+      <c r="Y241" s="3"/>
+      <c r="Z241" s="3"/>
+      <c r="AA241" s="3"/>
+      <c r="AB241" s="3"/>
+      <c r="AC241" s="3"/>
+      <c r="AD241" s="3"/>
+      <c r="AE241" s="3"/>
+      <c r="AF241" s="3"/>
+      <c r="AG241" s="3"/>
+      <c r="AH241" s="3"/>
+      <c r="AI241" s="3"/>
+      <c r="AJ241" s="3"/>
+      <c r="AK241" s="3"/>
+      <c r="AL241" s="3"/>
+      <c r="AM241" s="3"/>
+      <c r="AN241" s="3"/>
+      <c r="AO241" s="3"/>
+      <c r="AP241" s="3"/>
+      <c r="AQ241" s="3"/>
+      <c r="AR241" s="3"/>
+    </row>
+    <row r="242" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
@@ -8742,8 +13349,30 @@
       <c r="T242" s="3"/>
       <c r="U242" s="3"/>
       <c r="V242" s="3"/>
-    </row>
-    <row r="243" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W242" s="3"/>
+      <c r="X242" s="3"/>
+      <c r="Y242" s="3"/>
+      <c r="Z242" s="3"/>
+      <c r="AA242" s="3"/>
+      <c r="AB242" s="3"/>
+      <c r="AC242" s="3"/>
+      <c r="AD242" s="3"/>
+      <c r="AE242" s="3"/>
+      <c r="AF242" s="3"/>
+      <c r="AG242" s="3"/>
+      <c r="AH242" s="3"/>
+      <c r="AI242" s="3"/>
+      <c r="AJ242" s="3"/>
+      <c r="AK242" s="3"/>
+      <c r="AL242" s="3"/>
+      <c r="AM242" s="3"/>
+      <c r="AN242" s="3"/>
+      <c r="AO242" s="3"/>
+      <c r="AP242" s="3"/>
+      <c r="AQ242" s="3"/>
+      <c r="AR242" s="3"/>
+    </row>
+    <row r="243" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
@@ -8764,8 +13393,30 @@
       <c r="T243" s="3"/>
       <c r="U243" s="3"/>
       <c r="V243" s="3"/>
-    </row>
-    <row r="244" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W243" s="3"/>
+      <c r="X243" s="3"/>
+      <c r="Y243" s="3"/>
+      <c r="Z243" s="3"/>
+      <c r="AA243" s="3"/>
+      <c r="AB243" s="3"/>
+      <c r="AC243" s="3"/>
+      <c r="AD243" s="3"/>
+      <c r="AE243" s="3"/>
+      <c r="AF243" s="3"/>
+      <c r="AG243" s="3"/>
+      <c r="AH243" s="3"/>
+      <c r="AI243" s="3"/>
+      <c r="AJ243" s="3"/>
+      <c r="AK243" s="3"/>
+      <c r="AL243" s="3"/>
+      <c r="AM243" s="3"/>
+      <c r="AN243" s="3"/>
+      <c r="AO243" s="3"/>
+      <c r="AP243" s="3"/>
+      <c r="AQ243" s="3"/>
+      <c r="AR243" s="3"/>
+    </row>
+    <row r="244" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -8786,8 +13437,30 @@
       <c r="T244" s="3"/>
       <c r="U244" s="3"/>
       <c r="V244" s="3"/>
-    </row>
-    <row r="245" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W244" s="3"/>
+      <c r="X244" s="3"/>
+      <c r="Y244" s="3"/>
+      <c r="Z244" s="3"/>
+      <c r="AA244" s="3"/>
+      <c r="AB244" s="3"/>
+      <c r="AC244" s="3"/>
+      <c r="AD244" s="3"/>
+      <c r="AE244" s="3"/>
+      <c r="AF244" s="3"/>
+      <c r="AG244" s="3"/>
+      <c r="AH244" s="3"/>
+      <c r="AI244" s="3"/>
+      <c r="AJ244" s="3"/>
+      <c r="AK244" s="3"/>
+      <c r="AL244" s="3"/>
+      <c r="AM244" s="3"/>
+      <c r="AN244" s="3"/>
+      <c r="AO244" s="3"/>
+      <c r="AP244" s="3"/>
+      <c r="AQ244" s="3"/>
+      <c r="AR244" s="3"/>
+    </row>
+    <row r="245" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
       <c r="E245" s="3"/>
@@ -8808,8 +13481,30 @@
       <c r="T245" s="3"/>
       <c r="U245" s="3"/>
       <c r="V245" s="3"/>
-    </row>
-    <row r="246" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W245" s="3"/>
+      <c r="X245" s="3"/>
+      <c r="Y245" s="3"/>
+      <c r="Z245" s="3"/>
+      <c r="AA245" s="3"/>
+      <c r="AB245" s="3"/>
+      <c r="AC245" s="3"/>
+      <c r="AD245" s="3"/>
+      <c r="AE245" s="3"/>
+      <c r="AF245" s="3"/>
+      <c r="AG245" s="3"/>
+      <c r="AH245" s="3"/>
+      <c r="AI245" s="3"/>
+      <c r="AJ245" s="3"/>
+      <c r="AK245" s="3"/>
+      <c r="AL245" s="3"/>
+      <c r="AM245" s="3"/>
+      <c r="AN245" s="3"/>
+      <c r="AO245" s="3"/>
+      <c r="AP245" s="3"/>
+      <c r="AQ245" s="3"/>
+      <c r="AR245" s="3"/>
+    </row>
+    <row r="246" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
@@ -8830,8 +13525,30 @@
       <c r="T246" s="3"/>
       <c r="U246" s="3"/>
       <c r="V246" s="3"/>
-    </row>
-    <row r="247" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W246" s="3"/>
+      <c r="X246" s="3"/>
+      <c r="Y246" s="3"/>
+      <c r="Z246" s="3"/>
+      <c r="AA246" s="3"/>
+      <c r="AB246" s="3"/>
+      <c r="AC246" s="3"/>
+      <c r="AD246" s="3"/>
+      <c r="AE246" s="3"/>
+      <c r="AF246" s="3"/>
+      <c r="AG246" s="3"/>
+      <c r="AH246" s="3"/>
+      <c r="AI246" s="3"/>
+      <c r="AJ246" s="3"/>
+      <c r="AK246" s="3"/>
+      <c r="AL246" s="3"/>
+      <c r="AM246" s="3"/>
+      <c r="AN246" s="3"/>
+      <c r="AO246" s="3"/>
+      <c r="AP246" s="3"/>
+      <c r="AQ246" s="3"/>
+      <c r="AR246" s="3"/>
+    </row>
+    <row r="247" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
       <c r="E247" s="3"/>
@@ -8852,8 +13569,30 @@
       <c r="T247" s="3"/>
       <c r="U247" s="3"/>
       <c r="V247" s="3"/>
-    </row>
-    <row r="248" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W247" s="3"/>
+      <c r="X247" s="3"/>
+      <c r="Y247" s="3"/>
+      <c r="Z247" s="3"/>
+      <c r="AA247" s="3"/>
+      <c r="AB247" s="3"/>
+      <c r="AC247" s="3"/>
+      <c r="AD247" s="3"/>
+      <c r="AE247" s="3"/>
+      <c r="AF247" s="3"/>
+      <c r="AG247" s="3"/>
+      <c r="AH247" s="3"/>
+      <c r="AI247" s="3"/>
+      <c r="AJ247" s="3"/>
+      <c r="AK247" s="3"/>
+      <c r="AL247" s="3"/>
+      <c r="AM247" s="3"/>
+      <c r="AN247" s="3"/>
+      <c r="AO247" s="3"/>
+      <c r="AP247" s="3"/>
+      <c r="AQ247" s="3"/>
+      <c r="AR247" s="3"/>
+    </row>
+    <row r="248" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
@@ -8874,8 +13613,30 @@
       <c r="T248" s="3"/>
       <c r="U248" s="3"/>
       <c r="V248" s="3"/>
-    </row>
-    <row r="249" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W248" s="3"/>
+      <c r="X248" s="3"/>
+      <c r="Y248" s="3"/>
+      <c r="Z248" s="3"/>
+      <c r="AA248" s="3"/>
+      <c r="AB248" s="3"/>
+      <c r="AC248" s="3"/>
+      <c r="AD248" s="3"/>
+      <c r="AE248" s="3"/>
+      <c r="AF248" s="3"/>
+      <c r="AG248" s="3"/>
+      <c r="AH248" s="3"/>
+      <c r="AI248" s="3"/>
+      <c r="AJ248" s="3"/>
+      <c r="AK248" s="3"/>
+      <c r="AL248" s="3"/>
+      <c r="AM248" s="3"/>
+      <c r="AN248" s="3"/>
+      <c r="AO248" s="3"/>
+      <c r="AP248" s="3"/>
+      <c r="AQ248" s="3"/>
+      <c r="AR248" s="3"/>
+    </row>
+    <row r="249" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
       <c r="E249" s="3"/>
@@ -8896,8 +13657,30 @@
       <c r="T249" s="3"/>
       <c r="U249" s="3"/>
       <c r="V249" s="3"/>
-    </row>
-    <row r="250" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W249" s="3"/>
+      <c r="X249" s="3"/>
+      <c r="Y249" s="3"/>
+      <c r="Z249" s="3"/>
+      <c r="AA249" s="3"/>
+      <c r="AB249" s="3"/>
+      <c r="AC249" s="3"/>
+      <c r="AD249" s="3"/>
+      <c r="AE249" s="3"/>
+      <c r="AF249" s="3"/>
+      <c r="AG249" s="3"/>
+      <c r="AH249" s="3"/>
+      <c r="AI249" s="3"/>
+      <c r="AJ249" s="3"/>
+      <c r="AK249" s="3"/>
+      <c r="AL249" s="3"/>
+      <c r="AM249" s="3"/>
+      <c r="AN249" s="3"/>
+      <c r="AO249" s="3"/>
+      <c r="AP249" s="3"/>
+      <c r="AQ249" s="3"/>
+      <c r="AR249" s="3"/>
+    </row>
+    <row r="250" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -8918,8 +13701,30 @@
       <c r="T250" s="3"/>
       <c r="U250" s="3"/>
       <c r="V250" s="3"/>
-    </row>
-    <row r="251" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W250" s="3"/>
+      <c r="X250" s="3"/>
+      <c r="Y250" s="3"/>
+      <c r="Z250" s="3"/>
+      <c r="AA250" s="3"/>
+      <c r="AB250" s="3"/>
+      <c r="AC250" s="3"/>
+      <c r="AD250" s="3"/>
+      <c r="AE250" s="3"/>
+      <c r="AF250" s="3"/>
+      <c r="AG250" s="3"/>
+      <c r="AH250" s="3"/>
+      <c r="AI250" s="3"/>
+      <c r="AJ250" s="3"/>
+      <c r="AK250" s="3"/>
+      <c r="AL250" s="3"/>
+      <c r="AM250" s="3"/>
+      <c r="AN250" s="3"/>
+      <c r="AO250" s="3"/>
+      <c r="AP250" s="3"/>
+      <c r="AQ250" s="3"/>
+      <c r="AR250" s="3"/>
+    </row>
+    <row r="251" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C251" s="3"/>
       <c r="D251" s="3"/>
       <c r="E251" s="3"/>
@@ -8940,8 +13745,30 @@
       <c r="T251" s="3"/>
       <c r="U251" s="3"/>
       <c r="V251" s="3"/>
-    </row>
-    <row r="252" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W251" s="3"/>
+      <c r="X251" s="3"/>
+      <c r="Y251" s="3"/>
+      <c r="Z251" s="3"/>
+      <c r="AA251" s="3"/>
+      <c r="AB251" s="3"/>
+      <c r="AC251" s="3"/>
+      <c r="AD251" s="3"/>
+      <c r="AE251" s="3"/>
+      <c r="AF251" s="3"/>
+      <c r="AG251" s="3"/>
+      <c r="AH251" s="3"/>
+      <c r="AI251" s="3"/>
+      <c r="AJ251" s="3"/>
+      <c r="AK251" s="3"/>
+      <c r="AL251" s="3"/>
+      <c r="AM251" s="3"/>
+      <c r="AN251" s="3"/>
+      <c r="AO251" s="3"/>
+      <c r="AP251" s="3"/>
+      <c r="AQ251" s="3"/>
+      <c r="AR251" s="3"/>
+    </row>
+    <row r="252" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C252" s="3"/>
       <c r="D252" s="3"/>
       <c r="E252" s="3"/>
@@ -8962,8 +13789,30 @@
       <c r="T252" s="3"/>
       <c r="U252" s="3"/>
       <c r="V252" s="3"/>
-    </row>
-    <row r="253" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W252" s="3"/>
+      <c r="X252" s="3"/>
+      <c r="Y252" s="3"/>
+      <c r="Z252" s="3"/>
+      <c r="AA252" s="3"/>
+      <c r="AB252" s="3"/>
+      <c r="AC252" s="3"/>
+      <c r="AD252" s="3"/>
+      <c r="AE252" s="3"/>
+      <c r="AF252" s="3"/>
+      <c r="AG252" s="3"/>
+      <c r="AH252" s="3"/>
+      <c r="AI252" s="3"/>
+      <c r="AJ252" s="3"/>
+      <c r="AK252" s="3"/>
+      <c r="AL252" s="3"/>
+      <c r="AM252" s="3"/>
+      <c r="AN252" s="3"/>
+      <c r="AO252" s="3"/>
+      <c r="AP252" s="3"/>
+      <c r="AQ252" s="3"/>
+      <c r="AR252" s="3"/>
+    </row>
+    <row r="253" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C253" s="3"/>
       <c r="D253" s="3"/>
       <c r="E253" s="3"/>
@@ -8984,8 +13833,30 @@
       <c r="T253" s="3"/>
       <c r="U253" s="3"/>
       <c r="V253" s="3"/>
-    </row>
-    <row r="254" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W253" s="3"/>
+      <c r="X253" s="3"/>
+      <c r="Y253" s="3"/>
+      <c r="Z253" s="3"/>
+      <c r="AA253" s="3"/>
+      <c r="AB253" s="3"/>
+      <c r="AC253" s="3"/>
+      <c r="AD253" s="3"/>
+      <c r="AE253" s="3"/>
+      <c r="AF253" s="3"/>
+      <c r="AG253" s="3"/>
+      <c r="AH253" s="3"/>
+      <c r="AI253" s="3"/>
+      <c r="AJ253" s="3"/>
+      <c r="AK253" s="3"/>
+      <c r="AL253" s="3"/>
+      <c r="AM253" s="3"/>
+      <c r="AN253" s="3"/>
+      <c r="AO253" s="3"/>
+      <c r="AP253" s="3"/>
+      <c r="AQ253" s="3"/>
+      <c r="AR253" s="3"/>
+    </row>
+    <row r="254" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C254" s="3"/>
       <c r="D254" s="3"/>
       <c r="E254" s="3"/>
@@ -9006,8 +13877,30 @@
       <c r="T254" s="3"/>
       <c r="U254" s="3"/>
       <c r="V254" s="3"/>
-    </row>
-    <row r="255" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W254" s="3"/>
+      <c r="X254" s="3"/>
+      <c r="Y254" s="3"/>
+      <c r="Z254" s="3"/>
+      <c r="AA254" s="3"/>
+      <c r="AB254" s="3"/>
+      <c r="AC254" s="3"/>
+      <c r="AD254" s="3"/>
+      <c r="AE254" s="3"/>
+      <c r="AF254" s="3"/>
+      <c r="AG254" s="3"/>
+      <c r="AH254" s="3"/>
+      <c r="AI254" s="3"/>
+      <c r="AJ254" s="3"/>
+      <c r="AK254" s="3"/>
+      <c r="AL254" s="3"/>
+      <c r="AM254" s="3"/>
+      <c r="AN254" s="3"/>
+      <c r="AO254" s="3"/>
+      <c r="AP254" s="3"/>
+      <c r="AQ254" s="3"/>
+      <c r="AR254" s="3"/>
+    </row>
+    <row r="255" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C255" s="3"/>
       <c r="D255" s="3"/>
       <c r="E255" s="3"/>
@@ -9028,8 +13921,30 @@
       <c r="T255" s="3"/>
       <c r="U255" s="3"/>
       <c r="V255" s="3"/>
-    </row>
-    <row r="256" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W255" s="3"/>
+      <c r="X255" s="3"/>
+      <c r="Y255" s="3"/>
+      <c r="Z255" s="3"/>
+      <c r="AA255" s="3"/>
+      <c r="AB255" s="3"/>
+      <c r="AC255" s="3"/>
+      <c r="AD255" s="3"/>
+      <c r="AE255" s="3"/>
+      <c r="AF255" s="3"/>
+      <c r="AG255" s="3"/>
+      <c r="AH255" s="3"/>
+      <c r="AI255" s="3"/>
+      <c r="AJ255" s="3"/>
+      <c r="AK255" s="3"/>
+      <c r="AL255" s="3"/>
+      <c r="AM255" s="3"/>
+      <c r="AN255" s="3"/>
+      <c r="AO255" s="3"/>
+      <c r="AP255" s="3"/>
+      <c r="AQ255" s="3"/>
+      <c r="AR255" s="3"/>
+    </row>
+    <row r="256" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
@@ -9050,8 +13965,30 @@
       <c r="T256" s="3"/>
       <c r="U256" s="3"/>
       <c r="V256" s="3"/>
-    </row>
-    <row r="257" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W256" s="3"/>
+      <c r="X256" s="3"/>
+      <c r="Y256" s="3"/>
+      <c r="Z256" s="3"/>
+      <c r="AA256" s="3"/>
+      <c r="AB256" s="3"/>
+      <c r="AC256" s="3"/>
+      <c r="AD256" s="3"/>
+      <c r="AE256" s="3"/>
+      <c r="AF256" s="3"/>
+      <c r="AG256" s="3"/>
+      <c r="AH256" s="3"/>
+      <c r="AI256" s="3"/>
+      <c r="AJ256" s="3"/>
+      <c r="AK256" s="3"/>
+      <c r="AL256" s="3"/>
+      <c r="AM256" s="3"/>
+      <c r="AN256" s="3"/>
+      <c r="AO256" s="3"/>
+      <c r="AP256" s="3"/>
+      <c r="AQ256" s="3"/>
+      <c r="AR256" s="3"/>
+    </row>
+    <row r="257" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
@@ -9072,8 +14009,30 @@
       <c r="T257" s="3"/>
       <c r="U257" s="3"/>
       <c r="V257" s="3"/>
-    </row>
-    <row r="258" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W257" s="3"/>
+      <c r="X257" s="3"/>
+      <c r="Y257" s="3"/>
+      <c r="Z257" s="3"/>
+      <c r="AA257" s="3"/>
+      <c r="AB257" s="3"/>
+      <c r="AC257" s="3"/>
+      <c r="AD257" s="3"/>
+      <c r="AE257" s="3"/>
+      <c r="AF257" s="3"/>
+      <c r="AG257" s="3"/>
+      <c r="AH257" s="3"/>
+      <c r="AI257" s="3"/>
+      <c r="AJ257" s="3"/>
+      <c r="AK257" s="3"/>
+      <c r="AL257" s="3"/>
+      <c r="AM257" s="3"/>
+      <c r="AN257" s="3"/>
+      <c r="AO257" s="3"/>
+      <c r="AP257" s="3"/>
+      <c r="AQ257" s="3"/>
+      <c r="AR257" s="3"/>
+    </row>
+    <row r="258" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C258" s="3"/>
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
@@ -9094,8 +14053,30 @@
       <c r="T258" s="3"/>
       <c r="U258" s="3"/>
       <c r="V258" s="3"/>
-    </row>
-    <row r="259" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W258" s="3"/>
+      <c r="X258" s="3"/>
+      <c r="Y258" s="3"/>
+      <c r="Z258" s="3"/>
+      <c r="AA258" s="3"/>
+      <c r="AB258" s="3"/>
+      <c r="AC258" s="3"/>
+      <c r="AD258" s="3"/>
+      <c r="AE258" s="3"/>
+      <c r="AF258" s="3"/>
+      <c r="AG258" s="3"/>
+      <c r="AH258" s="3"/>
+      <c r="AI258" s="3"/>
+      <c r="AJ258" s="3"/>
+      <c r="AK258" s="3"/>
+      <c r="AL258" s="3"/>
+      <c r="AM258" s="3"/>
+      <c r="AN258" s="3"/>
+      <c r="AO258" s="3"/>
+      <c r="AP258" s="3"/>
+      <c r="AQ258" s="3"/>
+      <c r="AR258" s="3"/>
+    </row>
+    <row r="259" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C259" s="3"/>
       <c r="D259" s="3"/>
       <c r="E259" s="3"/>
@@ -9116,8 +14097,30 @@
       <c r="T259" s="3"/>
       <c r="U259" s="3"/>
       <c r="V259" s="3"/>
-    </row>
-    <row r="260" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W259" s="3"/>
+      <c r="X259" s="3"/>
+      <c r="Y259" s="3"/>
+      <c r="Z259" s="3"/>
+      <c r="AA259" s="3"/>
+      <c r="AB259" s="3"/>
+      <c r="AC259" s="3"/>
+      <c r="AD259" s="3"/>
+      <c r="AE259" s="3"/>
+      <c r="AF259" s="3"/>
+      <c r="AG259" s="3"/>
+      <c r="AH259" s="3"/>
+      <c r="AI259" s="3"/>
+      <c r="AJ259" s="3"/>
+      <c r="AK259" s="3"/>
+      <c r="AL259" s="3"/>
+      <c r="AM259" s="3"/>
+      <c r="AN259" s="3"/>
+      <c r="AO259" s="3"/>
+      <c r="AP259" s="3"/>
+      <c r="AQ259" s="3"/>
+      <c r="AR259" s="3"/>
+    </row>
+    <row r="260" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C260" s="3"/>
       <c r="D260" s="3"/>
       <c r="E260" s="3"/>
@@ -9138,8 +14141,30 @@
       <c r="T260" s="3"/>
       <c r="U260" s="3"/>
       <c r="V260" s="3"/>
-    </row>
-    <row r="261" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W260" s="3"/>
+      <c r="X260" s="3"/>
+      <c r="Y260" s="3"/>
+      <c r="Z260" s="3"/>
+      <c r="AA260" s="3"/>
+      <c r="AB260" s="3"/>
+      <c r="AC260" s="3"/>
+      <c r="AD260" s="3"/>
+      <c r="AE260" s="3"/>
+      <c r="AF260" s="3"/>
+      <c r="AG260" s="3"/>
+      <c r="AH260" s="3"/>
+      <c r="AI260" s="3"/>
+      <c r="AJ260" s="3"/>
+      <c r="AK260" s="3"/>
+      <c r="AL260" s="3"/>
+      <c r="AM260" s="3"/>
+      <c r="AN260" s="3"/>
+      <c r="AO260" s="3"/>
+      <c r="AP260" s="3"/>
+      <c r="AQ260" s="3"/>
+      <c r="AR260" s="3"/>
+    </row>
+    <row r="261" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C261" s="3"/>
       <c r="D261" s="3"/>
       <c r="E261" s="3"/>
@@ -9160,8 +14185,30 @@
       <c r="T261" s="3"/>
       <c r="U261" s="3"/>
       <c r="V261" s="3"/>
-    </row>
-    <row r="262" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W261" s="3"/>
+      <c r="X261" s="3"/>
+      <c r="Y261" s="3"/>
+      <c r="Z261" s="3"/>
+      <c r="AA261" s="3"/>
+      <c r="AB261" s="3"/>
+      <c r="AC261" s="3"/>
+      <c r="AD261" s="3"/>
+      <c r="AE261" s="3"/>
+      <c r="AF261" s="3"/>
+      <c r="AG261" s="3"/>
+      <c r="AH261" s="3"/>
+      <c r="AI261" s="3"/>
+      <c r="AJ261" s="3"/>
+      <c r="AK261" s="3"/>
+      <c r="AL261" s="3"/>
+      <c r="AM261" s="3"/>
+      <c r="AN261" s="3"/>
+      <c r="AO261" s="3"/>
+      <c r="AP261" s="3"/>
+      <c r="AQ261" s="3"/>
+      <c r="AR261" s="3"/>
+    </row>
+    <row r="262" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C262" s="3"/>
       <c r="D262" s="3"/>
       <c r="E262" s="3"/>
@@ -9182,8 +14229,30 @@
       <c r="T262" s="3"/>
       <c r="U262" s="3"/>
       <c r="V262" s="3"/>
-    </row>
-    <row r="263" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W262" s="3"/>
+      <c r="X262" s="3"/>
+      <c r="Y262" s="3"/>
+      <c r="Z262" s="3"/>
+      <c r="AA262" s="3"/>
+      <c r="AB262" s="3"/>
+      <c r="AC262" s="3"/>
+      <c r="AD262" s="3"/>
+      <c r="AE262" s="3"/>
+      <c r="AF262" s="3"/>
+      <c r="AG262" s="3"/>
+      <c r="AH262" s="3"/>
+      <c r="AI262" s="3"/>
+      <c r="AJ262" s="3"/>
+      <c r="AK262" s="3"/>
+      <c r="AL262" s="3"/>
+      <c r="AM262" s="3"/>
+      <c r="AN262" s="3"/>
+      <c r="AO262" s="3"/>
+      <c r="AP262" s="3"/>
+      <c r="AQ262" s="3"/>
+      <c r="AR262" s="3"/>
+    </row>
+    <row r="263" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C263" s="3"/>
       <c r="D263" s="3"/>
       <c r="E263" s="3"/>
@@ -9204,8 +14273,30 @@
       <c r="T263" s="3"/>
       <c r="U263" s="3"/>
       <c r="V263" s="3"/>
-    </row>
-    <row r="264" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W263" s="3"/>
+      <c r="X263" s="3"/>
+      <c r="Y263" s="3"/>
+      <c r="Z263" s="3"/>
+      <c r="AA263" s="3"/>
+      <c r="AB263" s="3"/>
+      <c r="AC263" s="3"/>
+      <c r="AD263" s="3"/>
+      <c r="AE263" s="3"/>
+      <c r="AF263" s="3"/>
+      <c r="AG263" s="3"/>
+      <c r="AH263" s="3"/>
+      <c r="AI263" s="3"/>
+      <c r="AJ263" s="3"/>
+      <c r="AK263" s="3"/>
+      <c r="AL263" s="3"/>
+      <c r="AM263" s="3"/>
+      <c r="AN263" s="3"/>
+      <c r="AO263" s="3"/>
+      <c r="AP263" s="3"/>
+      <c r="AQ263" s="3"/>
+      <c r="AR263" s="3"/>
+    </row>
+    <row r="264" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C264" s="3"/>
       <c r="D264" s="3"/>
       <c r="E264" s="3"/>
@@ -9226,8 +14317,30 @@
       <c r="T264" s="3"/>
       <c r="U264" s="3"/>
       <c r="V264" s="3"/>
-    </row>
-    <row r="265" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W264" s="3"/>
+      <c r="X264" s="3"/>
+      <c r="Y264" s="3"/>
+      <c r="Z264" s="3"/>
+      <c r="AA264" s="3"/>
+      <c r="AB264" s="3"/>
+      <c r="AC264" s="3"/>
+      <c r="AD264" s="3"/>
+      <c r="AE264" s="3"/>
+      <c r="AF264" s="3"/>
+      <c r="AG264" s="3"/>
+      <c r="AH264" s="3"/>
+      <c r="AI264" s="3"/>
+      <c r="AJ264" s="3"/>
+      <c r="AK264" s="3"/>
+      <c r="AL264" s="3"/>
+      <c r="AM264" s="3"/>
+      <c r="AN264" s="3"/>
+      <c r="AO264" s="3"/>
+      <c r="AP264" s="3"/>
+      <c r="AQ264" s="3"/>
+      <c r="AR264" s="3"/>
+    </row>
+    <row r="265" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C265" s="3"/>
       <c r="D265" s="3"/>
       <c r="E265" s="3"/>
@@ -9248,8 +14361,30 @@
       <c r="T265" s="3"/>
       <c r="U265" s="3"/>
       <c r="V265" s="3"/>
-    </row>
-    <row r="266" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W265" s="3"/>
+      <c r="X265" s="3"/>
+      <c r="Y265" s="3"/>
+      <c r="Z265" s="3"/>
+      <c r="AA265" s="3"/>
+      <c r="AB265" s="3"/>
+      <c r="AC265" s="3"/>
+      <c r="AD265" s="3"/>
+      <c r="AE265" s="3"/>
+      <c r="AF265" s="3"/>
+      <c r="AG265" s="3"/>
+      <c r="AH265" s="3"/>
+      <c r="AI265" s="3"/>
+      <c r="AJ265" s="3"/>
+      <c r="AK265" s="3"/>
+      <c r="AL265" s="3"/>
+      <c r="AM265" s="3"/>
+      <c r="AN265" s="3"/>
+      <c r="AO265" s="3"/>
+      <c r="AP265" s="3"/>
+      <c r="AQ265" s="3"/>
+      <c r="AR265" s="3"/>
+    </row>
+    <row r="266" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C266" s="3"/>
       <c r="D266" s="3"/>
       <c r="E266" s="3"/>
@@ -9270,8 +14405,30 @@
       <c r="T266" s="3"/>
       <c r="U266" s="3"/>
       <c r="V266" s="3"/>
-    </row>
-    <row r="267" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W266" s="3"/>
+      <c r="X266" s="3"/>
+      <c r="Y266" s="3"/>
+      <c r="Z266" s="3"/>
+      <c r="AA266" s="3"/>
+      <c r="AB266" s="3"/>
+      <c r="AC266" s="3"/>
+      <c r="AD266" s="3"/>
+      <c r="AE266" s="3"/>
+      <c r="AF266" s="3"/>
+      <c r="AG266" s="3"/>
+      <c r="AH266" s="3"/>
+      <c r="AI266" s="3"/>
+      <c r="AJ266" s="3"/>
+      <c r="AK266" s="3"/>
+      <c r="AL266" s="3"/>
+      <c r="AM266" s="3"/>
+      <c r="AN266" s="3"/>
+      <c r="AO266" s="3"/>
+      <c r="AP266" s="3"/>
+      <c r="AQ266" s="3"/>
+      <c r="AR266" s="3"/>
+    </row>
+    <row r="267" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C267" s="3"/>
       <c r="D267" s="3"/>
       <c r="E267" s="3"/>
@@ -9292,8 +14449,30 @@
       <c r="T267" s="3"/>
       <c r="U267" s="3"/>
       <c r="V267" s="3"/>
-    </row>
-    <row r="268" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W267" s="3"/>
+      <c r="X267" s="3"/>
+      <c r="Y267" s="3"/>
+      <c r="Z267" s="3"/>
+      <c r="AA267" s="3"/>
+      <c r="AB267" s="3"/>
+      <c r="AC267" s="3"/>
+      <c r="AD267" s="3"/>
+      <c r="AE267" s="3"/>
+      <c r="AF267" s="3"/>
+      <c r="AG267" s="3"/>
+      <c r="AH267" s="3"/>
+      <c r="AI267" s="3"/>
+      <c r="AJ267" s="3"/>
+      <c r="AK267" s="3"/>
+      <c r="AL267" s="3"/>
+      <c r="AM267" s="3"/>
+      <c r="AN267" s="3"/>
+      <c r="AO267" s="3"/>
+      <c r="AP267" s="3"/>
+      <c r="AQ267" s="3"/>
+      <c r="AR267" s="3"/>
+    </row>
+    <row r="268" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
       <c r="E268" s="3"/>
@@ -9314,8 +14493,30 @@
       <c r="T268" s="3"/>
       <c r="U268" s="3"/>
       <c r="V268" s="3"/>
-    </row>
-    <row r="269" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W268" s="3"/>
+      <c r="X268" s="3"/>
+      <c r="Y268" s="3"/>
+      <c r="Z268" s="3"/>
+      <c r="AA268" s="3"/>
+      <c r="AB268" s="3"/>
+      <c r="AC268" s="3"/>
+      <c r="AD268" s="3"/>
+      <c r="AE268" s="3"/>
+      <c r="AF268" s="3"/>
+      <c r="AG268" s="3"/>
+      <c r="AH268" s="3"/>
+      <c r="AI268" s="3"/>
+      <c r="AJ268" s="3"/>
+      <c r="AK268" s="3"/>
+      <c r="AL268" s="3"/>
+      <c r="AM268" s="3"/>
+      <c r="AN268" s="3"/>
+      <c r="AO268" s="3"/>
+      <c r="AP268" s="3"/>
+      <c r="AQ268" s="3"/>
+      <c r="AR268" s="3"/>
+    </row>
+    <row r="269" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
       <c r="E269" s="3"/>
@@ -9336,8 +14537,30 @@
       <c r="T269" s="3"/>
       <c r="U269" s="3"/>
       <c r="V269" s="3"/>
-    </row>
-    <row r="270" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W269" s="3"/>
+      <c r="X269" s="3"/>
+      <c r="Y269" s="3"/>
+      <c r="Z269" s="3"/>
+      <c r="AA269" s="3"/>
+      <c r="AB269" s="3"/>
+      <c r="AC269" s="3"/>
+      <c r="AD269" s="3"/>
+      <c r="AE269" s="3"/>
+      <c r="AF269" s="3"/>
+      <c r="AG269" s="3"/>
+      <c r="AH269" s="3"/>
+      <c r="AI269" s="3"/>
+      <c r="AJ269" s="3"/>
+      <c r="AK269" s="3"/>
+      <c r="AL269" s="3"/>
+      <c r="AM269" s="3"/>
+      <c r="AN269" s="3"/>
+      <c r="AO269" s="3"/>
+      <c r="AP269" s="3"/>
+      <c r="AQ269" s="3"/>
+      <c r="AR269" s="3"/>
+    </row>
+    <row r="270" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C270" s="3"/>
       <c r="D270" s="3"/>
       <c r="E270" s="3"/>
@@ -9358,8 +14581,30 @@
       <c r="T270" s="3"/>
       <c r="U270" s="3"/>
       <c r="V270" s="3"/>
-    </row>
-    <row r="271" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W270" s="3"/>
+      <c r="X270" s="3"/>
+      <c r="Y270" s="3"/>
+      <c r="Z270" s="3"/>
+      <c r="AA270" s="3"/>
+      <c r="AB270" s="3"/>
+      <c r="AC270" s="3"/>
+      <c r="AD270" s="3"/>
+      <c r="AE270" s="3"/>
+      <c r="AF270" s="3"/>
+      <c r="AG270" s="3"/>
+      <c r="AH270" s="3"/>
+      <c r="AI270" s="3"/>
+      <c r="AJ270" s="3"/>
+      <c r="AK270" s="3"/>
+      <c r="AL270" s="3"/>
+      <c r="AM270" s="3"/>
+      <c r="AN270" s="3"/>
+      <c r="AO270" s="3"/>
+      <c r="AP270" s="3"/>
+      <c r="AQ270" s="3"/>
+      <c r="AR270" s="3"/>
+    </row>
+    <row r="271" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
       <c r="E271" s="3"/>
@@ -9380,8 +14625,30 @@
       <c r="T271" s="3"/>
       <c r="U271" s="3"/>
       <c r="V271" s="3"/>
-    </row>
-    <row r="272" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W271" s="3"/>
+      <c r="X271" s="3"/>
+      <c r="Y271" s="3"/>
+      <c r="Z271" s="3"/>
+      <c r="AA271" s="3"/>
+      <c r="AB271" s="3"/>
+      <c r="AC271" s="3"/>
+      <c r="AD271" s="3"/>
+      <c r="AE271" s="3"/>
+      <c r="AF271" s="3"/>
+      <c r="AG271" s="3"/>
+      <c r="AH271" s="3"/>
+      <c r="AI271" s="3"/>
+      <c r="AJ271" s="3"/>
+      <c r="AK271" s="3"/>
+      <c r="AL271" s="3"/>
+      <c r="AM271" s="3"/>
+      <c r="AN271" s="3"/>
+      <c r="AO271" s="3"/>
+      <c r="AP271" s="3"/>
+      <c r="AQ271" s="3"/>
+      <c r="AR271" s="3"/>
+    </row>
+    <row r="272" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C272" s="3"/>
       <c r="D272" s="3"/>
       <c r="E272" s="3"/>
@@ -9402,8 +14669,30 @@
       <c r="T272" s="3"/>
       <c r="U272" s="3"/>
       <c r="V272" s="3"/>
-    </row>
-    <row r="273" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W272" s="3"/>
+      <c r="X272" s="3"/>
+      <c r="Y272" s="3"/>
+      <c r="Z272" s="3"/>
+      <c r="AA272" s="3"/>
+      <c r="AB272" s="3"/>
+      <c r="AC272" s="3"/>
+      <c r="AD272" s="3"/>
+      <c r="AE272" s="3"/>
+      <c r="AF272" s="3"/>
+      <c r="AG272" s="3"/>
+      <c r="AH272" s="3"/>
+      <c r="AI272" s="3"/>
+      <c r="AJ272" s="3"/>
+      <c r="AK272" s="3"/>
+      <c r="AL272" s="3"/>
+      <c r="AM272" s="3"/>
+      <c r="AN272" s="3"/>
+      <c r="AO272" s="3"/>
+      <c r="AP272" s="3"/>
+      <c r="AQ272" s="3"/>
+      <c r="AR272" s="3"/>
+    </row>
+    <row r="273" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C273" s="3"/>
       <c r="D273" s="3"/>
       <c r="E273" s="3"/>
@@ -9424,8 +14713,30 @@
       <c r="T273" s="3"/>
       <c r="U273" s="3"/>
       <c r="V273" s="3"/>
-    </row>
-    <row r="274" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W273" s="3"/>
+      <c r="X273" s="3"/>
+      <c r="Y273" s="3"/>
+      <c r="Z273" s="3"/>
+      <c r="AA273" s="3"/>
+      <c r="AB273" s="3"/>
+      <c r="AC273" s="3"/>
+      <c r="AD273" s="3"/>
+      <c r="AE273" s="3"/>
+      <c r="AF273" s="3"/>
+      <c r="AG273" s="3"/>
+      <c r="AH273" s="3"/>
+      <c r="AI273" s="3"/>
+      <c r="AJ273" s="3"/>
+      <c r="AK273" s="3"/>
+      <c r="AL273" s="3"/>
+      <c r="AM273" s="3"/>
+      <c r="AN273" s="3"/>
+      <c r="AO273" s="3"/>
+      <c r="AP273" s="3"/>
+      <c r="AQ273" s="3"/>
+      <c r="AR273" s="3"/>
+    </row>
+    <row r="274" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
       <c r="E274" s="3"/>
@@ -9446,8 +14757,30 @@
       <c r="T274" s="3"/>
       <c r="U274" s="3"/>
       <c r="V274" s="3"/>
-    </row>
-    <row r="275" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W274" s="3"/>
+      <c r="X274" s="3"/>
+      <c r="Y274" s="3"/>
+      <c r="Z274" s="3"/>
+      <c r="AA274" s="3"/>
+      <c r="AB274" s="3"/>
+      <c r="AC274" s="3"/>
+      <c r="AD274" s="3"/>
+      <c r="AE274" s="3"/>
+      <c r="AF274" s="3"/>
+      <c r="AG274" s="3"/>
+      <c r="AH274" s="3"/>
+      <c r="AI274" s="3"/>
+      <c r="AJ274" s="3"/>
+      <c r="AK274" s="3"/>
+      <c r="AL274" s="3"/>
+      <c r="AM274" s="3"/>
+      <c r="AN274" s="3"/>
+      <c r="AO274" s="3"/>
+      <c r="AP274" s="3"/>
+      <c r="AQ274" s="3"/>
+      <c r="AR274" s="3"/>
+    </row>
+    <row r="275" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="3"/>
@@ -9468,8 +14801,30 @@
       <c r="T275" s="3"/>
       <c r="U275" s="3"/>
       <c r="V275" s="3"/>
-    </row>
-    <row r="276" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W275" s="3"/>
+      <c r="X275" s="3"/>
+      <c r="Y275" s="3"/>
+      <c r="Z275" s="3"/>
+      <c r="AA275" s="3"/>
+      <c r="AB275" s="3"/>
+      <c r="AC275" s="3"/>
+      <c r="AD275" s="3"/>
+      <c r="AE275" s="3"/>
+      <c r="AF275" s="3"/>
+      <c r="AG275" s="3"/>
+      <c r="AH275" s="3"/>
+      <c r="AI275" s="3"/>
+      <c r="AJ275" s="3"/>
+      <c r="AK275" s="3"/>
+      <c r="AL275" s="3"/>
+      <c r="AM275" s="3"/>
+      <c r="AN275" s="3"/>
+      <c r="AO275" s="3"/>
+      <c r="AP275" s="3"/>
+      <c r="AQ275" s="3"/>
+      <c r="AR275" s="3"/>
+    </row>
+    <row r="276" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
       <c r="E276" s="3"/>
@@ -9490,8 +14845,30 @@
       <c r="T276" s="3"/>
       <c r="U276" s="3"/>
       <c r="V276" s="3"/>
-    </row>
-    <row r="277" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W276" s="3"/>
+      <c r="X276" s="3"/>
+      <c r="Y276" s="3"/>
+      <c r="Z276" s="3"/>
+      <c r="AA276" s="3"/>
+      <c r="AB276" s="3"/>
+      <c r="AC276" s="3"/>
+      <c r="AD276" s="3"/>
+      <c r="AE276" s="3"/>
+      <c r="AF276" s="3"/>
+      <c r="AG276" s="3"/>
+      <c r="AH276" s="3"/>
+      <c r="AI276" s="3"/>
+      <c r="AJ276" s="3"/>
+      <c r="AK276" s="3"/>
+      <c r="AL276" s="3"/>
+      <c r="AM276" s="3"/>
+      <c r="AN276" s="3"/>
+      <c r="AO276" s="3"/>
+      <c r="AP276" s="3"/>
+      <c r="AQ276" s="3"/>
+      <c r="AR276" s="3"/>
+    </row>
+    <row r="277" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
       <c r="E277" s="3"/>
@@ -9512,8 +14889,30 @@
       <c r="T277" s="3"/>
       <c r="U277" s="3"/>
       <c r="V277" s="3"/>
-    </row>
-    <row r="278" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W277" s="3"/>
+      <c r="X277" s="3"/>
+      <c r="Y277" s="3"/>
+      <c r="Z277" s="3"/>
+      <c r="AA277" s="3"/>
+      <c r="AB277" s="3"/>
+      <c r="AC277" s="3"/>
+      <c r="AD277" s="3"/>
+      <c r="AE277" s="3"/>
+      <c r="AF277" s="3"/>
+      <c r="AG277" s="3"/>
+      <c r="AH277" s="3"/>
+      <c r="AI277" s="3"/>
+      <c r="AJ277" s="3"/>
+      <c r="AK277" s="3"/>
+      <c r="AL277" s="3"/>
+      <c r="AM277" s="3"/>
+      <c r="AN277" s="3"/>
+      <c r="AO277" s="3"/>
+      <c r="AP277" s="3"/>
+      <c r="AQ277" s="3"/>
+      <c r="AR277" s="3"/>
+    </row>
+    <row r="278" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="3"/>
@@ -9534,8 +14933,30 @@
       <c r="T278" s="3"/>
       <c r="U278" s="3"/>
       <c r="V278" s="3"/>
-    </row>
-    <row r="279" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W278" s="3"/>
+      <c r="X278" s="3"/>
+      <c r="Y278" s="3"/>
+      <c r="Z278" s="3"/>
+      <c r="AA278" s="3"/>
+      <c r="AB278" s="3"/>
+      <c r="AC278" s="3"/>
+      <c r="AD278" s="3"/>
+      <c r="AE278" s="3"/>
+      <c r="AF278" s="3"/>
+      <c r="AG278" s="3"/>
+      <c r="AH278" s="3"/>
+      <c r="AI278" s="3"/>
+      <c r="AJ278" s="3"/>
+      <c r="AK278" s="3"/>
+      <c r="AL278" s="3"/>
+      <c r="AM278" s="3"/>
+      <c r="AN278" s="3"/>
+      <c r="AO278" s="3"/>
+      <c r="AP278" s="3"/>
+      <c r="AQ278" s="3"/>
+      <c r="AR278" s="3"/>
+    </row>
+    <row r="279" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
       <c r="E279" s="3"/>
@@ -9556,8 +14977,30 @@
       <c r="T279" s="3"/>
       <c r="U279" s="3"/>
       <c r="V279" s="3"/>
-    </row>
-    <row r="280" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W279" s="3"/>
+      <c r="X279" s="3"/>
+      <c r="Y279" s="3"/>
+      <c r="Z279" s="3"/>
+      <c r="AA279" s="3"/>
+      <c r="AB279" s="3"/>
+      <c r="AC279" s="3"/>
+      <c r="AD279" s="3"/>
+      <c r="AE279" s="3"/>
+      <c r="AF279" s="3"/>
+      <c r="AG279" s="3"/>
+      <c r="AH279" s="3"/>
+      <c r="AI279" s="3"/>
+      <c r="AJ279" s="3"/>
+      <c r="AK279" s="3"/>
+      <c r="AL279" s="3"/>
+      <c r="AM279" s="3"/>
+      <c r="AN279" s="3"/>
+      <c r="AO279" s="3"/>
+      <c r="AP279" s="3"/>
+      <c r="AQ279" s="3"/>
+      <c r="AR279" s="3"/>
+    </row>
+    <row r="280" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
       <c r="E280" s="3"/>
@@ -9578,8 +15021,30 @@
       <c r="T280" s="3"/>
       <c r="U280" s="3"/>
       <c r="V280" s="3"/>
-    </row>
-    <row r="281" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W280" s="3"/>
+      <c r="X280" s="3"/>
+      <c r="Y280" s="3"/>
+      <c r="Z280" s="3"/>
+      <c r="AA280" s="3"/>
+      <c r="AB280" s="3"/>
+      <c r="AC280" s="3"/>
+      <c r="AD280" s="3"/>
+      <c r="AE280" s="3"/>
+      <c r="AF280" s="3"/>
+      <c r="AG280" s="3"/>
+      <c r="AH280" s="3"/>
+      <c r="AI280" s="3"/>
+      <c r="AJ280" s="3"/>
+      <c r="AK280" s="3"/>
+      <c r="AL280" s="3"/>
+      <c r="AM280" s="3"/>
+      <c r="AN280" s="3"/>
+      <c r="AO280" s="3"/>
+      <c r="AP280" s="3"/>
+      <c r="AQ280" s="3"/>
+      <c r="AR280" s="3"/>
+    </row>
+    <row r="281" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
       <c r="E281" s="3"/>
@@ -9600,8 +15065,30 @@
       <c r="T281" s="3"/>
       <c r="U281" s="3"/>
       <c r="V281" s="3"/>
-    </row>
-    <row r="282" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W281" s="3"/>
+      <c r="X281" s="3"/>
+      <c r="Y281" s="3"/>
+      <c r="Z281" s="3"/>
+      <c r="AA281" s="3"/>
+      <c r="AB281" s="3"/>
+      <c r="AC281" s="3"/>
+      <c r="AD281" s="3"/>
+      <c r="AE281" s="3"/>
+      <c r="AF281" s="3"/>
+      <c r="AG281" s="3"/>
+      <c r="AH281" s="3"/>
+      <c r="AI281" s="3"/>
+      <c r="AJ281" s="3"/>
+      <c r="AK281" s="3"/>
+      <c r="AL281" s="3"/>
+      <c r="AM281" s="3"/>
+      <c r="AN281" s="3"/>
+      <c r="AO281" s="3"/>
+      <c r="AP281" s="3"/>
+      <c r="AQ281" s="3"/>
+      <c r="AR281" s="3"/>
+    </row>
+    <row r="282" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
       <c r="E282" s="3"/>
@@ -9622,8 +15109,30 @@
       <c r="T282" s="3"/>
       <c r="U282" s="3"/>
       <c r="V282" s="3"/>
-    </row>
-    <row r="283" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W282" s="3"/>
+      <c r="X282" s="3"/>
+      <c r="Y282" s="3"/>
+      <c r="Z282" s="3"/>
+      <c r="AA282" s="3"/>
+      <c r="AB282" s="3"/>
+      <c r="AC282" s="3"/>
+      <c r="AD282" s="3"/>
+      <c r="AE282" s="3"/>
+      <c r="AF282" s="3"/>
+      <c r="AG282" s="3"/>
+      <c r="AH282" s="3"/>
+      <c r="AI282" s="3"/>
+      <c r="AJ282" s="3"/>
+      <c r="AK282" s="3"/>
+      <c r="AL282" s="3"/>
+      <c r="AM282" s="3"/>
+      <c r="AN282" s="3"/>
+      <c r="AO282" s="3"/>
+      <c r="AP282" s="3"/>
+      <c r="AQ282" s="3"/>
+      <c r="AR282" s="3"/>
+    </row>
+    <row r="283" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
       <c r="E283" s="3"/>
@@ -9644,8 +15153,30 @@
       <c r="T283" s="3"/>
       <c r="U283" s="3"/>
       <c r="V283" s="3"/>
-    </row>
-    <row r="284" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W283" s="3"/>
+      <c r="X283" s="3"/>
+      <c r="Y283" s="3"/>
+      <c r="Z283" s="3"/>
+      <c r="AA283" s="3"/>
+      <c r="AB283" s="3"/>
+      <c r="AC283" s="3"/>
+      <c r="AD283" s="3"/>
+      <c r="AE283" s="3"/>
+      <c r="AF283" s="3"/>
+      <c r="AG283" s="3"/>
+      <c r="AH283" s="3"/>
+      <c r="AI283" s="3"/>
+      <c r="AJ283" s="3"/>
+      <c r="AK283" s="3"/>
+      <c r="AL283" s="3"/>
+      <c r="AM283" s="3"/>
+      <c r="AN283" s="3"/>
+      <c r="AO283" s="3"/>
+      <c r="AP283" s="3"/>
+      <c r="AQ283" s="3"/>
+      <c r="AR283" s="3"/>
+    </row>
+    <row r="284" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="3"/>
@@ -9666,8 +15197,30 @@
       <c r="T284" s="3"/>
       <c r="U284" s="3"/>
       <c r="V284" s="3"/>
-    </row>
-    <row r="285" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W284" s="3"/>
+      <c r="X284" s="3"/>
+      <c r="Y284" s="3"/>
+      <c r="Z284" s="3"/>
+      <c r="AA284" s="3"/>
+      <c r="AB284" s="3"/>
+      <c r="AC284" s="3"/>
+      <c r="AD284" s="3"/>
+      <c r="AE284" s="3"/>
+      <c r="AF284" s="3"/>
+      <c r="AG284" s="3"/>
+      <c r="AH284" s="3"/>
+      <c r="AI284" s="3"/>
+      <c r="AJ284" s="3"/>
+      <c r="AK284" s="3"/>
+      <c r="AL284" s="3"/>
+      <c r="AM284" s="3"/>
+      <c r="AN284" s="3"/>
+      <c r="AO284" s="3"/>
+      <c r="AP284" s="3"/>
+      <c r="AQ284" s="3"/>
+      <c r="AR284" s="3"/>
+    </row>
+    <row r="285" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C285" s="3"/>
       <c r="D285" s="3"/>
       <c r="E285" s="3"/>
@@ -9688,8 +15241,30 @@
       <c r="T285" s="3"/>
       <c r="U285" s="3"/>
       <c r="V285" s="3"/>
-    </row>
-    <row r="286" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W285" s="3"/>
+      <c r="X285" s="3"/>
+      <c r="Y285" s="3"/>
+      <c r="Z285" s="3"/>
+      <c r="AA285" s="3"/>
+      <c r="AB285" s="3"/>
+      <c r="AC285" s="3"/>
+      <c r="AD285" s="3"/>
+      <c r="AE285" s="3"/>
+      <c r="AF285" s="3"/>
+      <c r="AG285" s="3"/>
+      <c r="AH285" s="3"/>
+      <c r="AI285" s="3"/>
+      <c r="AJ285" s="3"/>
+      <c r="AK285" s="3"/>
+      <c r="AL285" s="3"/>
+      <c r="AM285" s="3"/>
+      <c r="AN285" s="3"/>
+      <c r="AO285" s="3"/>
+      <c r="AP285" s="3"/>
+      <c r="AQ285" s="3"/>
+      <c r="AR285" s="3"/>
+    </row>
+    <row r="286" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
       <c r="E286" s="3"/>
@@ -9710,8 +15285,30 @@
       <c r="T286" s="3"/>
       <c r="U286" s="3"/>
       <c r="V286" s="3"/>
-    </row>
-    <row r="287" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W286" s="3"/>
+      <c r="X286" s="3"/>
+      <c r="Y286" s="3"/>
+      <c r="Z286" s="3"/>
+      <c r="AA286" s="3"/>
+      <c r="AB286" s="3"/>
+      <c r="AC286" s="3"/>
+      <c r="AD286" s="3"/>
+      <c r="AE286" s="3"/>
+      <c r="AF286" s="3"/>
+      <c r="AG286" s="3"/>
+      <c r="AH286" s="3"/>
+      <c r="AI286" s="3"/>
+      <c r="AJ286" s="3"/>
+      <c r="AK286" s="3"/>
+      <c r="AL286" s="3"/>
+      <c r="AM286" s="3"/>
+      <c r="AN286" s="3"/>
+      <c r="AO286" s="3"/>
+      <c r="AP286" s="3"/>
+      <c r="AQ286" s="3"/>
+      <c r="AR286" s="3"/>
+    </row>
+    <row r="287" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C287" s="3"/>
       <c r="D287" s="3"/>
       <c r="E287" s="3"/>
@@ -9732,8 +15329,30 @@
       <c r="T287" s="3"/>
       <c r="U287" s="3"/>
       <c r="V287" s="3"/>
-    </row>
-    <row r="288" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W287" s="3"/>
+      <c r="X287" s="3"/>
+      <c r="Y287" s="3"/>
+      <c r="Z287" s="3"/>
+      <c r="AA287" s="3"/>
+      <c r="AB287" s="3"/>
+      <c r="AC287" s="3"/>
+      <c r="AD287" s="3"/>
+      <c r="AE287" s="3"/>
+      <c r="AF287" s="3"/>
+      <c r="AG287" s="3"/>
+      <c r="AH287" s="3"/>
+      <c r="AI287" s="3"/>
+      <c r="AJ287" s="3"/>
+      <c r="AK287" s="3"/>
+      <c r="AL287" s="3"/>
+      <c r="AM287" s="3"/>
+      <c r="AN287" s="3"/>
+      <c r="AO287" s="3"/>
+      <c r="AP287" s="3"/>
+      <c r="AQ287" s="3"/>
+      <c r="AR287" s="3"/>
+    </row>
+    <row r="288" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C288" s="3"/>
       <c r="D288" s="3"/>
       <c r="E288" s="3"/>
@@ -9754,8 +15373,30 @@
       <c r="T288" s="3"/>
       <c r="U288" s="3"/>
       <c r="V288" s="3"/>
-    </row>
-    <row r="289" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W288" s="3"/>
+      <c r="X288" s="3"/>
+      <c r="Y288" s="3"/>
+      <c r="Z288" s="3"/>
+      <c r="AA288" s="3"/>
+      <c r="AB288" s="3"/>
+      <c r="AC288" s="3"/>
+      <c r="AD288" s="3"/>
+      <c r="AE288" s="3"/>
+      <c r="AF288" s="3"/>
+      <c r="AG288" s="3"/>
+      <c r="AH288" s="3"/>
+      <c r="AI288" s="3"/>
+      <c r="AJ288" s="3"/>
+      <c r="AK288" s="3"/>
+      <c r="AL288" s="3"/>
+      <c r="AM288" s="3"/>
+      <c r="AN288" s="3"/>
+      <c r="AO288" s="3"/>
+      <c r="AP288" s="3"/>
+      <c r="AQ288" s="3"/>
+      <c r="AR288" s="3"/>
+    </row>
+    <row r="289" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
       <c r="E289" s="3"/>
@@ -9776,8 +15417,30 @@
       <c r="T289" s="3"/>
       <c r="U289" s="3"/>
       <c r="V289" s="3"/>
-    </row>
-    <row r="290" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W289" s="3"/>
+      <c r="X289" s="3"/>
+      <c r="Y289" s="3"/>
+      <c r="Z289" s="3"/>
+      <c r="AA289" s="3"/>
+      <c r="AB289" s="3"/>
+      <c r="AC289" s="3"/>
+      <c r="AD289" s="3"/>
+      <c r="AE289" s="3"/>
+      <c r="AF289" s="3"/>
+      <c r="AG289" s="3"/>
+      <c r="AH289" s="3"/>
+      <c r="AI289" s="3"/>
+      <c r="AJ289" s="3"/>
+      <c r="AK289" s="3"/>
+      <c r="AL289" s="3"/>
+      <c r="AM289" s="3"/>
+      <c r="AN289" s="3"/>
+      <c r="AO289" s="3"/>
+      <c r="AP289" s="3"/>
+      <c r="AQ289" s="3"/>
+      <c r="AR289" s="3"/>
+    </row>
+    <row r="290" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
       <c r="E290" s="3"/>
@@ -9798,8 +15461,30 @@
       <c r="T290" s="3"/>
       <c r="U290" s="3"/>
       <c r="V290" s="3"/>
-    </row>
-    <row r="291" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W290" s="3"/>
+      <c r="X290" s="3"/>
+      <c r="Y290" s="3"/>
+      <c r="Z290" s="3"/>
+      <c r="AA290" s="3"/>
+      <c r="AB290" s="3"/>
+      <c r="AC290" s="3"/>
+      <c r="AD290" s="3"/>
+      <c r="AE290" s="3"/>
+      <c r="AF290" s="3"/>
+      <c r="AG290" s="3"/>
+      <c r="AH290" s="3"/>
+      <c r="AI290" s="3"/>
+      <c r="AJ290" s="3"/>
+      <c r="AK290" s="3"/>
+      <c r="AL290" s="3"/>
+      <c r="AM290" s="3"/>
+      <c r="AN290" s="3"/>
+      <c r="AO290" s="3"/>
+      <c r="AP290" s="3"/>
+      <c r="AQ290" s="3"/>
+      <c r="AR290" s="3"/>
+    </row>
+    <row r="291" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
       <c r="E291" s="3"/>
@@ -9820,8 +15505,30 @@
       <c r="T291" s="3"/>
       <c r="U291" s="3"/>
       <c r="V291" s="3"/>
-    </row>
-    <row r="292" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W291" s="3"/>
+      <c r="X291" s="3"/>
+      <c r="Y291" s="3"/>
+      <c r="Z291" s="3"/>
+      <c r="AA291" s="3"/>
+      <c r="AB291" s="3"/>
+      <c r="AC291" s="3"/>
+      <c r="AD291" s="3"/>
+      <c r="AE291" s="3"/>
+      <c r="AF291" s="3"/>
+      <c r="AG291" s="3"/>
+      <c r="AH291" s="3"/>
+      <c r="AI291" s="3"/>
+      <c r="AJ291" s="3"/>
+      <c r="AK291" s="3"/>
+      <c r="AL291" s="3"/>
+      <c r="AM291" s="3"/>
+      <c r="AN291" s="3"/>
+      <c r="AO291" s="3"/>
+      <c r="AP291" s="3"/>
+      <c r="AQ291" s="3"/>
+      <c r="AR291" s="3"/>
+    </row>
+    <row r="292" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
       <c r="E292" s="3"/>
@@ -9842,8 +15549,30 @@
       <c r="T292" s="3"/>
       <c r="U292" s="3"/>
       <c r="V292" s="3"/>
-    </row>
-    <row r="293" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W292" s="3"/>
+      <c r="X292" s="3"/>
+      <c r="Y292" s="3"/>
+      <c r="Z292" s="3"/>
+      <c r="AA292" s="3"/>
+      <c r="AB292" s="3"/>
+      <c r="AC292" s="3"/>
+      <c r="AD292" s="3"/>
+      <c r="AE292" s="3"/>
+      <c r="AF292" s="3"/>
+      <c r="AG292" s="3"/>
+      <c r="AH292" s="3"/>
+      <c r="AI292" s="3"/>
+      <c r="AJ292" s="3"/>
+      <c r="AK292" s="3"/>
+      <c r="AL292" s="3"/>
+      <c r="AM292" s="3"/>
+      <c r="AN292" s="3"/>
+      <c r="AO292" s="3"/>
+      <c r="AP292" s="3"/>
+      <c r="AQ292" s="3"/>
+      <c r="AR292" s="3"/>
+    </row>
+    <row r="293" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
       <c r="E293" s="3"/>
@@ -9864,8 +15593,30 @@
       <c r="T293" s="3"/>
       <c r="U293" s="3"/>
       <c r="V293" s="3"/>
-    </row>
-    <row r="294" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W293" s="3"/>
+      <c r="X293" s="3"/>
+      <c r="Y293" s="3"/>
+      <c r="Z293" s="3"/>
+      <c r="AA293" s="3"/>
+      <c r="AB293" s="3"/>
+      <c r="AC293" s="3"/>
+      <c r="AD293" s="3"/>
+      <c r="AE293" s="3"/>
+      <c r="AF293" s="3"/>
+      <c r="AG293" s="3"/>
+      <c r="AH293" s="3"/>
+      <c r="AI293" s="3"/>
+      <c r="AJ293" s="3"/>
+      <c r="AK293" s="3"/>
+      <c r="AL293" s="3"/>
+      <c r="AM293" s="3"/>
+      <c r="AN293" s="3"/>
+      <c r="AO293" s="3"/>
+      <c r="AP293" s="3"/>
+      <c r="AQ293" s="3"/>
+      <c r="AR293" s="3"/>
+    </row>
+    <row r="294" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
       <c r="E294" s="3"/>
@@ -9886,8 +15637,30 @@
       <c r="T294" s="3"/>
       <c r="U294" s="3"/>
       <c r="V294" s="3"/>
-    </row>
-    <row r="295" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W294" s="3"/>
+      <c r="X294" s="3"/>
+      <c r="Y294" s="3"/>
+      <c r="Z294" s="3"/>
+      <c r="AA294" s="3"/>
+      <c r="AB294" s="3"/>
+      <c r="AC294" s="3"/>
+      <c r="AD294" s="3"/>
+      <c r="AE294" s="3"/>
+      <c r="AF294" s="3"/>
+      <c r="AG294" s="3"/>
+      <c r="AH294" s="3"/>
+      <c r="AI294" s="3"/>
+      <c r="AJ294" s="3"/>
+      <c r="AK294" s="3"/>
+      <c r="AL294" s="3"/>
+      <c r="AM294" s="3"/>
+      <c r="AN294" s="3"/>
+      <c r="AO294" s="3"/>
+      <c r="AP294" s="3"/>
+      <c r="AQ294" s="3"/>
+      <c r="AR294" s="3"/>
+    </row>
+    <row r="295" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
       <c r="E295" s="3"/>
@@ -9908,8 +15681,30 @@
       <c r="T295" s="3"/>
       <c r="U295" s="3"/>
       <c r="V295" s="3"/>
-    </row>
-    <row r="296" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W295" s="3"/>
+      <c r="X295" s="3"/>
+      <c r="Y295" s="3"/>
+      <c r="Z295" s="3"/>
+      <c r="AA295" s="3"/>
+      <c r="AB295" s="3"/>
+      <c r="AC295" s="3"/>
+      <c r="AD295" s="3"/>
+      <c r="AE295" s="3"/>
+      <c r="AF295" s="3"/>
+      <c r="AG295" s="3"/>
+      <c r="AH295" s="3"/>
+      <c r="AI295" s="3"/>
+      <c r="AJ295" s="3"/>
+      <c r="AK295" s="3"/>
+      <c r="AL295" s="3"/>
+      <c r="AM295" s="3"/>
+      <c r="AN295" s="3"/>
+      <c r="AO295" s="3"/>
+      <c r="AP295" s="3"/>
+      <c r="AQ295" s="3"/>
+      <c r="AR295" s="3"/>
+    </row>
+    <row r="296" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
       <c r="E296" s="3"/>
@@ -9930,8 +15725,30 @@
       <c r="T296" s="3"/>
       <c r="U296" s="3"/>
       <c r="V296" s="3"/>
-    </row>
-    <row r="297" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W296" s="3"/>
+      <c r="X296" s="3"/>
+      <c r="Y296" s="3"/>
+      <c r="Z296" s="3"/>
+      <c r="AA296" s="3"/>
+      <c r="AB296" s="3"/>
+      <c r="AC296" s="3"/>
+      <c r="AD296" s="3"/>
+      <c r="AE296" s="3"/>
+      <c r="AF296" s="3"/>
+      <c r="AG296" s="3"/>
+      <c r="AH296" s="3"/>
+      <c r="AI296" s="3"/>
+      <c r="AJ296" s="3"/>
+      <c r="AK296" s="3"/>
+      <c r="AL296" s="3"/>
+      <c r="AM296" s="3"/>
+      <c r="AN296" s="3"/>
+      <c r="AO296" s="3"/>
+      <c r="AP296" s="3"/>
+      <c r="AQ296" s="3"/>
+      <c r="AR296" s="3"/>
+    </row>
+    <row r="297" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
       <c r="E297" s="3"/>
@@ -9952,8 +15769,30 @@
       <c r="T297" s="3"/>
       <c r="U297" s="3"/>
       <c r="V297" s="3"/>
-    </row>
-    <row r="298" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W297" s="3"/>
+      <c r="X297" s="3"/>
+      <c r="Y297" s="3"/>
+      <c r="Z297" s="3"/>
+      <c r="AA297" s="3"/>
+      <c r="AB297" s="3"/>
+      <c r="AC297" s="3"/>
+      <c r="AD297" s="3"/>
+      <c r="AE297" s="3"/>
+      <c r="AF297" s="3"/>
+      <c r="AG297" s="3"/>
+      <c r="AH297" s="3"/>
+      <c r="AI297" s="3"/>
+      <c r="AJ297" s="3"/>
+      <c r="AK297" s="3"/>
+      <c r="AL297" s="3"/>
+      <c r="AM297" s="3"/>
+      <c r="AN297" s="3"/>
+      <c r="AO297" s="3"/>
+      <c r="AP297" s="3"/>
+      <c r="AQ297" s="3"/>
+      <c r="AR297" s="3"/>
+    </row>
+    <row r="298" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
       <c r="E298" s="3"/>
@@ -9974,8 +15813,30 @@
       <c r="T298" s="3"/>
       <c r="U298" s="3"/>
       <c r="V298" s="3"/>
-    </row>
-    <row r="299" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W298" s="3"/>
+      <c r="X298" s="3"/>
+      <c r="Y298" s="3"/>
+      <c r="Z298" s="3"/>
+      <c r="AA298" s="3"/>
+      <c r="AB298" s="3"/>
+      <c r="AC298" s="3"/>
+      <c r="AD298" s="3"/>
+      <c r="AE298" s="3"/>
+      <c r="AF298" s="3"/>
+      <c r="AG298" s="3"/>
+      <c r="AH298" s="3"/>
+      <c r="AI298" s="3"/>
+      <c r="AJ298" s="3"/>
+      <c r="AK298" s="3"/>
+      <c r="AL298" s="3"/>
+      <c r="AM298" s="3"/>
+      <c r="AN298" s="3"/>
+      <c r="AO298" s="3"/>
+      <c r="AP298" s="3"/>
+      <c r="AQ298" s="3"/>
+      <c r="AR298" s="3"/>
+    </row>
+    <row r="299" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
       <c r="E299" s="3"/>
@@ -9996,8 +15857,30 @@
       <c r="T299" s="3"/>
       <c r="U299" s="3"/>
       <c r="V299" s="3"/>
-    </row>
-    <row r="300" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W299" s="3"/>
+      <c r="X299" s="3"/>
+      <c r="Y299" s="3"/>
+      <c r="Z299" s="3"/>
+      <c r="AA299" s="3"/>
+      <c r="AB299" s="3"/>
+      <c r="AC299" s="3"/>
+      <c r="AD299" s="3"/>
+      <c r="AE299" s="3"/>
+      <c r="AF299" s="3"/>
+      <c r="AG299" s="3"/>
+      <c r="AH299" s="3"/>
+      <c r="AI299" s="3"/>
+      <c r="AJ299" s="3"/>
+      <c r="AK299" s="3"/>
+      <c r="AL299" s="3"/>
+      <c r="AM299" s="3"/>
+      <c r="AN299" s="3"/>
+      <c r="AO299" s="3"/>
+      <c r="AP299" s="3"/>
+      <c r="AQ299" s="3"/>
+      <c r="AR299" s="3"/>
+    </row>
+    <row r="300" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
       <c r="E300" s="3"/>
@@ -10019,7 +15902,7 @@
       <c r="U300" s="3"/>
       <c r="V300" s="3"/>
     </row>
-    <row r="301" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="301" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
       <c r="E301" s="3"/>
@@ -10041,7 +15924,7 @@
       <c r="U301" s="3"/>
       <c r="V301" s="3"/>
     </row>
-    <row r="302" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="302" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C302" s="3"/>
       <c r="D302" s="3"/>
       <c r="E302" s="3"/>
@@ -10063,7 +15946,7 @@
       <c r="U302" s="3"/>
       <c r="V302" s="3"/>
     </row>
-    <row r="303" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="303" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C303" s="3"/>
       <c r="D303" s="3"/>
       <c r="E303" s="3"/>
@@ -10085,7 +15968,7 @@
       <c r="U303" s="3"/>
       <c r="V303" s="3"/>
     </row>
-    <row r="304" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="304" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
       <c r="E304" s="3"/>

--- a/LULU.xlsx
+++ b/LULU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4958FF7-1954-4A7B-85E6-42D8FAD05E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D1959A-AF15-460B-B4C1-3B42379720A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{307BA413-EEF9-4958-8DCC-E913E47A6543}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{307BA413-EEF9-4958-8DCC-E913E47A6543}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -967,7 +967,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="16">
-        <v>156.36000000000001</v>
+        <v>127.35</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -998,7 +998,7 @@
       </c>
       <c r="I4" s="7">
         <f>I3*I2</f>
-        <v>17275.07043756</v>
+        <v>14069.968151849998</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="I7" s="7">
         <f>I4+I6-I5</f>
-        <v>15467.868437560001</v>
+        <v>12262.766151849999</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="I9" s="8">
         <f>+I4/Model!V28</f>
-        <v>9.51995928480736</v>
+        <v>7.7536890184204221</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="I10" s="8">
         <f>+I7/Model!V24</f>
-        <v>6.1730801599554921</v>
+        <v>4.8939541180956825</v>
       </c>
     </row>
   </sheetData>
@@ -1548,7 +1548,7 @@
         <v>4.8326431818181819</v>
       </c>
       <c r="Q8" s="10">
-        <f t="shared" ref="Q8:W8" si="10">+Q16/Q7</f>
+        <f t="shared" ref="Q8:V8" si="10">+Q16/Q7</f>
         <v>2.3173564154786148</v>
       </c>
       <c r="R8" s="10">

--- a/LULU.xlsx
+++ b/LULU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D1959A-AF15-460B-B4C1-3B42379720A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74152F2E-5DC6-467D-8D90-AD870C885894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{307BA413-EEF9-4958-8DCC-E913E47A6543}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{307BA413-EEF9-4958-8DCC-E913E47A6543}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="124">
   <si>
     <t>SEC</t>
   </si>
@@ -418,6 +418,18 @@
   <si>
     <t>FY25</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
@@ -429,13 +441,19 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -510,33 +528,36 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -563,16 +584,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>4763</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>157163</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>42863</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>33338</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>71438</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>23813</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -587,7 +608,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8586788" y="157163"/>
+          <a:off x="9844088" y="171450"/>
           <a:ext cx="28575" cy="5210175"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -967,7 +988,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="16">
-        <v>127.35</v>
+        <v>114.34</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -975,10 +996,10 @@
         <v>27</v>
       </c>
       <c r="I3" s="3">
-        <v>110.482671</v>
-      </c>
-      <c r="J3" s="17" t="s">
-        <v>61</v>
+        <v>108.437957</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -998,7 +1019,7 @@
       </c>
       <c r="I4" s="7">
         <f>I3*I2</f>
-        <v>14069.968151849998</v>
+        <v>12398.796003380001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1017,10 +1038,10 @@
         <v>4</v>
       </c>
       <c r="I5" s="7">
-        <v>1807.202</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>61</v>
+        <v>1514.729</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -1030,8 +1051,8 @@
       <c r="I6" s="7">
         <v>0</v>
       </c>
-      <c r="J6" s="17" t="s">
-        <v>61</v>
+      <c r="J6" s="18" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1040,7 +1061,7 @@
       </c>
       <c r="I7" s="7">
         <f>I4+I6-I5</f>
-        <v>12262.766151849999</v>
+        <v>10884.067003380002</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1048,8 +1069,8 @@
         <v>62</v>
       </c>
       <c r="I9" s="8">
-        <f>+I4/Model!V28</f>
-        <v>7.7536890184204221</v>
+        <f>+I4/Model!Z28</f>
+        <v>6.8327381679539894</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1057,8 +1078,8 @@
         <v>63</v>
       </c>
       <c r="I10" s="8">
-        <f>+I7/Model!V24</f>
-        <v>4.8939541180956825</v>
+        <f>+I7/Model!Z24</f>
+        <v>4.3437283132717157</v>
       </c>
     </row>
   </sheetData>
@@ -1072,7 +1093,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10BA731A-EDB9-4887-9C65-CEC0B0F7DA3D}">
-  <dimension ref="A1:AW324"/>
+  <dimension ref="A1:BA324"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -1080,12 +1101,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>39</v>
       </c>
@@ -1122,32 +1143,44 @@
       <c r="N2" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="O2" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="P2" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q2" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="R2" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="Z2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="W2" s="17" t="s">
+      <c r="AA2" s="17" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>51</v>
       </c>
@@ -1184,37 +1217,45 @@
       <c r="M3" s="4">
         <v>470</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="P3" s="4">
+      <c r="N3" s="2">
+        <v>476</v>
+      </c>
+      <c r="O3" s="4">
+        <v>476</v>
+      </c>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="T3" s="4">
         <f>285+64</f>
         <v>349</v>
       </c>
-      <c r="Q3" s="4">
+      <c r="U3" s="4">
         <f>306+63</f>
         <v>369</v>
       </c>
-      <c r="R3" s="4">
+      <c r="V3" s="4">
         <f>315+62</f>
         <v>377</v>
       </c>
-      <c r="S3" s="4">
+      <c r="W3" s="4">
         <f>324+63</f>
         <v>387</v>
       </c>
-      <c r="T3" s="4">
+      <c r="X3" s="4">
         <v>419</v>
       </c>
-      <c r="U3" s="4">
+      <c r="Y3" s="4">
         <v>438</v>
       </c>
-      <c r="V3" s="4">
+      <c r="Z3" s="4">
         <v>462</v>
       </c>
-      <c r="W3" s="2">
+      <c r="AA3" s="2">
         <v>476</v>
       </c>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>52</v>
       </c>
@@ -1251,33 +1292,41 @@
       <c r="M4" s="4">
         <v>165</v>
       </c>
-      <c r="N4" s="4"/>
-      <c r="P4" s="4">
+      <c r="N4" s="2">
+        <v>172</v>
+      </c>
+      <c r="O4" s="4">
+        <v>173</v>
+      </c>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="T4" s="4">
         <v>22</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="U4" s="4">
         <v>38</v>
       </c>
-      <c r="R4" s="4">
+      <c r="V4" s="4">
         <v>55</v>
       </c>
-      <c r="S4" s="4">
+      <c r="W4" s="4">
         <v>86</v>
       </c>
-      <c r="T4" s="4">
+      <c r="X4" s="4">
         <v>99</v>
       </c>
-      <c r="U4" s="4">
+      <c r="Y4" s="4">
         <v>127</v>
       </c>
-      <c r="V4" s="4">
+      <c r="Z4" s="4">
         <v>151</v>
       </c>
-      <c r="W4" s="2">
+      <c r="AA4" s="2">
         <v>172</v>
       </c>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>54</v>
       </c>
@@ -1314,37 +1363,45 @@
       <c r="M5" s="4">
         <v>112</v>
       </c>
-      <c r="N5" s="4"/>
-      <c r="P5" s="4">
+      <c r="N5" s="2">
+        <v>114</v>
+      </c>
+      <c r="O5" s="4">
+        <v>117</v>
+      </c>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="T5" s="4">
         <f>29+5+7+4+3</f>
         <v>48</v>
       </c>
-      <c r="Q5" s="4">
+      <c r="U5" s="4">
         <f>31+7+7+5+4+2</f>
         <v>56</v>
       </c>
-      <c r="R5" s="4">
+      <c r="V5" s="4">
         <f>31+7+7+6+4+2</f>
         <v>57</v>
       </c>
-      <c r="S5" s="4">
+      <c r="W5" s="4">
         <f>31+12+7+6+6+2</f>
         <v>64</v>
       </c>
-      <c r="T5" s="4">
+      <c r="X5" s="4">
         <v>91</v>
       </c>
-      <c r="U5" s="4">
+      <c r="Y5" s="4">
         <v>98</v>
       </c>
-      <c r="V5" s="4">
+      <c r="Z5" s="4">
         <v>107</v>
       </c>
-      <c r="W5" s="2">
+      <c r="AA5" s="2">
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>55</v>
       </c>
@@ -1381,37 +1438,45 @@
       <c r="M6" s="4">
         <v>49</v>
       </c>
-      <c r="N6" s="4"/>
-      <c r="P6" s="4">
+      <c r="N6" s="2">
+        <v>49</v>
+      </c>
+      <c r="O6" s="4">
+        <v>50</v>
+      </c>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="T6" s="4">
         <f>12+5+1+1+1+1</f>
         <v>21</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="U6" s="4">
         <f>14+6+3+2+1+1+1</f>
         <v>28</v>
       </c>
-      <c r="R6" s="4">
+      <c r="V6" s="4">
         <f>16+7+3+1+2+1+1+1</f>
         <v>32</v>
       </c>
-      <c r="S6" s="4">
+      <c r="W6" s="4">
         <f>17+9+3+3+2+1+1+1</f>
         <v>37</v>
       </c>
-      <c r="T6" s="4">
+      <c r="X6" s="4">
         <v>46</v>
       </c>
-      <c r="U6" s="4">
+      <c r="Y6" s="4">
         <v>48</v>
       </c>
-      <c r="V6" s="4">
+      <c r="Z6" s="4">
         <v>47</v>
       </c>
-      <c r="W6" s="2">
+      <c r="AA6" s="2">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
         <v>56</v>
       </c>
@@ -1444,7 +1509,7 @@
         <v>749</v>
       </c>
       <c r="J7" s="9">
-        <f t="shared" ref="J7:M7" si="1">+SUM(J3:J6)</f>
+        <f t="shared" ref="J7:O7" si="1">+SUM(J3:J6)</f>
         <v>767</v>
       </c>
       <c r="K7" s="9">
@@ -1459,42 +1524,52 @@
         <f t="shared" si="1"/>
         <v>796</v>
       </c>
-      <c r="N7" s="9"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="9">
-        <f>+SUM(P3:P6)</f>
+      <c r="N7" s="9">
+        <f t="shared" si="1"/>
+        <v>811</v>
+      </c>
+      <c r="O7" s="9">
+        <f t="shared" si="1"/>
+        <v>816</v>
+      </c>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="9">
+        <f>+SUM(T3:T6)</f>
         <v>440</v>
       </c>
-      <c r="Q7" s="9">
-        <f t="shared" ref="Q7" si="2">+SUM(Q3:Q6)</f>
+      <c r="U7" s="9">
+        <f t="shared" ref="U7" si="2">+SUM(U3:U6)</f>
         <v>491</v>
       </c>
-      <c r="R7" s="9">
-        <f t="shared" ref="R7" si="3">+SUM(R3:R6)</f>
+      <c r="V7" s="9">
+        <f t="shared" ref="V7" si="3">+SUM(V3:V6)</f>
         <v>521</v>
       </c>
-      <c r="S7" s="9">
-        <f t="shared" ref="S7" si="4">+SUM(S3:S6)</f>
+      <c r="W7" s="9">
+        <f t="shared" ref="W7" si="4">+SUM(W3:W6)</f>
         <v>574</v>
       </c>
-      <c r="T7" s="9">
-        <f t="shared" ref="T7" si="5">+SUM(T3:T6)</f>
+      <c r="X7" s="9">
+        <f t="shared" ref="X7" si="5">+SUM(X3:X6)</f>
         <v>655</v>
       </c>
-      <c r="U7" s="9">
-        <f t="shared" ref="U7" si="6">+SUM(U3:U6)</f>
+      <c r="Y7" s="9">
+        <f t="shared" ref="Y7" si="6">+SUM(Y3:Y6)</f>
         <v>711</v>
       </c>
-      <c r="V7" s="9">
-        <f t="shared" ref="V7:W7" si="7">+SUM(V3:V6)</f>
+      <c r="Z7" s="9">
+        <f t="shared" ref="Z7:AA7" si="7">+SUM(Z3:Z6)</f>
         <v>767</v>
       </c>
-      <c r="W7" s="9">
+      <c r="AA7" s="9">
         <f t="shared" si="7"/>
         <v>811</v>
       </c>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>57</v>
       </c>
@@ -1542,41 +1617,51 @@
         <f t="shared" si="9"/>
         <v>1.3401381909547738</v>
       </c>
-      <c r="N8" s="10"/>
-      <c r="P8" s="10">
-        <f>+P16/P7</f>
+      <c r="N8" s="10">
+        <f>+N16/N7</f>
+        <v>1.7695770653514173</v>
+      </c>
+      <c r="O8" s="10">
+        <f>+O16/O7</f>
+        <v>1.4618137254901959</v>
+      </c>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="T8" s="10">
+        <f>+T16/T7</f>
         <v>4.8326431818181819</v>
       </c>
-      <c r="Q8" s="10">
-        <f t="shared" ref="Q8:V8" si="10">+Q16/Q7</f>
+      <c r="U8" s="10">
+        <f t="shared" ref="U8:Z8" si="10">+U16/U7</f>
         <v>2.3173564154786148</v>
       </c>
-      <c r="R8" s="10">
+      <c r="V8" s="10">
         <f t="shared" si="10"/>
         <v>3.1831228406909786</v>
       </c>
-      <c r="S8" s="10">
+      <c r="W8" s="10">
         <f t="shared" si="10"/>
         <v>4.9154999999999998</v>
       </c>
-      <c r="T8" s="10">
+      <c r="X8" s="10">
         <f t="shared" si="10"/>
         <v>5.5696595419847323</v>
       </c>
-      <c r="U8" s="10">
+      <c r="Y8" s="10">
         <f t="shared" si="10"/>
         <v>6.2038762306610407</v>
       </c>
-      <c r="V8" s="10">
+      <c r="Z8" s="10">
         <f t="shared" si="10"/>
         <v>6.5291681877444594</v>
       </c>
-      <c r="W8" s="10">
-        <f>+W16/W7</f>
+      <c r="AA8" s="10">
+        <f>+AA16/AA7</f>
         <v>6.2265647348951907</v>
       </c>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.2">
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -1589,15 +1674,19 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
       <c r="T9" s="4"/>
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
-    </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="4"/>
+    </row>
+    <row r="10" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
@@ -1611,7 +1700,7 @@
         <v>1732.3979999999999</v>
       </c>
       <c r="F10" s="3">
-        <f>+U10-SUM(C10:E10)</f>
+        <f>+Y10-SUM(C10:E10)</f>
         <v>2611.7380000000003</v>
       </c>
       <c r="G10" s="3">
@@ -1624,7 +1713,7 @@
         <v>1770.3820000000001</v>
       </c>
       <c r="J10" s="3">
-        <f t="shared" ref="J10:J18" si="11">+V10-SUM(G10:I10)</f>
+        <f t="shared" ref="J10:J18" si="11">+Z10-SUM(G10:I10)</f>
         <v>2794.0770000000002</v>
       </c>
       <c r="K10" s="3">
@@ -1636,40 +1725,45 @@
       <c r="M10" s="3">
         <v>1733.3820000000001</v>
       </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3">
+      <c r="N10" s="3">
+        <f>+AA10-SUM(K10:M10)</f>
+        <v>2680.8869999999997</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1621.21</v>
+      </c>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3">
         <f>2363.374+565.105</f>
         <v>2928.4789999999998</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="U10" s="3">
         <f>2854.364+649.114</f>
         <v>3503.4780000000001</v>
       </c>
-      <c r="R10" s="3">
+      <c r="V10" s="3">
         <f>3015.133+672.607</f>
         <v>3687.74</v>
       </c>
-      <c r="S10" s="3">
+      <c r="W10" s="3">
         <f>4345.687+954.219</f>
         <v>5299.9059999999999</v>
       </c>
-      <c r="T10" s="3">
+      <c r="X10" s="3">
         <v>6817.4539999999997</v>
       </c>
-      <c r="U10" s="3">
+      <c r="Y10" s="3">
         <v>7631.6469999999999</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Z10" s="3">
         <v>7928.1559999999999</v>
       </c>
-      <c r="W10" s="3">
+      <c r="AA10" s="3">
         <v>7847.0439999999999</v>
       </c>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="3"/>
       <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
@@ -1692,8 +1786,12 @@
       <c r="AU10" s="3"/>
       <c r="AV10" s="3"/>
       <c r="AW10" s="3"/>
-    </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AX10" s="3"/>
+      <c r="AY10" s="3"/>
+      <c r="AZ10" s="3"/>
+      <c r="BA10" s="3"/>
+    </row>
+    <row r="11" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>53</v>
       </c>
@@ -1707,7 +1805,7 @@
         <v>228.595</v>
       </c>
       <c r="F11" s="3">
-        <f t="shared" ref="F11:F18" si="12">+U11-SUM(C11:E11)</f>
+        <f t="shared" ref="F11:F18" si="12">+Y11-SUM(C11:E11)</f>
         <v>290.65199999999993</v>
       </c>
       <c r="G11" s="3">
@@ -1732,36 +1830,41 @@
       <c r="M11" s="3">
         <v>465.36200000000002</v>
       </c>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3">
+      <c r="N11" s="3">
+        <f t="shared" ref="N11:N27" si="13">+AA11-SUM(K11:M11)</f>
+        <v>484.33399999999983</v>
+      </c>
+      <c r="O11" s="3">
+        <v>529.803</v>
+      </c>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3">
         <v>0</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="U11" s="3">
         <v>0</v>
       </c>
-      <c r="R11" s="3">
+      <c r="V11" s="3">
         <v>0</v>
       </c>
-      <c r="S11" s="3">
+      <c r="W11" s="3">
         <v>0</v>
       </c>
-      <c r="T11" s="3">
+      <c r="X11" s="3">
         <v>576.50300000000004</v>
       </c>
-      <c r="U11" s="3">
+      <c r="Y11" s="3">
         <v>963.76</v>
       </c>
-      <c r="V11" s="3">
+      <c r="Z11" s="3">
         <v>1361.337</v>
       </c>
-      <c r="W11" s="3">
+      <c r="AA11" s="3">
         <v>1754.799</v>
       </c>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
@@ -1784,8 +1887,12 @@
       <c r="AU11" s="3"/>
       <c r="AV11" s="3"/>
       <c r="AW11" s="3"/>
-    </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AX11" s="3"/>
+      <c r="AY11" s="3"/>
+      <c r="AZ11" s="3"/>
+      <c r="BA11" s="3"/>
+    </row>
+    <row r="12" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>44</v>
       </c>
@@ -1824,36 +1931,41 @@
       <c r="M12" s="3">
         <v>367.17599999999999</v>
       </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3">
+      <c r="N12" s="3">
+        <f t="shared" si="13"/>
+        <v>475.58000000000015</v>
+      </c>
+      <c r="O12" s="3">
+        <v>320.58999999999997</v>
+      </c>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3">
         <v>359.84</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="U12" s="3">
         <v>475.81799999999998</v>
       </c>
-      <c r="R12" s="3">
+      <c r="V12" s="3">
         <v>624.13900000000001</v>
       </c>
-      <c r="S12" s="3">
+      <c r="W12" s="3">
         <v>956.71100000000001</v>
       </c>
-      <c r="T12" s="3">
+      <c r="X12" s="3">
         <v>716.56100000000004</v>
       </c>
-      <c r="U12" s="3">
+      <c r="Y12" s="3">
         <v>1023.871</v>
       </c>
-      <c r="V12" s="3">
+      <c r="Z12" s="3">
         <v>1298.633</v>
       </c>
-      <c r="W12" s="3">
+      <c r="AA12" s="3">
         <v>1500.7570000000001</v>
       </c>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
@@ -1876,8 +1988,12 @@
       <c r="AU12" s="3"/>
       <c r="AV12" s="3"/>
       <c r="AW12" s="3"/>
-    </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AX12" s="3"/>
+      <c r="AY12" s="3"/>
+      <c r="AZ12" s="3"/>
+      <c r="BA12" s="3"/>
+    </row>
+    <row r="13" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>45</v>
       </c>
@@ -1916,36 +2032,41 @@
       <c r="M13" s="3">
         <v>1644.952</v>
       </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3">
+      <c r="N13" s="3">
+        <f t="shared" si="13"/>
+        <v>2267.92</v>
+      </c>
+      <c r="O13" s="3">
+        <v>1602.9849999999999</v>
+      </c>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3">
         <v>2352.788</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="U13" s="3">
         <v>2790.9969999999998</v>
       </c>
-      <c r="R13" s="3">
+      <c r="V13" s="3">
         <v>3049.9059999999999</v>
       </c>
-      <c r="S13" s="3">
+      <c r="W13" s="3">
         <v>4171.7619999999997</v>
       </c>
-      <c r="T13" s="3">
+      <c r="X13" s="3">
         <v>5259.8029999999999</v>
       </c>
-      <c r="U13" s="3">
+      <c r="Y13" s="3">
         <v>6147.3720000000003</v>
       </c>
-      <c r="V13" s="3">
+      <c r="Z13" s="3">
         <v>6692.63</v>
       </c>
-      <c r="W13" s="3">
+      <c r="AA13" s="3">
         <v>6995.3649999999998</v>
       </c>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
@@ -1968,8 +2089,12 @@
       <c r="AU13" s="3"/>
       <c r="AV13" s="3"/>
       <c r="AW13" s="3"/>
-    </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AX13" s="3"/>
+      <c r="AY13" s="3"/>
+      <c r="AZ13" s="3"/>
+      <c r="BA13" s="3"/>
+    </row>
+    <row r="14" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>46</v>
       </c>
@@ -2008,36 +2133,41 @@
       <c r="M14" s="3">
         <v>596.24099999999999</v>
       </c>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3">
+      <c r="N14" s="3">
+        <f t="shared" si="13"/>
+        <v>901.35899999999992</v>
+      </c>
+      <c r="O14" s="3">
+        <v>581.87800000000004</v>
+      </c>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3">
         <v>694.92100000000005</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="U14" s="3">
         <v>933.76700000000005</v>
       </c>
-      <c r="R14" s="3">
+      <c r="V14" s="3">
         <v>953.18299999999999</v>
       </c>
-      <c r="S14" s="3">
+      <c r="W14" s="3">
         <v>1535.85</v>
       </c>
-      <c r="T14" s="3">
+      <c r="X14" s="3">
         <v>1956.6020000000001</v>
       </c>
-      <c r="U14" s="3">
+      <c r="Y14" s="3">
         <v>2252.7530000000002</v>
       </c>
-      <c r="V14" s="3">
+      <c r="Z14" s="3">
         <v>2558.38</v>
       </c>
-      <c r="W14" s="3">
+      <c r="AA14" s="3">
         <v>2666.9859999999999</v>
       </c>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
@@ -2060,8 +2190,12 @@
       <c r="AU14" s="3"/>
       <c r="AV14" s="3"/>
       <c r="AW14" s="3"/>
-    </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AX14" s="3"/>
+      <c r="AY14" s="3"/>
+      <c r="AZ14" s="3"/>
+      <c r="BA14" s="3"/>
+    </row>
+    <row r="15" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>47</v>
       </c>
@@ -2100,36 +2234,41 @@
       <c r="M15" s="3">
         <v>324.72699999999998</v>
       </c>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3">
+      <c r="N15" s="3">
+        <f t="shared" si="13"/>
+        <v>474.52200000000005</v>
+      </c>
+      <c r="O15" s="3">
+        <v>286.74</v>
+      </c>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3">
         <v>240.61</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="U15" s="3">
         <v>254.53200000000001</v>
       </c>
-      <c r="R15" s="3">
+      <c r="V15" s="3">
         <v>398.79</v>
       </c>
-      <c r="S15" s="3">
+      <c r="W15" s="3">
         <v>549.005</v>
       </c>
-      <c r="T15" s="3">
+      <c r="X15" s="3">
         <v>894.11300000000006</v>
       </c>
-      <c r="U15" s="3">
+      <c r="Y15" s="3">
         <v>1219.153</v>
       </c>
-      <c r="V15" s="3">
+      <c r="Z15" s="3">
         <v>1337.116</v>
       </c>
-      <c r="W15" s="3">
+      <c r="AA15" s="3">
         <v>1443.249</v>
       </c>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
@@ -2152,8 +2291,12 @@
       <c r="AU15" s="3"/>
       <c r="AV15" s="3"/>
       <c r="AW15" s="3"/>
-    </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AX15" s="3"/>
+      <c r="AY15" s="3"/>
+      <c r="AZ15" s="3"/>
+      <c r="BA15" s="3"/>
+    </row>
+    <row r="16" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>48</v>
       </c>
@@ -2192,36 +2335,41 @@
       <c r="M16" s="3">
         <v>1206.558</v>
       </c>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3">
+      <c r="N16" s="3">
+        <f t="shared" si="13"/>
+        <v>1435.1269999999995</v>
+      </c>
+      <c r="O16" s="3">
+        <v>1192.8399999999999</v>
+      </c>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3">
         <v>2126.3629999999998</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="U16" s="3">
         <v>1137.8219999999999</v>
       </c>
-      <c r="R16" s="3">
+      <c r="V16" s="3">
         <v>1658.4069999999999</v>
       </c>
-      <c r="S16" s="3">
+      <c r="W16" s="3">
         <v>2821.4969999999998</v>
       </c>
-      <c r="T16" s="3">
+      <c r="X16" s="3">
         <v>3648.127</v>
       </c>
-      <c r="U16" s="3">
+      <c r="Y16" s="3">
         <v>4410.9560000000001</v>
       </c>
-      <c r="V16" s="3">
+      <c r="Z16" s="3">
         <v>5007.8720000000003</v>
       </c>
-      <c r="W16" s="3">
+      <c r="AA16" s="3">
         <v>5049.7439999999997</v>
       </c>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
@@ -2244,8 +2392,12 @@
       <c r="AU16" s="3"/>
       <c r="AV16" s="3"/>
       <c r="AW16" s="3"/>
-    </row>
-    <row r="17" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX16" s="3"/>
+      <c r="AY16" s="3"/>
+      <c r="AZ16" s="3"/>
+      <c r="BA16" s="3"/>
+    </row>
+    <row r="17" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>49</v>
       </c>
@@ -2284,36 +2436,41 @@
       <c r="M17" s="3">
         <v>1066.75</v>
       </c>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3">
+      <c r="N17" s="3">
+        <f t="shared" si="13"/>
+        <v>1897.9639999999999</v>
+      </c>
+      <c r="O17" s="3">
+        <v>997.44200000000001</v>
+      </c>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="3">
         <v>858.85599999999999</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="U17" s="3">
         <v>2501.067</v>
       </c>
-      <c r="R17" s="3">
+      <c r="V17" s="3">
         <v>2284.0680000000002</v>
       </c>
-      <c r="S17" s="3">
+      <c r="W17" s="3">
         <v>2777.944</v>
       </c>
-      <c r="T17" s="3">
+      <c r="X17" s="3">
         <v>3699.7910000000002</v>
       </c>
-      <c r="U17" s="3">
+      <c r="Y17" s="3">
         <v>4311.1099999999997</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Z17" s="3">
         <v>4570.4459999999999</v>
       </c>
-      <c r="W17" s="3">
+      <c r="AA17" s="3">
         <v>4918.6970000000001</v>
       </c>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
-      <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
@@ -2336,8 +2493,12 @@
       <c r="AU17" s="3"/>
       <c r="AV17" s="3"/>
       <c r="AW17" s="3"/>
-    </row>
-    <row r="18" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX17" s="3"/>
+      <c r="AY17" s="3"/>
+      <c r="AZ17" s="3"/>
+      <c r="BA17" s="3"/>
+    </row>
+    <row r="18" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>50</v>
       </c>
@@ -2376,36 +2537,41 @@
       <c r="M18" s="3">
         <v>292.61200000000002</v>
       </c>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3">
+      <c r="N18" s="3">
+        <f t="shared" si="13"/>
+        <v>307.71000000000004</v>
+      </c>
+      <c r="O18" s="3">
+        <v>281.32100000000003</v>
+      </c>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3">
         <v>303.10000000000002</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="U18" s="3">
         <v>340.40699999999998</v>
       </c>
-      <c r="R18" s="3">
+      <c r="V18" s="3">
         <v>459.00400000000002</v>
       </c>
-      <c r="S18" s="3">
+      <c r="W18" s="3">
         <v>657.17600000000004</v>
       </c>
-      <c r="T18" s="3">
+      <c r="X18" s="3">
         <v>762.6</v>
       </c>
-      <c r="U18" s="3">
+      <c r="Y18" s="3">
         <v>897.21199999999999</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Z18" s="3">
         <v>1009.808</v>
       </c>
-      <c r="W18" s="3">
+      <c r="AA18" s="3">
         <v>1134.1590000000001</v>
       </c>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-      <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
@@ -2428,8 +2594,12 @@
       <c r="AU18" s="3"/>
       <c r="AV18" s="3"/>
       <c r="AW18" s="3"/>
-    </row>
-    <row r="19" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX18" s="3"/>
+      <c r="AY18" s="3"/>
+      <c r="AZ18" s="3"/>
+      <c r="BA18" s="3"/>
+    </row>
+    <row r="19" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
@@ -2466,34 +2636,43 @@
       <c r="M19" s="11">
         <v>2565.92</v>
       </c>
-      <c r="N19" s="11"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="11">
+      <c r="N19" s="11">
+        <f t="shared" si="13"/>
+        <v>3640.8010000000004</v>
+      </c>
+      <c r="O19" s="11">
+        <v>2471.6030000000001</v>
+      </c>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="11">
         <v>3288.319</v>
       </c>
-      <c r="Q19" s="11">
+      <c r="U19" s="11">
         <v>3979.2959999999998</v>
       </c>
-      <c r="R19" s="11">
+      <c r="V19" s="11">
         <v>4401.8789999999999</v>
       </c>
-      <c r="S19" s="11">
+      <c r="W19" s="11">
         <v>6256.6170000000002</v>
       </c>
-      <c r="T19" s="11">
+      <c r="X19" s="11">
         <v>8110.518</v>
       </c>
-      <c r="U19" s="11">
+      <c r="Y19" s="11">
         <v>9619.2780000000002</v>
       </c>
-      <c r="V19" s="11">
+      <c r="Z19" s="11">
         <v>10588.126</v>
       </c>
-      <c r="W19" s="11">
+      <c r="AA19" s="11">
         <v>11102.6</v>
       </c>
     </row>
-    <row r="20" spans="2:49" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>19</v>
       </c>
@@ -2530,34 +2709,43 @@
       <c r="M20" s="3">
         <v>1140.0039999999999</v>
       </c>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3">
+      <c r="N20" s="3">
+        <f t="shared" si="13"/>
+        <v>1642.913</v>
+      </c>
+      <c r="O20" s="3">
+        <v>1132.7850000000001</v>
+      </c>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3">
         <v>1472.0309999999999</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="U20" s="3">
         <v>1755.91</v>
       </c>
-      <c r="R20" s="3">
+      <c r="V20" s="3">
         <v>1937.8879999999999</v>
       </c>
-      <c r="S20" s="3">
+      <c r="W20" s="3">
         <v>2648.0520000000001</v>
       </c>
-      <c r="T20" s="3">
+      <c r="X20" s="3">
         <v>3618.1779999999999</v>
       </c>
-      <c r="U20" s="3">
+      <c r="Y20" s="3">
         <v>4009.873</v>
       </c>
-      <c r="V20" s="3">
+      <c r="Z20" s="3">
         <v>4317.3149999999996</v>
       </c>
-      <c r="W20" s="2">
+      <c r="AA20" s="2">
         <v>4818.4679999999998</v>
       </c>
     </row>
-    <row r="21" spans="2:49" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>20</v>
       </c>
@@ -2566,15 +2754,15 @@
         <v>1150.8049999999998</v>
       </c>
       <c r="D21" s="3">
-        <f t="shared" ref="D21:F21" si="13">D19-D20</f>
+        <f t="shared" ref="D21:F21" si="14">D19-D20</f>
         <v>1298.511</v>
       </c>
       <c r="E21" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1256.6639999999998</v>
       </c>
       <c r="F21" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1903.425</v>
       </c>
       <c r="G21" s="3">
@@ -2582,65 +2770,75 @@
         <v>1275.0680000000002</v>
       </c>
       <c r="H21" s="3">
-        <f t="shared" ref="H21:M21" si="14">H19-H20</f>
+        <f t="shared" ref="H21:O21" si="15">H19-H20</f>
         <v>1412.1849999999999</v>
       </c>
       <c r="I21" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1401.6059999999998</v>
       </c>
       <c r="J21" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2181.9519999999998</v>
       </c>
       <c r="K21" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1383.1259999999997</v>
       </c>
       <c r="L21" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1477.202</v>
       </c>
       <c r="M21" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1425.9160000000002</v>
       </c>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3">
-        <f t="shared" ref="P21" si="15">P19-P20</f>
+      <c r="N21" s="3">
+        <f t="shared" si="15"/>
+        <v>1997.8880000000004</v>
+      </c>
+      <c r="O21" s="3">
+        <f t="shared" si="15"/>
+        <v>1338.818</v>
+      </c>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3">
+        <f t="shared" ref="T21" si="16">T19-T20</f>
         <v>1816.288</v>
       </c>
-      <c r="Q21" s="3">
-        <f t="shared" ref="Q21" si="16">Q19-Q20</f>
+      <c r="U21" s="3">
+        <f t="shared" ref="U21" si="17">U19-U20</f>
         <v>2223.3859999999995</v>
       </c>
-      <c r="R21" s="3">
-        <f t="shared" ref="R21" si="17">R19-R20</f>
+      <c r="V21" s="3">
+        <f t="shared" ref="V21" si="18">V19-V20</f>
         <v>2463.991</v>
       </c>
-      <c r="S21" s="3">
-        <f t="shared" ref="S21" si="18">S19-S20</f>
+      <c r="W21" s="3">
+        <f t="shared" ref="W21" si="19">W19-W20</f>
         <v>3608.5650000000001</v>
       </c>
-      <c r="T21" s="3">
-        <f t="shared" ref="T21" si="19">T19-T20</f>
+      <c r="X21" s="3">
+        <f t="shared" ref="X21" si="20">X19-X20</f>
         <v>4492.34</v>
       </c>
-      <c r="U21" s="3">
-        <f t="shared" ref="U21" si="20">U19-U20</f>
+      <c r="Y21" s="3">
+        <f t="shared" ref="Y21" si="21">Y19-Y20</f>
         <v>5609.4050000000007</v>
       </c>
-      <c r="V21" s="3">
-        <f t="shared" ref="V21:W21" si="21">V19-V20</f>
+      <c r="Z21" s="3">
+        <f t="shared" ref="Z21:AA21" si="22">Z19-Z20</f>
         <v>6270.8110000000006</v>
       </c>
-      <c r="W21" s="3">
-        <f t="shared" si="21"/>
+      <c r="AA21" s="3">
+        <f t="shared" si="22"/>
         <v>6284.1320000000005</v>
       </c>
     </row>
-    <row r="22" spans="2:49" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>21</v>
       </c>
@@ -2677,34 +2875,43 @@
       <c r="M22" s="3">
         <v>988.25400000000002</v>
       </c>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3">
+      <c r="N22" s="3">
+        <f t="shared" si="13"/>
+        <v>1183.7730000000001</v>
+      </c>
+      <c r="O22" s="3">
+        <v>1059.9880000000001</v>
+      </c>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3">
         <v>1100.3789999999999</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="U22" s="3">
         <v>1334.2470000000001</v>
       </c>
-      <c r="R22" s="3">
+      <c r="V22" s="3">
         <v>1609.0029999999999</v>
       </c>
-      <c r="S22" s="3">
+      <c r="W22" s="3">
         <v>2225.0340000000001</v>
       </c>
-      <c r="T22" s="3">
+      <c r="X22" s="3">
         <v>2757.4470000000001</v>
       </c>
-      <c r="U22" s="3">
+      <c r="Y22" s="3">
         <v>3397.2179999999998</v>
       </c>
-      <c r="V22" s="3">
+      <c r="Z22" s="3">
         <v>3762.3789999999999</v>
       </c>
-      <c r="W22" s="2">
+      <c r="AA22" s="2">
         <v>4066.556</v>
       </c>
     </row>
-    <row r="23" spans="2:49" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
@@ -2742,51 +2949,60 @@
       <c r="M23" s="3">
         <v>1.776</v>
       </c>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3">
+      <c r="N23" s="3">
+        <f t="shared" si="13"/>
+        <v>1.8250000000000002</v>
+      </c>
+      <c r="O23" s="3">
+        <v>1.8839999999999999</v>
+      </c>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="U23" s="3">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="R23" s="3">
+      <c r="V23" s="3">
         <f>5.16+29.842</f>
         <v>35.001999999999995</v>
       </c>
-      <c r="S23" s="3">
+      <c r="W23" s="3">
         <f>8.782+41.394</f>
         <v>50.176000000000002</v>
       </c>
-      <c r="T23" s="3">
+      <c r="X23" s="3">
         <f>407.913+8.752-10.18</f>
         <v>406.48500000000001</v>
       </c>
-      <c r="U23" s="3">
+      <c r="Y23" s="3">
         <f>74.501+5.01</f>
         <v>79.51100000000001</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Z23" s="3">
         <v>2.7349999999999999</v>
       </c>
-      <c r="W23" s="2">
+      <c r="AA23" s="2">
         <v>6.9610000000000003</v>
       </c>
     </row>
-    <row r="24" spans="2:49" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C24" s="3">
-        <f t="shared" ref="C24:E24" si="22">C21-SUM(C22:C23)</f>
+        <f t="shared" ref="C24:E24" si="23">C21-SUM(C22:C23)</f>
         <v>401.41399999999976</v>
       </c>
       <c r="D24" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>479.25699999999995</v>
       </c>
       <c r="E24" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>338.11499999999978</v>
       </c>
       <c r="F24" s="3">
@@ -2798,67 +3014,73 @@
         <v>432.64200000000017</v>
       </c>
       <c r="H24" s="3">
-        <f t="shared" ref="H24:M24" si="23">H21-SUM(H22:H23)</f>
+        <f t="shared" ref="H24:O24" si="24">H21-SUM(H22:H23)</f>
         <v>540.226</v>
       </c>
       <c r="I24" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>490.66099999999972</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1042.1679999999999</v>
       </c>
       <c r="K24" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>438.62499999999977</v>
       </c>
       <c r="L24" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>523.81399999999996</v>
       </c>
       <c r="M24" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>435.88600000000019</v>
       </c>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3">
-        <f t="shared" ref="P24" si="24">P21-SUM(P22:P23)</f>
+      <c r="N24" s="3">
+        <f t="shared" si="24"/>
+        <v>812.29000000000019</v>
+      </c>
+      <c r="O24" s="3">
+        <f t="shared" si="24"/>
+        <v>276.94599999999991</v>
+      </c>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3">
+        <f t="shared" ref="T24" si="25">T21-SUM(T22:T23)</f>
         <v>715.83700000000022</v>
       </c>
-      <c r="Q24" s="3">
-        <f t="shared" ref="Q24" si="25">Q21-SUM(Q22:Q23)</f>
+      <c r="U24" s="3">
+        <f t="shared" ref="U24" si="26">U21-SUM(U22:U23)</f>
         <v>889.10999999999945</v>
       </c>
-      <c r="R24" s="3">
-        <f t="shared" ref="R24" si="26">R21-SUM(R22:R23)</f>
+      <c r="V24" s="3">
+        <f t="shared" ref="V24" si="27">V21-SUM(V22:V23)</f>
         <v>819.9860000000001</v>
       </c>
-      <c r="S24" s="3">
-        <f>S21-SUM(S22:S23)</f>
+      <c r="W24" s="3">
+        <f>W21-SUM(W22:W23)</f>
         <v>1333.355</v>
       </c>
-      <c r="T24" s="3">
-        <f t="shared" ref="T24" si="27">T21-SUM(T22:T23)</f>
+      <c r="X24" s="3">
+        <f t="shared" ref="X24" si="28">X21-SUM(X22:X23)</f>
         <v>1328.4079999999999</v>
       </c>
-      <c r="U24" s="3">
-        <f t="shared" ref="U24" si="28">U21-SUM(U22:U23)</f>
+      <c r="Y24" s="3">
+        <f t="shared" ref="Y24" si="29">Y21-SUM(Y22:Y23)</f>
         <v>2132.6760000000008</v>
       </c>
-      <c r="V24" s="3">
-        <f t="shared" ref="V24:W24" si="29">V21-SUM(V22:V23)</f>
+      <c r="Z24" s="3">
+        <f t="shared" ref="Z24:AA24" si="30">Z21-SUM(Z22:Z23)</f>
         <v>2505.6970000000006</v>
       </c>
-      <c r="W24" s="3">
-        <f t="shared" si="29"/>
+      <c r="AA24" s="3">
+        <f t="shared" si="30"/>
         <v>2210.6150000000007</v>
       </c>
-      <c r="AA24" s="1"/>
-      <c r="AB24" s="1"/>
-      <c r="AC24" s="1"/>
-      <c r="AD24" s="1"/>
       <c r="AE24" s="1"/>
       <c r="AF24" s="1"/>
       <c r="AG24" s="1"/>
@@ -2867,8 +3089,12 @@
       <c r="AJ24" s="1"/>
       <c r="AK24" s="1"/>
       <c r="AL24" s="1"/>
-    </row>
-    <row r="25" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AM24" s="1"/>
+      <c r="AN24" s="1"/>
+      <c r="AO24" s="1"/>
+      <c r="AP24" s="1"/>
+    </row>
+    <row r="25" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>23</v>
       </c>
@@ -2905,34 +3131,43 @@
       <c r="M25" s="3">
         <v>5.8540000000000001</v>
       </c>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3">
+      <c r="N25" s="3">
+        <f t="shared" si="13"/>
+        <v>0.97500000000000142</v>
+      </c>
+      <c r="O25" s="3">
+        <v>9.1310000000000002</v>
+      </c>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3">
         <v>9.4139999999999997</v>
       </c>
-      <c r="Q25" s="3">
+      <c r="U25" s="3">
         <v>8.2829999999999995</v>
       </c>
-      <c r="R25" s="3">
+      <c r="V25" s="3">
         <v>-0.63600000000000001</v>
       </c>
-      <c r="S25" s="3">
+      <c r="W25" s="3">
         <v>0.51400000000000001</v>
       </c>
-      <c r="T25" s="3">
+      <c r="X25" s="3">
         <v>4.1630000000000003</v>
       </c>
-      <c r="U25" s="3">
+      <c r="Y25" s="3">
         <v>43.058999999999997</v>
       </c>
-      <c r="V25" s="3">
+      <c r="Z25" s="3">
         <v>70.38</v>
       </c>
-      <c r="W25" s="2">
+      <c r="AA25" s="2">
         <v>28.352</v>
       </c>
     </row>
-    <row r="26" spans="2:49" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>24</v>
       </c>
@@ -2941,15 +3176,15 @@
         <v>409.43899999999974</v>
       </c>
       <c r="D26" s="3">
-        <f t="shared" ref="D26:F26" si="30">D24+D25</f>
+        <f t="shared" ref="D26:F26" si="31">D24+D25</f>
         <v>486.61899999999997</v>
       </c>
       <c r="E26" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>347.95699999999977</v>
       </c>
       <c r="F26" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>931.72</v>
       </c>
       <c r="G26" s="3">
@@ -2957,65 +3192,75 @@
         <v>455.92500000000018</v>
       </c>
       <c r="H26" s="3">
-        <f t="shared" ref="H26:M26" si="31">H24+H25</f>
+        <f t="shared" ref="H26:O26" si="32">H24+H25</f>
         <v>558.22</v>
       </c>
       <c r="I26" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>504.40399999999971</v>
       </c>
       <c r="J26" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1057.5279999999998</v>
       </c>
       <c r="K26" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>450.41099999999977</v>
       </c>
       <c r="L26" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>533.55099999999993</v>
       </c>
       <c r="M26" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>441.74000000000018</v>
       </c>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3">
-        <f t="shared" ref="P26" si="32">P24+P25</f>
+      <c r="N26" s="3">
+        <f t="shared" si="32"/>
+        <v>813.26500000000021</v>
+      </c>
+      <c r="O26" s="3">
+        <f t="shared" si="32"/>
+        <v>286.07699999999988</v>
+      </c>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3">
+        <f t="shared" ref="T26" si="33">T24+T25</f>
         <v>725.2510000000002</v>
       </c>
-      <c r="Q26" s="3">
-        <f t="shared" ref="Q26" si="33">Q24+Q25</f>
+      <c r="U26" s="3">
+        <f t="shared" ref="U26" si="34">U24+U25</f>
         <v>897.39299999999946</v>
       </c>
-      <c r="R26" s="3">
-        <f t="shared" ref="R26" si="34">R24+R25</f>
+      <c r="V26" s="3">
+        <f t="shared" ref="V26" si="35">V24+V25</f>
         <v>819.35000000000014</v>
       </c>
-      <c r="S26" s="3">
-        <f t="shared" ref="S26" si="35">S24+S25</f>
+      <c r="W26" s="3">
+        <f t="shared" ref="W26" si="36">W24+W25</f>
         <v>1333.8689999999999</v>
       </c>
-      <c r="T26" s="3">
-        <f t="shared" ref="T26" si="36">T24+T25</f>
+      <c r="X26" s="3">
+        <f t="shared" ref="X26" si="37">X24+X25</f>
         <v>1332.5709999999999</v>
       </c>
-      <c r="U26" s="3">
-        <f t="shared" ref="U26" si="37">U24+U25</f>
+      <c r="Y26" s="3">
+        <f t="shared" ref="Y26" si="38">Y24+Y25</f>
         <v>2175.735000000001</v>
       </c>
-      <c r="V26" s="3">
-        <f t="shared" ref="V26:W26" si="38">V24+V25</f>
+      <c r="Z26" s="3">
+        <f t="shared" ref="Z26:AA26" si="39">Z24+Z25</f>
         <v>2576.0770000000007</v>
       </c>
-      <c r="W26" s="3">
-        <f t="shared" si="38"/>
+      <c r="AA26" s="3">
+        <f t="shared" si="39"/>
         <v>2238.9670000000006</v>
       </c>
     </row>
-    <row r="27" spans="2:49" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>25</v>
       </c>
@@ -3052,34 +3297,43 @@
       <c r="M27" s="3">
         <v>134.905</v>
       </c>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3">
+      <c r="N27" s="3">
+        <f t="shared" si="13"/>
+        <v>226.39400000000001</v>
+      </c>
+      <c r="O27" s="3">
+        <v>91.028999999999996</v>
+      </c>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3">
         <v>231.44900000000001</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="U27" s="3">
         <v>251.797</v>
       </c>
-      <c r="R27" s="3">
+      <c r="V27" s="3">
         <v>230.43700000000001</v>
       </c>
-      <c r="S27" s="3">
+      <c r="W27" s="3">
         <v>358.54700000000003</v>
       </c>
-      <c r="T27" s="3">
+      <c r="X27" s="3">
         <v>477.77100000000002</v>
       </c>
-      <c r="U27" s="3">
+      <c r="Y27" s="3">
         <v>625.54499999999996</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Z27" s="3">
         <v>761.46100000000001</v>
       </c>
-      <c r="W27" s="2">
+      <c r="AA27" s="2">
         <v>659.78399999999999</v>
       </c>
     </row>
-    <row r="28" spans="2:49" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>26</v>
       </c>
@@ -3088,15 +3342,15 @@
         <v>290.40499999999975</v>
       </c>
       <c r="D28" s="3">
-        <f t="shared" ref="D28:F28" si="39">D26-D27</f>
+        <f t="shared" ref="D28:F28" si="40">D26-D27</f>
         <v>341.60299999999995</v>
       </c>
       <c r="E28" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>248.71399999999977</v>
       </c>
       <c r="F28" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>669.46800000000007</v>
       </c>
       <c r="G28" s="3">
@@ -3104,65 +3358,75 @@
         <v>321.42100000000016</v>
       </c>
       <c r="H28" s="3">
-        <f t="shared" ref="H28:M28" si="40">H26-H27</f>
+        <f t="shared" ref="H28:O28" si="41">H26-H27</f>
         <v>392.92200000000003</v>
       </c>
       <c r="I28" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>351.86999999999972</v>
       </c>
       <c r="J28" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>748.40299999999979</v>
       </c>
       <c r="K28" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>314.57199999999978</v>
       </c>
       <c r="L28" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>370.90499999999997</v>
       </c>
       <c r="M28" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>306.83500000000015</v>
       </c>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3">
-        <f t="shared" ref="P28:W28" si="41">P26-P27</f>
+      <c r="N28" s="3">
+        <f t="shared" si="41"/>
+        <v>586.87100000000021</v>
+      </c>
+      <c r="O28" s="3">
+        <f t="shared" si="41"/>
+        <v>195.04799999999989</v>
+      </c>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3">
+        <f t="shared" ref="T28:AA28" si="42">T26-T27</f>
         <v>493.80200000000019</v>
       </c>
-      <c r="Q28" s="3">
-        <f t="shared" si="41"/>
+      <c r="U28" s="3">
+        <f t="shared" si="42"/>
         <v>645.59599999999944</v>
       </c>
-      <c r="R28" s="3">
-        <f t="shared" si="41"/>
+      <c r="V28" s="3">
+        <f t="shared" si="42"/>
         <v>588.91300000000012</v>
       </c>
-      <c r="S28" s="3">
-        <f t="shared" si="41"/>
+      <c r="W28" s="3">
+        <f t="shared" si="42"/>
         <v>975.32199999999989</v>
       </c>
-      <c r="T28" s="3">
-        <f t="shared" si="41"/>
+      <c r="X28" s="3">
+        <f t="shared" si="42"/>
         <v>854.8</v>
       </c>
-      <c r="U28" s="3">
-        <f t="shared" si="41"/>
+      <c r="Y28" s="3">
+        <f t="shared" si="42"/>
         <v>1550.190000000001</v>
       </c>
-      <c r="V28" s="3">
-        <f t="shared" si="41"/>
+      <c r="Z28" s="3">
+        <f t="shared" si="42"/>
         <v>1814.6160000000007</v>
       </c>
-      <c r="W28" s="3">
-        <f t="shared" si="41"/>
+      <c r="AA28" s="3">
+        <f t="shared" si="42"/>
         <v>1579.1830000000004</v>
       </c>
     </row>
-    <row r="29" spans="2:49" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -3183,99 +3447,113 @@
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
-    </row>
-    <row r="30" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="W29" s="3"/>
+      <c r="X29" s="3"/>
+      <c r="Y29" s="3"/>
+      <c r="Z29" s="3"/>
+    </row>
+    <row r="30" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C30" s="14">
-        <f t="shared" ref="C30:M30" si="42">C28/C31</f>
+        <f t="shared" ref="C30:O30" si="43">C28/C31</f>
         <v>2.2822328403250376</v>
       </c>
       <c r="D30" s="14">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2.69044412415629</v>
       </c>
       <c r="E30" s="14">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.9667404712952694</v>
       </c>
       <c r="F30" s="14">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>5.3036410305162098</v>
       </c>
       <c r="G30" s="14">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2.5530270536466042</v>
       </c>
       <c r="H30" s="14">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>3.1504077100087398</v>
       </c>
       <c r="I30" s="14">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2.8677962786376172</v>
       </c>
       <c r="J30" s="14">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>6.1504318598325138</v>
       </c>
       <c r="K30" s="14">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2.6076994495656192</v>
       </c>
       <c r="L30" s="14">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>3.1012123745819395</v>
       </c>
       <c r="M30" s="14">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2.588560340827605</v>
       </c>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14">
-        <f>+P28/P31</f>
+      <c r="N30" s="14">
+        <f t="shared" si="43"/>
+        <v>4.9324766139131482</v>
+      </c>
+      <c r="O30" s="14">
+        <f t="shared" si="43"/>
+        <v>1.689985616996204</v>
+      </c>
+      <c r="P30" s="14"/>
+      <c r="Q30" s="14"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14">
+        <f>+T28/T31</f>
         <v>3.7013034711759736</v>
       </c>
-      <c r="Q30" s="14">
-        <f t="shared" ref="Q30:W30" si="43">+Q28/Q31</f>
+      <c r="U30" s="14">
+        <f t="shared" ref="U30:AA30" si="44">+U28/U31</f>
         <v>4.9511553534315444</v>
       </c>
-      <c r="R30" s="14">
-        <f t="shared" si="43"/>
+      <c r="V30" s="14">
+        <f t="shared" si="44"/>
         <v>4.5200515776466181</v>
       </c>
-      <c r="S30" s="14">
-        <f t="shared" si="43"/>
+      <c r="W30" s="14">
+        <f t="shared" si="44"/>
         <v>7.515889895814067</v>
       </c>
-      <c r="T30" s="14">
-        <f t="shared" si="43"/>
+      <c r="X30" s="14">
+        <f t="shared" si="44"/>
         <v>6.6955963216518102</v>
       </c>
-      <c r="U30" s="14">
-        <f t="shared" si="43"/>
+      <c r="Y30" s="14">
+        <f t="shared" si="44"/>
         <v>12.23261209223049</v>
       </c>
-      <c r="V30" s="14">
-        <f t="shared" si="43"/>
+      <c r="Z30" s="14">
+        <f t="shared" si="44"/>
         <v>14.665341253485277</v>
       </c>
-      <c r="W30" s="14">
-        <f t="shared" si="43"/>
+      <c r="AA30" s="14">
+        <f t="shared" si="44"/>
         <v>13.272564527109374</v>
       </c>
-      <c r="X30" s="14"/>
-      <c r="Y30" s="14"/>
-      <c r="Z30" s="14"/>
-      <c r="AA30" s="14"/>
       <c r="AB30" s="14"/>
       <c r="AC30" s="14"/>
       <c r="AD30" s="14"/>
       <c r="AE30" s="14"/>
-    </row>
-    <row r="31" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AF30" s="14"/>
+      <c r="AG30" s="14"/>
+      <c r="AH30" s="14"/>
+      <c r="AI30" s="14"/>
+    </row>
+    <row r="31" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>27</v>
       </c>
@@ -3312,34 +3590,42 @@
       <c r="M31" s="3">
         <v>118.535</v>
       </c>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3">
+      <c r="N31" s="2">
+        <v>118.98099999999999</v>
+      </c>
+      <c r="O31" s="2">
+        <v>115.414</v>
+      </c>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3">
         <v>133.41300000000001</v>
       </c>
-      <c r="Q31" s="3">
+      <c r="U31" s="3">
         <v>130.393</v>
       </c>
-      <c r="R31" s="3">
+      <c r="V31" s="3">
         <v>130.28899999999999</v>
       </c>
-      <c r="S31" s="3">
+      <c r="W31" s="3">
         <v>129.768</v>
       </c>
-      <c r="T31" s="3">
+      <c r="X31" s="3">
         <v>127.666</v>
       </c>
-      <c r="U31" s="3">
+      <c r="Y31" s="3">
         <v>126.726</v>
       </c>
-      <c r="V31" s="3">
+      <c r="Z31" s="3">
         <v>123.735</v>
       </c>
-      <c r="W31" s="2">
+      <c r="AA31" s="2">
         <v>118.98099999999999</v>
       </c>
     </row>
-    <row r="32" spans="2:49" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -3353,8 +3639,12 @@
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B33" s="1" t="s">
         <v>32</v>
       </c>
@@ -3367,382 +3657,444 @@
         <v>0.10400831270816768</v>
       </c>
       <c r="H33" s="12">
-        <f t="shared" ref="H33:M33" si="44">H19/D19-1</f>
+        <f t="shared" ref="H33:M33" si="45">H19/D19-1</f>
         <v>7.3291492486980303E-2</v>
       </c>
       <c r="I33" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.7306246478342953E-2</v>
       </c>
       <c r="J33" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.12679592512315518</v>
       </c>
       <c r="K33" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>7.3235392783075115E-2</v>
       </c>
       <c r="L33" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>6.50088272085525E-2</v>
       </c>
       <c r="M33" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" ref="M33" si="46">M19/I19-1</f>
         <v>7.062328407033136E-2</v>
       </c>
-      <c r="N33" s="13"/>
-      <c r="O33" s="3"/>
+      <c r="N33" s="12">
+        <f t="shared" ref="N33" si="47">N19/J19-1</f>
+        <v>8.1140867623592516E-3</v>
+      </c>
+      <c r="O33" s="12">
+        <f t="shared" ref="O33" si="48">O19/K19-1</f>
+        <v>4.258012536593192E-2</v>
+      </c>
       <c r="P33" s="13"/>
-      <c r="Q33" s="12">
-        <f t="shared" ref="Q33:T33" si="45">Q19/P19-1</f>
+      <c r="Q33" s="13"/>
+      <c r="R33" s="13"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="13"/>
+      <c r="U33" s="12">
+        <f t="shared" ref="U33:X33" si="49">U19/T19-1</f>
         <v>0.21013076894303739</v>
       </c>
-      <c r="R33" s="12">
-        <f t="shared" si="45"/>
+      <c r="V33" s="12">
+        <f t="shared" si="49"/>
         <v>0.10619541748088102</v>
       </c>
-      <c r="S33" s="12">
-        <f t="shared" si="45"/>
+      <c r="W33" s="12">
+        <f t="shared" si="49"/>
         <v>0.42135142742451581</v>
       </c>
-      <c r="T33" s="12">
-        <f t="shared" si="45"/>
+      <c r="X33" s="12">
+        <f t="shared" si="49"/>
         <v>0.29631045020016411</v>
       </c>
-      <c r="U33" s="12">
-        <f>U19/T19-1</f>
+      <c r="Y33" s="12">
+        <f>Y19/X19-1</f>
         <v>0.18602510961691965</v>
       </c>
-      <c r="V33" s="12">
-        <f>V19/U19-1</f>
+      <c r="Z33" s="12">
+        <f>Z19/Y19-1</f>
         <v>0.1007194095024595</v>
       </c>
-      <c r="W33" s="12">
-        <f>W19/V19-1</f>
+      <c r="AA33" s="12">
+        <f>AA19/Z19-1</f>
         <v>4.8589712664923068E-2</v>
       </c>
     </row>
-    <row r="34" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C34" s="13">
-        <f t="shared" ref="C34:J34" si="46">C21/C19</f>
+        <f t="shared" ref="C34:J34" si="50">C21/C19</f>
         <v>0.57517473080660053</v>
       </c>
       <c r="D34" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>0.58778361960288161</v>
       </c>
       <c r="E34" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>0.57011783770933722</v>
       </c>
       <c r="F34" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>0.59387327021939695</v>
       </c>
       <c r="G34" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>0.57724351269483198</v>
       </c>
       <c r="H34" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>0.59558774532090464</v>
       </c>
       <c r="I34" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>0.58481636944748105</v>
       </c>
       <c r="J34" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>0.60416829918452097</v>
       </c>
       <c r="K34" s="13">
-        <f t="shared" ref="K34:L34" si="47">K21/K19</f>
+        <f t="shared" ref="K34:L34" si="51">K21/K19</f>
         <v>0.58343499278681876</v>
       </c>
       <c r="L34" s="13">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>0.58497975819126968</v>
       </c>
-      <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="3"/>
-      <c r="P34" s="13">
-        <f t="shared" ref="P34:T34" si="48">P21/P19</f>
+      <c r="M34" s="13">
+        <f t="shared" ref="M34:O34" si="52">M21/M19</f>
+        <v>0.55571335037725267</v>
+      </c>
+      <c r="N34" s="13">
+        <f t="shared" si="52"/>
+        <v>0.54874957461283935</v>
+      </c>
+      <c r="O34" s="13">
+        <f t="shared" si="52"/>
+        <v>0.54168003518364394</v>
+      </c>
+      <c r="P34" s="13"/>
+      <c r="Q34" s="13"/>
+      <c r="R34" s="13"/>
+      <c r="S34" s="3"/>
+      <c r="T34" s="13">
+        <f t="shared" ref="T34:X34" si="53">T21/T19</f>
         <v>0.5523454385052059</v>
       </c>
-      <c r="Q34" s="13">
-        <f t="shared" si="48"/>
+      <c r="U34" s="13">
+        <f t="shared" si="53"/>
         <v>0.55873853063456436</v>
       </c>
-      <c r="R34" s="13">
-        <f t="shared" si="48"/>
+      <c r="V34" s="13">
+        <f t="shared" si="53"/>
         <v>0.55975891204642381</v>
       </c>
-      <c r="S34" s="13">
-        <f t="shared" si="48"/>
+      <c r="W34" s="13">
+        <f t="shared" si="53"/>
         <v>0.57675977289324243</v>
       </c>
-      <c r="T34" s="13">
-        <f t="shared" si="48"/>
+      <c r="X34" s="13">
+        <f t="shared" si="53"/>
         <v>0.55389063929085669</v>
       </c>
-      <c r="U34" s="13">
-        <f>U21/U19</f>
+      <c r="Y34" s="13">
+        <f>Y21/Y19</f>
         <v>0.58314199880697914</v>
       </c>
-      <c r="V34" s="13">
-        <f>V21/V19</f>
+      <c r="Z34" s="13">
+        <f>Z21/Z19</f>
         <v>0.59224937444076509</v>
       </c>
-      <c r="W34" s="13">
-        <f>W21/W19</f>
+      <c r="AA34" s="13">
+        <f>AA21/AA19</f>
         <v>0.56600544016716803</v>
       </c>
     </row>
-    <row r="35" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C35" s="13">
-        <f t="shared" ref="C35:J35" si="49">C24/C19</f>
+        <f t="shared" ref="C35:J35" si="54">C24/C19</f>
         <v>0.20062755148961001</v>
       </c>
       <c r="D35" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="54"/>
         <v>0.21694033718622191</v>
       </c>
       <c r="E35" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="54"/>
         <v>0.15339453720094828</v>
       </c>
       <c r="F35" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="54"/>
         <v>0.28513592230889301</v>
       </c>
       <c r="G35" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="54"/>
         <v>0.19586389731317669</v>
       </c>
       <c r="H35" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="54"/>
         <v>0.22783982644181255</v>
       </c>
       <c r="I35" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="54"/>
         <v>0.20472699506813638</v>
       </c>
       <c r="J35" s="13">
-        <f t="shared" si="49"/>
+        <f t="shared" si="54"/>
         <v>0.2885695322466002</v>
       </c>
       <c r="K35" s="13">
-        <f t="shared" ref="K35:L35" si="50">K24/K19</f>
+        <f t="shared" ref="K35:L35" si="55">K24/K19</f>
         <v>0.18502231446095171</v>
       </c>
       <c r="L35" s="13">
-        <f t="shared" si="50"/>
+        <f t="shared" si="55"/>
         <v>0.20743309788180747</v>
       </c>
-      <c r="M35" s="13"/>
-      <c r="N35" s="13"/>
-      <c r="O35" s="3"/>
-      <c r="P35" s="13">
-        <f t="shared" ref="P35:T35" si="51">P24/P19</f>
+      <c r="M35" s="13">
+        <f t="shared" ref="M35:O35" si="56">M24/M19</f>
+        <v>0.16987513250607977</v>
+      </c>
+      <c r="N35" s="13">
+        <f t="shared" si="56"/>
+        <v>0.22310749749849007</v>
+      </c>
+      <c r="O35" s="13">
+        <f t="shared" si="56"/>
+        <v>0.11205116679337253</v>
+      </c>
+      <c r="P35" s="13"/>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="13"/>
+      <c r="S35" s="3"/>
+      <c r="T35" s="13">
+        <f t="shared" ref="T35:X35" si="57">T24/T19</f>
         <v>0.21769086271739457</v>
       </c>
-      <c r="Q35" s="13">
-        <f t="shared" si="51"/>
+      <c r="U35" s="13">
+        <f t="shared" si="57"/>
         <v>0.2234339943547802</v>
       </c>
-      <c r="R35" s="13">
-        <f t="shared" si="51"/>
+      <c r="V35" s="13">
+        <f t="shared" si="57"/>
         <v>0.18628090413207635</v>
       </c>
-      <c r="S35" s="13">
-        <f t="shared" si="51"/>
+      <c r="W35" s="13">
+        <f t="shared" si="57"/>
         <v>0.21311117493687085</v>
       </c>
-      <c r="T35" s="13">
-        <f t="shared" si="51"/>
+      <c r="X35" s="13">
+        <f t="shared" si="57"/>
         <v>0.163788305506504</v>
       </c>
-      <c r="U35" s="13">
-        <f>U24/U19</f>
+      <c r="Y35" s="13">
+        <f>Y24/Y19</f>
         <v>0.22170853155507106</v>
       </c>
-      <c r="V35" s="13">
-        <f>V24/V19</f>
+      <c r="Z35" s="13">
+        <f>Z24/Z19</f>
         <v>0.23665160388155568</v>
       </c>
-      <c r="W35" s="13">
-        <f>W24/W19</f>
+      <c r="AA35" s="13">
+        <f>AA24/AA19</f>
         <v>0.19910786662583543</v>
       </c>
     </row>
-    <row r="36" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C36" s="13">
-        <f t="shared" ref="C36:J36" si="52">C28/C19</f>
+        <f t="shared" ref="C36:J36" si="58">C28/C19</f>
         <v>0.14514502257106174</v>
       </c>
       <c r="D36" s="13">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>0.15462991673324536</v>
       </c>
       <c r="E36" s="13">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>0.11283548178991361</v>
       </c>
       <c r="F36" s="13">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>0.20887565859817925</v>
       </c>
       <c r="G36" s="13">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>0.14551238607971156</v>
       </c>
       <c r="H36" s="13">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>0.16571449779383049</v>
       </c>
       <c r="I36" s="13">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>0.14681682007460373</v>
       </c>
       <c r="J36" s="13">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>0.20722791684445532</v>
       </c>
       <c r="K36" s="13">
-        <f t="shared" ref="K36:L36" si="53">K28/K19</f>
+        <f t="shared" ref="K36:L36" si="59">K28/K19</f>
         <v>0.13269384897032885</v>
       </c>
       <c r="L36" s="13">
-        <f t="shared" si="53"/>
+        <f t="shared" si="59"/>
         <v>0.14688032998326084</v>
       </c>
-      <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="3"/>
-      <c r="P36" s="13">
-        <f t="shared" ref="P36:T36" si="54">P28/P19</f>
+      <c r="M36" s="13">
+        <f t="shared" ref="M36:O36" si="60">M28/M19</f>
+        <v>0.11958089106441359</v>
+      </c>
+      <c r="N36" s="13">
+        <f t="shared" si="60"/>
+        <v>0.16119282542495461</v>
+      </c>
+      <c r="O36" s="13">
+        <f t="shared" si="60"/>
+        <v>7.8915586362372878E-2</v>
+      </c>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="13"/>
+      <c r="S36" s="3"/>
+      <c r="T36" s="13">
+        <f t="shared" ref="T36:X36" si="61">T28/T19</f>
         <v>0.1501685207548295</v>
       </c>
-      <c r="Q36" s="13">
-        <f t="shared" si="54"/>
+      <c r="U36" s="13">
+        <f t="shared" si="61"/>
         <v>0.16223874775839733</v>
       </c>
-      <c r="R36" s="13">
-        <f t="shared" si="54"/>
+      <c r="V36" s="13">
+        <f t="shared" si="61"/>
         <v>0.13378673062117341</v>
       </c>
-      <c r="S36" s="13">
-        <f t="shared" si="54"/>
+      <c r="W36" s="13">
+        <f t="shared" si="61"/>
         <v>0.15588647986603621</v>
       </c>
-      <c r="T36" s="13">
-        <f t="shared" si="54"/>
+      <c r="X36" s="13">
+        <f t="shared" si="61"/>
         <v>0.10539400812623805</v>
       </c>
-      <c r="U36" s="13">
-        <f>U28/U19</f>
+      <c r="Y36" s="13">
+        <f>Y28/Y19</f>
         <v>0.16115450660642108</v>
       </c>
-      <c r="V36" s="13">
-        <f>V28/V19</f>
+      <c r="Z36" s="13">
+        <f>Z28/Z19</f>
         <v>0.17138216904483386</v>
       </c>
-      <c r="W36" s="13">
-        <f>W28/W19</f>
+      <c r="AA36" s="13">
+        <f>AA28/AA19</f>
         <v>0.1422354223335075</v>
       </c>
     </row>
-    <row r="37" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C37" s="13">
-        <f t="shared" ref="C37:J37" si="55">C27/C26</f>
+        <f t="shared" ref="C37:J37" si="62">C27/C26</f>
         <v>0.29072462564631135</v>
       </c>
       <c r="D37" s="13">
-        <f t="shared" si="55"/>
+        <f t="shared" si="62"/>
         <v>0.29800727057513166</v>
       </c>
       <c r="E37" s="13">
-        <f t="shared" si="55"/>
+        <f t="shared" si="62"/>
         <v>0.28521627672384825</v>
       </c>
       <c r="F37" s="13">
-        <f t="shared" si="55"/>
+        <f t="shared" si="62"/>
         <v>0.28147082814579488</v>
       </c>
       <c r="G37" s="13">
-        <f t="shared" si="55"/>
+        <f t="shared" si="62"/>
         <v>0.29501343422712056</v>
       </c>
       <c r="H37" s="13">
-        <f t="shared" si="55"/>
+        <f t="shared" si="62"/>
         <v>0.29611622657733511</v>
       </c>
       <c r="I37" s="13">
-        <f t="shared" si="55"/>
+        <f t="shared" si="62"/>
         <v>0.30240442185232486</v>
       </c>
       <c r="J37" s="13">
-        <f t="shared" si="55"/>
+        <f t="shared" si="62"/>
         <v>0.29230904524513779</v>
       </c>
       <c r="K37" s="13">
-        <f t="shared" ref="K37:L37" si="56">K27/K26</f>
+        <f t="shared" ref="K37:L37" si="63">K27/K26</f>
         <v>0.30158899316402143</v>
       </c>
       <c r="L37" s="13">
-        <f t="shared" si="56"/>
+        <f t="shared" si="63"/>
         <v>0.30483683846530135</v>
       </c>
-      <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="3"/>
-      <c r="P37" s="13">
-        <f t="shared" ref="P37:T37" si="57">P27/P26</f>
+      <c r="M37" s="13">
+        <f t="shared" ref="M37:O37" si="64">M27/M26</f>
+        <v>0.30539457599492903</v>
+      </c>
+      <c r="N37" s="13">
+        <f t="shared" si="64"/>
+        <v>0.27837666689209539</v>
+      </c>
+      <c r="O37" s="13">
+        <f t="shared" si="64"/>
+        <v>0.31819754821254431</v>
+      </c>
+      <c r="P37" s="13"/>
+      <c r="Q37" s="13"/>
+      <c r="R37" s="13"/>
+      <c r="S37" s="3"/>
+      <c r="T37" s="13">
+        <f t="shared" ref="T37:X37" si="65">T27/T26</f>
         <v>0.319129515160958</v>
       </c>
-      <c r="Q37" s="13">
-        <f t="shared" si="57"/>
+      <c r="U37" s="13">
+        <f t="shared" si="65"/>
         <v>0.28058721206873705</v>
       </c>
-      <c r="R37" s="13">
-        <f t="shared" si="57"/>
+      <c r="V37" s="13">
+        <f t="shared" si="65"/>
         <v>0.28124366876182338</v>
       </c>
-      <c r="S37" s="13">
-        <f t="shared" si="57"/>
+      <c r="W37" s="13">
+        <f t="shared" si="65"/>
         <v>0.2688022586925703</v>
       </c>
-      <c r="T37" s="13">
-        <f t="shared" si="57"/>
+      <c r="X37" s="13">
+        <f t="shared" si="65"/>
         <v>0.35853324138075948</v>
       </c>
-      <c r="U37" s="13">
-        <f>U27/U26</f>
+      <c r="Y37" s="13">
+        <f>Y27/Y26</f>
         <v>0.28750973808850788</v>
       </c>
-      <c r="V37" s="13">
-        <f>V27/V26</f>
+      <c r="Z37" s="13">
+        <f>Z27/Z26</f>
         <v>0.2955893787336325</v>
       </c>
-      <c r="W37" s="13">
-        <f>W27/W26</f>
+      <c r="AA37" s="13">
+        <f>AA27/AA26</f>
         <v>0.29468232448267428</v>
       </c>
     </row>
-    <row r="38" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:48" x14ac:dyDescent="0.2">
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -3763,8 +4115,12 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
-    </row>
-    <row r="39" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="W38" s="3"/>
+      <c r="X38" s="3"/>
+      <c r="Y38" s="3"/>
+      <c r="Z38" s="3"/>
+    </row>
+    <row r="39" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B39" s="15" t="s">
         <v>65</v>
       </c>
@@ -3786,17 +4142,21 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-      <c r="U39" s="3">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3">
         <v>2243.971</v>
       </c>
-      <c r="V39" s="3">
+      <c r="Z39" s="3">
         <v>1984.336</v>
       </c>
-      <c r="W39" s="3">
+      <c r="AA39" s="3">
         <v>1807.202</v>
       </c>
     </row>
-    <row r="40" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B40" s="15" t="s">
         <v>66</v>
       </c>
@@ -3818,17 +4178,21 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-      <c r="U40" s="3">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3">
         <v>124.76900000000001</v>
       </c>
-      <c r="V40" s="3">
+      <c r="Z40" s="3">
         <v>120.173</v>
       </c>
-      <c r="W40" s="3">
+      <c r="AA40" s="3">
         <v>190.65700000000001</v>
       </c>
     </row>
-    <row r="41" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B41" s="15" t="s">
         <v>67</v>
       </c>
@@ -3850,17 +4214,21 @@
       <c r="R41" s="3"/>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
-      <c r="U41" s="3">
+      <c r="U41" s="3"/>
+      <c r="V41" s="3"/>
+      <c r="W41" s="3"/>
+      <c r="X41" s="3"/>
+      <c r="Y41" s="3">
         <v>1323.6020000000001</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Z41" s="3">
         <v>1442.0809999999999</v>
       </c>
-      <c r="W41" s="3">
+      <c r="AA41" s="3">
         <v>1700.7529999999999</v>
       </c>
     </row>
-    <row r="42" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B42" s="15" t="s">
         <v>68</v>
       </c>
@@ -3882,17 +4250,21 @@
       <c r="R42" s="3"/>
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
-      <c r="U42" s="3">
+      <c r="U42" s="3"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3">
         <v>183.733</v>
       </c>
-      <c r="V42" s="3">
+      <c r="Z42" s="3">
         <v>182.25299999999999</v>
       </c>
-      <c r="W42" s="3">
+      <c r="AA42" s="3">
         <v>352.46899999999999</v>
       </c>
     </row>
-    <row r="43" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B43" s="15" t="s">
         <v>69</v>
       </c>
@@ -3914,17 +4286,21 @@
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
-      <c r="U43" s="3">
+      <c r="U43" s="3"/>
+      <c r="V43" s="3"/>
+      <c r="W43" s="3"/>
+      <c r="X43" s="3"/>
+      <c r="Y43" s="3">
         <v>184.50200000000001</v>
       </c>
-      <c r="V43" s="3">
+      <c r="Z43" s="3">
         <v>251.459</v>
       </c>
-      <c r="W43" s="3">
+      <c r="AA43" s="3">
         <v>211.62</v>
       </c>
     </row>
-    <row r="44" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B44" s="15" t="s">
         <v>70</v>
       </c>
@@ -3944,30 +4320,30 @@
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
       <c r="R44" s="3"/>
-      <c r="S44" s="3">
-        <f t="shared" ref="S44:U44" si="58">+SUM(S39:S43)</f>
+      <c r="S44" s="3"/>
+      <c r="T44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="V44" s="3"/>
+      <c r="W44" s="3">
+        <f t="shared" ref="W44:Y44" si="66">+SUM(W39:W43)</f>
         <v>0</v>
       </c>
-      <c r="T44" s="3">
-        <f t="shared" si="58"/>
+      <c r="X44" s="3">
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
-      <c r="U44" s="3">
-        <f t="shared" si="58"/>
+      <c r="Y44" s="3">
+        <f t="shared" si="66"/>
         <v>4060.5769999999998</v>
       </c>
-      <c r="V44" s="3">
-        <f>+SUM(V39:V43)</f>
+      <c r="Z44" s="3">
+        <f>+SUM(Z39:Z43)</f>
         <v>3980.3020000000001</v>
       </c>
-      <c r="W44" s="3">
-        <f>+SUM(W39:W43)</f>
+      <c r="AA44" s="3">
+        <f>+SUM(AA39:AA43)</f>
         <v>4262.701</v>
       </c>
-      <c r="X44" s="3"/>
-      <c r="Y44" s="3"/>
-      <c r="Z44" s="3"/>
-      <c r="AA44" s="3"/>
       <c r="AB44" s="3"/>
       <c r="AC44" s="3"/>
       <c r="AD44" s="3"/>
@@ -3985,8 +4361,12 @@
       <c r="AP44" s="3"/>
       <c r="AQ44" s="3"/>
       <c r="AR44" s="3"/>
-    </row>
-    <row r="45" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS44" s="3"/>
+      <c r="AT44" s="3"/>
+      <c r="AU44" s="3"/>
+      <c r="AV44" s="3"/>
+    </row>
+    <row r="45" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B45" s="15" t="s">
         <v>71</v>
       </c>
@@ -4008,19 +4388,19 @@
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3"/>
-      <c r="U45" s="3">
+      <c r="U45" s="3"/>
+      <c r="V45" s="3"/>
+      <c r="W45" s="3"/>
+      <c r="X45" s="3"/>
+      <c r="Y45" s="3">
         <v>1545.8109999999999</v>
       </c>
-      <c r="V45" s="3">
+      <c r="Z45" s="3">
         <v>1780.617</v>
       </c>
-      <c r="W45" s="3">
+      <c r="AA45" s="3">
         <v>2033.72</v>
       </c>
-      <c r="X45" s="3"/>
-      <c r="Y45" s="3"/>
-      <c r="Z45" s="3"/>
-      <c r="AA45" s="3"/>
       <c r="AB45" s="3"/>
       <c r="AC45" s="3"/>
       <c r="AD45" s="3"/>
@@ -4038,8 +4418,12 @@
       <c r="AP45" s="3"/>
       <c r="AQ45" s="3"/>
       <c r="AR45" s="3"/>
-    </row>
-    <row r="46" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS45" s="3"/>
+      <c r="AT45" s="3"/>
+      <c r="AU45" s="3"/>
+      <c r="AV45" s="3"/>
+    </row>
+    <row r="46" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B46" s="15" t="s">
         <v>72</v>
       </c>
@@ -4061,19 +4445,19 @@
       <c r="R46" s="3"/>
       <c r="S46" s="3"/>
       <c r="T46" s="3"/>
-      <c r="U46" s="3">
+      <c r="U46" s="3"/>
+      <c r="V46" s="3"/>
+      <c r="W46" s="3"/>
+      <c r="X46" s="3"/>
+      <c r="Y46" s="3">
         <v>1265.6099999999999</v>
       </c>
-      <c r="V46" s="3">
+      <c r="Z46" s="3">
         <v>1416.2560000000001</v>
       </c>
-      <c r="W46" s="3">
+      <c r="AA46" s="3">
         <v>1630.181</v>
       </c>
-      <c r="X46" s="3"/>
-      <c r="Y46" s="3"/>
-      <c r="Z46" s="3"/>
-      <c r="AA46" s="3"/>
       <c r="AB46" s="3"/>
       <c r="AC46" s="3"/>
       <c r="AD46" s="3"/>
@@ -4091,8 +4475,12 @@
       <c r="AP46" s="3"/>
       <c r="AQ46" s="3"/>
       <c r="AR46" s="3"/>
-    </row>
-    <row r="47" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS46" s="3"/>
+      <c r="AT46" s="3"/>
+      <c r="AU46" s="3"/>
+      <c r="AV46" s="3"/>
+    </row>
+    <row r="47" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B47" s="15" t="s">
         <v>73</v>
       </c>
@@ -4114,19 +4502,19 @@
       <c r="R47" s="3"/>
       <c r="S47" s="3"/>
       <c r="T47" s="3"/>
-      <c r="U47" s="3">
+      <c r="U47" s="3"/>
+      <c r="V47" s="3"/>
+      <c r="W47" s="3"/>
+      <c r="X47" s="3"/>
+      <c r="Y47" s="3">
         <v>24.082999999999998</v>
       </c>
-      <c r="V47" s="3">
+      <c r="Z47" s="3">
         <v>159.518</v>
       </c>
-      <c r="W47" s="3">
+      <c r="AA47" s="3">
         <v>184.911</v>
       </c>
-      <c r="X47" s="3"/>
-      <c r="Y47" s="3"/>
-      <c r="Z47" s="3"/>
-      <c r="AA47" s="3"/>
       <c r="AB47" s="3"/>
       <c r="AC47" s="3"/>
       <c r="AD47" s="3"/>
@@ -4144,8 +4532,12 @@
       <c r="AP47" s="3"/>
       <c r="AQ47" s="3"/>
       <c r="AR47" s="3"/>
-    </row>
-    <row r="48" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS47" s="3"/>
+      <c r="AT47" s="3"/>
+      <c r="AU47" s="3"/>
+      <c r="AV47" s="3"/>
+    </row>
+    <row r="48" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B48" s="15" t="s">
         <v>74</v>
       </c>
@@ -4167,19 +4559,19 @@
       <c r="R48" s="3"/>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
-      <c r="U48" s="3">
+      <c r="U48" s="3"/>
+      <c r="V48" s="3"/>
+      <c r="W48" s="3"/>
+      <c r="X48" s="3"/>
+      <c r="Y48" s="3">
         <v>0</v>
       </c>
-      <c r="V48" s="3">
+      <c r="Z48" s="3">
         <v>11.673</v>
       </c>
-      <c r="W48" s="3">
+      <c r="AA48" s="3">
         <v>6.2830000000000004</v>
       </c>
-      <c r="X48" s="3"/>
-      <c r="Y48" s="3"/>
-      <c r="Z48" s="3"/>
-      <c r="AA48" s="3"/>
       <c r="AB48" s="3"/>
       <c r="AC48" s="3"/>
       <c r="AD48" s="3"/>
@@ -4197,8 +4589,12 @@
       <c r="AP48" s="3"/>
       <c r="AQ48" s="3"/>
       <c r="AR48" s="3"/>
-    </row>
-    <row r="49" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS48" s="3"/>
+      <c r="AT48" s="3"/>
+      <c r="AU48" s="3"/>
+      <c r="AV48" s="3"/>
+    </row>
+    <row r="49" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B49" s="15" t="s">
         <v>75</v>
       </c>
@@ -4220,19 +4616,19 @@
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
-      <c r="U49" s="3">
+      <c r="U49" s="3"/>
+      <c r="V49" s="3"/>
+      <c r="W49" s="3"/>
+      <c r="X49" s="3"/>
+      <c r="Y49" s="3">
         <v>9.1760000000000002</v>
       </c>
-      <c r="V49" s="3">
+      <c r="Z49" s="3">
         <v>17.085000000000001</v>
       </c>
-      <c r="W49" s="3">
+      <c r="AA49" s="3">
         <v>24.036999999999999</v>
       </c>
-      <c r="X49" s="3"/>
-      <c r="Y49" s="3"/>
-      <c r="Z49" s="3"/>
-      <c r="AA49" s="3"/>
       <c r="AB49" s="3"/>
       <c r="AC49" s="3"/>
       <c r="AD49" s="3"/>
@@ -4250,8 +4646,12 @@
       <c r="AP49" s="3"/>
       <c r="AQ49" s="3"/>
       <c r="AR49" s="3"/>
-    </row>
-    <row r="50" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS49" s="3"/>
+      <c r="AT49" s="3"/>
+      <c r="AU49" s="3"/>
+      <c r="AV49" s="3"/>
+    </row>
+    <row r="50" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B50" s="15" t="s">
         <v>47</v>
       </c>
@@ -4273,19 +4673,19 @@
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
-      <c r="U50" s="3">
+      <c r="U50" s="3"/>
+      <c r="V50" s="3"/>
+      <c r="W50" s="3"/>
+      <c r="X50" s="3"/>
+      <c r="Y50" s="3">
         <v>186.684</v>
       </c>
-      <c r="V50" s="3">
+      <c r="Z50" s="3">
         <v>237.84100000000001</v>
       </c>
-      <c r="W50" s="3">
+      <c r="AA50" s="3">
         <v>314.91000000000003</v>
       </c>
-      <c r="X50" s="3"/>
-      <c r="Y50" s="3"/>
-      <c r="Z50" s="3"/>
-      <c r="AA50" s="3"/>
       <c r="AB50" s="3"/>
       <c r="AC50" s="3"/>
       <c r="AD50" s="3"/>
@@ -4303,8 +4703,12 @@
       <c r="AP50" s="3"/>
       <c r="AQ50" s="3"/>
       <c r="AR50" s="3"/>
-    </row>
-    <row r="51" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS50" s="3"/>
+      <c r="AT50" s="3"/>
+      <c r="AU50" s="3"/>
+      <c r="AV50" s="3"/>
+    </row>
+    <row r="51" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B51" s="15" t="s">
         <v>76</v>
       </c>
@@ -4325,26 +4729,26 @@
       <c r="Q51" s="3"/>
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
-      <c r="T51" s="3">
-        <f t="shared" ref="T51:U51" si="59">+SUM(T45:T50)</f>
+      <c r="T51" s="3"/>
+      <c r="U51" s="3"/>
+      <c r="V51" s="3"/>
+      <c r="W51" s="3"/>
+      <c r="X51" s="3">
+        <f t="shared" ref="X51:Y51" si="67">+SUM(X45:X50)</f>
         <v>0</v>
       </c>
-      <c r="U51" s="3">
-        <f t="shared" si="59"/>
+      <c r="Y51" s="3">
+        <f t="shared" si="67"/>
         <v>3031.364</v>
       </c>
-      <c r="V51" s="3">
-        <f>+SUM(V45:V50)</f>
+      <c r="Z51" s="3">
+        <f>+SUM(Z45:Z50)</f>
         <v>3622.99</v>
       </c>
-      <c r="W51" s="3">
-        <f>+SUM(W45:W50)</f>
+      <c r="AA51" s="3">
+        <f>+SUM(AA45:AA50)</f>
         <v>4194.0419999999995</v>
       </c>
-      <c r="X51" s="3"/>
-      <c r="Y51" s="3"/>
-      <c r="Z51" s="3"/>
-      <c r="AA51" s="3"/>
       <c r="AB51" s="3"/>
       <c r="AC51" s="3"/>
       <c r="AD51" s="3"/>
@@ -4362,8 +4766,12 @@
       <c r="AP51" s="3"/>
       <c r="AQ51" s="3"/>
       <c r="AR51" s="3"/>
-    </row>
-    <row r="52" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS51" s="3"/>
+      <c r="AT51" s="3"/>
+      <c r="AU51" s="3"/>
+      <c r="AV51" s="3"/>
+    </row>
+    <row r="52" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
         <v>77</v>
       </c>
@@ -4384,26 +4792,26 @@
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
-      <c r="T52" s="11">
-        <f t="shared" ref="T52:U52" si="60">+T51+T44</f>
+      <c r="T52" s="3"/>
+      <c r="U52" s="3"/>
+      <c r="V52" s="3"/>
+      <c r="W52" s="3"/>
+      <c r="X52" s="11">
+        <f t="shared" ref="X52:Y52" si="68">+X51+X44</f>
         <v>0</v>
       </c>
-      <c r="U52" s="11">
-        <f t="shared" si="60"/>
+      <c r="Y52" s="11">
+        <f t="shared" si="68"/>
         <v>7091.9409999999998</v>
       </c>
-      <c r="V52" s="11">
-        <f>+V51+V44</f>
+      <c r="Z52" s="11">
+        <f>+Z51+Z44</f>
         <v>7603.2919999999995</v>
       </c>
-      <c r="W52" s="11">
-        <f>+W51+W44</f>
+      <c r="AA52" s="11">
+        <f>+AA51+AA44</f>
         <v>8456.7429999999986</v>
       </c>
-      <c r="X52" s="3"/>
-      <c r="Y52" s="3"/>
-      <c r="Z52" s="3"/>
-      <c r="AA52" s="3"/>
       <c r="AB52" s="3"/>
       <c r="AC52" s="3"/>
       <c r="AD52" s="3"/>
@@ -4421,8 +4829,12 @@
       <c r="AP52" s="3"/>
       <c r="AQ52" s="3"/>
       <c r="AR52" s="3"/>
-    </row>
-    <row r="53" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS52" s="3"/>
+      <c r="AT52" s="3"/>
+      <c r="AU52" s="3"/>
+      <c r="AV52" s="3"/>
+    </row>
+    <row r="53" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B53" s="15" t="s">
         <v>80</v>
       </c>
@@ -4444,19 +4856,19 @@
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
       <c r="T53" s="3"/>
-      <c r="U53" s="3">
+      <c r="U53" s="3"/>
+      <c r="V53" s="3"/>
+      <c r="W53" s="3"/>
+      <c r="X53" s="3"/>
+      <c r="Y53" s="3">
         <v>348.44099999999997</v>
       </c>
-      <c r="V53" s="3">
+      <c r="Z53" s="3">
         <v>271.40600000000001</v>
       </c>
-      <c r="W53" s="3">
+      <c r="AA53" s="3">
         <v>331.42099999999999</v>
       </c>
-      <c r="X53" s="3"/>
-      <c r="Y53" s="3"/>
-      <c r="Z53" s="3"/>
-      <c r="AA53" s="3"/>
       <c r="AB53" s="3"/>
       <c r="AC53" s="3"/>
       <c r="AD53" s="3"/>
@@ -4474,8 +4886,12 @@
       <c r="AP53" s="3"/>
       <c r="AQ53" s="3"/>
       <c r="AR53" s="3"/>
-    </row>
-    <row r="54" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS53" s="3"/>
+      <c r="AT53" s="3"/>
+      <c r="AU53" s="3"/>
+      <c r="AV53" s="3"/>
+    </row>
+    <row r="54" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B54" s="15" t="s">
         <v>81</v>
       </c>
@@ -4497,19 +4913,19 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
-      <c r="U54" s="3">
+      <c r="U54" s="3"/>
+      <c r="V54" s="3"/>
+      <c r="W54" s="3"/>
+      <c r="X54" s="3"/>
+      <c r="Y54" s="3">
         <v>348.55500000000001</v>
       </c>
-      <c r="V54" s="3">
+      <c r="Z54" s="3">
         <v>559.46299999999997</v>
       </c>
-      <c r="W54" s="3">
+      <c r="AA54" s="3">
         <v>662.98199999999997</v>
       </c>
-      <c r="X54" s="3"/>
-      <c r="Y54" s="3"/>
-      <c r="Z54" s="3"/>
-      <c r="AA54" s="3"/>
       <c r="AB54" s="3"/>
       <c r="AC54" s="3"/>
       <c r="AD54" s="3"/>
@@ -4527,8 +4943,12 @@
       <c r="AP54" s="3"/>
       <c r="AQ54" s="3"/>
       <c r="AR54" s="3"/>
-    </row>
-    <row r="55" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS54" s="3"/>
+      <c r="AT54" s="3"/>
+      <c r="AU54" s="3"/>
+      <c r="AV54" s="3"/>
+    </row>
+    <row r="55" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B55" s="15" t="s">
         <v>82</v>
       </c>
@@ -4550,19 +4970,19 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-      <c r="U55" s="3">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3">
         <v>326.11</v>
       </c>
-      <c r="V55" s="3">
+      <c r="Z55" s="3">
         <v>204.54300000000001</v>
       </c>
-      <c r="W55" s="3">
+      <c r="AA55" s="3">
         <v>187.887</v>
       </c>
-      <c r="X55" s="3"/>
-      <c r="Y55" s="3"/>
-      <c r="Z55" s="3"/>
-      <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
@@ -4580,8 +5000,12 @@
       <c r="AP55" s="3"/>
       <c r="AQ55" s="3"/>
       <c r="AR55" s="3"/>
-    </row>
-    <row r="56" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS55" s="3"/>
+      <c r="AT55" s="3"/>
+      <c r="AU55" s="3"/>
+      <c r="AV55" s="3"/>
+    </row>
+    <row r="56" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B56" s="15" t="s">
         <v>83</v>
       </c>
@@ -4603,19 +5027,19 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-      <c r="U56" s="3">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3">
         <v>249.27</v>
       </c>
-      <c r="V56" s="3">
+      <c r="Z56" s="3">
         <v>275.154</v>
       </c>
-      <c r="W56" s="3">
+      <c r="AA56" s="3">
         <v>298.72399999999999</v>
       </c>
-      <c r="X56" s="3"/>
-      <c r="Y56" s="3"/>
-      <c r="Z56" s="3"/>
-      <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
@@ -4633,8 +5057,12 @@
       <c r="AP56" s="3"/>
       <c r="AQ56" s="3"/>
       <c r="AR56" s="3"/>
-    </row>
-    <row r="57" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS56" s="3"/>
+      <c r="AT56" s="3"/>
+      <c r="AU56" s="3"/>
+      <c r="AV56" s="3"/>
+    </row>
+    <row r="57" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B57" s="15" t="s">
         <v>84</v>
       </c>
@@ -4656,19 +5084,19 @@
       <c r="R57" s="3"/>
       <c r="S57" s="3"/>
       <c r="T57" s="3"/>
-      <c r="U57" s="3">
+      <c r="U57" s="3"/>
+      <c r="V57" s="3"/>
+      <c r="W57" s="3"/>
+      <c r="X57" s="3"/>
+      <c r="Y57" s="3">
         <v>12.098000000000001</v>
       </c>
-      <c r="V57" s="3">
+      <c r="Z57" s="3">
         <v>183.126</v>
       </c>
-      <c r="W57" s="3">
+      <c r="AA57" s="3">
         <v>43.948</v>
       </c>
-      <c r="X57" s="3"/>
-      <c r="Y57" s="3"/>
-      <c r="Z57" s="3"/>
-      <c r="AA57" s="3"/>
       <c r="AB57" s="3"/>
       <c r="AC57" s="3"/>
       <c r="AD57" s="3"/>
@@ -4686,8 +5114,12 @@
       <c r="AP57" s="3"/>
       <c r="AQ57" s="3"/>
       <c r="AR57" s="3"/>
-    </row>
-    <row r="58" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS57" s="3"/>
+      <c r="AT57" s="3"/>
+      <c r="AU57" s="3"/>
+      <c r="AV57" s="3"/>
+    </row>
+    <row r="58" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B58" s="15" t="s">
         <v>85</v>
       </c>
@@ -4709,19 +5141,19 @@
       <c r="R58" s="3"/>
       <c r="S58" s="3"/>
       <c r="T58" s="3"/>
-      <c r="U58" s="3">
+      <c r="U58" s="3"/>
+      <c r="V58" s="3"/>
+      <c r="W58" s="3"/>
+      <c r="X58" s="3"/>
+      <c r="Y58" s="3">
         <v>306.47899999999998</v>
       </c>
-      <c r="V58" s="3">
+      <c r="Z58" s="3">
         <v>308.35199999999998</v>
       </c>
-      <c r="W58" s="3">
+      <c r="AA58" s="3">
         <v>316.63200000000001</v>
       </c>
-      <c r="X58" s="3"/>
-      <c r="Y58" s="3"/>
-      <c r="Z58" s="3"/>
-      <c r="AA58" s="3"/>
       <c r="AB58" s="3"/>
       <c r="AC58" s="3"/>
       <c r="AD58" s="3"/>
@@ -4739,8 +5171,12 @@
       <c r="AP58" s="3"/>
       <c r="AQ58" s="3"/>
       <c r="AR58" s="3"/>
-    </row>
-    <row r="59" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS58" s="3"/>
+      <c r="AT58" s="3"/>
+      <c r="AU58" s="3"/>
+      <c r="AV58" s="3"/>
+    </row>
+    <row r="59" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B59" s="15" t="s">
         <v>47</v>
       </c>
@@ -4762,19 +5198,19 @@
       <c r="R59" s="3"/>
       <c r="S59" s="3"/>
       <c r="T59" s="3"/>
-      <c r="U59" s="3">
+      <c r="U59" s="3"/>
+      <c r="V59" s="3"/>
+      <c r="W59" s="3"/>
+      <c r="X59" s="3"/>
+      <c r="Y59" s="3">
         <v>40.308</v>
       </c>
-      <c r="V59" s="3">
+      <c r="Z59" s="3">
         <v>37.585999999999999</v>
       </c>
-      <c r="W59" s="3">
+      <c r="AA59" s="3">
         <v>45.954000000000001</v>
       </c>
-      <c r="X59" s="3"/>
-      <c r="Y59" s="3"/>
-      <c r="Z59" s="3"/>
-      <c r="AA59" s="3"/>
       <c r="AB59" s="3"/>
       <c r="AC59" s="3"/>
       <c r="AD59" s="3"/>
@@ -4792,8 +5228,12 @@
       <c r="AP59" s="3"/>
       <c r="AQ59" s="3"/>
       <c r="AR59" s="3"/>
-    </row>
-    <row r="60" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS59" s="3"/>
+      <c r="AT59" s="3"/>
+      <c r="AU59" s="3"/>
+      <c r="AV59" s="3"/>
+    </row>
+    <row r="60" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B60" s="15" t="s">
         <v>86</v>
       </c>
@@ -4814,26 +5254,26 @@
       <c r="Q60" s="3"/>
       <c r="R60" s="3"/>
       <c r="S60" s="3"/>
-      <c r="T60" s="3">
-        <f t="shared" ref="T60:U60" si="61">+SUM(T53:T59)</f>
+      <c r="T60" s="3"/>
+      <c r="U60" s="3"/>
+      <c r="V60" s="3"/>
+      <c r="W60" s="3"/>
+      <c r="X60" s="3">
+        <f t="shared" ref="X60:Y60" si="69">+SUM(X53:X59)</f>
         <v>0</v>
       </c>
-      <c r="U60" s="3">
-        <f t="shared" si="61"/>
+      <c r="Y60" s="3">
+        <f t="shared" si="69"/>
         <v>1631.261</v>
       </c>
-      <c r="V60" s="3">
-        <f>+SUM(V53:V59)</f>
+      <c r="Z60" s="3">
+        <f>+SUM(Z53:Z59)</f>
         <v>1839.6299999999999</v>
       </c>
-      <c r="W60" s="3">
-        <f>+SUM(W53:W59)</f>
+      <c r="AA60" s="3">
+        <f>+SUM(AA53:AA59)</f>
         <v>1887.548</v>
       </c>
-      <c r="X60" s="3"/>
-      <c r="Y60" s="3"/>
-      <c r="Z60" s="3"/>
-      <c r="AA60" s="3"/>
       <c r="AB60" s="3"/>
       <c r="AC60" s="3"/>
       <c r="AD60" s="3"/>
@@ -4851,8 +5291,12 @@
       <c r="AP60" s="3"/>
       <c r="AQ60" s="3"/>
       <c r="AR60" s="3"/>
-    </row>
-    <row r="61" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS60" s="3"/>
+      <c r="AT60" s="3"/>
+      <c r="AU60" s="3"/>
+      <c r="AV60" s="3"/>
+    </row>
+    <row r="61" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B61" s="15" t="s">
         <v>83</v>
       </c>
@@ -4874,19 +5318,19 @@
       <c r="R61" s="3"/>
       <c r="S61" s="3"/>
       <c r="T61" s="3"/>
-      <c r="U61" s="3">
+      <c r="U61" s="3"/>
+      <c r="V61" s="3"/>
+      <c r="W61" s="3"/>
+      <c r="X61" s="3"/>
+      <c r="Y61" s="3">
         <v>1154.0119999999999</v>
       </c>
-      <c r="V61" s="3">
+      <c r="Z61" s="3">
         <v>1300.6369999999999</v>
       </c>
-      <c r="W61" s="3">
+      <c r="AA61" s="3">
         <v>1499.7170000000001</v>
       </c>
-      <c r="X61" s="3"/>
-      <c r="Y61" s="3"/>
-      <c r="Z61" s="3"/>
-      <c r="AA61" s="3"/>
       <c r="AB61" s="3"/>
       <c r="AC61" s="3"/>
       <c r="AD61" s="3"/>
@@ -4904,8 +5348,12 @@
       <c r="AP61" s="3"/>
       <c r="AQ61" s="3"/>
       <c r="AR61" s="3"/>
-    </row>
-    <row r="62" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS61" s="3"/>
+      <c r="AT61" s="3"/>
+      <c r="AU61" s="3"/>
+      <c r="AV61" s="3"/>
+    </row>
+    <row r="62" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B62" s="15" t="s">
         <v>84</v>
       </c>
@@ -4927,19 +5375,19 @@
       <c r="R62" s="3"/>
       <c r="S62" s="3"/>
       <c r="T62" s="3"/>
-      <c r="U62" s="3">
+      <c r="U62" s="3"/>
+      <c r="V62" s="3"/>
+      <c r="W62" s="3"/>
+      <c r="X62" s="3"/>
+      <c r="Y62" s="3">
         <v>15.864000000000001</v>
       </c>
-      <c r="V62" s="3">
+      <c r="Z62" s="3">
         <v>0</v>
       </c>
-      <c r="W62" s="3">
+      <c r="AA62" s="3">
         <v>0</v>
       </c>
-      <c r="X62" s="3"/>
-      <c r="Y62" s="3"/>
-      <c r="Z62" s="3"/>
-      <c r="AA62" s="3"/>
       <c r="AB62" s="3"/>
       <c r="AC62" s="3"/>
       <c r="AD62" s="3"/>
@@ -4957,8 +5405,12 @@
       <c r="AP62" s="3"/>
       <c r="AQ62" s="3"/>
       <c r="AR62" s="3"/>
-    </row>
-    <row r="63" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS62" s="3"/>
+      <c r="AT62" s="3"/>
+      <c r="AU62" s="3"/>
+      <c r="AV62" s="3"/>
+    </row>
+    <row r="63" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B63" s="15" t="s">
         <v>75</v>
       </c>
@@ -4980,19 +5432,19 @@
       <c r="R63" s="3"/>
       <c r="S63" s="3"/>
       <c r="T63" s="3"/>
-      <c r="U63" s="3">
+      <c r="U63" s="3"/>
+      <c r="V63" s="3"/>
+      <c r="W63" s="3"/>
+      <c r="X63" s="3"/>
+      <c r="Y63" s="3">
         <v>29.521999999999998</v>
       </c>
-      <c r="V63" s="3">
+      <c r="Z63" s="3">
         <v>98.188000000000002</v>
       </c>
-      <c r="W63" s="3">
+      <c r="AA63" s="3">
         <v>52.277999999999999</v>
       </c>
-      <c r="X63" s="3"/>
-      <c r="Y63" s="3"/>
-      <c r="Z63" s="3"/>
-      <c r="AA63" s="3"/>
       <c r="AB63" s="3"/>
       <c r="AC63" s="3"/>
       <c r="AD63" s="3"/>
@@ -5010,8 +5462,12 @@
       <c r="AP63" s="3"/>
       <c r="AQ63" s="3"/>
       <c r="AR63" s="3"/>
-    </row>
-    <row r="64" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS63" s="3"/>
+      <c r="AT63" s="3"/>
+      <c r="AU63" s="3"/>
+      <c r="AV63" s="3"/>
+    </row>
+    <row r="64" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B64" s="15" t="s">
         <v>47</v>
       </c>
@@ -5033,19 +5489,19 @@
       <c r="R64" s="3"/>
       <c r="S64" s="3"/>
       <c r="T64" s="3"/>
-      <c r="U64" s="3">
+      <c r="U64" s="3"/>
+      <c r="V64" s="3"/>
+      <c r="W64" s="3"/>
+      <c r="X64" s="3"/>
+      <c r="Y64" s="3">
         <v>29.201000000000001</v>
       </c>
-      <c r="V64" s="3">
+      <c r="Z64" s="3">
         <v>40.79</v>
       </c>
-      <c r="W64" s="3">
+      <c r="AA64" s="3">
         <v>55.36</v>
       </c>
-      <c r="X64" s="3"/>
-      <c r="Y64" s="3"/>
-      <c r="Z64" s="3"/>
-      <c r="AA64" s="3"/>
       <c r="AB64" s="3"/>
       <c r="AC64" s="3"/>
       <c r="AD64" s="3"/>
@@ -5063,8 +5519,12 @@
       <c r="AP64" s="3"/>
       <c r="AQ64" s="3"/>
       <c r="AR64" s="3"/>
-    </row>
-    <row r="65" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS64" s="3"/>
+      <c r="AT64" s="3"/>
+      <c r="AU64" s="3"/>
+      <c r="AV64" s="3"/>
+    </row>
+    <row r="65" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B65" s="15" t="s">
         <v>79</v>
       </c>
@@ -5086,22 +5546,22 @@
       <c r="R65" s="3"/>
       <c r="S65" s="3"/>
       <c r="T65" s="3"/>
-      <c r="U65" s="3">
-        <f>+SUM(U61:U64)</f>
+      <c r="U65" s="3"/>
+      <c r="V65" s="3"/>
+      <c r="W65" s="3"/>
+      <c r="X65" s="3"/>
+      <c r="Y65" s="3">
+        <f>+SUM(Y61:Y64)</f>
         <v>1228.5989999999999</v>
       </c>
-      <c r="V65" s="3">
-        <f>+SUM(V61:V64)</f>
+      <c r="Z65" s="3">
+        <f>+SUM(Z61:Z64)</f>
         <v>1439.615</v>
       </c>
-      <c r="W65" s="3">
-        <f>+SUM(W61:W64)</f>
+      <c r="AA65" s="3">
+        <f>+SUM(AA61:AA64)</f>
         <v>1607.355</v>
       </c>
-      <c r="X65" s="3"/>
-      <c r="Y65" s="3"/>
-      <c r="Z65" s="3"/>
-      <c r="AA65" s="3"/>
       <c r="AB65" s="3"/>
       <c r="AC65" s="3"/>
       <c r="AD65" s="3"/>
@@ -5119,8 +5579,12 @@
       <c r="AP65" s="3"/>
       <c r="AQ65" s="3"/>
       <c r="AR65" s="3"/>
-    </row>
-    <row r="66" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS65" s="3"/>
+      <c r="AT65" s="3"/>
+      <c r="AU65" s="3"/>
+      <c r="AV65" s="3"/>
+    </row>
+    <row r="66" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B66" s="15" t="s">
         <v>87</v>
       </c>
@@ -5142,19 +5606,19 @@
       <c r="R66" s="3"/>
       <c r="S66" s="3"/>
       <c r="T66" s="3"/>
-      <c r="U66" s="3">
+      <c r="U66" s="3"/>
+      <c r="V66" s="3"/>
+      <c r="W66" s="3"/>
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3">
         <v>4232.0810000000001</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Z66" s="3">
         <v>4324.0469999999996</v>
       </c>
-      <c r="W66" s="3">
+      <c r="AA66" s="3">
         <v>4961.84</v>
       </c>
-      <c r="X66" s="3"/>
-      <c r="Y66" s="3"/>
-      <c r="Z66" s="3"/>
-      <c r="AA66" s="3"/>
       <c r="AB66" s="3"/>
       <c r="AC66" s="3"/>
       <c r="AD66" s="3"/>
@@ -5172,8 +5636,12 @@
       <c r="AP66" s="3"/>
       <c r="AQ66" s="3"/>
       <c r="AR66" s="3"/>
-    </row>
-    <row r="67" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS66" s="3"/>
+      <c r="AT66" s="3"/>
+      <c r="AU66" s="3"/>
+      <c r="AV66" s="3"/>
+    </row>
+    <row r="67" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B67" s="1" t="s">
         <v>78</v>
       </c>
@@ -5194,26 +5662,26 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-      <c r="T67" s="11">
-        <f t="shared" ref="T67:U67" si="62">+T66+T65+T60</f>
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+      <c r="X67" s="11">
+        <f t="shared" ref="X67:Y67" si="70">+X66+X65+X60</f>
         <v>0</v>
       </c>
-      <c r="U67" s="11">
-        <f t="shared" si="62"/>
+      <c r="Y67" s="11">
+        <f t="shared" si="70"/>
         <v>7091.9410000000007</v>
       </c>
-      <c r="V67" s="11">
-        <f>+V66+V65+V60</f>
+      <c r="Z67" s="11">
+        <f>+Z66+Z65+Z60</f>
         <v>7603.2919999999995</v>
       </c>
-      <c r="W67" s="11">
-        <f>+W66+W65+W60</f>
+      <c r="AA67" s="11">
+        <f>+AA66+AA65+AA60</f>
         <v>8456.7430000000004</v>
       </c>
-      <c r="X67" s="3"/>
-      <c r="Y67" s="3"/>
-      <c r="Z67" s="3"/>
-      <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
@@ -5231,8 +5699,12 @@
       <c r="AP67" s="3"/>
       <c r="AQ67" s="3"/>
       <c r="AR67" s="3"/>
-    </row>
-    <row r="68" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS67" s="3"/>
+      <c r="AT67" s="3"/>
+      <c r="AU67" s="3"/>
+      <c r="AV67" s="3"/>
+    </row>
+    <row r="68" spans="2:48" x14ac:dyDescent="0.2">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -5275,8 +5747,12 @@
       <c r="AP68" s="3"/>
       <c r="AQ68" s="3"/>
       <c r="AR68" s="3"/>
-    </row>
-    <row r="69" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS68" s="3"/>
+      <c r="AT68" s="3"/>
+      <c r="AU68" s="3"/>
+      <c r="AV68" s="3"/>
+    </row>
+    <row r="69" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B69" s="15" t="s">
         <v>26</v>
       </c>
@@ -5297,26 +5773,26 @@
       <c r="Q69" s="3"/>
       <c r="R69" s="3"/>
       <c r="S69" s="3"/>
-      <c r="T69" s="3">
-        <f t="shared" ref="T69:U69" si="63">+T28</f>
+      <c r="T69" s="3"/>
+      <c r="U69" s="3"/>
+      <c r="V69" s="3"/>
+      <c r="W69" s="3"/>
+      <c r="X69" s="3">
+        <f t="shared" ref="X69:Y69" si="71">+X28</f>
         <v>854.8</v>
       </c>
-      <c r="U69" s="3">
-        <f t="shared" si="63"/>
+      <c r="Y69" s="3">
+        <f t="shared" si="71"/>
         <v>1550.190000000001</v>
       </c>
-      <c r="V69" s="3">
-        <f>+V28</f>
+      <c r="Z69" s="3">
+        <f>+Z28</f>
         <v>1814.6160000000007</v>
       </c>
-      <c r="W69" s="3">
-        <f>+W28</f>
+      <c r="AA69" s="3">
+        <f>+AA28</f>
         <v>1579.1830000000004</v>
       </c>
-      <c r="X69" s="3"/>
-      <c r="Y69" s="3"/>
-      <c r="Z69" s="3"/>
-      <c r="AA69" s="3"/>
       <c r="AB69" s="3"/>
       <c r="AC69" s="3"/>
       <c r="AD69" s="3"/>
@@ -5334,8 +5810,12 @@
       <c r="AP69" s="3"/>
       <c r="AQ69" s="3"/>
       <c r="AR69" s="3"/>
-    </row>
-    <row r="70" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS69" s="3"/>
+      <c r="AT69" s="3"/>
+      <c r="AU69" s="3"/>
+      <c r="AV69" s="3"/>
+    </row>
+    <row r="70" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B70" s="15" t="s">
         <v>89</v>
       </c>
@@ -5356,22 +5836,22 @@
       <c r="Q70" s="3"/>
       <c r="R70" s="3"/>
       <c r="S70" s="3"/>
-      <c r="T70" s="3">
+      <c r="T70" s="3"/>
+      <c r="U70" s="3"/>
+      <c r="V70" s="3"/>
+      <c r="W70" s="3"/>
+      <c r="X70" s="3">
         <v>291.791</v>
       </c>
-      <c r="U70" s="3">
+      <c r="Y70" s="3">
         <v>379.38400000000001</v>
       </c>
-      <c r="V70" s="3">
+      <c r="Z70" s="3">
         <v>446.524</v>
       </c>
-      <c r="W70" s="3">
+      <c r="AA70" s="3">
         <v>496.22800000000001</v>
       </c>
-      <c r="X70" s="3"/>
-      <c r="Y70" s="3"/>
-      <c r="Z70" s="3"/>
-      <c r="AA70" s="3"/>
       <c r="AB70" s="3"/>
       <c r="AC70" s="3"/>
       <c r="AD70" s="3"/>
@@ -5389,8 +5869,12 @@
       <c r="AP70" s="3"/>
       <c r="AQ70" s="3"/>
       <c r="AR70" s="3"/>
-    </row>
-    <row r="71" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS70" s="3"/>
+      <c r="AT70" s="3"/>
+      <c r="AU70" s="3"/>
+      <c r="AV70" s="3"/>
+    </row>
+    <row r="71" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B71" s="15" t="s">
         <v>90</v>
       </c>
@@ -5411,24 +5895,24 @@
       <c r="Q71" s="3"/>
       <c r="R71" s="3"/>
       <c r="S71" s="3"/>
-      <c r="T71" s="3">
+      <c r="T71" s="3"/>
+      <c r="U71" s="3"/>
+      <c r="V71" s="3"/>
+      <c r="W71" s="3"/>
+      <c r="X71" s="3">
         <f>62.928+407.913-10.18</f>
         <v>460.661</v>
       </c>
-      <c r="U71" s="3">
+      <c r="Y71" s="3">
         <f>23.709+74.501</f>
         <v>98.210000000000008</v>
       </c>
-      <c r="V71" s="3">
+      <c r="Z71" s="3">
         <v>0</v>
       </c>
-      <c r="W71" s="3">
+      <c r="AA71" s="3">
         <v>0</v>
       </c>
-      <c r="X71" s="3"/>
-      <c r="Y71" s="3"/>
-      <c r="Z71" s="3"/>
-      <c r="AA71" s="3"/>
       <c r="AB71" s="3"/>
       <c r="AC71" s="3"/>
       <c r="AD71" s="3"/>
@@ -5446,8 +5930,12 @@
       <c r="AP71" s="3"/>
       <c r="AQ71" s="3"/>
       <c r="AR71" s="3"/>
-    </row>
-    <row r="72" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS71" s="3"/>
+      <c r="AT71" s="3"/>
+      <c r="AU71" s="3"/>
+      <c r="AV71" s="3"/>
+    </row>
+    <row r="72" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B72" s="15" t="s">
         <v>91</v>
       </c>
@@ -5468,22 +5956,22 @@
       <c r="Q72" s="3"/>
       <c r="R72" s="3"/>
       <c r="S72" s="3"/>
-      <c r="T72" s="3">
+      <c r="T72" s="3"/>
+      <c r="U72" s="3"/>
+      <c r="V72" s="3"/>
+      <c r="W72" s="3"/>
+      <c r="X72" s="3">
         <v>78.075000000000003</v>
       </c>
-      <c r="U72" s="3">
+      <c r="Y72" s="3">
         <v>93.56</v>
       </c>
-      <c r="V72" s="3">
+      <c r="Z72" s="3">
         <v>90.010999999999996</v>
       </c>
-      <c r="W72" s="3">
+      <c r="AA72" s="3">
         <v>62.203000000000003</v>
       </c>
-      <c r="X72" s="3"/>
-      <c r="Y72" s="3"/>
-      <c r="Z72" s="3"/>
-      <c r="AA72" s="3"/>
       <c r="AB72" s="3"/>
       <c r="AC72" s="3"/>
       <c r="AD72" s="3"/>
@@ -5501,8 +5989,12 @@
       <c r="AP72" s="3"/>
       <c r="AQ72" s="3"/>
       <c r="AR72" s="3"/>
-    </row>
-    <row r="73" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS72" s="3"/>
+      <c r="AT72" s="3"/>
+      <c r="AU72" s="3"/>
+      <c r="AV72" s="3"/>
+    </row>
+    <row r="73" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B73" s="15" t="s">
         <v>92</v>
       </c>
@@ -5523,22 +6015,22 @@
       <c r="Q73" s="3"/>
       <c r="R73" s="3"/>
       <c r="S73" s="3"/>
-      <c r="T73" s="3">
+      <c r="T73" s="3"/>
+      <c r="U73" s="3"/>
+      <c r="V73" s="3"/>
+      <c r="W73" s="3"/>
+      <c r="X73" s="3">
         <v>-23.337</v>
       </c>
-      <c r="U73" s="3">
+      <c r="Y73" s="3">
         <v>-28.547000000000001</v>
       </c>
-      <c r="V73" s="3">
+      <c r="Z73" s="3">
         <v>-36.231000000000002</v>
       </c>
-      <c r="W73" s="3">
+      <c r="AA73" s="3">
         <v>-37.765999999999998</v>
       </c>
-      <c r="X73" s="3"/>
-      <c r="Y73" s="3"/>
-      <c r="Z73" s="3"/>
-      <c r="AA73" s="3"/>
       <c r="AB73" s="3"/>
       <c r="AC73" s="3"/>
       <c r="AD73" s="3"/>
@@ -5556,8 +6048,12 @@
       <c r="AP73" s="3"/>
       <c r="AQ73" s="3"/>
       <c r="AR73" s="3"/>
-    </row>
-    <row r="74" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS73" s="3"/>
+      <c r="AT73" s="3"/>
+      <c r="AU73" s="3"/>
+      <c r="AV73" s="3"/>
+    </row>
+    <row r="74" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B74" s="15" t="s">
         <v>93</v>
       </c>
@@ -5578,22 +6074,22 @@
       <c r="Q74" s="3"/>
       <c r="R74" s="3"/>
       <c r="S74" s="3"/>
-      <c r="T74" s="3">
+      <c r="T74" s="3"/>
+      <c r="U74" s="3"/>
+      <c r="V74" s="3"/>
+      <c r="W74" s="3"/>
+      <c r="X74" s="3">
         <v>-38.649000000000001</v>
       </c>
-      <c r="U74" s="3">
+      <c r="Y74" s="3">
         <v>32.527000000000001</v>
       </c>
-      <c r="V74" s="3">
+      <c r="Z74" s="3">
         <v>-47.762999999999998</v>
       </c>
-      <c r="W74" s="3">
+      <c r="AA74" s="3">
         <v>-34.552</v>
       </c>
-      <c r="X74" s="3"/>
-      <c r="Y74" s="3"/>
-      <c r="Z74" s="3"/>
-      <c r="AA74" s="3"/>
       <c r="AB74" s="3"/>
       <c r="AC74" s="3"/>
       <c r="AD74" s="3"/>
@@ -5611,8 +6107,12 @@
       <c r="AP74" s="3"/>
       <c r="AQ74" s="3"/>
       <c r="AR74" s="3"/>
-    </row>
-    <row r="75" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS74" s="3"/>
+      <c r="AT74" s="3"/>
+      <c r="AU74" s="3"/>
+      <c r="AV74" s="3"/>
+    </row>
+    <row r="75" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B75" s="15" t="s">
         <v>75</v>
       </c>
@@ -5633,22 +6133,22 @@
       <c r="Q75" s="3"/>
       <c r="R75" s="3"/>
       <c r="S75" s="3"/>
-      <c r="T75" s="3">
+      <c r="T75" s="3"/>
+      <c r="U75" s="3"/>
+      <c r="V75" s="3"/>
+      <c r="W75" s="3"/>
+      <c r="X75" s="3">
         <v>3.0419999999999998</v>
       </c>
-      <c r="U75" s="3">
+      <c r="Y75" s="3">
         <v>-28.382999999999999</v>
       </c>
-      <c r="V75" s="3">
+      <c r="Z75" s="3">
         <v>57.451000000000001</v>
       </c>
-      <c r="W75" s="3">
+      <c r="AA75" s="3">
         <v>-53.378999999999998</v>
       </c>
-      <c r="X75" s="3"/>
-      <c r="Y75" s="3"/>
-      <c r="Z75" s="3"/>
-      <c r="AA75" s="3"/>
       <c r="AB75" s="3"/>
       <c r="AC75" s="3"/>
       <c r="AD75" s="3"/>
@@ -5666,8 +6166,12 @@
       <c r="AP75" s="3"/>
       <c r="AQ75" s="3"/>
       <c r="AR75" s="3"/>
-    </row>
-    <row r="76" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS75" s="3"/>
+      <c r="AT75" s="3"/>
+      <c r="AU75" s="3"/>
+      <c r="AV75" s="3"/>
+    </row>
+    <row r="76" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B76" s="15" t="s">
         <v>94</v>
       </c>
@@ -5688,22 +6192,22 @@
       <c r="Q76" s="3"/>
       <c r="R76" s="3"/>
       <c r="S76" s="3"/>
-      <c r="T76" s="3">
+      <c r="T76" s="3"/>
+      <c r="U76" s="3"/>
+      <c r="V76" s="3"/>
+      <c r="W76" s="3"/>
+      <c r="X76" s="3">
         <v>-58.987000000000002</v>
       </c>
-      <c r="U76" s="3">
+      <c r="Y76" s="3">
         <v>6.58</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Z76" s="3">
         <v>1.6259999999999999</v>
       </c>
-      <c r="W76" s="3">
+      <c r="AA76" s="3">
         <v>-65.754999999999995</v>
       </c>
-      <c r="X76" s="3"/>
-      <c r="Y76" s="3"/>
-      <c r="Z76" s="3"/>
-      <c r="AA76" s="3"/>
       <c r="AB76" s="3"/>
       <c r="AC76" s="3"/>
       <c r="AD76" s="3"/>
@@ -5721,8 +6225,12 @@
       <c r="AP76" s="3"/>
       <c r="AQ76" s="3"/>
       <c r="AR76" s="3"/>
-    </row>
-    <row r="77" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS76" s="3"/>
+      <c r="AT76" s="3"/>
+      <c r="AU76" s="3"/>
+      <c r="AV76" s="3"/>
+    </row>
+    <row r="77" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B77" s="15" t="s">
         <v>106</v>
       </c>
@@ -5743,22 +6251,22 @@
       <c r="Q77" s="3"/>
       <c r="R77" s="3"/>
       <c r="S77" s="3"/>
-      <c r="T77" s="3">
+      <c r="T77" s="3"/>
+      <c r="U77" s="3"/>
+      <c r="V77" s="3"/>
+      <c r="W77" s="3"/>
+      <c r="X77" s="3">
         <v>-573.43799999999999</v>
       </c>
-      <c r="U77" s="3">
+      <c r="Y77" s="3">
         <v>66.584000000000003</v>
       </c>
-      <c r="V77" s="3">
+      <c r="Z77" s="3">
         <v>-156.08500000000001</v>
       </c>
-      <c r="W77" s="3">
+      <c r="AA77" s="3">
         <v>-188.71</v>
       </c>
-      <c r="X77" s="3"/>
-      <c r="Y77" s="3"/>
-      <c r="Z77" s="3"/>
-      <c r="AA77" s="3"/>
       <c r="AB77" s="3"/>
       <c r="AC77" s="3"/>
       <c r="AD77" s="3"/>
@@ -5776,8 +6284,12 @@
       <c r="AP77" s="3"/>
       <c r="AQ77" s="3"/>
       <c r="AR77" s="3"/>
-    </row>
-    <row r="78" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS77" s="3"/>
+      <c r="AT77" s="3"/>
+      <c r="AU77" s="3"/>
+      <c r="AV77" s="3"/>
+    </row>
+    <row r="78" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B78" s="15" t="s">
         <v>95</v>
       </c>
@@ -5798,22 +6310,22 @@
       <c r="Q78" s="3"/>
       <c r="R78" s="3"/>
       <c r="S78" s="3"/>
-      <c r="T78" s="3">
+      <c r="T78" s="3"/>
+      <c r="U78" s="3"/>
+      <c r="V78" s="3"/>
+      <c r="W78" s="3"/>
+      <c r="X78" s="3">
         <v>-66.713999999999999</v>
       </c>
-      <c r="U78" s="3">
+      <c r="Y78" s="3">
         <v>1.9079999999999999</v>
       </c>
-      <c r="V78" s="3">
+      <c r="Z78" s="3">
         <v>-2.0310000000000001</v>
       </c>
-      <c r="W78" s="3">
+      <c r="AA78" s="3">
         <v>-170.21600000000001</v>
       </c>
-      <c r="X78" s="3"/>
-      <c r="Y78" s="3"/>
-      <c r="Z78" s="3"/>
-      <c r="AA78" s="3"/>
       <c r="AB78" s="3"/>
       <c r="AC78" s="3"/>
       <c r="AD78" s="3"/>
@@ -5831,8 +6343,12 @@
       <c r="AP78" s="3"/>
       <c r="AQ78" s="3"/>
       <c r="AR78" s="3"/>
-    </row>
-    <row r="79" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS78" s="3"/>
+      <c r="AT78" s="3"/>
+      <c r="AU78" s="3"/>
+      <c r="AV78" s="3"/>
+    </row>
+    <row r="79" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B79" s="15" t="s">
         <v>96</v>
       </c>
@@ -5853,22 +6369,22 @@
       <c r="Q79" s="3"/>
       <c r="R79" s="3"/>
       <c r="S79" s="3"/>
-      <c r="T79" s="3">
+      <c r="T79" s="3"/>
+      <c r="U79" s="3"/>
+      <c r="V79" s="3"/>
+      <c r="W79" s="3"/>
+      <c r="X79" s="3">
         <v>-54.832999999999998</v>
       </c>
-      <c r="U79" s="3">
+      <c r="Y79" s="3">
         <v>40.587000000000003</v>
       </c>
-      <c r="V79" s="3">
+      <c r="Z79" s="3">
         <v>-71.789000000000001</v>
       </c>
-      <c r="W79" s="3">
+      <c r="AA79" s="3">
         <v>47.779000000000003</v>
       </c>
-      <c r="X79" s="3"/>
-      <c r="Y79" s="3"/>
-      <c r="Z79" s="3"/>
-      <c r="AA79" s="3"/>
       <c r="AB79" s="3"/>
       <c r="AC79" s="3"/>
       <c r="AD79" s="3"/>
@@ -5886,8 +6402,12 @@
       <c r="AP79" s="3"/>
       <c r="AQ79" s="3"/>
       <c r="AR79" s="3"/>
-    </row>
-    <row r="80" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS79" s="3"/>
+      <c r="AT79" s="3"/>
+      <c r="AU79" s="3"/>
+      <c r="AV79" s="3"/>
+    </row>
+    <row r="80" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B80" s="15" t="s">
         <v>97</v>
       </c>
@@ -5908,22 +6428,22 @@
       <c r="Q80" s="3"/>
       <c r="R80" s="3"/>
       <c r="S80" s="3"/>
-      <c r="T80" s="3">
+      <c r="T80" s="3"/>
+      <c r="U80" s="3"/>
+      <c r="V80" s="3"/>
+      <c r="W80" s="3"/>
+      <c r="X80" s="3">
         <v>-36.518000000000001</v>
       </c>
-      <c r="U80" s="3">
+      <c r="Y80" s="3">
         <v>-53.28</v>
       </c>
-      <c r="V80" s="3">
+      <c r="Z80" s="3">
         <v>-73.204999999999998</v>
       </c>
-      <c r="W80" s="3">
+      <c r="AA80" s="3">
         <v>-70.350999999999999</v>
       </c>
-      <c r="X80" s="3"/>
-      <c r="Y80" s="3"/>
-      <c r="Z80" s="3"/>
-      <c r="AA80" s="3"/>
       <c r="AB80" s="3"/>
       <c r="AC80" s="3"/>
       <c r="AD80" s="3"/>
@@ -5941,8 +6461,12 @@
       <c r="AP80" s="3"/>
       <c r="AQ80" s="3"/>
       <c r="AR80" s="3"/>
-    </row>
-    <row r="81" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS80" s="3"/>
+      <c r="AT80" s="3"/>
+      <c r="AU80" s="3"/>
+      <c r="AV80" s="3"/>
+    </row>
+    <row r="81" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B81" s="15" t="s">
         <v>98</v>
       </c>
@@ -5963,22 +6487,22 @@
       <c r="Q81" s="3"/>
       <c r="R81" s="3"/>
       <c r="S81" s="3"/>
-      <c r="T81" s="3">
+      <c r="T81" s="3"/>
+      <c r="U81" s="3"/>
+      <c r="V81" s="3"/>
+      <c r="W81" s="3"/>
+      <c r="X81" s="3">
         <v>-107.28</v>
       </c>
-      <c r="U81" s="3">
+      <c r="Y81" s="3">
         <v>177.36699999999999</v>
       </c>
-      <c r="V81" s="3">
+      <c r="Z81" s="3">
         <v>-57.043999999999997</v>
       </c>
-      <c r="W81" s="3">
+      <c r="AA81" s="3">
         <v>45.856000000000002</v>
       </c>
-      <c r="X81" s="3"/>
-      <c r="Y81" s="3"/>
-      <c r="Z81" s="3"/>
-      <c r="AA81" s="3"/>
       <c r="AB81" s="3"/>
       <c r="AC81" s="3"/>
       <c r="AD81" s="3"/>
@@ -5996,8 +6520,12 @@
       <c r="AP81" s="3"/>
       <c r="AQ81" s="3"/>
       <c r="AR81" s="3"/>
-    </row>
-    <row r="82" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS81" s="3"/>
+      <c r="AT81" s="3"/>
+      <c r="AU81" s="3"/>
+      <c r="AV81" s="3"/>
+    </row>
+    <row r="82" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B82" s="15" t="s">
         <v>99</v>
       </c>
@@ -6018,22 +6546,22 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-      <c r="T82" s="3">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+      <c r="X82" s="3">
         <v>65.364000000000004</v>
       </c>
-      <c r="U82" s="3">
+      <c r="Y82" s="3">
         <v>-71.733999999999995</v>
       </c>
-      <c r="V82" s="3">
+      <c r="Z82" s="3">
         <v>193.13900000000001</v>
       </c>
-      <c r="W82" s="3">
+      <c r="AA82" s="3">
         <v>98.421000000000006</v>
       </c>
-      <c r="X82" s="3"/>
-      <c r="Y82" s="3"/>
-      <c r="Z82" s="3"/>
-      <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
@@ -6051,8 +6579,12 @@
       <c r="AP82" s="3"/>
       <c r="AQ82" s="3"/>
       <c r="AR82" s="3"/>
-    </row>
-    <row r="83" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS82" s="3"/>
+      <c r="AT82" s="3"/>
+      <c r="AU82" s="3"/>
+      <c r="AV82" s="3"/>
+    </row>
+    <row r="83" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B83" s="15" t="s">
         <v>100</v>
       </c>
@@ -6073,22 +6605,22 @@
       <c r="Q83" s="3"/>
       <c r="R83" s="3"/>
       <c r="S83" s="3"/>
-      <c r="T83" s="3">
+      <c r="T83" s="3"/>
+      <c r="U83" s="3"/>
+      <c r="V83" s="3"/>
+      <c r="W83" s="3"/>
+      <c r="X83" s="3">
         <v>47.253999999999998</v>
       </c>
-      <c r="U83" s="3">
+      <c r="Y83" s="3">
         <v>70.326999999999998</v>
       </c>
-      <c r="V83" s="3">
+      <c r="Z83" s="3">
         <v>-112.11</v>
       </c>
-      <c r="W83" s="3">
+      <c r="AA83" s="3">
         <v>-24.736999999999998</v>
       </c>
-      <c r="X83" s="3"/>
-      <c r="Y83" s="3"/>
-      <c r="Z83" s="3"/>
-      <c r="AA83" s="3"/>
       <c r="AB83" s="3"/>
       <c r="AC83" s="3"/>
       <c r="AD83" s="3"/>
@@ -6106,8 +6638,12 @@
       <c r="AP83" s="3"/>
       <c r="AQ83" s="3"/>
       <c r="AR83" s="3"/>
-    </row>
-    <row r="84" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS83" s="3"/>
+      <c r="AT83" s="3"/>
+      <c r="AU83" s="3"/>
+      <c r="AV83" s="3"/>
+    </row>
+    <row r="84" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B84" s="15" t="s">
         <v>101</v>
       </c>
@@ -6128,22 +6664,22 @@
       <c r="Q84" s="3"/>
       <c r="R84" s="3"/>
       <c r="S84" s="3"/>
-      <c r="T84" s="3">
+      <c r="T84" s="3"/>
+      <c r="U84" s="3"/>
+      <c r="V84" s="3"/>
+      <c r="W84" s="3"/>
+      <c r="X84" s="3">
         <v>35.985999999999997</v>
       </c>
-      <c r="U84" s="3">
+      <c r="Y84" s="3">
         <v>-173.196</v>
       </c>
-      <c r="V84" s="3">
+      <c r="Z84" s="3">
         <v>157.20500000000001</v>
       </c>
-      <c r="W84" s="3">
+      <c r="AA84" s="3">
         <v>-150.48599999999999</v>
       </c>
-      <c r="X84" s="3"/>
-      <c r="Y84" s="3"/>
-      <c r="Z84" s="3"/>
-      <c r="AA84" s="3"/>
       <c r="AB84" s="3"/>
       <c r="AC84" s="3"/>
       <c r="AD84" s="3"/>
@@ -6161,8 +6697,12 @@
       <c r="AP84" s="3"/>
       <c r="AQ84" s="3"/>
       <c r="AR84" s="3"/>
-    </row>
-    <row r="85" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS84" s="3"/>
+      <c r="AT84" s="3"/>
+      <c r="AU84" s="3"/>
+      <c r="AV84" s="3"/>
+    </row>
+    <row r="85" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B85" s="15" t="s">
         <v>102</v>
       </c>
@@ -6183,22 +6723,22 @@
       <c r="Q85" s="3"/>
       <c r="R85" s="3"/>
       <c r="S85" s="3"/>
-      <c r="T85" s="3">
+      <c r="T85" s="3"/>
+      <c r="U85" s="3"/>
+      <c r="V85" s="3"/>
+      <c r="W85" s="3"/>
+      <c r="X85" s="3">
         <v>68.266000000000005</v>
       </c>
-      <c r="U85" s="3">
+      <c r="Y85" s="3">
         <v>84.314999999999998</v>
       </c>
-      <c r="V85" s="3">
+      <c r="Z85" s="3">
         <v>42.41</v>
       </c>
-      <c r="W85" s="3">
+      <c r="AA85" s="3">
         <v>41.253</v>
       </c>
-      <c r="X85" s="3"/>
-      <c r="Y85" s="3"/>
-      <c r="Z85" s="3"/>
-      <c r="AA85" s="3"/>
       <c r="AB85" s="3"/>
       <c r="AC85" s="3"/>
       <c r="AD85" s="3"/>
@@ -6216,8 +6756,12 @@
       <c r="AP85" s="3"/>
       <c r="AQ85" s="3"/>
       <c r="AR85" s="3"/>
-    </row>
-    <row r="86" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS85" s="3"/>
+      <c r="AT85" s="3"/>
+      <c r="AU85" s="3"/>
+      <c r="AV85" s="3"/>
+    </row>
+    <row r="86" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B86" s="15" t="s">
         <v>103</v>
       </c>
@@ -6238,22 +6782,22 @@
       <c r="Q86" s="3"/>
       <c r="R86" s="3"/>
       <c r="S86" s="3"/>
-      <c r="T86" s="3">
+      <c r="T86" s="3"/>
+      <c r="U86" s="3"/>
+      <c r="V86" s="3"/>
+      <c r="W86" s="3"/>
+      <c r="X86" s="3">
         <v>23.905000000000001</v>
       </c>
-      <c r="U86" s="3">
+      <c r="Y86" s="3">
         <v>37.534999999999997</v>
       </c>
-      <c r="V86" s="3">
+      <c r="Z86" s="3">
         <v>23.501000000000001</v>
       </c>
-      <c r="W86" s="3">
+      <c r="AA86" s="3">
         <v>6.8840000000000003</v>
       </c>
-      <c r="X86" s="3"/>
-      <c r="Y86" s="3"/>
-      <c r="Z86" s="3"/>
-      <c r="AA86" s="3"/>
       <c r="AB86" s="3"/>
       <c r="AC86" s="3"/>
       <c r="AD86" s="3"/>
@@ -6271,8 +6815,12 @@
       <c r="AP86" s="3"/>
       <c r="AQ86" s="3"/>
       <c r="AR86" s="3"/>
-    </row>
-    <row r="87" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS86" s="3"/>
+      <c r="AT86" s="3"/>
+      <c r="AU86" s="3"/>
+      <c r="AV86" s="3"/>
+    </row>
+    <row r="87" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B87" s="15" t="s">
         <v>104</v>
       </c>
@@ -6293,22 +6841,22 @@
       <c r="Q87" s="3"/>
       <c r="R87" s="3"/>
       <c r="S87" s="3"/>
-      <c r="T87" s="3">
+      <c r="T87" s="3"/>
+      <c r="U87" s="3"/>
+      <c r="V87" s="3"/>
+      <c r="W87" s="3"/>
+      <c r="X87" s="3">
         <v>-2.9249999999999998</v>
       </c>
-      <c r="U87" s="3">
+      <c r="Y87" s="3">
         <v>12.23</v>
       </c>
-      <c r="V87" s="3">
+      <c r="Z87" s="3">
         <v>2.488</v>
       </c>
-      <c r="W87" s="3">
+      <c r="AA87" s="3">
         <v>20.632000000000001</v>
       </c>
-      <c r="X87" s="3"/>
-      <c r="Y87" s="3"/>
-      <c r="Z87" s="3"/>
-      <c r="AA87" s="3"/>
       <c r="AB87" s="3"/>
       <c r="AC87" s="3"/>
       <c r="AD87" s="3"/>
@@ -6326,8 +6874,12 @@
       <c r="AP87" s="3"/>
       <c r="AQ87" s="3"/>
       <c r="AR87" s="3"/>
-    </row>
-    <row r="88" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS87" s="3"/>
+      <c r="AT87" s="3"/>
+      <c r="AU87" s="3"/>
+      <c r="AV87" s="3"/>
+    </row>
+    <row r="88" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B88" s="15" t="s">
         <v>105</v>
       </c>
@@ -6347,30 +6899,30 @@
       <c r="P88" s="3"/>
       <c r="Q88" s="3"/>
       <c r="R88" s="3"/>
-      <c r="S88" s="3">
-        <f t="shared" ref="S88:U88" si="64">+SUM(S76:S87)</f>
+      <c r="S88" s="3"/>
+      <c r="T88" s="3"/>
+      <c r="U88" s="3"/>
+      <c r="V88" s="3"/>
+      <c r="W88" s="3">
+        <f t="shared" ref="W88:Y88" si="72">+SUM(W76:W87)</f>
         <v>0</v>
       </c>
-      <c r="T88" s="3">
-        <f t="shared" si="64"/>
+      <c r="X88" s="3">
+        <f t="shared" si="72"/>
         <v>-659.91999999999985</v>
       </c>
-      <c r="U88" s="3">
-        <f t="shared" si="64"/>
+      <c r="Y88" s="3">
+        <f t="shared" si="72"/>
         <v>199.22299999999998</v>
       </c>
-      <c r="V88" s="3">
-        <f>+SUM(V76:V87)</f>
+      <c r="Z88" s="3">
+        <f>+SUM(Z76:Z87)</f>
         <v>-51.894999999999953</v>
       </c>
-      <c r="W88" s="3">
-        <f>+SUM(W76:W87)</f>
+      <c r="AA88" s="3">
+        <f>+SUM(AA76:AA87)</f>
         <v>-409.43000000000006</v>
       </c>
-      <c r="X88" s="3"/>
-      <c r="Y88" s="3"/>
-      <c r="Z88" s="3"/>
-      <c r="AA88" s="3"/>
       <c r="AB88" s="3"/>
       <c r="AC88" s="3"/>
       <c r="AD88" s="3"/>
@@ -6388,8 +6940,12 @@
       <c r="AP88" s="3"/>
       <c r="AQ88" s="3"/>
       <c r="AR88" s="3"/>
-    </row>
-    <row r="89" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS88" s="3"/>
+      <c r="AT88" s="3"/>
+      <c r="AU88" s="3"/>
+      <c r="AV88" s="3"/>
+    </row>
+    <row r="89" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B89" s="1" t="s">
         <v>88</v>
       </c>
@@ -6406,42 +6962,42 @@
       <c r="M89" s="3"/>
       <c r="N89" s="3"/>
       <c r="O89" s="3"/>
-      <c r="P89" s="11">
-        <f t="shared" ref="P89:U89" si="65">+SUM(P88,P69:P75)</f>
+      <c r="P89" s="3"/>
+      <c r="Q89" s="3"/>
+      <c r="R89" s="3"/>
+      <c r="S89" s="3"/>
+      <c r="T89" s="11">
+        <f t="shared" ref="T89:Y89" si="73">+SUM(T88,T69:T75)</f>
         <v>0</v>
       </c>
-      <c r="Q89" s="11">
-        <f t="shared" si="65"/>
+      <c r="U89" s="11">
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
-      <c r="R89" s="11">
-        <f t="shared" si="65"/>
+      <c r="V89" s="11">
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
-      <c r="S89" s="11">
-        <f t="shared" si="65"/>
+      <c r="W89" s="11">
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
-      <c r="T89" s="11">
-        <f t="shared" si="65"/>
+      <c r="X89" s="11">
+        <f t="shared" si="73"/>
         <v>966.46300000000019</v>
       </c>
-      <c r="U89" s="11">
-        <f t="shared" si="65"/>
+      <c r="Y89" s="11">
+        <f t="shared" si="73"/>
         <v>2296.1640000000011</v>
       </c>
-      <c r="V89" s="11">
-        <f>+SUM(V88,V69:V75)</f>
+      <c r="Z89" s="11">
+        <f>+SUM(Z88,Z69:Z75)</f>
         <v>2272.7130000000006</v>
       </c>
-      <c r="W89" s="11">
-        <f>+SUM(W88,W69:W75)</f>
+      <c r="AA89" s="11">
+        <f>+SUM(AA88,AA69:AA75)</f>
         <v>1602.4870000000005</v>
       </c>
-      <c r="X89" s="3"/>
-      <c r="Y89" s="3"/>
-      <c r="Z89" s="3"/>
-      <c r="AA89" s="3"/>
       <c r="AB89" s="3"/>
       <c r="AC89" s="3"/>
       <c r="AD89" s="3"/>
@@ -6459,8 +7015,12 @@
       <c r="AP89" s="3"/>
       <c r="AQ89" s="3"/>
       <c r="AR89" s="3"/>
-    </row>
-    <row r="90" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS89" s="3"/>
+      <c r="AT89" s="3"/>
+      <c r="AU89" s="3"/>
+      <c r="AV89" s="3"/>
+    </row>
+    <row r="90" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B90" s="15" t="s">
         <v>108</v>
       </c>
@@ -6481,22 +7041,22 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-      <c r="T90" s="3">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+      <c r="X90" s="3">
         <v>-638.65700000000004</v>
       </c>
-      <c r="U90" s="3">
+      <c r="Y90" s="3">
         <v>-651.86500000000001</v>
       </c>
-      <c r="V90" s="3">
+      <c r="Z90" s="3">
         <v>-689.23199999999997</v>
       </c>
-      <c r="W90" s="3">
+      <c r="AA90" s="3">
         <v>-680.80200000000002</v>
       </c>
-      <c r="X90" s="3"/>
-      <c r="Y90" s="3"/>
-      <c r="Z90" s="3"/>
-      <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
@@ -6514,8 +7074,12 @@
       <c r="AP90" s="3"/>
       <c r="AQ90" s="3"/>
       <c r="AR90" s="3"/>
-    </row>
-    <row r="91" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS90" s="3"/>
+      <c r="AT90" s="3"/>
+      <c r="AU90" s="3"/>
+      <c r="AV90" s="3"/>
+    </row>
+    <row r="91" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B91" s="15" t="s">
         <v>109</v>
       </c>
@@ -6536,22 +7100,22 @@
       <c r="Q91" s="3"/>
       <c r="R91" s="3"/>
       <c r="S91" s="3"/>
-      <c r="T91" s="3">
+      <c r="T91" s="3"/>
+      <c r="U91" s="3"/>
+      <c r="V91" s="3"/>
+      <c r="W91" s="3"/>
+      <c r="X91" s="3">
         <v>47.804000000000002</v>
       </c>
-      <c r="U91" s="3">
+      <c r="Y91" s="3">
         <v>-1.609</v>
       </c>
-      <c r="V91" s="3">
+      <c r="Z91" s="3">
         <v>50.213000000000001</v>
       </c>
-      <c r="W91" s="3">
+      <c r="AA91" s="3">
         <v>27.204999999999998</v>
       </c>
-      <c r="X91" s="3"/>
-      <c r="Y91" s="3"/>
-      <c r="Z91" s="3"/>
-      <c r="AA91" s="3"/>
       <c r="AB91" s="3"/>
       <c r="AC91" s="3"/>
       <c r="AD91" s="3"/>
@@ -6569,8 +7133,12 @@
       <c r="AP91" s="3"/>
       <c r="AQ91" s="3"/>
       <c r="AR91" s="3"/>
-    </row>
-    <row r="92" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS91" s="3"/>
+      <c r="AT91" s="3"/>
+      <c r="AU91" s="3"/>
+      <c r="AV91" s="3"/>
+    </row>
+    <row r="92" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B92" s="15" t="s">
         <v>110</v>
       </c>
@@ -6591,22 +7159,22 @@
       <c r="Q92" s="3"/>
       <c r="R92" s="3"/>
       <c r="S92" s="3"/>
-      <c r="T92" s="3">
+      <c r="T92" s="3"/>
+      <c r="U92" s="3"/>
+      <c r="V92" s="3"/>
+      <c r="W92" s="3"/>
+      <c r="X92" s="3">
         <v>0</v>
       </c>
-      <c r="U92" s="3">
+      <c r="Y92" s="3">
         <v>0</v>
       </c>
-      <c r="V92" s="3">
+      <c r="Z92" s="3">
         <v>-154.14599999999999</v>
       </c>
-      <c r="W92" s="3">
+      <c r="AA92" s="3">
         <v>0</v>
       </c>
-      <c r="X92" s="3"/>
-      <c r="Y92" s="3"/>
-      <c r="Z92" s="3"/>
-      <c r="AA92" s="3"/>
       <c r="AB92" s="3"/>
       <c r="AC92" s="3"/>
       <c r="AD92" s="3"/>
@@ -6624,8 +7192,12 @@
       <c r="AP92" s="3"/>
       <c r="AQ92" s="3"/>
       <c r="AR92" s="3"/>
-    </row>
-    <row r="93" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS92" s="3"/>
+      <c r="AT92" s="3"/>
+      <c r="AU92" s="3"/>
+      <c r="AV92" s="3"/>
+    </row>
+    <row r="93" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B93" s="15" t="s">
         <v>47</v>
       </c>
@@ -6646,22 +7218,22 @@
       <c r="Q93" s="3"/>
       <c r="R93" s="3"/>
       <c r="S93" s="3"/>
-      <c r="T93" s="3">
+      <c r="T93" s="3"/>
+      <c r="U93" s="3"/>
+      <c r="V93" s="3"/>
+      <c r="W93" s="3"/>
+      <c r="X93" s="3">
         <v>20.916</v>
       </c>
-      <c r="U93" s="3">
+      <c r="Y93" s="3">
         <v>-0.65800000000000003</v>
       </c>
-      <c r="V93" s="3">
+      <c r="Z93" s="3">
         <v>-5.0090000000000003</v>
       </c>
-      <c r="W93" s="3">
+      <c r="AA93" s="3">
         <v>-8.5210000000000008</v>
       </c>
-      <c r="X93" s="3"/>
-      <c r="Y93" s="3"/>
-      <c r="Z93" s="3"/>
-      <c r="AA93" s="3"/>
       <c r="AB93" s="3"/>
       <c r="AC93" s="3"/>
       <c r="AD93" s="3"/>
@@ -6679,8 +7251,12 @@
       <c r="AP93" s="3"/>
       <c r="AQ93" s="3"/>
       <c r="AR93" s="3"/>
-    </row>
-    <row r="94" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS93" s="3"/>
+      <c r="AT93" s="3"/>
+      <c r="AU93" s="3"/>
+      <c r="AV93" s="3"/>
+    </row>
+    <row r="94" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B94" s="1" t="s">
         <v>107</v>
       </c>
@@ -6700,30 +7276,30 @@
       <c r="P94" s="3"/>
       <c r="Q94" s="3"/>
       <c r="R94" s="3"/>
-      <c r="S94" s="11">
-        <f t="shared" ref="S94:U94" si="66">+SUM(S90:S93)</f>
+      <c r="S94" s="3"/>
+      <c r="T94" s="3"/>
+      <c r="U94" s="3"/>
+      <c r="V94" s="3"/>
+      <c r="W94" s="11">
+        <f t="shared" ref="W94:Y94" si="74">+SUM(W90:W93)</f>
         <v>0</v>
       </c>
-      <c r="T94" s="11">
-        <f t="shared" si="66"/>
+      <c r="X94" s="11">
+        <f t="shared" si="74"/>
         <v>-569.93700000000001</v>
       </c>
-      <c r="U94" s="11">
-        <f t="shared" si="66"/>
+      <c r="Y94" s="11">
+        <f t="shared" si="74"/>
         <v>-654.13200000000006</v>
       </c>
-      <c r="V94" s="11">
-        <f>+SUM(V90:V93)</f>
+      <c r="Z94" s="11">
+        <f>+SUM(Z90:Z93)</f>
         <v>-798.17399999999998</v>
       </c>
-      <c r="W94" s="11">
-        <f>+SUM(W90:W93)</f>
+      <c r="AA94" s="11">
+        <f>+SUM(AA90:AA93)</f>
         <v>-662.11799999999994</v>
       </c>
-      <c r="X94" s="3"/>
-      <c r="Y94" s="3"/>
-      <c r="Z94" s="3"/>
-      <c r="AA94" s="3"/>
       <c r="AB94" s="3"/>
       <c r="AC94" s="3"/>
       <c r="AD94" s="3"/>
@@ -6741,8 +7317,12 @@
       <c r="AP94" s="3"/>
       <c r="AQ94" s="3"/>
       <c r="AR94" s="3"/>
-    </row>
-    <row r="95" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS94" s="3"/>
+      <c r="AT94" s="3"/>
+      <c r="AU94" s="3"/>
+      <c r="AV94" s="3"/>
+    </row>
+    <row r="95" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B95" s="15" t="s">
         <v>111</v>
       </c>
@@ -6763,22 +7343,22 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-      <c r="T95" s="3">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+      <c r="X95" s="3">
         <v>11.704000000000001</v>
       </c>
-      <c r="U95" s="3">
+      <c r="Y95" s="3">
         <v>42.43</v>
       </c>
-      <c r="V95" s="3">
+      <c r="Z95" s="3">
         <v>19.812999999999999</v>
       </c>
-      <c r="W95" s="3">
+      <c r="AA95" s="3">
         <v>8.3770000000000007</v>
       </c>
-      <c r="X95" s="3"/>
-      <c r="Y95" s="3"/>
-      <c r="Z95" s="3"/>
-      <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
@@ -6796,8 +7376,12 @@
       <c r="AP95" s="3"/>
       <c r="AQ95" s="3"/>
       <c r="AR95" s="3"/>
-    </row>
-    <row r="96" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS95" s="3"/>
+      <c r="AT95" s="3"/>
+      <c r="AU95" s="3"/>
+      <c r="AV95" s="3"/>
+    </row>
+    <row r="96" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B96" s="15" t="s">
         <v>112</v>
       </c>
@@ -6818,22 +7402,22 @@
       <c r="Q96" s="3"/>
       <c r="R96" s="3"/>
       <c r="S96" s="3"/>
-      <c r="T96" s="3">
+      <c r="T96" s="3"/>
+      <c r="U96" s="3"/>
+      <c r="V96" s="3"/>
+      <c r="W96" s="3"/>
+      <c r="X96" s="3">
         <v>-35.158000000000001</v>
       </c>
-      <c r="U96" s="3">
+      <c r="Y96" s="3">
         <v>-32.573999999999998</v>
       </c>
-      <c r="V96" s="3">
+      <c r="Z96" s="3">
         <v>-35.409999999999997</v>
       </c>
-      <c r="W96" s="3">
+      <c r="AA96" s="3">
         <v>-27.372</v>
       </c>
-      <c r="X96" s="3"/>
-      <c r="Y96" s="3"/>
-      <c r="Z96" s="3"/>
-      <c r="AA96" s="3"/>
       <c r="AB96" s="3"/>
       <c r="AC96" s="3"/>
       <c r="AD96" s="3"/>
@@ -6851,8 +7435,12 @@
       <c r="AP96" s="3"/>
       <c r="AQ96" s="3"/>
       <c r="AR96" s="3"/>
-    </row>
-    <row r="97" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS96" s="3"/>
+      <c r="AT96" s="3"/>
+      <c r="AU96" s="3"/>
+      <c r="AV96" s="3"/>
+    </row>
+    <row r="97" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B97" s="15" t="s">
         <v>113</v>
       </c>
@@ -6873,22 +7461,22 @@
       <c r="Q97" s="3"/>
       <c r="R97" s="3"/>
       <c r="S97" s="3"/>
-      <c r="T97" s="3">
+      <c r="T97" s="3"/>
+      <c r="U97" s="3"/>
+      <c r="V97" s="3"/>
+      <c r="W97" s="3"/>
+      <c r="X97" s="3">
         <v>-444.00099999999998</v>
       </c>
-      <c r="U97" s="3">
+      <c r="Y97" s="3">
         <v>-558.65200000000004</v>
       </c>
-      <c r="V97" s="3">
+      <c r="Z97" s="3">
         <v>-1636.8789999999999</v>
       </c>
-      <c r="W97" s="3">
+      <c r="AA97" s="3">
         <v>-1178.3489999999999</v>
       </c>
-      <c r="X97" s="3"/>
-      <c r="Y97" s="3"/>
-      <c r="Z97" s="3"/>
-      <c r="AA97" s="3"/>
       <c r="AB97" s="3"/>
       <c r="AC97" s="3"/>
       <c r="AD97" s="3"/>
@@ -6906,8 +7494,12 @@
       <c r="AP97" s="3"/>
       <c r="AQ97" s="3"/>
       <c r="AR97" s="3"/>
-    </row>
-    <row r="98" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS97" s="3"/>
+      <c r="AT97" s="3"/>
+      <c r="AU97" s="3"/>
+      <c r="AV97" s="3"/>
+    </row>
+    <row r="98" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B98" s="15" t="s">
         <v>47</v>
       </c>
@@ -6928,22 +7520,22 @@
       <c r="Q98" s="3"/>
       <c r="R98" s="3"/>
       <c r="S98" s="3"/>
-      <c r="T98" s="3">
+      <c r="T98" s="3"/>
+      <c r="U98" s="3"/>
+      <c r="V98" s="3"/>
+      <c r="W98" s="3"/>
+      <c r="X98" s="3">
         <v>-3.2000000000000001E-2</v>
       </c>
-      <c r="U98" s="3">
+      <c r="Y98" s="3">
         <v>-3.2000000000000001E-2</v>
       </c>
-      <c r="V98" s="3">
+      <c r="Z98" s="3">
         <v>-3.2000000000000001E-2</v>
       </c>
-      <c r="W98" s="3">
+      <c r="AA98" s="3">
         <v>-11.311999999999999</v>
       </c>
-      <c r="X98" s="3"/>
-      <c r="Y98" s="3"/>
-      <c r="Z98" s="3"/>
-      <c r="AA98" s="3"/>
       <c r="AB98" s="3"/>
       <c r="AC98" s="3"/>
       <c r="AD98" s="3"/>
@@ -6961,8 +7553,12 @@
       <c r="AP98" s="3"/>
       <c r="AQ98" s="3"/>
       <c r="AR98" s="3"/>
-    </row>
-    <row r="99" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS98" s="3"/>
+      <c r="AT98" s="3"/>
+      <c r="AU98" s="3"/>
+      <c r="AV98" s="3"/>
+    </row>
+    <row r="99" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B99" s="1" t="s">
         <v>114</v>
       </c>
@@ -6982,30 +7578,30 @@
       <c r="P99" s="3"/>
       <c r="Q99" s="3"/>
       <c r="R99" s="3"/>
-      <c r="S99" s="11">
-        <f t="shared" ref="S99:U99" si="67">+SUM(S95:S98)</f>
+      <c r="S99" s="3"/>
+      <c r="T99" s="3"/>
+      <c r="U99" s="3"/>
+      <c r="V99" s="3"/>
+      <c r="W99" s="11">
+        <f t="shared" ref="W99:Y99" si="75">+SUM(W95:W98)</f>
         <v>0</v>
       </c>
-      <c r="T99" s="11">
-        <f t="shared" si="67"/>
+      <c r="X99" s="11">
+        <f t="shared" si="75"/>
         <v>-467.48699999999997</v>
       </c>
-      <c r="U99" s="11">
-        <f t="shared" si="67"/>
+      <c r="Y99" s="11">
+        <f t="shared" si="75"/>
         <v>-548.82800000000009</v>
       </c>
-      <c r="V99" s="11">
-        <f>+SUM(V95:V98)</f>
+      <c r="Z99" s="11">
+        <f>+SUM(Z95:Z98)</f>
         <v>-1652.5079999999998</v>
       </c>
-      <c r="W99" s="11">
-        <f>+SUM(W95:W98)</f>
+      <c r="AA99" s="11">
+        <f>+SUM(AA95:AA98)</f>
         <v>-1208.6559999999997</v>
       </c>
-      <c r="X99" s="3"/>
-      <c r="Y99" s="3"/>
-      <c r="Z99" s="3"/>
-      <c r="AA99" s="3"/>
       <c r="AB99" s="3"/>
       <c r="AC99" s="3"/>
       <c r="AD99" s="3"/>
@@ -7023,8 +7619,12 @@
       <c r="AP99" s="3"/>
       <c r="AQ99" s="3"/>
       <c r="AR99" s="3"/>
-    </row>
-    <row r="100" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS99" s="3"/>
+      <c r="AT99" s="3"/>
+      <c r="AU99" s="3"/>
+      <c r="AV99" s="3"/>
+    </row>
+    <row r="100" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B100" s="15" t="s">
         <v>115</v>
       </c>
@@ -7045,22 +7645,22 @@
       <c r="Q100" s="3"/>
       <c r="R100" s="3"/>
       <c r="S100" s="3"/>
-      <c r="T100" s="3">
+      <c r="T100" s="3"/>
+      <c r="U100" s="3"/>
+      <c r="V100" s="3"/>
+      <c r="W100" s="3"/>
+      <c r="X100" s="3">
         <v>-34.042999999999999</v>
       </c>
-      <c r="U100" s="3">
+      <c r="Y100" s="3">
         <v>-4.0999999999999996</v>
       </c>
-      <c r="V100" s="3">
+      <c r="Z100" s="3">
         <v>-81.665999999999997</v>
       </c>
-      <c r="W100" s="3">
+      <c r="AA100" s="3">
         <v>91.162999999999997</v>
       </c>
-      <c r="X100" s="3"/>
-      <c r="Y100" s="3"/>
-      <c r="Z100" s="3"/>
-      <c r="AA100" s="3"/>
       <c r="AB100" s="3"/>
       <c r="AC100" s="3"/>
       <c r="AD100" s="3"/>
@@ -7078,8 +7678,12 @@
       <c r="AP100" s="3"/>
       <c r="AQ100" s="3"/>
       <c r="AR100" s="3"/>
-    </row>
-    <row r="101" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS100" s="3"/>
+      <c r="AT100" s="3"/>
+      <c r="AU100" s="3"/>
+      <c r="AV100" s="3"/>
+    </row>
+    <row r="101" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B101" s="15" t="s">
         <v>116</v>
       </c>
@@ -7099,30 +7703,30 @@
       <c r="P101" s="3"/>
       <c r="Q101" s="3"/>
       <c r="R101" s="3"/>
-      <c r="S101" s="3">
-        <f t="shared" ref="S101:U101" si="68">+SUM(S99,S100,S94,S89)</f>
+      <c r="S101" s="3"/>
+      <c r="T101" s="3"/>
+      <c r="U101" s="3"/>
+      <c r="V101" s="3"/>
+      <c r="W101" s="3">
+        <f t="shared" ref="W101:Y101" si="76">+SUM(W99,W100,W94,W89)</f>
         <v>0</v>
       </c>
-      <c r="T101" s="3">
-        <f t="shared" si="68"/>
+      <c r="X101" s="3">
+        <f t="shared" si="76"/>
         <v>-105.00399999999991</v>
       </c>
-      <c r="U101" s="3">
-        <f t="shared" si="68"/>
+      <c r="Y101" s="3">
+        <f t="shared" si="76"/>
         <v>1089.104000000001</v>
       </c>
-      <c r="V101" s="3">
-        <f>+SUM(V99,V100,V94,V89)</f>
+      <c r="Z101" s="3">
+        <f>+SUM(Z99,Z100,Z94,Z89)</f>
         <v>-259.63499999999931</v>
       </c>
-      <c r="W101" s="3">
-        <f>+SUM(W99,W100,W94,W89)</f>
+      <c r="AA101" s="3">
+        <f>+SUM(AA99,AA100,AA94,AA89)</f>
         <v>-177.12399999999911</v>
       </c>
-      <c r="X101" s="3"/>
-      <c r="Y101" s="3"/>
-      <c r="Z101" s="3"/>
-      <c r="AA101" s="3"/>
       <c r="AB101" s="3"/>
       <c r="AC101" s="3"/>
       <c r="AD101" s="3"/>
@@ -7140,8 +7744,12 @@
       <c r="AP101" s="3"/>
       <c r="AQ101" s="3"/>
       <c r="AR101" s="3"/>
-    </row>
-    <row r="102" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS101" s="3"/>
+      <c r="AT101" s="3"/>
+      <c r="AU101" s="3"/>
+      <c r="AV101" s="3"/>
+    </row>
+    <row r="102" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B102" s="15" t="s">
         <v>117</v>
       </c>
@@ -7162,23 +7770,23 @@
       <c r="Q102" s="3"/>
       <c r="R102" s="3"/>
       <c r="S102" s="3"/>
-      <c r="T102" s="3">
+      <c r="T102" s="3"/>
+      <c r="U102" s="3"/>
+      <c r="V102" s="3"/>
+      <c r="W102" s="3"/>
+      <c r="X102" s="3">
         <v>1259.8710000000001</v>
       </c>
-      <c r="U102" s="3">
+      <c r="Y102" s="3">
         <v>1154.867</v>
       </c>
-      <c r="V102" s="3">
+      <c r="Z102" s="3">
         <v>2243.971</v>
       </c>
-      <c r="W102" s="3">
-        <f>+V103</f>
+      <c r="AA102" s="3">
+        <f>+Z103</f>
         <v>1984.3360000000007</v>
       </c>
-      <c r="X102" s="3"/>
-      <c r="Y102" s="3"/>
-      <c r="Z102" s="3"/>
-      <c r="AA102" s="3"/>
       <c r="AB102" s="3"/>
       <c r="AC102" s="3"/>
       <c r="AD102" s="3"/>
@@ -7196,8 +7804,12 @@
       <c r="AP102" s="3"/>
       <c r="AQ102" s="3"/>
       <c r="AR102" s="3"/>
-    </row>
-    <row r="103" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS102" s="3"/>
+      <c r="AT102" s="3"/>
+      <c r="AU102" s="3"/>
+      <c r="AV102" s="3"/>
+    </row>
+    <row r="103" spans="2:48" x14ac:dyDescent="0.2">
       <c r="B103" s="15" t="s">
         <v>118</v>
       </c>
@@ -7218,26 +7830,26 @@
       <c r="Q103" s="3"/>
       <c r="R103" s="3"/>
       <c r="S103" s="3"/>
-      <c r="T103" s="3">
-        <f>+U102</f>
+      <c r="T103" s="3"/>
+      <c r="U103" s="3"/>
+      <c r="V103" s="3"/>
+      <c r="W103" s="3"/>
+      <c r="X103" s="3">
+        <f>+Y102</f>
         <v>1154.867</v>
       </c>
-      <c r="U103" s="3">
-        <f>+V102</f>
+      <c r="Y103" s="3">
+        <f>+Z102</f>
         <v>2243.971</v>
       </c>
-      <c r="V103" s="3">
-        <f>+V102+V101</f>
+      <c r="Z103" s="3">
+        <f>+Z102+Z101</f>
         <v>1984.3360000000007</v>
       </c>
-      <c r="W103" s="3">
-        <f>+W101+W102</f>
+      <c r="AA103" s="3">
+        <f>+AA101+AA102</f>
         <v>1807.2120000000016</v>
       </c>
-      <c r="X103" s="3"/>
-      <c r="Y103" s="3"/>
-      <c r="Z103" s="3"/>
-      <c r="AA103" s="3"/>
       <c r="AB103" s="3"/>
       <c r="AC103" s="3"/>
       <c r="AD103" s="3"/>
@@ -7255,8 +7867,12 @@
       <c r="AP103" s="3"/>
       <c r="AQ103" s="3"/>
       <c r="AR103" s="3"/>
-    </row>
-    <row r="104" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS103" s="3"/>
+      <c r="AT103" s="3"/>
+      <c r="AU103" s="3"/>
+      <c r="AV103" s="3"/>
+    </row>
+    <row r="104" spans="2:48" x14ac:dyDescent="0.2">
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
@@ -7299,8 +7915,12 @@
       <c r="AP104" s="3"/>
       <c r="AQ104" s="3"/>
       <c r="AR104" s="3"/>
-    </row>
-    <row r="105" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS104" s="3"/>
+      <c r="AT104" s="3"/>
+      <c r="AU104" s="3"/>
+      <c r="AV104" s="3"/>
+    </row>
+    <row r="105" spans="2:48" x14ac:dyDescent="0.2">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -7343,8 +7963,12 @@
       <c r="AP105" s="3"/>
       <c r="AQ105" s="3"/>
       <c r="AR105" s="3"/>
-    </row>
-    <row r="106" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS105" s="3"/>
+      <c r="AT105" s="3"/>
+      <c r="AU105" s="3"/>
+      <c r="AV105" s="3"/>
+    </row>
+    <row r="106" spans="2:48" x14ac:dyDescent="0.2">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -7387,8 +8011,12 @@
       <c r="AP106" s="3"/>
       <c r="AQ106" s="3"/>
       <c r="AR106" s="3"/>
-    </row>
-    <row r="107" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS106" s="3"/>
+      <c r="AT106" s="3"/>
+      <c r="AU106" s="3"/>
+      <c r="AV106" s="3"/>
+    </row>
+    <row r="107" spans="2:48" x14ac:dyDescent="0.2">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -7431,8 +8059,12 @@
       <c r="AP107" s="3"/>
       <c r="AQ107" s="3"/>
       <c r="AR107" s="3"/>
-    </row>
-    <row r="108" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS107" s="3"/>
+      <c r="AT107" s="3"/>
+      <c r="AU107" s="3"/>
+      <c r="AV107" s="3"/>
+    </row>
+    <row r="108" spans="2:48" x14ac:dyDescent="0.2">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -7475,8 +8107,12 @@
       <c r="AP108" s="3"/>
       <c r="AQ108" s="3"/>
       <c r="AR108" s="3"/>
-    </row>
-    <row r="109" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS108" s="3"/>
+      <c r="AT108" s="3"/>
+      <c r="AU108" s="3"/>
+      <c r="AV108" s="3"/>
+    </row>
+    <row r="109" spans="2:48" x14ac:dyDescent="0.2">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -7519,8 +8155,12 @@
       <c r="AP109" s="3"/>
       <c r="AQ109" s="3"/>
       <c r="AR109" s="3"/>
-    </row>
-    <row r="110" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS109" s="3"/>
+      <c r="AT109" s="3"/>
+      <c r="AU109" s="3"/>
+      <c r="AV109" s="3"/>
+    </row>
+    <row r="110" spans="2:48" x14ac:dyDescent="0.2">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -7563,8 +8203,12 @@
       <c r="AP110" s="3"/>
       <c r="AQ110" s="3"/>
       <c r="AR110" s="3"/>
-    </row>
-    <row r="111" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS110" s="3"/>
+      <c r="AT110" s="3"/>
+      <c r="AU110" s="3"/>
+      <c r="AV110" s="3"/>
+    </row>
+    <row r="111" spans="2:48" x14ac:dyDescent="0.2">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -7607,8 +8251,12 @@
       <c r="AP111" s="3"/>
       <c r="AQ111" s="3"/>
       <c r="AR111" s="3"/>
-    </row>
-    <row r="112" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="AS111" s="3"/>
+      <c r="AT111" s="3"/>
+      <c r="AU111" s="3"/>
+      <c r="AV111" s="3"/>
+    </row>
+    <row r="112" spans="2:48" x14ac:dyDescent="0.2">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -7651,8 +8299,12 @@
       <c r="AP112" s="3"/>
       <c r="AQ112" s="3"/>
       <c r="AR112" s="3"/>
-    </row>
-    <row r="113" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS112" s="3"/>
+      <c r="AT112" s="3"/>
+      <c r="AU112" s="3"/>
+      <c r="AV112" s="3"/>
+    </row>
+    <row r="113" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -7695,8 +8347,12 @@
       <c r="AP113" s="3"/>
       <c r="AQ113" s="3"/>
       <c r="AR113" s="3"/>
-    </row>
-    <row r="114" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS113" s="3"/>
+      <c r="AT113" s="3"/>
+      <c r="AU113" s="3"/>
+      <c r="AV113" s="3"/>
+    </row>
+    <row r="114" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -7739,8 +8395,12 @@
       <c r="AP114" s="3"/>
       <c r="AQ114" s="3"/>
       <c r="AR114" s="3"/>
-    </row>
-    <row r="115" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS114" s="3"/>
+      <c r="AT114" s="3"/>
+      <c r="AU114" s="3"/>
+      <c r="AV114" s="3"/>
+    </row>
+    <row r="115" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -7783,8 +8443,12 @@
       <c r="AP115" s="3"/>
       <c r="AQ115" s="3"/>
       <c r="AR115" s="3"/>
-    </row>
-    <row r="116" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS115" s="3"/>
+      <c r="AT115" s="3"/>
+      <c r="AU115" s="3"/>
+      <c r="AV115" s="3"/>
+    </row>
+    <row r="116" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -7827,8 +8491,12 @@
       <c r="AP116" s="3"/>
       <c r="AQ116" s="3"/>
       <c r="AR116" s="3"/>
-    </row>
-    <row r="117" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS116" s="3"/>
+      <c r="AT116" s="3"/>
+      <c r="AU116" s="3"/>
+      <c r="AV116" s="3"/>
+    </row>
+    <row r="117" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -7871,8 +8539,12 @@
       <c r="AP117" s="3"/>
       <c r="AQ117" s="3"/>
       <c r="AR117" s="3"/>
-    </row>
-    <row r="118" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS117" s="3"/>
+      <c r="AT117" s="3"/>
+      <c r="AU117" s="3"/>
+      <c r="AV117" s="3"/>
+    </row>
+    <row r="118" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -7915,8 +8587,12 @@
       <c r="AP118" s="3"/>
       <c r="AQ118" s="3"/>
       <c r="AR118" s="3"/>
-    </row>
-    <row r="119" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS118" s="3"/>
+      <c r="AT118" s="3"/>
+      <c r="AU118" s="3"/>
+      <c r="AV118" s="3"/>
+    </row>
+    <row r="119" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -7959,8 +8635,12 @@
       <c r="AP119" s="3"/>
       <c r="AQ119" s="3"/>
       <c r="AR119" s="3"/>
-    </row>
-    <row r="120" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS119" s="3"/>
+      <c r="AT119" s="3"/>
+      <c r="AU119" s="3"/>
+      <c r="AV119" s="3"/>
+    </row>
+    <row r="120" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -8003,8 +8683,12 @@
       <c r="AP120" s="3"/>
       <c r="AQ120" s="3"/>
       <c r="AR120" s="3"/>
-    </row>
-    <row r="121" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS120" s="3"/>
+      <c r="AT120" s="3"/>
+      <c r="AU120" s="3"/>
+      <c r="AV120" s="3"/>
+    </row>
+    <row r="121" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -8047,8 +8731,12 @@
       <c r="AP121" s="3"/>
       <c r="AQ121" s="3"/>
       <c r="AR121" s="3"/>
-    </row>
-    <row r="122" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS121" s="3"/>
+      <c r="AT121" s="3"/>
+      <c r="AU121" s="3"/>
+      <c r="AV121" s="3"/>
+    </row>
+    <row r="122" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -8091,8 +8779,12 @@
       <c r="AP122" s="3"/>
       <c r="AQ122" s="3"/>
       <c r="AR122" s="3"/>
-    </row>
-    <row r="123" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS122" s="3"/>
+      <c r="AT122" s="3"/>
+      <c r="AU122" s="3"/>
+      <c r="AV122" s="3"/>
+    </row>
+    <row r="123" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -8135,8 +8827,12 @@
       <c r="AP123" s="3"/>
       <c r="AQ123" s="3"/>
       <c r="AR123" s="3"/>
-    </row>
-    <row r="124" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS123" s="3"/>
+      <c r="AT123" s="3"/>
+      <c r="AU123" s="3"/>
+      <c r="AV123" s="3"/>
+    </row>
+    <row r="124" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -8179,8 +8875,12 @@
       <c r="AP124" s="3"/>
       <c r="AQ124" s="3"/>
       <c r="AR124" s="3"/>
-    </row>
-    <row r="125" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS124" s="3"/>
+      <c r="AT124" s="3"/>
+      <c r="AU124" s="3"/>
+      <c r="AV124" s="3"/>
+    </row>
+    <row r="125" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -8223,8 +8923,12 @@
       <c r="AP125" s="3"/>
       <c r="AQ125" s="3"/>
       <c r="AR125" s="3"/>
-    </row>
-    <row r="126" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS125" s="3"/>
+      <c r="AT125" s="3"/>
+      <c r="AU125" s="3"/>
+      <c r="AV125" s="3"/>
+    </row>
+    <row r="126" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -8267,8 +8971,12 @@
       <c r="AP126" s="3"/>
       <c r="AQ126" s="3"/>
       <c r="AR126" s="3"/>
-    </row>
-    <row r="127" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS126" s="3"/>
+      <c r="AT126" s="3"/>
+      <c r="AU126" s="3"/>
+      <c r="AV126" s="3"/>
+    </row>
+    <row r="127" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -8311,8 +9019,12 @@
       <c r="AP127" s="3"/>
       <c r="AQ127" s="3"/>
       <c r="AR127" s="3"/>
-    </row>
-    <row r="128" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS127" s="3"/>
+      <c r="AT127" s="3"/>
+      <c r="AU127" s="3"/>
+      <c r="AV127" s="3"/>
+    </row>
+    <row r="128" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -8355,8 +9067,12 @@
       <c r="AP128" s="3"/>
       <c r="AQ128" s="3"/>
       <c r="AR128" s="3"/>
-    </row>
-    <row r="129" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS128" s="3"/>
+      <c r="AT128" s="3"/>
+      <c r="AU128" s="3"/>
+      <c r="AV128" s="3"/>
+    </row>
+    <row r="129" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -8399,8 +9115,12 @@
       <c r="AP129" s="3"/>
       <c r="AQ129" s="3"/>
       <c r="AR129" s="3"/>
-    </row>
-    <row r="130" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS129" s="3"/>
+      <c r="AT129" s="3"/>
+      <c r="AU129" s="3"/>
+      <c r="AV129" s="3"/>
+    </row>
+    <row r="130" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -8443,8 +9163,12 @@
       <c r="AP130" s="3"/>
       <c r="AQ130" s="3"/>
       <c r="AR130" s="3"/>
-    </row>
-    <row r="131" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS130" s="3"/>
+      <c r="AT130" s="3"/>
+      <c r="AU130" s="3"/>
+      <c r="AV130" s="3"/>
+    </row>
+    <row r="131" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -8487,8 +9211,12 @@
       <c r="AP131" s="3"/>
       <c r="AQ131" s="3"/>
       <c r="AR131" s="3"/>
-    </row>
-    <row r="132" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS131" s="3"/>
+      <c r="AT131" s="3"/>
+      <c r="AU131" s="3"/>
+      <c r="AV131" s="3"/>
+    </row>
+    <row r="132" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -8531,8 +9259,12 @@
       <c r="AP132" s="3"/>
       <c r="AQ132" s="3"/>
       <c r="AR132" s="3"/>
-    </row>
-    <row r="133" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS132" s="3"/>
+      <c r="AT132" s="3"/>
+      <c r="AU132" s="3"/>
+      <c r="AV132" s="3"/>
+    </row>
+    <row r="133" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -8575,8 +9307,12 @@
       <c r="AP133" s="3"/>
       <c r="AQ133" s="3"/>
       <c r="AR133" s="3"/>
-    </row>
-    <row r="134" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS133" s="3"/>
+      <c r="AT133" s="3"/>
+      <c r="AU133" s="3"/>
+      <c r="AV133" s="3"/>
+    </row>
+    <row r="134" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -8619,8 +9355,12 @@
       <c r="AP134" s="3"/>
       <c r="AQ134" s="3"/>
       <c r="AR134" s="3"/>
-    </row>
-    <row r="135" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS134" s="3"/>
+      <c r="AT134" s="3"/>
+      <c r="AU134" s="3"/>
+      <c r="AV134" s="3"/>
+    </row>
+    <row r="135" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -8663,8 +9403,12 @@
       <c r="AP135" s="3"/>
       <c r="AQ135" s="3"/>
       <c r="AR135" s="3"/>
-    </row>
-    <row r="136" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS135" s="3"/>
+      <c r="AT135" s="3"/>
+      <c r="AU135" s="3"/>
+      <c r="AV135" s="3"/>
+    </row>
+    <row r="136" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -8707,8 +9451,12 @@
       <c r="AP136" s="3"/>
       <c r="AQ136" s="3"/>
       <c r="AR136" s="3"/>
-    </row>
-    <row r="137" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS136" s="3"/>
+      <c r="AT136" s="3"/>
+      <c r="AU136" s="3"/>
+      <c r="AV136" s="3"/>
+    </row>
+    <row r="137" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -8751,8 +9499,12 @@
       <c r="AP137" s="3"/>
       <c r="AQ137" s="3"/>
       <c r="AR137" s="3"/>
-    </row>
-    <row r="138" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS137" s="3"/>
+      <c r="AT137" s="3"/>
+      <c r="AU137" s="3"/>
+      <c r="AV137" s="3"/>
+    </row>
+    <row r="138" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -8795,8 +9547,12 @@
       <c r="AP138" s="3"/>
       <c r="AQ138" s="3"/>
       <c r="AR138" s="3"/>
-    </row>
-    <row r="139" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS138" s="3"/>
+      <c r="AT138" s="3"/>
+      <c r="AU138" s="3"/>
+      <c r="AV138" s="3"/>
+    </row>
+    <row r="139" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -8839,8 +9595,12 @@
       <c r="AP139" s="3"/>
       <c r="AQ139" s="3"/>
       <c r="AR139" s="3"/>
-    </row>
-    <row r="140" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS139" s="3"/>
+      <c r="AT139" s="3"/>
+      <c r="AU139" s="3"/>
+      <c r="AV139" s="3"/>
+    </row>
+    <row r="140" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -8883,8 +9643,12 @@
       <c r="AP140" s="3"/>
       <c r="AQ140" s="3"/>
       <c r="AR140" s="3"/>
-    </row>
-    <row r="141" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS140" s="3"/>
+      <c r="AT140" s="3"/>
+      <c r="AU140" s="3"/>
+      <c r="AV140" s="3"/>
+    </row>
+    <row r="141" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -8927,8 +9691,12 @@
       <c r="AP141" s="3"/>
       <c r="AQ141" s="3"/>
       <c r="AR141" s="3"/>
-    </row>
-    <row r="142" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS141" s="3"/>
+      <c r="AT141" s="3"/>
+      <c r="AU141" s="3"/>
+      <c r="AV141" s="3"/>
+    </row>
+    <row r="142" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -8971,8 +9739,12 @@
       <c r="AP142" s="3"/>
       <c r="AQ142" s="3"/>
       <c r="AR142" s="3"/>
-    </row>
-    <row r="143" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS142" s="3"/>
+      <c r="AT142" s="3"/>
+      <c r="AU142" s="3"/>
+      <c r="AV142" s="3"/>
+    </row>
+    <row r="143" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -9015,8 +9787,12 @@
       <c r="AP143" s="3"/>
       <c r="AQ143" s="3"/>
       <c r="AR143" s="3"/>
-    </row>
-    <row r="144" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS143" s="3"/>
+      <c r="AT143" s="3"/>
+      <c r="AU143" s="3"/>
+      <c r="AV143" s="3"/>
+    </row>
+    <row r="144" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -9059,8 +9835,12 @@
       <c r="AP144" s="3"/>
       <c r="AQ144" s="3"/>
       <c r="AR144" s="3"/>
-    </row>
-    <row r="145" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS144" s="3"/>
+      <c r="AT144" s="3"/>
+      <c r="AU144" s="3"/>
+      <c r="AV144" s="3"/>
+    </row>
+    <row r="145" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -9103,8 +9883,12 @@
       <c r="AP145" s="3"/>
       <c r="AQ145" s="3"/>
       <c r="AR145" s="3"/>
-    </row>
-    <row r="146" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS145" s="3"/>
+      <c r="AT145" s="3"/>
+      <c r="AU145" s="3"/>
+      <c r="AV145" s="3"/>
+    </row>
+    <row r="146" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -9147,8 +9931,12 @@
       <c r="AP146" s="3"/>
       <c r="AQ146" s="3"/>
       <c r="AR146" s="3"/>
-    </row>
-    <row r="147" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS146" s="3"/>
+      <c r="AT146" s="3"/>
+      <c r="AU146" s="3"/>
+      <c r="AV146" s="3"/>
+    </row>
+    <row r="147" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -9191,8 +9979,12 @@
       <c r="AP147" s="3"/>
       <c r="AQ147" s="3"/>
       <c r="AR147" s="3"/>
-    </row>
-    <row r="148" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS147" s="3"/>
+      <c r="AT147" s="3"/>
+      <c r="AU147" s="3"/>
+      <c r="AV147" s="3"/>
+    </row>
+    <row r="148" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -9235,8 +10027,12 @@
       <c r="AP148" s="3"/>
       <c r="AQ148" s="3"/>
       <c r="AR148" s="3"/>
-    </row>
-    <row r="149" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS148" s="3"/>
+      <c r="AT148" s="3"/>
+      <c r="AU148" s="3"/>
+      <c r="AV148" s="3"/>
+    </row>
+    <row r="149" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -9279,8 +10075,12 @@
       <c r="AP149" s="3"/>
       <c r="AQ149" s="3"/>
       <c r="AR149" s="3"/>
-    </row>
-    <row r="150" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS149" s="3"/>
+      <c r="AT149" s="3"/>
+      <c r="AU149" s="3"/>
+      <c r="AV149" s="3"/>
+    </row>
+    <row r="150" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -9323,8 +10123,12 @@
       <c r="AP150" s="3"/>
       <c r="AQ150" s="3"/>
       <c r="AR150" s="3"/>
-    </row>
-    <row r="151" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS150" s="3"/>
+      <c r="AT150" s="3"/>
+      <c r="AU150" s="3"/>
+      <c r="AV150" s="3"/>
+    </row>
+    <row r="151" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -9367,8 +10171,12 @@
       <c r="AP151" s="3"/>
       <c r="AQ151" s="3"/>
       <c r="AR151" s="3"/>
-    </row>
-    <row r="152" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS151" s="3"/>
+      <c r="AT151" s="3"/>
+      <c r="AU151" s="3"/>
+      <c r="AV151" s="3"/>
+    </row>
+    <row r="152" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -9411,8 +10219,12 @@
       <c r="AP152" s="3"/>
       <c r="AQ152" s="3"/>
       <c r="AR152" s="3"/>
-    </row>
-    <row r="153" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS152" s="3"/>
+      <c r="AT152" s="3"/>
+      <c r="AU152" s="3"/>
+      <c r="AV152" s="3"/>
+    </row>
+    <row r="153" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -9455,8 +10267,12 @@
       <c r="AP153" s="3"/>
       <c r="AQ153" s="3"/>
       <c r="AR153" s="3"/>
-    </row>
-    <row r="154" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS153" s="3"/>
+      <c r="AT153" s="3"/>
+      <c r="AU153" s="3"/>
+      <c r="AV153" s="3"/>
+    </row>
+    <row r="154" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -9499,8 +10315,12 @@
       <c r="AP154" s="3"/>
       <c r="AQ154" s="3"/>
       <c r="AR154" s="3"/>
-    </row>
-    <row r="155" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS154" s="3"/>
+      <c r="AT154" s="3"/>
+      <c r="AU154" s="3"/>
+      <c r="AV154" s="3"/>
+    </row>
+    <row r="155" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -9543,8 +10363,12 @@
       <c r="AP155" s="3"/>
       <c r="AQ155" s="3"/>
       <c r="AR155" s="3"/>
-    </row>
-    <row r="156" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS155" s="3"/>
+      <c r="AT155" s="3"/>
+      <c r="AU155" s="3"/>
+      <c r="AV155" s="3"/>
+    </row>
+    <row r="156" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -9587,8 +10411,12 @@
       <c r="AP156" s="3"/>
       <c r="AQ156" s="3"/>
       <c r="AR156" s="3"/>
-    </row>
-    <row r="157" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS156" s="3"/>
+      <c r="AT156" s="3"/>
+      <c r="AU156" s="3"/>
+      <c r="AV156" s="3"/>
+    </row>
+    <row r="157" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -9631,8 +10459,12 @@
       <c r="AP157" s="3"/>
       <c r="AQ157" s="3"/>
       <c r="AR157" s="3"/>
-    </row>
-    <row r="158" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS157" s="3"/>
+      <c r="AT157" s="3"/>
+      <c r="AU157" s="3"/>
+      <c r="AV157" s="3"/>
+    </row>
+    <row r="158" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -9675,8 +10507,12 @@
       <c r="AP158" s="3"/>
       <c r="AQ158" s="3"/>
       <c r="AR158" s="3"/>
-    </row>
-    <row r="159" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS158" s="3"/>
+      <c r="AT158" s="3"/>
+      <c r="AU158" s="3"/>
+      <c r="AV158" s="3"/>
+    </row>
+    <row r="159" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -9719,8 +10555,12 @@
       <c r="AP159" s="3"/>
       <c r="AQ159" s="3"/>
       <c r="AR159" s="3"/>
-    </row>
-    <row r="160" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS159" s="3"/>
+      <c r="AT159" s="3"/>
+      <c r="AU159" s="3"/>
+      <c r="AV159" s="3"/>
+    </row>
+    <row r="160" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -9763,8 +10603,12 @@
       <c r="AP160" s="3"/>
       <c r="AQ160" s="3"/>
       <c r="AR160" s="3"/>
-    </row>
-    <row r="161" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS160" s="3"/>
+      <c r="AT160" s="3"/>
+      <c r="AU160" s="3"/>
+      <c r="AV160" s="3"/>
+    </row>
+    <row r="161" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -9807,8 +10651,12 @@
       <c r="AP161" s="3"/>
       <c r="AQ161" s="3"/>
       <c r="AR161" s="3"/>
-    </row>
-    <row r="162" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS161" s="3"/>
+      <c r="AT161" s="3"/>
+      <c r="AU161" s="3"/>
+      <c r="AV161" s="3"/>
+    </row>
+    <row r="162" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -9851,8 +10699,12 @@
       <c r="AP162" s="3"/>
       <c r="AQ162" s="3"/>
       <c r="AR162" s="3"/>
-    </row>
-    <row r="163" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS162" s="3"/>
+      <c r="AT162" s="3"/>
+      <c r="AU162" s="3"/>
+      <c r="AV162" s="3"/>
+    </row>
+    <row r="163" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -9895,8 +10747,12 @@
       <c r="AP163" s="3"/>
       <c r="AQ163" s="3"/>
       <c r="AR163" s="3"/>
-    </row>
-    <row r="164" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS163" s="3"/>
+      <c r="AT163" s="3"/>
+      <c r="AU163" s="3"/>
+      <c r="AV163" s="3"/>
+    </row>
+    <row r="164" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -9939,8 +10795,12 @@
       <c r="AP164" s="3"/>
       <c r="AQ164" s="3"/>
       <c r="AR164" s="3"/>
-    </row>
-    <row r="165" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS164" s="3"/>
+      <c r="AT164" s="3"/>
+      <c r="AU164" s="3"/>
+      <c r="AV164" s="3"/>
+    </row>
+    <row r="165" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -9983,8 +10843,12 @@
       <c r="AP165" s="3"/>
       <c r="AQ165" s="3"/>
       <c r="AR165" s="3"/>
-    </row>
-    <row r="166" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS165" s="3"/>
+      <c r="AT165" s="3"/>
+      <c r="AU165" s="3"/>
+      <c r="AV165" s="3"/>
+    </row>
+    <row r="166" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -10027,8 +10891,12 @@
       <c r="AP166" s="3"/>
       <c r="AQ166" s="3"/>
       <c r="AR166" s="3"/>
-    </row>
-    <row r="167" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS166" s="3"/>
+      <c r="AT166" s="3"/>
+      <c r="AU166" s="3"/>
+      <c r="AV166" s="3"/>
+    </row>
+    <row r="167" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -10071,8 +10939,12 @@
       <c r="AP167" s="3"/>
       <c r="AQ167" s="3"/>
       <c r="AR167" s="3"/>
-    </row>
-    <row r="168" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS167" s="3"/>
+      <c r="AT167" s="3"/>
+      <c r="AU167" s="3"/>
+      <c r="AV167" s="3"/>
+    </row>
+    <row r="168" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -10115,8 +10987,12 @@
       <c r="AP168" s="3"/>
       <c r="AQ168" s="3"/>
       <c r="AR168" s="3"/>
-    </row>
-    <row r="169" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS168" s="3"/>
+      <c r="AT168" s="3"/>
+      <c r="AU168" s="3"/>
+      <c r="AV168" s="3"/>
+    </row>
+    <row r="169" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -10159,8 +11035,12 @@
       <c r="AP169" s="3"/>
       <c r="AQ169" s="3"/>
       <c r="AR169" s="3"/>
-    </row>
-    <row r="170" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS169" s="3"/>
+      <c r="AT169" s="3"/>
+      <c r="AU169" s="3"/>
+      <c r="AV169" s="3"/>
+    </row>
+    <row r="170" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -10203,8 +11083,12 @@
       <c r="AP170" s="3"/>
       <c r="AQ170" s="3"/>
       <c r="AR170" s="3"/>
-    </row>
-    <row r="171" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS170" s="3"/>
+      <c r="AT170" s="3"/>
+      <c r="AU170" s="3"/>
+      <c r="AV170" s="3"/>
+    </row>
+    <row r="171" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -10247,8 +11131,12 @@
       <c r="AP171" s="3"/>
       <c r="AQ171" s="3"/>
       <c r="AR171" s="3"/>
-    </row>
-    <row r="172" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS171" s="3"/>
+      <c r="AT171" s="3"/>
+      <c r="AU171" s="3"/>
+      <c r="AV171" s="3"/>
+    </row>
+    <row r="172" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -10291,8 +11179,12 @@
       <c r="AP172" s="3"/>
       <c r="AQ172" s="3"/>
       <c r="AR172" s="3"/>
-    </row>
-    <row r="173" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS172" s="3"/>
+      <c r="AT172" s="3"/>
+      <c r="AU172" s="3"/>
+      <c r="AV172" s="3"/>
+    </row>
+    <row r="173" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -10335,8 +11227,12 @@
       <c r="AP173" s="3"/>
       <c r="AQ173" s="3"/>
       <c r="AR173" s="3"/>
-    </row>
-    <row r="174" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS173" s="3"/>
+      <c r="AT173" s="3"/>
+      <c r="AU173" s="3"/>
+      <c r="AV173" s="3"/>
+    </row>
+    <row r="174" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -10379,8 +11275,12 @@
       <c r="AP174" s="3"/>
       <c r="AQ174" s="3"/>
       <c r="AR174" s="3"/>
-    </row>
-    <row r="175" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS174" s="3"/>
+      <c r="AT174" s="3"/>
+      <c r="AU174" s="3"/>
+      <c r="AV174" s="3"/>
+    </row>
+    <row r="175" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -10423,8 +11323,12 @@
       <c r="AP175" s="3"/>
       <c r="AQ175" s="3"/>
       <c r="AR175" s="3"/>
-    </row>
-    <row r="176" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS175" s="3"/>
+      <c r="AT175" s="3"/>
+      <c r="AU175" s="3"/>
+      <c r="AV175" s="3"/>
+    </row>
+    <row r="176" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -10467,8 +11371,12 @@
       <c r="AP176" s="3"/>
       <c r="AQ176" s="3"/>
       <c r="AR176" s="3"/>
-    </row>
-    <row r="177" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS176" s="3"/>
+      <c r="AT176" s="3"/>
+      <c r="AU176" s="3"/>
+      <c r="AV176" s="3"/>
+    </row>
+    <row r="177" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -10511,8 +11419,12 @@
       <c r="AP177" s="3"/>
       <c r="AQ177" s="3"/>
       <c r="AR177" s="3"/>
-    </row>
-    <row r="178" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS177" s="3"/>
+      <c r="AT177" s="3"/>
+      <c r="AU177" s="3"/>
+      <c r="AV177" s="3"/>
+    </row>
+    <row r="178" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -10555,8 +11467,12 @@
       <c r="AP178" s="3"/>
       <c r="AQ178" s="3"/>
       <c r="AR178" s="3"/>
-    </row>
-    <row r="179" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS178" s="3"/>
+      <c r="AT178" s="3"/>
+      <c r="AU178" s="3"/>
+      <c r="AV178" s="3"/>
+    </row>
+    <row r="179" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -10599,8 +11515,12 @@
       <c r="AP179" s="3"/>
       <c r="AQ179" s="3"/>
       <c r="AR179" s="3"/>
-    </row>
-    <row r="180" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS179" s="3"/>
+      <c r="AT179" s="3"/>
+      <c r="AU179" s="3"/>
+      <c r="AV179" s="3"/>
+    </row>
+    <row r="180" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -10643,8 +11563,12 @@
       <c r="AP180" s="3"/>
       <c r="AQ180" s="3"/>
       <c r="AR180" s="3"/>
-    </row>
-    <row r="181" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS180" s="3"/>
+      <c r="AT180" s="3"/>
+      <c r="AU180" s="3"/>
+      <c r="AV180" s="3"/>
+    </row>
+    <row r="181" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -10687,8 +11611,12 @@
       <c r="AP181" s="3"/>
       <c r="AQ181" s="3"/>
       <c r="AR181" s="3"/>
-    </row>
-    <row r="182" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS181" s="3"/>
+      <c r="AT181" s="3"/>
+      <c r="AU181" s="3"/>
+      <c r="AV181" s="3"/>
+    </row>
+    <row r="182" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -10731,8 +11659,12 @@
       <c r="AP182" s="3"/>
       <c r="AQ182" s="3"/>
       <c r="AR182" s="3"/>
-    </row>
-    <row r="183" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS182" s="3"/>
+      <c r="AT182" s="3"/>
+      <c r="AU182" s="3"/>
+      <c r="AV182" s="3"/>
+    </row>
+    <row r="183" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -10775,8 +11707,12 @@
       <c r="AP183" s="3"/>
       <c r="AQ183" s="3"/>
       <c r="AR183" s="3"/>
-    </row>
-    <row r="184" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS183" s="3"/>
+      <c r="AT183" s="3"/>
+      <c r="AU183" s="3"/>
+      <c r="AV183" s="3"/>
+    </row>
+    <row r="184" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -10819,8 +11755,12 @@
       <c r="AP184" s="3"/>
       <c r="AQ184" s="3"/>
       <c r="AR184" s="3"/>
-    </row>
-    <row r="185" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS184" s="3"/>
+      <c r="AT184" s="3"/>
+      <c r="AU184" s="3"/>
+      <c r="AV184" s="3"/>
+    </row>
+    <row r="185" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -10863,8 +11803,12 @@
       <c r="AP185" s="3"/>
       <c r="AQ185" s="3"/>
       <c r="AR185" s="3"/>
-    </row>
-    <row r="186" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS185" s="3"/>
+      <c r="AT185" s="3"/>
+      <c r="AU185" s="3"/>
+      <c r="AV185" s="3"/>
+    </row>
+    <row r="186" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -10907,8 +11851,12 @@
       <c r="AP186" s="3"/>
       <c r="AQ186" s="3"/>
       <c r="AR186" s="3"/>
-    </row>
-    <row r="187" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS186" s="3"/>
+      <c r="AT186" s="3"/>
+      <c r="AU186" s="3"/>
+      <c r="AV186" s="3"/>
+    </row>
+    <row r="187" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -10951,8 +11899,12 @@
       <c r="AP187" s="3"/>
       <c r="AQ187" s="3"/>
       <c r="AR187" s="3"/>
-    </row>
-    <row r="188" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS187" s="3"/>
+      <c r="AT187" s="3"/>
+      <c r="AU187" s="3"/>
+      <c r="AV187" s="3"/>
+    </row>
+    <row r="188" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -10995,8 +11947,12 @@
       <c r="AP188" s="3"/>
       <c r="AQ188" s="3"/>
       <c r="AR188" s="3"/>
-    </row>
-    <row r="189" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS188" s="3"/>
+      <c r="AT188" s="3"/>
+      <c r="AU188" s="3"/>
+      <c r="AV188" s="3"/>
+    </row>
+    <row r="189" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -11039,8 +11995,12 @@
       <c r="AP189" s="3"/>
       <c r="AQ189" s="3"/>
       <c r="AR189" s="3"/>
-    </row>
-    <row r="190" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS189" s="3"/>
+      <c r="AT189" s="3"/>
+      <c r="AU189" s="3"/>
+      <c r="AV189" s="3"/>
+    </row>
+    <row r="190" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -11083,8 +12043,12 @@
       <c r="AP190" s="3"/>
       <c r="AQ190" s="3"/>
       <c r="AR190" s="3"/>
-    </row>
-    <row r="191" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS190" s="3"/>
+      <c r="AT190" s="3"/>
+      <c r="AU190" s="3"/>
+      <c r="AV190" s="3"/>
+    </row>
+    <row r="191" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -11127,8 +12091,12 @@
       <c r="AP191" s="3"/>
       <c r="AQ191" s="3"/>
       <c r="AR191" s="3"/>
-    </row>
-    <row r="192" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS191" s="3"/>
+      <c r="AT191" s="3"/>
+      <c r="AU191" s="3"/>
+      <c r="AV191" s="3"/>
+    </row>
+    <row r="192" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -11171,8 +12139,12 @@
       <c r="AP192" s="3"/>
       <c r="AQ192" s="3"/>
       <c r="AR192" s="3"/>
-    </row>
-    <row r="193" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS192" s="3"/>
+      <c r="AT192" s="3"/>
+      <c r="AU192" s="3"/>
+      <c r="AV192" s="3"/>
+    </row>
+    <row r="193" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -11215,8 +12187,12 @@
       <c r="AP193" s="3"/>
       <c r="AQ193" s="3"/>
       <c r="AR193" s="3"/>
-    </row>
-    <row r="194" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS193" s="3"/>
+      <c r="AT193" s="3"/>
+      <c r="AU193" s="3"/>
+      <c r="AV193" s="3"/>
+    </row>
+    <row r="194" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -11259,8 +12235,12 @@
       <c r="AP194" s="3"/>
       <c r="AQ194" s="3"/>
       <c r="AR194" s="3"/>
-    </row>
-    <row r="195" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS194" s="3"/>
+      <c r="AT194" s="3"/>
+      <c r="AU194" s="3"/>
+      <c r="AV194" s="3"/>
+    </row>
+    <row r="195" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -11303,8 +12283,12 @@
       <c r="AP195" s="3"/>
       <c r="AQ195" s="3"/>
       <c r="AR195" s="3"/>
-    </row>
-    <row r="196" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS195" s="3"/>
+      <c r="AT195" s="3"/>
+      <c r="AU195" s="3"/>
+      <c r="AV195" s="3"/>
+    </row>
+    <row r="196" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -11347,8 +12331,12 @@
       <c r="AP196" s="3"/>
       <c r="AQ196" s="3"/>
       <c r="AR196" s="3"/>
-    </row>
-    <row r="197" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS196" s="3"/>
+      <c r="AT196" s="3"/>
+      <c r="AU196" s="3"/>
+      <c r="AV196" s="3"/>
+    </row>
+    <row r="197" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -11391,8 +12379,12 @@
       <c r="AP197" s="3"/>
       <c r="AQ197" s="3"/>
       <c r="AR197" s="3"/>
-    </row>
-    <row r="198" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS197" s="3"/>
+      <c r="AT197" s="3"/>
+      <c r="AU197" s="3"/>
+      <c r="AV197" s="3"/>
+    </row>
+    <row r="198" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -11435,8 +12427,12 @@
       <c r="AP198" s="3"/>
       <c r="AQ198" s="3"/>
       <c r="AR198" s="3"/>
-    </row>
-    <row r="199" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS198" s="3"/>
+      <c r="AT198" s="3"/>
+      <c r="AU198" s="3"/>
+      <c r="AV198" s="3"/>
+    </row>
+    <row r="199" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -11479,8 +12475,12 @@
       <c r="AP199" s="3"/>
       <c r="AQ199" s="3"/>
       <c r="AR199" s="3"/>
-    </row>
-    <row r="200" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS199" s="3"/>
+      <c r="AT199" s="3"/>
+      <c r="AU199" s="3"/>
+      <c r="AV199" s="3"/>
+    </row>
+    <row r="200" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -11523,8 +12523,12 @@
       <c r="AP200" s="3"/>
       <c r="AQ200" s="3"/>
       <c r="AR200" s="3"/>
-    </row>
-    <row r="201" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS200" s="3"/>
+      <c r="AT200" s="3"/>
+      <c r="AU200" s="3"/>
+      <c r="AV200" s="3"/>
+    </row>
+    <row r="201" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -11567,8 +12571,12 @@
       <c r="AP201" s="3"/>
       <c r="AQ201" s="3"/>
       <c r="AR201" s="3"/>
-    </row>
-    <row r="202" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS201" s="3"/>
+      <c r="AT201" s="3"/>
+      <c r="AU201" s="3"/>
+      <c r="AV201" s="3"/>
+    </row>
+    <row r="202" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -11611,8 +12619,12 @@
       <c r="AP202" s="3"/>
       <c r="AQ202" s="3"/>
       <c r="AR202" s="3"/>
-    </row>
-    <row r="203" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS202" s="3"/>
+      <c r="AT202" s="3"/>
+      <c r="AU202" s="3"/>
+      <c r="AV202" s="3"/>
+    </row>
+    <row r="203" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -11655,8 +12667,12 @@
       <c r="AP203" s="3"/>
       <c r="AQ203" s="3"/>
       <c r="AR203" s="3"/>
-    </row>
-    <row r="204" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS203" s="3"/>
+      <c r="AT203" s="3"/>
+      <c r="AU203" s="3"/>
+      <c r="AV203" s="3"/>
+    </row>
+    <row r="204" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -11699,8 +12715,12 @@
       <c r="AP204" s="3"/>
       <c r="AQ204" s="3"/>
       <c r="AR204" s="3"/>
-    </row>
-    <row r="205" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS204" s="3"/>
+      <c r="AT204" s="3"/>
+      <c r="AU204" s="3"/>
+      <c r="AV204" s="3"/>
+    </row>
+    <row r="205" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -11743,8 +12763,12 @@
       <c r="AP205" s="3"/>
       <c r="AQ205" s="3"/>
       <c r="AR205" s="3"/>
-    </row>
-    <row r="206" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS205" s="3"/>
+      <c r="AT205" s="3"/>
+      <c r="AU205" s="3"/>
+      <c r="AV205" s="3"/>
+    </row>
+    <row r="206" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -11787,8 +12811,12 @@
       <c r="AP206" s="3"/>
       <c r="AQ206" s="3"/>
       <c r="AR206" s="3"/>
-    </row>
-    <row r="207" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS206" s="3"/>
+      <c r="AT206" s="3"/>
+      <c r="AU206" s="3"/>
+      <c r="AV206" s="3"/>
+    </row>
+    <row r="207" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -11831,8 +12859,12 @@
       <c r="AP207" s="3"/>
       <c r="AQ207" s="3"/>
       <c r="AR207" s="3"/>
-    </row>
-    <row r="208" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS207" s="3"/>
+      <c r="AT207" s="3"/>
+      <c r="AU207" s="3"/>
+      <c r="AV207" s="3"/>
+    </row>
+    <row r="208" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -11875,8 +12907,12 @@
       <c r="AP208" s="3"/>
       <c r="AQ208" s="3"/>
       <c r="AR208" s="3"/>
-    </row>
-    <row r="209" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS208" s="3"/>
+      <c r="AT208" s="3"/>
+      <c r="AU208" s="3"/>
+      <c r="AV208" s="3"/>
+    </row>
+    <row r="209" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -11919,8 +12955,12 @@
       <c r="AP209" s="3"/>
       <c r="AQ209" s="3"/>
       <c r="AR209" s="3"/>
-    </row>
-    <row r="210" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS209" s="3"/>
+      <c r="AT209" s="3"/>
+      <c r="AU209" s="3"/>
+      <c r="AV209" s="3"/>
+    </row>
+    <row r="210" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -11963,8 +13003,12 @@
       <c r="AP210" s="3"/>
       <c r="AQ210" s="3"/>
       <c r="AR210" s="3"/>
-    </row>
-    <row r="211" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS210" s="3"/>
+      <c r="AT210" s="3"/>
+      <c r="AU210" s="3"/>
+      <c r="AV210" s="3"/>
+    </row>
+    <row r="211" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -12007,8 +13051,12 @@
       <c r="AP211" s="3"/>
       <c r="AQ211" s="3"/>
       <c r="AR211" s="3"/>
-    </row>
-    <row r="212" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS211" s="3"/>
+      <c r="AT211" s="3"/>
+      <c r="AU211" s="3"/>
+      <c r="AV211" s="3"/>
+    </row>
+    <row r="212" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -12051,8 +13099,12 @@
       <c r="AP212" s="3"/>
       <c r="AQ212" s="3"/>
       <c r="AR212" s="3"/>
-    </row>
-    <row r="213" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS212" s="3"/>
+      <c r="AT212" s="3"/>
+      <c r="AU212" s="3"/>
+      <c r="AV212" s="3"/>
+    </row>
+    <row r="213" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -12095,8 +13147,12 @@
       <c r="AP213" s="3"/>
       <c r="AQ213" s="3"/>
       <c r="AR213" s="3"/>
-    </row>
-    <row r="214" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS213" s="3"/>
+      <c r="AT213" s="3"/>
+      <c r="AU213" s="3"/>
+      <c r="AV213" s="3"/>
+    </row>
+    <row r="214" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -12139,8 +13195,12 @@
       <c r="AP214" s="3"/>
       <c r="AQ214" s="3"/>
       <c r="AR214" s="3"/>
-    </row>
-    <row r="215" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS214" s="3"/>
+      <c r="AT214" s="3"/>
+      <c r="AU214" s="3"/>
+      <c r="AV214" s="3"/>
+    </row>
+    <row r="215" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -12183,8 +13243,12 @@
       <c r="AP215" s="3"/>
       <c r="AQ215" s="3"/>
       <c r="AR215" s="3"/>
-    </row>
-    <row r="216" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS215" s="3"/>
+      <c r="AT215" s="3"/>
+      <c r="AU215" s="3"/>
+      <c r="AV215" s="3"/>
+    </row>
+    <row r="216" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -12227,8 +13291,12 @@
       <c r="AP216" s="3"/>
       <c r="AQ216" s="3"/>
       <c r="AR216" s="3"/>
-    </row>
-    <row r="217" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS216" s="3"/>
+      <c r="AT216" s="3"/>
+      <c r="AU216" s="3"/>
+      <c r="AV216" s="3"/>
+    </row>
+    <row r="217" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -12271,8 +13339,12 @@
       <c r="AP217" s="3"/>
       <c r="AQ217" s="3"/>
       <c r="AR217" s="3"/>
-    </row>
-    <row r="218" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS217" s="3"/>
+      <c r="AT217" s="3"/>
+      <c r="AU217" s="3"/>
+      <c r="AV217" s="3"/>
+    </row>
+    <row r="218" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -12315,8 +13387,12 @@
       <c r="AP218" s="3"/>
       <c r="AQ218" s="3"/>
       <c r="AR218" s="3"/>
-    </row>
-    <row r="219" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS218" s="3"/>
+      <c r="AT218" s="3"/>
+      <c r="AU218" s="3"/>
+      <c r="AV218" s="3"/>
+    </row>
+    <row r="219" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -12359,8 +13435,12 @@
       <c r="AP219" s="3"/>
       <c r="AQ219" s="3"/>
       <c r="AR219" s="3"/>
-    </row>
-    <row r="220" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS219" s="3"/>
+      <c r="AT219" s="3"/>
+      <c r="AU219" s="3"/>
+      <c r="AV219" s="3"/>
+    </row>
+    <row r="220" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -12403,8 +13483,12 @@
       <c r="AP220" s="3"/>
       <c r="AQ220" s="3"/>
       <c r="AR220" s="3"/>
-    </row>
-    <row r="221" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS220" s="3"/>
+      <c r="AT220" s="3"/>
+      <c r="AU220" s="3"/>
+      <c r="AV220" s="3"/>
+    </row>
+    <row r="221" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -12447,8 +13531,12 @@
       <c r="AP221" s="3"/>
       <c r="AQ221" s="3"/>
       <c r="AR221" s="3"/>
-    </row>
-    <row r="222" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS221" s="3"/>
+      <c r="AT221" s="3"/>
+      <c r="AU221" s="3"/>
+      <c r="AV221" s="3"/>
+    </row>
+    <row r="222" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -12491,8 +13579,12 @@
       <c r="AP222" s="3"/>
       <c r="AQ222" s="3"/>
       <c r="AR222" s="3"/>
-    </row>
-    <row r="223" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS222" s="3"/>
+      <c r="AT222" s="3"/>
+      <c r="AU222" s="3"/>
+      <c r="AV222" s="3"/>
+    </row>
+    <row r="223" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -12535,8 +13627,12 @@
       <c r="AP223" s="3"/>
       <c r="AQ223" s="3"/>
       <c r="AR223" s="3"/>
-    </row>
-    <row r="224" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS223" s="3"/>
+      <c r="AT223" s="3"/>
+      <c r="AU223" s="3"/>
+      <c r="AV223" s="3"/>
+    </row>
+    <row r="224" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -12579,8 +13675,12 @@
       <c r="AP224" s="3"/>
       <c r="AQ224" s="3"/>
       <c r="AR224" s="3"/>
-    </row>
-    <row r="225" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS224" s="3"/>
+      <c r="AT224" s="3"/>
+      <c r="AU224" s="3"/>
+      <c r="AV224" s="3"/>
+    </row>
+    <row r="225" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
@@ -12623,8 +13723,12 @@
       <c r="AP225" s="3"/>
       <c r="AQ225" s="3"/>
       <c r="AR225" s="3"/>
-    </row>
-    <row r="226" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS225" s="3"/>
+      <c r="AT225" s="3"/>
+      <c r="AU225" s="3"/>
+      <c r="AV225" s="3"/>
+    </row>
+    <row r="226" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
@@ -12667,8 +13771,12 @@
       <c r="AP226" s="3"/>
       <c r="AQ226" s="3"/>
       <c r="AR226" s="3"/>
-    </row>
-    <row r="227" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS226" s="3"/>
+      <c r="AT226" s="3"/>
+      <c r="AU226" s="3"/>
+      <c r="AV226" s="3"/>
+    </row>
+    <row r="227" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
       <c r="E227" s="3"/>
@@ -12711,8 +13819,12 @@
       <c r="AP227" s="3"/>
       <c r="AQ227" s="3"/>
       <c r="AR227" s="3"/>
-    </row>
-    <row r="228" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS227" s="3"/>
+      <c r="AT227" s="3"/>
+      <c r="AU227" s="3"/>
+      <c r="AV227" s="3"/>
+    </row>
+    <row r="228" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -12755,8 +13867,12 @@
       <c r="AP228" s="3"/>
       <c r="AQ228" s="3"/>
       <c r="AR228" s="3"/>
-    </row>
-    <row r="229" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS228" s="3"/>
+      <c r="AT228" s="3"/>
+      <c r="AU228" s="3"/>
+      <c r="AV228" s="3"/>
+    </row>
+    <row r="229" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -12799,8 +13915,12 @@
       <c r="AP229" s="3"/>
       <c r="AQ229" s="3"/>
       <c r="AR229" s="3"/>
-    </row>
-    <row r="230" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS229" s="3"/>
+      <c r="AT229" s="3"/>
+      <c r="AU229" s="3"/>
+      <c r="AV229" s="3"/>
+    </row>
+    <row r="230" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -12843,8 +13963,12 @@
       <c r="AP230" s="3"/>
       <c r="AQ230" s="3"/>
       <c r="AR230" s="3"/>
-    </row>
-    <row r="231" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS230" s="3"/>
+      <c r="AT230" s="3"/>
+      <c r="AU230" s="3"/>
+      <c r="AV230" s="3"/>
+    </row>
+    <row r="231" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
@@ -12887,8 +14011,12 @@
       <c r="AP231" s="3"/>
       <c r="AQ231" s="3"/>
       <c r="AR231" s="3"/>
-    </row>
-    <row r="232" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS231" s="3"/>
+      <c r="AT231" s="3"/>
+      <c r="AU231" s="3"/>
+      <c r="AV231" s="3"/>
+    </row>
+    <row r="232" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -12931,8 +14059,12 @@
       <c r="AP232" s="3"/>
       <c r="AQ232" s="3"/>
       <c r="AR232" s="3"/>
-    </row>
-    <row r="233" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS232" s="3"/>
+      <c r="AT232" s="3"/>
+      <c r="AU232" s="3"/>
+      <c r="AV232" s="3"/>
+    </row>
+    <row r="233" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
@@ -12975,8 +14107,12 @@
       <c r="AP233" s="3"/>
       <c r="AQ233" s="3"/>
       <c r="AR233" s="3"/>
-    </row>
-    <row r="234" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS233" s="3"/>
+      <c r="AT233" s="3"/>
+      <c r="AU233" s="3"/>
+      <c r="AV233" s="3"/>
+    </row>
+    <row r="234" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -13019,8 +14155,12 @@
       <c r="AP234" s="3"/>
       <c r="AQ234" s="3"/>
       <c r="AR234" s="3"/>
-    </row>
-    <row r="235" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS234" s="3"/>
+      <c r="AT234" s="3"/>
+      <c r="AU234" s="3"/>
+      <c r="AV234" s="3"/>
+    </row>
+    <row r="235" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
@@ -13063,8 +14203,12 @@
       <c r="AP235" s="3"/>
       <c r="AQ235" s="3"/>
       <c r="AR235" s="3"/>
-    </row>
-    <row r="236" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS235" s="3"/>
+      <c r="AT235" s="3"/>
+      <c r="AU235" s="3"/>
+      <c r="AV235" s="3"/>
+    </row>
+    <row r="236" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -13107,8 +14251,12 @@
       <c r="AP236" s="3"/>
       <c r="AQ236" s="3"/>
       <c r="AR236" s="3"/>
-    </row>
-    <row r="237" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS236" s="3"/>
+      <c r="AT236" s="3"/>
+      <c r="AU236" s="3"/>
+      <c r="AV236" s="3"/>
+    </row>
+    <row r="237" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="3"/>
@@ -13151,8 +14299,12 @@
       <c r="AP237" s="3"/>
       <c r="AQ237" s="3"/>
       <c r="AR237" s="3"/>
-    </row>
-    <row r="238" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS237" s="3"/>
+      <c r="AT237" s="3"/>
+      <c r="AU237" s="3"/>
+      <c r="AV237" s="3"/>
+    </row>
+    <row r="238" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -13195,8 +14347,12 @@
       <c r="AP238" s="3"/>
       <c r="AQ238" s="3"/>
       <c r="AR238" s="3"/>
-    </row>
-    <row r="239" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS238" s="3"/>
+      <c r="AT238" s="3"/>
+      <c r="AU238" s="3"/>
+      <c r="AV238" s="3"/>
+    </row>
+    <row r="239" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
       <c r="E239" s="3"/>
@@ -13239,8 +14395,12 @@
       <c r="AP239" s="3"/>
       <c r="AQ239" s="3"/>
       <c r="AR239" s="3"/>
-    </row>
-    <row r="240" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS239" s="3"/>
+      <c r="AT239" s="3"/>
+      <c r="AU239" s="3"/>
+      <c r="AV239" s="3"/>
+    </row>
+    <row r="240" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
@@ -13283,8 +14443,12 @@
       <c r="AP240" s="3"/>
       <c r="AQ240" s="3"/>
       <c r="AR240" s="3"/>
-    </row>
-    <row r="241" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS240" s="3"/>
+      <c r="AT240" s="3"/>
+      <c r="AU240" s="3"/>
+      <c r="AV240" s="3"/>
+    </row>
+    <row r="241" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
       <c r="E241" s="3"/>
@@ -13327,8 +14491,12 @@
       <c r="AP241" s="3"/>
       <c r="AQ241" s="3"/>
       <c r="AR241" s="3"/>
-    </row>
-    <row r="242" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS241" s="3"/>
+      <c r="AT241" s="3"/>
+      <c r="AU241" s="3"/>
+      <c r="AV241" s="3"/>
+    </row>
+    <row r="242" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
@@ -13371,8 +14539,12 @@
       <c r="AP242" s="3"/>
       <c r="AQ242" s="3"/>
       <c r="AR242" s="3"/>
-    </row>
-    <row r="243" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS242" s="3"/>
+      <c r="AT242" s="3"/>
+      <c r="AU242" s="3"/>
+      <c r="AV242" s="3"/>
+    </row>
+    <row r="243" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
@@ -13415,8 +14587,12 @@
       <c r="AP243" s="3"/>
       <c r="AQ243" s="3"/>
       <c r="AR243" s="3"/>
-    </row>
-    <row r="244" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS243" s="3"/>
+      <c r="AT243" s="3"/>
+      <c r="AU243" s="3"/>
+      <c r="AV243" s="3"/>
+    </row>
+    <row r="244" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -13459,8 +14635,12 @@
       <c r="AP244" s="3"/>
       <c r="AQ244" s="3"/>
       <c r="AR244" s="3"/>
-    </row>
-    <row r="245" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS244" s="3"/>
+      <c r="AT244" s="3"/>
+      <c r="AU244" s="3"/>
+      <c r="AV244" s="3"/>
+    </row>
+    <row r="245" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
       <c r="E245" s="3"/>
@@ -13503,8 +14683,12 @@
       <c r="AP245" s="3"/>
       <c r="AQ245" s="3"/>
       <c r="AR245" s="3"/>
-    </row>
-    <row r="246" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS245" s="3"/>
+      <c r="AT245" s="3"/>
+      <c r="AU245" s="3"/>
+      <c r="AV245" s="3"/>
+    </row>
+    <row r="246" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
@@ -13547,8 +14731,12 @@
       <c r="AP246" s="3"/>
       <c r="AQ246" s="3"/>
       <c r="AR246" s="3"/>
-    </row>
-    <row r="247" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS246" s="3"/>
+      <c r="AT246" s="3"/>
+      <c r="AU246" s="3"/>
+      <c r="AV246" s="3"/>
+    </row>
+    <row r="247" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
       <c r="E247" s="3"/>
@@ -13591,8 +14779,12 @@
       <c r="AP247" s="3"/>
       <c r="AQ247" s="3"/>
       <c r="AR247" s="3"/>
-    </row>
-    <row r="248" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS247" s="3"/>
+      <c r="AT247" s="3"/>
+      <c r="AU247" s="3"/>
+      <c r="AV247" s="3"/>
+    </row>
+    <row r="248" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
@@ -13635,8 +14827,12 @@
       <c r="AP248" s="3"/>
       <c r="AQ248" s="3"/>
       <c r="AR248" s="3"/>
-    </row>
-    <row r="249" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS248" s="3"/>
+      <c r="AT248" s="3"/>
+      <c r="AU248" s="3"/>
+      <c r="AV248" s="3"/>
+    </row>
+    <row r="249" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
       <c r="E249" s="3"/>
@@ -13679,8 +14875,12 @@
       <c r="AP249" s="3"/>
       <c r="AQ249" s="3"/>
       <c r="AR249" s="3"/>
-    </row>
-    <row r="250" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS249" s="3"/>
+      <c r="AT249" s="3"/>
+      <c r="AU249" s="3"/>
+      <c r="AV249" s="3"/>
+    </row>
+    <row r="250" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -13723,8 +14923,12 @@
       <c r="AP250" s="3"/>
       <c r="AQ250" s="3"/>
       <c r="AR250" s="3"/>
-    </row>
-    <row r="251" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS250" s="3"/>
+      <c r="AT250" s="3"/>
+      <c r="AU250" s="3"/>
+      <c r="AV250" s="3"/>
+    </row>
+    <row r="251" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C251" s="3"/>
       <c r="D251" s="3"/>
       <c r="E251" s="3"/>
@@ -13767,8 +14971,12 @@
       <c r="AP251" s="3"/>
       <c r="AQ251" s="3"/>
       <c r="AR251" s="3"/>
-    </row>
-    <row r="252" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS251" s="3"/>
+      <c r="AT251" s="3"/>
+      <c r="AU251" s="3"/>
+      <c r="AV251" s="3"/>
+    </row>
+    <row r="252" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C252" s="3"/>
       <c r="D252" s="3"/>
       <c r="E252" s="3"/>
@@ -13811,8 +15019,12 @@
       <c r="AP252" s="3"/>
       <c r="AQ252" s="3"/>
       <c r="AR252" s="3"/>
-    </row>
-    <row r="253" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS252" s="3"/>
+      <c r="AT252" s="3"/>
+      <c r="AU252" s="3"/>
+      <c r="AV252" s="3"/>
+    </row>
+    <row r="253" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C253" s="3"/>
       <c r="D253" s="3"/>
       <c r="E253" s="3"/>
@@ -13855,8 +15067,12 @@
       <c r="AP253" s="3"/>
       <c r="AQ253" s="3"/>
       <c r="AR253" s="3"/>
-    </row>
-    <row r="254" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS253" s="3"/>
+      <c r="AT253" s="3"/>
+      <c r="AU253" s="3"/>
+      <c r="AV253" s="3"/>
+    </row>
+    <row r="254" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C254" s="3"/>
       <c r="D254" s="3"/>
       <c r="E254" s="3"/>
@@ -13899,8 +15115,12 @@
       <c r="AP254" s="3"/>
       <c r="AQ254" s="3"/>
       <c r="AR254" s="3"/>
-    </row>
-    <row r="255" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS254" s="3"/>
+      <c r="AT254" s="3"/>
+      <c r="AU254" s="3"/>
+      <c r="AV254" s="3"/>
+    </row>
+    <row r="255" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C255" s="3"/>
       <c r="D255" s="3"/>
       <c r="E255" s="3"/>
@@ -13943,8 +15163,12 @@
       <c r="AP255" s="3"/>
       <c r="AQ255" s="3"/>
       <c r="AR255" s="3"/>
-    </row>
-    <row r="256" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS255" s="3"/>
+      <c r="AT255" s="3"/>
+      <c r="AU255" s="3"/>
+      <c r="AV255" s="3"/>
+    </row>
+    <row r="256" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
@@ -13987,8 +15211,12 @@
       <c r="AP256" s="3"/>
       <c r="AQ256" s="3"/>
       <c r="AR256" s="3"/>
-    </row>
-    <row r="257" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS256" s="3"/>
+      <c r="AT256" s="3"/>
+      <c r="AU256" s="3"/>
+      <c r="AV256" s="3"/>
+    </row>
+    <row r="257" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
@@ -14031,8 +15259,12 @@
       <c r="AP257" s="3"/>
       <c r="AQ257" s="3"/>
       <c r="AR257" s="3"/>
-    </row>
-    <row r="258" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS257" s="3"/>
+      <c r="AT257" s="3"/>
+      <c r="AU257" s="3"/>
+      <c r="AV257" s="3"/>
+    </row>
+    <row r="258" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C258" s="3"/>
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
@@ -14075,8 +15307,12 @@
       <c r="AP258" s="3"/>
       <c r="AQ258" s="3"/>
       <c r="AR258" s="3"/>
-    </row>
-    <row r="259" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS258" s="3"/>
+      <c r="AT258" s="3"/>
+      <c r="AU258" s="3"/>
+      <c r="AV258" s="3"/>
+    </row>
+    <row r="259" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C259" s="3"/>
       <c r="D259" s="3"/>
       <c r="E259" s="3"/>
@@ -14119,8 +15355,12 @@
       <c r="AP259" s="3"/>
       <c r="AQ259" s="3"/>
       <c r="AR259" s="3"/>
-    </row>
-    <row r="260" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS259" s="3"/>
+      <c r="AT259" s="3"/>
+      <c r="AU259" s="3"/>
+      <c r="AV259" s="3"/>
+    </row>
+    <row r="260" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C260" s="3"/>
       <c r="D260" s="3"/>
       <c r="E260" s="3"/>
@@ -14163,8 +15403,12 @@
       <c r="AP260" s="3"/>
       <c r="AQ260" s="3"/>
       <c r="AR260" s="3"/>
-    </row>
-    <row r="261" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS260" s="3"/>
+      <c r="AT260" s="3"/>
+      <c r="AU260" s="3"/>
+      <c r="AV260" s="3"/>
+    </row>
+    <row r="261" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C261" s="3"/>
       <c r="D261" s="3"/>
       <c r="E261" s="3"/>
@@ -14207,8 +15451,12 @@
       <c r="AP261" s="3"/>
       <c r="AQ261" s="3"/>
       <c r="AR261" s="3"/>
-    </row>
-    <row r="262" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS261" s="3"/>
+      <c r="AT261" s="3"/>
+      <c r="AU261" s="3"/>
+      <c r="AV261" s="3"/>
+    </row>
+    <row r="262" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C262" s="3"/>
       <c r="D262" s="3"/>
       <c r="E262" s="3"/>
@@ -14251,8 +15499,12 @@
       <c r="AP262" s="3"/>
       <c r="AQ262" s="3"/>
       <c r="AR262" s="3"/>
-    </row>
-    <row r="263" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS262" s="3"/>
+      <c r="AT262" s="3"/>
+      <c r="AU262" s="3"/>
+      <c r="AV262" s="3"/>
+    </row>
+    <row r="263" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C263" s="3"/>
       <c r="D263" s="3"/>
       <c r="E263" s="3"/>
@@ -14295,8 +15547,12 @@
       <c r="AP263" s="3"/>
       <c r="AQ263" s="3"/>
       <c r="AR263" s="3"/>
-    </row>
-    <row r="264" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS263" s="3"/>
+      <c r="AT263" s="3"/>
+      <c r="AU263" s="3"/>
+      <c r="AV263" s="3"/>
+    </row>
+    <row r="264" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C264" s="3"/>
       <c r="D264" s="3"/>
       <c r="E264" s="3"/>
@@ -14339,8 +15595,12 @@
       <c r="AP264" s="3"/>
       <c r="AQ264" s="3"/>
       <c r="AR264" s="3"/>
-    </row>
-    <row r="265" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS264" s="3"/>
+      <c r="AT264" s="3"/>
+      <c r="AU264" s="3"/>
+      <c r="AV264" s="3"/>
+    </row>
+    <row r="265" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C265" s="3"/>
       <c r="D265" s="3"/>
       <c r="E265" s="3"/>
@@ -14383,8 +15643,12 @@
       <c r="AP265" s="3"/>
       <c r="AQ265" s="3"/>
       <c r="AR265" s="3"/>
-    </row>
-    <row r="266" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS265" s="3"/>
+      <c r="AT265" s="3"/>
+      <c r="AU265" s="3"/>
+      <c r="AV265" s="3"/>
+    </row>
+    <row r="266" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C266" s="3"/>
       <c r="D266" s="3"/>
       <c r="E266" s="3"/>
@@ -14427,8 +15691,12 @@
       <c r="AP266" s="3"/>
       <c r="AQ266" s="3"/>
       <c r="AR266" s="3"/>
-    </row>
-    <row r="267" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS266" s="3"/>
+      <c r="AT266" s="3"/>
+      <c r="AU266" s="3"/>
+      <c r="AV266" s="3"/>
+    </row>
+    <row r="267" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C267" s="3"/>
       <c r="D267" s="3"/>
       <c r="E267" s="3"/>
@@ -14471,8 +15739,12 @@
       <c r="AP267" s="3"/>
       <c r="AQ267" s="3"/>
       <c r="AR267" s="3"/>
-    </row>
-    <row r="268" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS267" s="3"/>
+      <c r="AT267" s="3"/>
+      <c r="AU267" s="3"/>
+      <c r="AV267" s="3"/>
+    </row>
+    <row r="268" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
       <c r="E268" s="3"/>
@@ -14515,8 +15787,12 @@
       <c r="AP268" s="3"/>
       <c r="AQ268" s="3"/>
       <c r="AR268" s="3"/>
-    </row>
-    <row r="269" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS268" s="3"/>
+      <c r="AT268" s="3"/>
+      <c r="AU268" s="3"/>
+      <c r="AV268" s="3"/>
+    </row>
+    <row r="269" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
       <c r="E269" s="3"/>
@@ -14559,8 +15835,12 @@
       <c r="AP269" s="3"/>
       <c r="AQ269" s="3"/>
       <c r="AR269" s="3"/>
-    </row>
-    <row r="270" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS269" s="3"/>
+      <c r="AT269" s="3"/>
+      <c r="AU269" s="3"/>
+      <c r="AV269" s="3"/>
+    </row>
+    <row r="270" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C270" s="3"/>
       <c r="D270" s="3"/>
       <c r="E270" s="3"/>
@@ -14603,8 +15883,12 @@
       <c r="AP270" s="3"/>
       <c r="AQ270" s="3"/>
       <c r="AR270" s="3"/>
-    </row>
-    <row r="271" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS270" s="3"/>
+      <c r="AT270" s="3"/>
+      <c r="AU270" s="3"/>
+      <c r="AV270" s="3"/>
+    </row>
+    <row r="271" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
       <c r="E271" s="3"/>
@@ -14647,8 +15931,12 @@
       <c r="AP271" s="3"/>
       <c r="AQ271" s="3"/>
       <c r="AR271" s="3"/>
-    </row>
-    <row r="272" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS271" s="3"/>
+      <c r="AT271" s="3"/>
+      <c r="AU271" s="3"/>
+      <c r="AV271" s="3"/>
+    </row>
+    <row r="272" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C272" s="3"/>
       <c r="D272" s="3"/>
       <c r="E272" s="3"/>
@@ -14691,8 +15979,12 @@
       <c r="AP272" s="3"/>
       <c r="AQ272" s="3"/>
       <c r="AR272" s="3"/>
-    </row>
-    <row r="273" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS272" s="3"/>
+      <c r="AT272" s="3"/>
+      <c r="AU272" s="3"/>
+      <c r="AV272" s="3"/>
+    </row>
+    <row r="273" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C273" s="3"/>
       <c r="D273" s="3"/>
       <c r="E273" s="3"/>
@@ -14735,8 +16027,12 @@
       <c r="AP273" s="3"/>
       <c r="AQ273" s="3"/>
       <c r="AR273" s="3"/>
-    </row>
-    <row r="274" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS273" s="3"/>
+      <c r="AT273" s="3"/>
+      <c r="AU273" s="3"/>
+      <c r="AV273" s="3"/>
+    </row>
+    <row r="274" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
       <c r="E274" s="3"/>
@@ -14779,8 +16075,12 @@
       <c r="AP274" s="3"/>
       <c r="AQ274" s="3"/>
       <c r="AR274" s="3"/>
-    </row>
-    <row r="275" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS274" s="3"/>
+      <c r="AT274" s="3"/>
+      <c r="AU274" s="3"/>
+      <c r="AV274" s="3"/>
+    </row>
+    <row r="275" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="3"/>
@@ -14823,8 +16123,12 @@
       <c r="AP275" s="3"/>
       <c r="AQ275" s="3"/>
       <c r="AR275" s="3"/>
-    </row>
-    <row r="276" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS275" s="3"/>
+      <c r="AT275" s="3"/>
+      <c r="AU275" s="3"/>
+      <c r="AV275" s="3"/>
+    </row>
+    <row r="276" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
       <c r="E276" s="3"/>
@@ -14867,8 +16171,12 @@
       <c r="AP276" s="3"/>
       <c r="AQ276" s="3"/>
       <c r="AR276" s="3"/>
-    </row>
-    <row r="277" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS276" s="3"/>
+      <c r="AT276" s="3"/>
+      <c r="AU276" s="3"/>
+      <c r="AV276" s="3"/>
+    </row>
+    <row r="277" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
       <c r="E277" s="3"/>
@@ -14911,8 +16219,12 @@
       <c r="AP277" s="3"/>
       <c r="AQ277" s="3"/>
       <c r="AR277" s="3"/>
-    </row>
-    <row r="278" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS277" s="3"/>
+      <c r="AT277" s="3"/>
+      <c r="AU277" s="3"/>
+      <c r="AV277" s="3"/>
+    </row>
+    <row r="278" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="3"/>
@@ -14955,8 +16267,12 @@
       <c r="AP278" s="3"/>
       <c r="AQ278" s="3"/>
       <c r="AR278" s="3"/>
-    </row>
-    <row r="279" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS278" s="3"/>
+      <c r="AT278" s="3"/>
+      <c r="AU278" s="3"/>
+      <c r="AV278" s="3"/>
+    </row>
+    <row r="279" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
       <c r="E279" s="3"/>
@@ -14999,8 +16315,12 @@
       <c r="AP279" s="3"/>
       <c r="AQ279" s="3"/>
       <c r="AR279" s="3"/>
-    </row>
-    <row r="280" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS279" s="3"/>
+      <c r="AT279" s="3"/>
+      <c r="AU279" s="3"/>
+      <c r="AV279" s="3"/>
+    </row>
+    <row r="280" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
       <c r="E280" s="3"/>
@@ -15043,8 +16363,12 @@
       <c r="AP280" s="3"/>
       <c r="AQ280" s="3"/>
       <c r="AR280" s="3"/>
-    </row>
-    <row r="281" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS280" s="3"/>
+      <c r="AT280" s="3"/>
+      <c r="AU280" s="3"/>
+      <c r="AV280" s="3"/>
+    </row>
+    <row r="281" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
       <c r="E281" s="3"/>
@@ -15087,8 +16411,12 @@
       <c r="AP281" s="3"/>
       <c r="AQ281" s="3"/>
       <c r="AR281" s="3"/>
-    </row>
-    <row r="282" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS281" s="3"/>
+      <c r="AT281" s="3"/>
+      <c r="AU281" s="3"/>
+      <c r="AV281" s="3"/>
+    </row>
+    <row r="282" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
       <c r="E282" s="3"/>
@@ -15131,8 +16459,12 @@
       <c r="AP282" s="3"/>
       <c r="AQ282" s="3"/>
       <c r="AR282" s="3"/>
-    </row>
-    <row r="283" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS282" s="3"/>
+      <c r="AT282" s="3"/>
+      <c r="AU282" s="3"/>
+      <c r="AV282" s="3"/>
+    </row>
+    <row r="283" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
       <c r="E283" s="3"/>
@@ -15175,8 +16507,12 @@
       <c r="AP283" s="3"/>
       <c r="AQ283" s="3"/>
       <c r="AR283" s="3"/>
-    </row>
-    <row r="284" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS283" s="3"/>
+      <c r="AT283" s="3"/>
+      <c r="AU283" s="3"/>
+      <c r="AV283" s="3"/>
+    </row>
+    <row r="284" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="3"/>
@@ -15219,8 +16555,12 @@
       <c r="AP284" s="3"/>
       <c r="AQ284" s="3"/>
       <c r="AR284" s="3"/>
-    </row>
-    <row r="285" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS284" s="3"/>
+      <c r="AT284" s="3"/>
+      <c r="AU284" s="3"/>
+      <c r="AV284" s="3"/>
+    </row>
+    <row r="285" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C285" s="3"/>
       <c r="D285" s="3"/>
       <c r="E285" s="3"/>
@@ -15263,8 +16603,12 @@
       <c r="AP285" s="3"/>
       <c r="AQ285" s="3"/>
       <c r="AR285" s="3"/>
-    </row>
-    <row r="286" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS285" s="3"/>
+      <c r="AT285" s="3"/>
+      <c r="AU285" s="3"/>
+      <c r="AV285" s="3"/>
+    </row>
+    <row r="286" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
       <c r="E286" s="3"/>
@@ -15307,8 +16651,12 @@
       <c r="AP286" s="3"/>
       <c r="AQ286" s="3"/>
       <c r="AR286" s="3"/>
-    </row>
-    <row r="287" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS286" s="3"/>
+      <c r="AT286" s="3"/>
+      <c r="AU286" s="3"/>
+      <c r="AV286" s="3"/>
+    </row>
+    <row r="287" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C287" s="3"/>
       <c r="D287" s="3"/>
       <c r="E287" s="3"/>
@@ -15351,8 +16699,12 @@
       <c r="AP287" s="3"/>
       <c r="AQ287" s="3"/>
       <c r="AR287" s="3"/>
-    </row>
-    <row r="288" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS287" s="3"/>
+      <c r="AT287" s="3"/>
+      <c r="AU287" s="3"/>
+      <c r="AV287" s="3"/>
+    </row>
+    <row r="288" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C288" s="3"/>
       <c r="D288" s="3"/>
       <c r="E288" s="3"/>
@@ -15395,8 +16747,12 @@
       <c r="AP288" s="3"/>
       <c r="AQ288" s="3"/>
       <c r="AR288" s="3"/>
-    </row>
-    <row r="289" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS288" s="3"/>
+      <c r="AT288" s="3"/>
+      <c r="AU288" s="3"/>
+      <c r="AV288" s="3"/>
+    </row>
+    <row r="289" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
       <c r="E289" s="3"/>
@@ -15439,8 +16795,12 @@
       <c r="AP289" s="3"/>
       <c r="AQ289" s="3"/>
       <c r="AR289" s="3"/>
-    </row>
-    <row r="290" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS289" s="3"/>
+      <c r="AT289" s="3"/>
+      <c r="AU289" s="3"/>
+      <c r="AV289" s="3"/>
+    </row>
+    <row r="290" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
       <c r="E290" s="3"/>
@@ -15483,8 +16843,12 @@
       <c r="AP290" s="3"/>
       <c r="AQ290" s="3"/>
       <c r="AR290" s="3"/>
-    </row>
-    <row r="291" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS290" s="3"/>
+      <c r="AT290" s="3"/>
+      <c r="AU290" s="3"/>
+      <c r="AV290" s="3"/>
+    </row>
+    <row r="291" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
       <c r="E291" s="3"/>
@@ -15527,8 +16891,12 @@
       <c r="AP291" s="3"/>
       <c r="AQ291" s="3"/>
       <c r="AR291" s="3"/>
-    </row>
-    <row r="292" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS291" s="3"/>
+      <c r="AT291" s="3"/>
+      <c r="AU291" s="3"/>
+      <c r="AV291" s="3"/>
+    </row>
+    <row r="292" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
       <c r="E292" s="3"/>
@@ -15571,8 +16939,12 @@
       <c r="AP292" s="3"/>
       <c r="AQ292" s="3"/>
       <c r="AR292" s="3"/>
-    </row>
-    <row r="293" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS292" s="3"/>
+      <c r="AT292" s="3"/>
+      <c r="AU292" s="3"/>
+      <c r="AV292" s="3"/>
+    </row>
+    <row r="293" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
       <c r="E293" s="3"/>
@@ -15615,8 +16987,12 @@
       <c r="AP293" s="3"/>
       <c r="AQ293" s="3"/>
       <c r="AR293" s="3"/>
-    </row>
-    <row r="294" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS293" s="3"/>
+      <c r="AT293" s="3"/>
+      <c r="AU293" s="3"/>
+      <c r="AV293" s="3"/>
+    </row>
+    <row r="294" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
       <c r="E294" s="3"/>
@@ -15659,8 +17035,12 @@
       <c r="AP294" s="3"/>
       <c r="AQ294" s="3"/>
       <c r="AR294" s="3"/>
-    </row>
-    <row r="295" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS294" s="3"/>
+      <c r="AT294" s="3"/>
+      <c r="AU294" s="3"/>
+      <c r="AV294" s="3"/>
+    </row>
+    <row r="295" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
       <c r="E295" s="3"/>
@@ -15703,8 +17083,12 @@
       <c r="AP295" s="3"/>
       <c r="AQ295" s="3"/>
       <c r="AR295" s="3"/>
-    </row>
-    <row r="296" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS295" s="3"/>
+      <c r="AT295" s="3"/>
+      <c r="AU295" s="3"/>
+      <c r="AV295" s="3"/>
+    </row>
+    <row r="296" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
       <c r="E296" s="3"/>
@@ -15747,8 +17131,12 @@
       <c r="AP296" s="3"/>
       <c r="AQ296" s="3"/>
       <c r="AR296" s="3"/>
-    </row>
-    <row r="297" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS296" s="3"/>
+      <c r="AT296" s="3"/>
+      <c r="AU296" s="3"/>
+      <c r="AV296" s="3"/>
+    </row>
+    <row r="297" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
       <c r="E297" s="3"/>
@@ -15791,8 +17179,12 @@
       <c r="AP297" s="3"/>
       <c r="AQ297" s="3"/>
       <c r="AR297" s="3"/>
-    </row>
-    <row r="298" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS297" s="3"/>
+      <c r="AT297" s="3"/>
+      <c r="AU297" s="3"/>
+      <c r="AV297" s="3"/>
+    </row>
+    <row r="298" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
       <c r="E298" s="3"/>
@@ -15835,8 +17227,12 @@
       <c r="AP298" s="3"/>
       <c r="AQ298" s="3"/>
       <c r="AR298" s="3"/>
-    </row>
-    <row r="299" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS298" s="3"/>
+      <c r="AT298" s="3"/>
+      <c r="AU298" s="3"/>
+      <c r="AV298" s="3"/>
+    </row>
+    <row r="299" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
       <c r="E299" s="3"/>
@@ -15879,8 +17275,12 @@
       <c r="AP299" s="3"/>
       <c r="AQ299" s="3"/>
       <c r="AR299" s="3"/>
-    </row>
-    <row r="300" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="AS299" s="3"/>
+      <c r="AT299" s="3"/>
+      <c r="AU299" s="3"/>
+      <c r="AV299" s="3"/>
+    </row>
+    <row r="300" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
       <c r="E300" s="3"/>
@@ -15901,8 +17301,12 @@
       <c r="T300" s="3"/>
       <c r="U300" s="3"/>
       <c r="V300" s="3"/>
-    </row>
-    <row r="301" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="W300" s="3"/>
+      <c r="X300" s="3"/>
+      <c r="Y300" s="3"/>
+      <c r="Z300" s="3"/>
+    </row>
+    <row r="301" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
       <c r="E301" s="3"/>
@@ -15923,8 +17327,12 @@
       <c r="T301" s="3"/>
       <c r="U301" s="3"/>
       <c r="V301" s="3"/>
-    </row>
-    <row r="302" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="W301" s="3"/>
+      <c r="X301" s="3"/>
+      <c r="Y301" s="3"/>
+      <c r="Z301" s="3"/>
+    </row>
+    <row r="302" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C302" s="3"/>
       <c r="D302" s="3"/>
       <c r="E302" s="3"/>
@@ -15945,8 +17353,12 @@
       <c r="T302" s="3"/>
       <c r="U302" s="3"/>
       <c r="V302" s="3"/>
-    </row>
-    <row r="303" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="W302" s="3"/>
+      <c r="X302" s="3"/>
+      <c r="Y302" s="3"/>
+      <c r="Z302" s="3"/>
+    </row>
+    <row r="303" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C303" s="3"/>
       <c r="D303" s="3"/>
       <c r="E303" s="3"/>
@@ -15967,8 +17379,12 @@
       <c r="T303" s="3"/>
       <c r="U303" s="3"/>
       <c r="V303" s="3"/>
-    </row>
-    <row r="304" spans="3:44" x14ac:dyDescent="0.2">
+      <c r="W303" s="3"/>
+      <c r="X303" s="3"/>
+      <c r="Y303" s="3"/>
+      <c r="Z303" s="3"/>
+    </row>
+    <row r="304" spans="3:48" x14ac:dyDescent="0.2">
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
       <c r="E304" s="3"/>
@@ -15989,8 +17405,12 @@
       <c r="T304" s="3"/>
       <c r="U304" s="3"/>
       <c r="V304" s="3"/>
-    </row>
-    <row r="305" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W304" s="3"/>
+      <c r="X304" s="3"/>
+      <c r="Y304" s="3"/>
+      <c r="Z304" s="3"/>
+    </row>
+    <row r="305" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
       <c r="E305" s="3"/>
@@ -16011,8 +17431,12 @@
       <c r="T305" s="3"/>
       <c r="U305" s="3"/>
       <c r="V305" s="3"/>
-    </row>
-    <row r="306" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W305" s="3"/>
+      <c r="X305" s="3"/>
+      <c r="Y305" s="3"/>
+      <c r="Z305" s="3"/>
+    </row>
+    <row r="306" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C306" s="3"/>
       <c r="D306" s="3"/>
       <c r="E306" s="3"/>
@@ -16033,8 +17457,12 @@
       <c r="T306" s="3"/>
       <c r="U306" s="3"/>
       <c r="V306" s="3"/>
-    </row>
-    <row r="307" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W306" s="3"/>
+      <c r="X306" s="3"/>
+      <c r="Y306" s="3"/>
+      <c r="Z306" s="3"/>
+    </row>
+    <row r="307" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C307" s="3"/>
       <c r="D307" s="3"/>
       <c r="E307" s="3"/>
@@ -16055,8 +17483,12 @@
       <c r="T307" s="3"/>
       <c r="U307" s="3"/>
       <c r="V307" s="3"/>
-    </row>
-    <row r="308" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W307" s="3"/>
+      <c r="X307" s="3"/>
+      <c r="Y307" s="3"/>
+      <c r="Z307" s="3"/>
+    </row>
+    <row r="308" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C308" s="3"/>
       <c r="D308" s="3"/>
       <c r="E308" s="3"/>
@@ -16077,8 +17509,12 @@
       <c r="T308" s="3"/>
       <c r="U308" s="3"/>
       <c r="V308" s="3"/>
-    </row>
-    <row r="309" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W308" s="3"/>
+      <c r="X308" s="3"/>
+      <c r="Y308" s="3"/>
+      <c r="Z308" s="3"/>
+    </row>
+    <row r="309" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C309" s="3"/>
       <c r="D309" s="3"/>
       <c r="E309" s="3"/>
@@ -16099,8 +17535,12 @@
       <c r="T309" s="3"/>
       <c r="U309" s="3"/>
       <c r="V309" s="3"/>
-    </row>
-    <row r="310" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W309" s="3"/>
+      <c r="X309" s="3"/>
+      <c r="Y309" s="3"/>
+      <c r="Z309" s="3"/>
+    </row>
+    <row r="310" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C310" s="3"/>
       <c r="D310" s="3"/>
       <c r="E310" s="3"/>
@@ -16121,8 +17561,12 @@
       <c r="T310" s="3"/>
       <c r="U310" s="3"/>
       <c r="V310" s="3"/>
-    </row>
-    <row r="311" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W310" s="3"/>
+      <c r="X310" s="3"/>
+      <c r="Y310" s="3"/>
+      <c r="Z310" s="3"/>
+    </row>
+    <row r="311" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C311" s="3"/>
       <c r="D311" s="3"/>
       <c r="E311" s="3"/>
@@ -16143,8 +17587,12 @@
       <c r="T311" s="3"/>
       <c r="U311" s="3"/>
       <c r="V311" s="3"/>
-    </row>
-    <row r="312" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W311" s="3"/>
+      <c r="X311" s="3"/>
+      <c r="Y311" s="3"/>
+      <c r="Z311" s="3"/>
+    </row>
+    <row r="312" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C312" s="3"/>
       <c r="D312" s="3"/>
       <c r="E312" s="3"/>
@@ -16165,8 +17613,12 @@
       <c r="T312" s="3"/>
       <c r="U312" s="3"/>
       <c r="V312" s="3"/>
-    </row>
-    <row r="313" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W312" s="3"/>
+      <c r="X312" s="3"/>
+      <c r="Y312" s="3"/>
+      <c r="Z312" s="3"/>
+    </row>
+    <row r="313" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C313" s="3"/>
       <c r="D313" s="3"/>
       <c r="E313" s="3"/>
@@ -16187,8 +17639,12 @@
       <c r="T313" s="3"/>
       <c r="U313" s="3"/>
       <c r="V313" s="3"/>
-    </row>
-    <row r="314" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W313" s="3"/>
+      <c r="X313" s="3"/>
+      <c r="Y313" s="3"/>
+      <c r="Z313" s="3"/>
+    </row>
+    <row r="314" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C314" s="3"/>
       <c r="D314" s="3"/>
       <c r="E314" s="3"/>
@@ -16209,8 +17665,12 @@
       <c r="T314" s="3"/>
       <c r="U314" s="3"/>
       <c r="V314" s="3"/>
-    </row>
-    <row r="315" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W314" s="3"/>
+      <c r="X314" s="3"/>
+      <c r="Y314" s="3"/>
+      <c r="Z314" s="3"/>
+    </row>
+    <row r="315" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C315" s="3"/>
       <c r="D315" s="3"/>
       <c r="E315" s="3"/>
@@ -16231,8 +17691,12 @@
       <c r="T315" s="3"/>
       <c r="U315" s="3"/>
       <c r="V315" s="3"/>
-    </row>
-    <row r="316" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W315" s="3"/>
+      <c r="X315" s="3"/>
+      <c r="Y315" s="3"/>
+      <c r="Z315" s="3"/>
+    </row>
+    <row r="316" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C316" s="3"/>
       <c r="D316" s="3"/>
       <c r="E316" s="3"/>
@@ -16253,8 +17717,12 @@
       <c r="T316" s="3"/>
       <c r="U316" s="3"/>
       <c r="V316" s="3"/>
-    </row>
-    <row r="317" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W316" s="3"/>
+      <c r="X316" s="3"/>
+      <c r="Y316" s="3"/>
+      <c r="Z316" s="3"/>
+    </row>
+    <row r="317" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C317" s="3"/>
       <c r="D317" s="3"/>
       <c r="E317" s="3"/>
@@ -16275,8 +17743,12 @@
       <c r="T317" s="3"/>
       <c r="U317" s="3"/>
       <c r="V317" s="3"/>
-    </row>
-    <row r="318" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W317" s="3"/>
+      <c r="X317" s="3"/>
+      <c r="Y317" s="3"/>
+      <c r="Z317" s="3"/>
+    </row>
+    <row r="318" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C318" s="3"/>
       <c r="D318" s="3"/>
       <c r="E318" s="3"/>
@@ -16297,8 +17769,12 @@
       <c r="T318" s="3"/>
       <c r="U318" s="3"/>
       <c r="V318" s="3"/>
-    </row>
-    <row r="319" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W318" s="3"/>
+      <c r="X318" s="3"/>
+      <c r="Y318" s="3"/>
+      <c r="Z318" s="3"/>
+    </row>
+    <row r="319" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C319" s="3"/>
       <c r="D319" s="3"/>
       <c r="E319" s="3"/>
@@ -16319,8 +17795,12 @@
       <c r="T319" s="3"/>
       <c r="U319" s="3"/>
       <c r="V319" s="3"/>
-    </row>
-    <row r="320" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W319" s="3"/>
+      <c r="X319" s="3"/>
+      <c r="Y319" s="3"/>
+      <c r="Z319" s="3"/>
+    </row>
+    <row r="320" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C320" s="3"/>
       <c r="D320" s="3"/>
       <c r="E320" s="3"/>
@@ -16341,8 +17821,12 @@
       <c r="T320" s="3"/>
       <c r="U320" s="3"/>
       <c r="V320" s="3"/>
-    </row>
-    <row r="321" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W320" s="3"/>
+      <c r="X320" s="3"/>
+      <c r="Y320" s="3"/>
+      <c r="Z320" s="3"/>
+    </row>
+    <row r="321" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C321" s="3"/>
       <c r="D321" s="3"/>
       <c r="E321" s="3"/>
@@ -16363,8 +17847,12 @@
       <c r="T321" s="3"/>
       <c r="U321" s="3"/>
       <c r="V321" s="3"/>
-    </row>
-    <row r="322" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W321" s="3"/>
+      <c r="X321" s="3"/>
+      <c r="Y321" s="3"/>
+      <c r="Z321" s="3"/>
+    </row>
+    <row r="322" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C322" s="3"/>
       <c r="D322" s="3"/>
       <c r="E322" s="3"/>
@@ -16385,8 +17873,12 @@
       <c r="T322" s="3"/>
       <c r="U322" s="3"/>
       <c r="V322" s="3"/>
-    </row>
-    <row r="323" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W322" s="3"/>
+      <c r="X322" s="3"/>
+      <c r="Y322" s="3"/>
+      <c r="Z322" s="3"/>
+    </row>
+    <row r="323" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C323" s="3"/>
       <c r="D323" s="3"/>
       <c r="E323" s="3"/>
@@ -16407,8 +17899,12 @@
       <c r="T323" s="3"/>
       <c r="U323" s="3"/>
       <c r="V323" s="3"/>
-    </row>
-    <row r="324" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W323" s="3"/>
+      <c r="X323" s="3"/>
+      <c r="Y323" s="3"/>
+      <c r="Z323" s="3"/>
+    </row>
+    <row r="324" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C324" s="3"/>
       <c r="D324" s="3"/>
       <c r="E324" s="3"/>
@@ -16429,6 +17925,10 @@
       <c r="T324" s="3"/>
       <c r="U324" s="3"/>
       <c r="V324" s="3"/>
+      <c r="W324" s="3"/>
+      <c r="X324" s="3"/>
+      <c r="Y324" s="3"/>
+      <c r="Z324" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/LULU.xlsx
+++ b/LULU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74152F2E-5DC6-467D-8D90-AD870C885894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B69C93-FBDE-4FD6-894F-D4B87F45FEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{307BA413-EEF9-4958-8DCC-E913E47A6543}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{307BA413-EEF9-4958-8DCC-E913E47A6543}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="125">
   <si>
     <t>SEC</t>
   </si>
@@ -430,6 +430,9 @@
   <si>
     <t>Q426</t>
   </si>
+  <si>
+    <t>Free Cashflow</t>
+  </si>
 </sst>
 </file>
 
@@ -441,13 +444,19 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -528,39 +537,40 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -988,7 +998,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="16">
-        <v>114.34</v>
+        <v>110.86</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1019,7 +1029,7 @@
       </c>
       <c r="I4" s="7">
         <f>I3*I2</f>
-        <v>12398.796003380001</v>
+        <v>12021.43191302</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1061,7 +1071,7 @@
       </c>
       <c r="I7" s="7">
         <f>I4+I6-I5</f>
-        <v>10884.067003380002</v>
+        <v>10506.702913020001</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1070,7 +1080,7 @@
       </c>
       <c r="I9" s="8">
         <f>+I4/Model!Z28</f>
-        <v>6.8327381679539894</v>
+        <v>6.6247800708359215</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1079,7 +1089,7 @@
       </c>
       <c r="I10" s="8">
         <f>+I7/Model!Z24</f>
-        <v>4.3437283132717157</v>
+        <v>4.193125869975499</v>
       </c>
     </row>
   </sheetData>
@@ -3657,7 +3667,7 @@
         <v>0.10400831270816768</v>
       </c>
       <c r="H33" s="12">
-        <f t="shared" ref="H33:M33" si="45">H19/D19-1</f>
+        <f t="shared" ref="H33:L33" si="45">H19/D19-1</f>
         <v>7.3291492486980303E-2</v>
       </c>
       <c r="I33" s="12">
@@ -7969,6 +7979,9 @@
       <c r="AV105" s="3"/>
     </row>
     <row r="106" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B106" s="19" t="s">
+        <v>124</v>
+      </c>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -7990,10 +8003,22 @@
       <c r="U106" s="3"/>
       <c r="V106" s="3"/>
       <c r="W106" s="3"/>
-      <c r="X106" s="3"/>
-      <c r="Y106" s="3"/>
-      <c r="Z106" s="3"/>
-      <c r="AA106" s="3"/>
+      <c r="X106" s="3">
+        <f t="shared" ref="X106:AA106" si="77">+X89+X90</f>
+        <v>327.80600000000015</v>
+      </c>
+      <c r="Y106" s="3">
+        <f t="shared" si="77"/>
+        <v>1644.2990000000011</v>
+      </c>
+      <c r="Z106" s="3">
+        <f t="shared" si="77"/>
+        <v>1583.4810000000007</v>
+      </c>
+      <c r="AA106" s="3">
+        <f>+AA89+AA90</f>
+        <v>921.68500000000051</v>
+      </c>
       <c r="AB106" s="3"/>
       <c r="AC106" s="3"/>
       <c r="AD106" s="3"/>
